--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -1728,7 +1728,8 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.png?v=3623a09a3d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.jpg?v=80a1acf4b1
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_2.jpg?v=3bc5b750c8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1855,7 +1856,7 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>02E305045</t>
         </is>
       </c>
     </row>
@@ -1959,7 +1960,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E927770AL_1.png?v=1ed880b735</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E927770AL_1.jpg?v=33f87a4d3d</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -2051,8 +2052,12 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.png?v=01ff072142
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.png?v=5bada80f79</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_1.jpg?v=4bef52858f
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_2.jpg?v=51009e1a44
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_3.jpg?v=3853ddfc7c
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_4.jpg?v=b1fa594eb7
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_5.jpg?v=0c8d694a18
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02e305045_6.jpg?v=4431d765b0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -2131,8 +2136,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=7ea3564566
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.png?v=b6b7265cda</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=65c46f9b97</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -2208,8 +2212,8 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.png?v=925edc897f
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.png?v=2dddb3884d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_1.jpg?v=d8bbde66cd
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325025B_2.jpg?v=7b0c4bba6e</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -2376,7 +2380,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.png?v=23bde7d308</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.jpg?v=e5d075d0e9</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -2454,7 +2458,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.png?v=ef9e5c1565</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.jpg?v=3e45838a06</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -2536,7 +2540,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.png?v=8bec31bf8f</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.jpg?v=3a3aaf7762</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -2611,8 +2615,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.png?v=558065bb93
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.png?v=34e4e88bf6</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.jpg?v=44a9ab31fd</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2689,7 +2692,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_2.png?v=e49b0e06dd</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.jpg?v=70f40f556e</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -2765,8 +2768,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=1d88443a00
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.png?v=65f505cb0b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=9d51d969ea</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2848,9 +2850,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.png?v=328a4437fe
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_2.png?v=2aa1c70ce2
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_3.png?v=4043339148</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.jpg?v=6cc2257c48</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -2930,7 +2930,8 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.png?v=645157a9ae</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.jpg?v=ea79e81563
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_2.jpg?v=4529f855b6</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -3009,7 +3010,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.png?v=7dfb22192b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.jpg?v=fbdb72784c</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -3328,7 +3329,7 @@
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0BH325183 B</t>
+          <t>0BH325183B</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3438,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.png?v=9a506331a9</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.jpg?v=bf2cf0a479</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3515,9 +3516,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.png?v=45a69e38a1
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.png?v=4b4f837537
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_3.png?v=e1488b6f03</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.jpg?v=21cf6a4fc0</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -3600,8 +3599,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H-1.png?v=936073c4cf
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_4.jpg?v=851b886533</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.jpg?v=df6ff84458</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3691,9 +3689,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.png?v=4ec9bb8ca0
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_2.png?v=838071f395
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_3.png?v=b93ad38a77</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.jpg?v=815184defd</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3861,7 +3857,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_2.png?v=fc60a3cbb2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.jpg?v=e1a894f60b</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -4027,8 +4023,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.png?v=00a6063ad1
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_2.png?v=7cb0bd4a20</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.jpg?v=23a46f0590</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -4107,7 +4102,10 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.png?v=9a4139b864</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.jpg?v=5f0a06c746
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.jpg?v=f610170a4d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_3.jpg?v=77f42b52d2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_4.jpg?v=714b21e00d</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -4185,7 +4183,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l.png?v=b796fe8aab</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.jpg?v=c010c7bbdf</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
@@ -4264,7 +4262,9 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m.png?v=2ec99b161d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.jpg?v=ba44318fd7
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_2.jpg?v=fd9283f1f7
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_3.jpg?v=b7ac56b9b3</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
@@ -4418,7 +4418,9 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.png?v=04fb90265c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.jpg?v=5190638fc3
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.jpg?v=77fc244bbc
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_3.jpg?v=4d3606b157</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
@@ -4496,7 +4498,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.png?v=462ec457c3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.jpg?v=3b3b076322</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
@@ -4823,7 +4825,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.png?v=3fb6a6ed69</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.jpg?v=3f30a503c8</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -4871,7 +4873,7 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325025C</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4905,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.png?v=997df2de75</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.jpg?v=693a4298e8</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -4981,8 +4983,8 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=7e06c6a5f1
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.png?v=86b168fdd7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=cbeca4b59a
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_2.jpg?v=a9a9967b4d</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -5077,8 +5079,8 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.png?v=9f571585c3
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_4.png?v=9fbf2bb6f0</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.jpg?v=ffb6e141cb
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.jpg?v=1af750811c</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
@@ -5176,7 +5178,8 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e.png?v=9e53670a82</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.jpg?v=ad51750acf
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_2.jpg?v=579c860e1a</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
@@ -5299,7 +5302,7 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>0am325091eset</t>
         </is>
       </c>
     </row>
@@ -5352,7 +5355,8 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f.png?v=8cfd86455e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.jpg?v=fc28fbc227
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_2.jpg?v=94ce98509a</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
@@ -5475,7 +5479,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325091fset</t>
         </is>
       </c>
     </row>
@@ -5666,8 +5670,9 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.png?v=ebfa02ae85
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=9185e154b7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -5760,9 +5765,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025.png?v=b98621fc0a
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.png?v=e41c86e98b
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025-2.png?v=45a69e38a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -5846,7 +5849,8 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=9c731d1419</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=77a111eb34
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=40c2597cb3</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
@@ -5939,7 +5943,8 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.png?v=ebfa02ae85</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -6030,13 +6035,9 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.png?v=197acf8189
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.png?v=ff168c7b41
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.png?v=197acf8189
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._4.png?v=86b168fdd7
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._5.png?v=78bf59e6bd
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._6.png?v=71a27c560b
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._7.png?v=ce40d7f683</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.jpg?v=3e0abf9ec7
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.jpg?v=b12c6dac21
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.jpg?v=bd237a81d2</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6084,7 +6085,7 @@
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0c</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6169,7 @@
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>122390AKAF</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6346,7 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>123014AF</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6435,7 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>31705-1XF0C</t>
+          <t>317051XF0C</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6521,7 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>31705-X428B</t>
+          <t>31705X428B</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6563,8 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.png?v=c51183578d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
@@ -6639,7 +6641,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.png?v=ee5f7fcab1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -6714,7 +6716,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.png?v=434a7e1a34</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
@@ -6966,7 +6968,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=63685aa19d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -7055,7 +7057,20 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=34d94b6ab7</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_11.jpg?v=b00b729a6f
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_12.jpg?v=3e5bb95f61
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_13.jpg?v=b5e4690bb8
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_14.jpg?v=293affdbb4
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_3.jpg?v=8b53715593
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_4.jpg?v=87672fa5cf
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_5.jpg?v=22b635f676
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_6.jpg?v=60c3947305
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_7.jpg?v=6455c2a999
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_8.jpg?v=1c56d278b5
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
@@ -7132,7 +7147,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.png?v=1d34e63372</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
@@ -7207,7 +7222,8 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.png?v=995613c21a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=be20ada597
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=87268821a3</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
@@ -7255,7 +7271,7 @@
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>filtrsetka0b5orig</t>
         </is>
       </c>
     </row>
@@ -7282,7 +7298,9 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.png?v=a21cf79b1b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -7330,7 +7348,7 @@
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>gidroakkumulyatororig</t>
         </is>
       </c>
     </row>
@@ -7358,7 +7376,8 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=648c289289</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
@@ -7433,7 +7452,8 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_1.png?v=5d4d3c5107</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_1.jpg?v=9eba78df5d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -7481,7 +7501,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>klipsyshtokov2sht</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7577,7 @@
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>korpusfiltra0bh325159</t>
         </is>
       </c>
     </row>
@@ -7584,7 +7604,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.png?v=cef8cc4537</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -7632,7 +7652,7 @@
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>plankasolenoid2sht</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7679,8 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.png?v=9ce5d50d5b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -7707,7 +7728,7 @@
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plastinysolenoidorig</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7755,9 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.png?v=16f48e3b34</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=efa8557d9d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=759d463fe2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=3f11b4e476</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -7782,7 +7805,7 @@
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plitafiltr</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7832,8 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.png?v=b85e77777e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -7857,7 +7881,7 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plitafiltrpylniki</t>
         </is>
       </c>
     </row>
@@ -7932,7 +7956,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plitafiltrpylnikiorig</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8031,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plitafiltrpylnikisal</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8107,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plitafiltrsalnikiorig</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8182,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plitafiltrv2</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8257,7 @@
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plitapylnikisalnikiorig</t>
         </is>
       </c>
     </row>
@@ -8308,7 +8332,7 @@
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plitapylnikisalnikiorigv2</t>
         </is>
       </c>
     </row>
@@ -8335,8 +8359,8 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.png?v=bcd5b49d99
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.png?v=51d4844731</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
@@ -8384,7 +8408,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>podshipnikvilki6</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8483,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>porshniusilpylnikikryshki</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8510,8 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.png?v=b93ad38a77</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -8534,7 +8559,7 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>porshniusilpylnikikryshkiv2</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8634,7 @@
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>pylnikishtokovorig</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8709,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>pylnikishtokovorigv2</t>
         </is>
       </c>
     </row>
@@ -8759,7 +8784,7 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>remkomplektshtokovorig</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8811,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.png?v=45a69e38a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
@@ -8834,7 +8859,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>remkomplektshtokovorigv2</t>
         </is>
       </c>
     </row>
@@ -8861,8 +8886,8 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.png?v=197acf8189
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.png?v=78bf59e6bd</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
@@ -8910,7 +8935,7 @@
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>salnikshtokaorig</t>
         </is>
       </c>
     </row>
@@ -8985,7 +9010,7 @@
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>salnikshtokaorigv2</t>
         </is>
       </c>
     </row>
@@ -9012,8 +9037,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.png?v=b11e893ec2
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_2.png?v=462ec457c3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
@@ -9061,7 +9085,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salniktolkatelyaalum</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9112,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.png?v=ce40d7f683</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
@@ -9136,7 +9160,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnikishtokov2sht</t>
         </is>
       </c>
     </row>
@@ -9163,7 +9187,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.png?v=e1488b6f03</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
@@ -9211,7 +9235,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salnikishtokovorig</t>
         </is>
       </c>
     </row>
@@ -9238,8 +9262,8 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.png?v=36677687b8
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.png?v=770b55f1cb</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
@@ -9287,7 +9311,7 @@
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salnikitolkatelya4sht</t>
         </is>
       </c>
     </row>
@@ -9314,7 +9338,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.png?v=40460a2392</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
@@ -9362,7 +9386,7 @@
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salnikprivodl</t>
         </is>
       </c>
     </row>
@@ -9389,7 +9413,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.png?v=7c32dc35c6</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
@@ -9437,7 +9461,7 @@
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnikprivodr</t>
         </is>
       </c>
     </row>
@@ -9464,7 +9488,8 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.png?v=5538a2da6a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
@@ -9614,7 +9639,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.png?v=d8d1c20493</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
@@ -9662,7 +9687,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>stalnayavstavkaplity</t>
         </is>
       </c>
     </row>
@@ -9689,7 +9714,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.png?v=55bef0c347</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
@@ -9737,7 +9762,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>tolkateli4salniki4</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9789,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.png?v=3583dce094</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
@@ -9812,7 +9837,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>tolkatelisalnikialumkomplekt</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9864,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.png?v=923daa8d8d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
@@ -9887,7 +9912,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>vtulkishtokov2sht</t>
         </is>
       </c>
     </row>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -1728,8 +1728,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.jpg?v=80a1acf4b1
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_2.jpg?v=3bc5b750c8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.jpg?v=3bc5b750c8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2615,7 +2614,8 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.jpg?v=44a9ab31fd</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.jpg?v=c45a2498aa
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.jpg?v=44a9ab31fd</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -2930,8 +2930,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.jpg?v=ea79e81563
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_2.jpg?v=4529f855b6</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_2.jpg?v=4529f855b6</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -7452,8 +7451,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_1.jpg?v=9eba78df5d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2855,11 +2855,11 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 0AM325587E</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал VAG 0AM325587E</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>8890</v>
+        <v>9850</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Мехатроник в сборе DSG7 DQ200 0AM/0CW</t>
+          <t>Мехатроник DSG7 DQ200 0AM/0CW ПРОВЕРЕН НА АВТО</t>
         </is>
       </c>
       <c r="AH28" t="n">
@@ -7292,7 +7292,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>🔧 Новый оригинальный (VAG) гидроаккумулятор мехатроника DSG7 DQ200 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Новый оригинал, а не восстановленный — от него напрямую зависит чёткость переключений.</t>
+          <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>Новый оригинальный гидроаккумулятор VAG мехатроника DSG7 DQ200</t>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
         </is>
       </c>
       <c r="AH72" t="n">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF106"/>
+  <dimension ref="A1:BF109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="3"/>
@@ -7815,103 +7815,103 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t>plita-filtr-orig</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.png?v=b8cb2f02a1</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="AH79" t="n">
+        <v>7500</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN79" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>plitafiltrorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>plita-filtr-pylniki</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
-        </is>
-      </c>
-      <c r="AH79" t="n">
-        <v>8500</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL79" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>plitafiltrpylniki</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-orig</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="AH80" t="n">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikiorig</t>
+          <t>plitafiltrpylniki</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -7976,21 +7976,21 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="AH81" t="n">
-        <v>9500</v>
+        <v>8500</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikisal</t>
+          <t>plitafiltrpylnikiorig</t>
         </is>
       </c>
     </row>
@@ -8041,221 +8041,221 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t>plita-filtr-pylniki-sal</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="AH82" t="n">
+        <v>9500</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>plitafiltrpylnikisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal-orig</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.png?v=e34fb25bfd</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="AH83" t="n">
+        <v>9500</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN83" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>plitafiltrpylnikisalorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
           <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png?v=9157b6c42a</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
-      <c r="AH82" t="n">
+      <c r="AH84" t="n">
         <v>8500</v>
       </c>
-      <c r="AJ82" t="inlineStr">
+      <c r="AJ84" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK82" t="inlineStr">
+      <c r="AK84" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL82" t="inlineStr">
+      <c r="AL84" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
+      <c r="AM84" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
+      <c r="AN84" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO82" t="inlineStr">
+      <c r="AO84" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR82" t="inlineStr">
+      <c r="AR84" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS82" t="inlineStr">
+      <c r="AS84" t="inlineStr">
         <is>
           <t>plitafiltrsalnikiorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png?v=16f48e3b34</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
-        </is>
-      </c>
-      <c r="AH83" t="n">
-        <v>7500</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL83" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr">
-        <is>
-          <t>plitafiltrv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH84" t="n">
-        <v>9500</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>plitapylnikisalnikiorig</t>
         </is>
       </c>
     </row>
@@ -8267,7 +8267,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -8277,21 +8277,21 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png?v=b98621fc0a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png?v=16f48e3b34</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>9500</v>
+        <v>7500</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>plitapylnikisalnikiorigv2</t>
+          <t>plitafiltrv2</t>
         </is>
       </c>
     </row>
@@ -8342,447 +8342,447 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>plita-pylniki-salniki</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.png?v=fd0e412e14</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+        </is>
+      </c>
+      <c r="AH86" t="n">
+        <v>8500</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN86" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>plitapylnikisalniki</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH87" t="n">
+        <v>9500</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>plitapylnikisalnikiorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig-v2</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png?v=b98621fc0a</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="AH88" t="n">
+        <v>9500</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN88" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>plitapylnikisalnikiorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
           <t>podshipnik-vilki-6</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
         </is>
       </c>
-      <c r="AH86" t="n">
+      <c r="AH89" t="n">
         <v>1240</v>
       </c>
-      <c r="AJ86" t="inlineStr">
+      <c r="AJ89" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK86" t="inlineStr">
+      <c r="AK89" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL86" t="inlineStr">
+      <c r="AL89" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
+      <c r="AM89" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN86" t="inlineStr">
+      <c r="AN89" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO86" t="inlineStr">
+      <c r="AO89" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR86" t="inlineStr">
+      <c r="AR89" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS86" t="inlineStr">
+      <c r="AS89" t="inlineStr">
         <is>
           <t>podshipnikvilki6</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
-      <c r="AH87" t="n">
+      <c r="AH90" t="n">
         <v>3990</v>
       </c>
-      <c r="AJ87" t="inlineStr">
+      <c r="AJ90" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK87" t="inlineStr">
+      <c r="AK90" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL87" t="inlineStr">
+      <c r="AL90" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
+      <c r="AM90" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN87" t="inlineStr">
+      <c r="AN90" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO87" t="inlineStr">
+      <c r="AO90" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR87" t="inlineStr">
+      <c r="AR90" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS87" t="inlineStr">
+      <c r="AS90" t="inlineStr">
         <is>
           <t>porshniusilpylnikikryshki</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
         </is>
       </c>
-      <c r="AH88" t="n">
+      <c r="AH91" t="n">
         <v>3990</v>
       </c>
-      <c r="AJ88" t="inlineStr">
+      <c r="AJ91" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK88" t="inlineStr">
+      <c r="AK91" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL88" t="inlineStr">
+      <c r="AL91" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
+      <c r="AM91" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
+      <c r="AN91" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO88" t="inlineStr">
+      <c r="AO91" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR88" t="inlineStr">
+      <c r="AR91" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS88" t="inlineStr">
+      <c r="AS91" t="inlineStr">
         <is>
           <t>porshniusilpylnikikryshkiv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH89" t="n">
-        <v>1850</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL89" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr">
-        <is>
-          <t>pylnikishtokovorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig-v2</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
-        </is>
-      </c>
-      <c r="AH90" t="n">
-        <v>1850</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>pylnikishtokovorigv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>remkomplekt-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH91" t="n">
-        <v>2850</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL91" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr">
-        <is>
-          <t>remkomplektshtokovorig</t>
         </is>
       </c>
     </row>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8804,21 +8804,21 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH92" t="n">
-        <v>2850</v>
+        <v>1850</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Переключение передач</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>remkomplektshtokovorigv2</t>
+          <t>pylnikishtokovorig</t>
         </is>
       </c>
     </row>
@@ -8869,296 +8869,296 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
+          <t>pylniki-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="AH93" t="n">
+        <v>1850</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>pylnikishtokovorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH94" t="n">
+        <v>2850</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN94" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>remkomplektshtokovorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="AH95" t="n">
+        <v>2850</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN95" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>remkomplektshtokovorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>salnik-shtoka-orig</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="P96" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="S96" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH93" t="n">
+      <c r="AH96" t="n">
         <v>1490</v>
       </c>
-      <c r="AJ93" t="inlineStr">
+      <c r="AJ96" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK93" t="inlineStr">
+      <c r="AK96" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL93" t="inlineStr">
+      <c r="AL96" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
+      <c r="AM96" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN93" t="inlineStr">
+      <c r="AN96" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO93" t="inlineStr">
+      <c r="AO96" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR93" t="inlineStr">
+      <c r="AR96" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS93" t="inlineStr">
+      <c r="AS96" t="inlineStr">
         <is>
           <t>salnikshtokaorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig-v2</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
-        </is>
-      </c>
-      <c r="AH94" t="n">
-        <v>1490</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL94" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>salnikshtokaorigv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>salnik-tolkatelya-alum</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH95" t="n">
-        <v>2490</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL95" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>salniktolkatelyaalum</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
-        </is>
-      </c>
-      <c r="AH96" t="n">
-        <v>1690</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL96" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>salnikishtokov2sht</t>
         </is>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -9180,21 +9180,21 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="AH97" t="n">
-        <v>1890</v>
+        <v>1490</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>salnikishtokovorig</t>
+          <t>salnikshtokaorigv2</t>
         </is>
       </c>
     </row>
@@ -9245,522 +9245,522 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
+          <t>salnik-tolkatelya-alum</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH98" t="n">
+        <v>2490</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>salniktolkatelyaalum</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="AH99" t="n">
+        <v>1690</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>salnikishtokov2sht</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH100" t="n">
+        <v>1890</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>salnikishtokovorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
           <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="S101" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
         </is>
       </c>
-      <c r="AH98" t="n">
+      <c r="AH101" t="n">
         <v>1950</v>
       </c>
-      <c r="AJ98" t="inlineStr">
+      <c r="AJ101" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK98" t="inlineStr">
+      <c r="AK101" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL98" t="inlineStr">
+      <c r="AL101" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
+      <c r="AM101" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
+      <c r="AN101" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO98" t="inlineStr">
+      <c r="AO101" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR98" t="inlineStr">
+      <c r="AR101" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS98" t="inlineStr">
+      <c r="AS101" t="inlineStr">
         <is>
           <t>salnikitolkatelya4sht</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>salnikprivod-l</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="Q102" t="inlineStr">
         <is>
           <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="S102" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH99" t="n">
+      <c r="AH102" t="n">
         <v>999</v>
       </c>
-      <c r="AJ99" t="inlineStr">
+      <c r="AJ102" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK99" t="inlineStr">
+      <c r="AK102" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL99" t="inlineStr">
+      <c r="AL102" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
+      <c r="AM102" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
+      <c r="AN102" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO99" t="inlineStr">
+      <c r="AO102" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR99" t="inlineStr">
+      <c r="AR102" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS99" t="inlineStr">
+      <c r="AS102" t="inlineStr">
         <is>
           <t>salnikprivodl</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>salnikprivod-r</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH100" t="n">
+      <c r="AH103" t="n">
         <v>999</v>
       </c>
-      <c r="AJ100" t="inlineStr">
+      <c r="AJ103" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK100" t="inlineStr">
+      <c r="AK103" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL100" t="inlineStr">
+      <c r="AL103" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
+      <c r="AM103" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
+      <c r="AN103" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO100" t="inlineStr">
+      <c r="AO103" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR100" t="inlineStr">
+      <c r="AR103" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS100" t="inlineStr">
+      <c r="AS103" t="inlineStr">
         <is>
           <t>salnikprivodr</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>salnikvhod</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH101" t="n">
+      <c r="AH104" t="n">
         <v>999</v>
       </c>
-      <c r="AJ101" t="inlineStr">
+      <c r="AJ104" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK101" t="inlineStr">
+      <c r="AK104" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL101" t="inlineStr">
+      <c r="AL104" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
+      <c r="AM104" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
+      <c r="AN104" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO101" t="inlineStr">
+      <c r="AO104" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR101" t="inlineStr">
+      <c r="AR104" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS101" t="inlineStr">
+      <c r="AS104" t="inlineStr">
         <is>
           <t>salnikvhod</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH102" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>stalnaya-vstavka-plity</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH103" t="n">
-        <v>1950</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>stalnayavstavkaplity</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>tolkateli-4-salniki-4</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
-        </is>
-      </c>
-      <c r="AH104" t="n">
-        <v>7400</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL104" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>tolkateli4salniki4</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9782,21 +9782,21 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH105" t="n">
-        <v>8900</v>
+        <v>999</v>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>tolkatelisalnikialumkomplekt</t>
+          <t>salnikvihod</t>
         </is>
       </c>
     </row>
@@ -9847,68 +9847,293 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH106" t="n">
+        <v>1950</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN106" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>stalnayavstavkaplity</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="AH107" t="n">
+        <v>7400</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN107" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>tolkateli4salniki4</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+        </is>
+      </c>
+      <c r="AH108" t="n">
+        <v>8900</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN108" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>tolkatelisalnikialumkomplekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr">
+      <c r="P109" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q106" t="inlineStr">
+      <c r="Q109" t="inlineStr">
         <is>
           <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr">
+      <c r="S109" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
-      <c r="AH106" t="n">
+      <c r="AH109" t="n">
         <v>4990</v>
       </c>
-      <c r="AJ106" t="inlineStr">
+      <c r="AJ109" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK106" t="inlineStr">
+      <c r="AK109" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL106" t="inlineStr">
+      <c r="AL109" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
+      <c r="AM109" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN106" t="inlineStr">
+      <c r="AN109" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO106" t="inlineStr">
+      <c r="AO109" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR106" t="inlineStr">
+      <c r="AR109" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS106" t="inlineStr">
+      <c r="AS109" t="inlineStr">
         <is>
           <t>vtulkishtokov2sht</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF109"/>
+  <dimension ref="A1:BF110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="3"/>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW 01X301127C</t>
+          <t>Болт мехатроника короткий DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="AH5" t="n">
@@ -1799,7 +1799,7 @@
       <c r="Q6" t="inlineStr">
         <is>
           <t>Набор корпус фильтра + фильтр DQ250 DSG 6 02E305045
-Резиновое кольцо в комплекте 
+Резиновое кольцо в комплекте
 Новые
 Отличное качество
 Уменьшает температуру масла, улучшает теплоотвод</t>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250</t>
         </is>
       </c>
       <c r="AH6" t="n">
@@ -1883,8 +1883,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png?v=853ce5f975
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg?v=0fc1c93a07</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg?v=0fc1c93a07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1964,7 +1963,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Мехатроник DSG6 DQ250 в сборе с электронной платой 02E927770AL</t>
+          <t>Мехатроник DSG6 DQ250 в сборе с электронной</t>
         </is>
       </c>
       <c r="AH8" t="n">
@@ -2061,7 +2060,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG6 DQ250 02E305045</t>
+          <t>Корпус масляного фильтра мехатроника DSG6 DQ250</t>
         </is>
       </c>
       <c r="AH9" t="n">
@@ -2140,7 +2139,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200 0AM301212A</t>
+          <t>Заглушка корпуса КПП мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH10" t="n">
@@ -2205,7 +2204,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом) 
+          <t>В наличии новый соленоид DSG 7 DQ200 0AM 0CW регулятор давления (соленоиды dq200 также продаются комплектом)
 Соленоиды мехатроника DSG7 DQ200Соленоиды мехатроника DSG7 DQ200 являются ключевыми компонентами для трансмиссий с двойным сцеплением, обеспечивая надежное и эффективное управление переключением передач. Эти соленоиды, играют критическую роль в работе трансмиссии.?Основные характеристики товара соленоиды DSG7 DQ200:?Совместимость: Подходят для трансмиссий, применяемых в автомобилях со всеми коробками передач DSG7 DQ200. Они совместимы с моделями 0AM и 0CW.?Функция: Соленоиды дсг 7, включая соленоид DSG DQ200 регулятор давления, влияют на точность переключения передач и общую эффективность работы трансмиссии. Они обеспечивают плавное и быстрое переключение, минимизируя потери мощности и повышая комфорт вождения.?Качество и надежность: Соленоиды DSG 7 (DQ200) произведены из высококачественных материалов (фирма Bosch), что гарантирует долговечность и надежность в работе. Эти компоненты предназначены для замены старых или изношенных элементов трансмиссии, что позволяет значительно улучшить производительность автомобиля.?Покупка и замена: Если вам нужны соленоиды DSG 7 для замены, вы можете купить их у нас! При выборе обратите внимание на совместимость с вашей трансмиссией.Клапан DSG DQ200 регулятор давления всегда в наличии!??Другие клапана (соленоиды shift) DSG 7 также в продаже!?Соленоиды dsg 7 dq200 можно приобрести комплектом 8 штук (2 соленоида регулятора давления и 6 шифтовых)??Соленоиды мехатроника DSG7 DQ200, включая модели 0AM и 0cw, являются важной частью системы трансмиссии и способствуют её надёжной работе. Обновление или замена старых соленоидов на новые, такие как соленоиды DSG7 DQ200 от фирмы Bosch, обеспечит вам долгосрочную эксплуатацию и оптимальные эксплуатационные характеристики автомобиля</t>
         </is>
       </c>
@@ -2295,7 +2294,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A</t>
+          <t>Транспортная заглушка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH12" t="n">
@@ -2384,7 +2383,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200 0AM325219C</t>
+          <t>Оригинальная крышка мехатроника VAG DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH13" t="n">
@@ -2462,7 +2461,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Сальник толкателя вилки мехатроника DSG7 DQ200 0AM325413A</t>
+          <t>Сальник толкателя вилки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH14" t="n">
@@ -2620,7 +2619,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200 0AM325443D</t>
+          <t>Усиленная прокладка крышки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH16" t="n">
@@ -2686,7 +2685,7 @@
       <c r="Q17" t="inlineStr">
         <is>
           <t>Сепараторная пластина под плиту мехатроника DSG7 DQ200 0AM325467J
-Новая 
+Новая
 Отличное качество</t>
         </is>
       </c>
@@ -2697,7 +2696,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Оригинальная сепараторная пластина мехатроника VAG DSG7 DQ200 0AM325467J</t>
+          <t>Оригинальная сепараторная пластина мехатроника</t>
         </is>
       </c>
       <c r="AH17" t="n">
@@ -2838,8 +2837,24 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E) 
-📦 Назначение:Компенсирует утечку давления, возникающую при перегреве или износе уплотнений. Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар). ✅ Совместимость:DSG 7 (DQ200), мехатроники 0AM/0CWVolkswagen, Audi, Skoda, Seat (2007–2023 и далее)Артикул: 0AM325587E📌 Признаки износа/неисправности:Рывки при трогании с местаДолгое задержание передач D/RКод ошибки (например, P0841)Появление металлической стружки в маслеВибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200 💡 Преимущества замены:Снижает риск повреждения мехатроника и сцепленияУвеличивает ресурс гидроблока📦 Отправка — максимально быстро
+          <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E)
+📦 Назначение:
+Компенсирует утечку давления, возникающую при перегреве или износе уплотнений.
+Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар).
+✅ Совместимость:
+DSG 7 (DQ200), мехатроники 0AM/0CW
+Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)
+Артикул: 0AM325587E
+📌 Признаки износа/неисправности:
+Рывки при трогании с места
+Долгое задержание передач D/R
+Код ошибки (например, P0841)
+Появление металлической стружки в масле
+Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200
+💡 Преимущества замены:
+Снижает риск повреждения мехатроника и сцепления
+Увеличивает ресурс гидроблока
+📦 Отправка — максимально быстро
 Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.
 Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.
 Номер 0am325587e
@@ -2855,7 +2870,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал VAG 0AM325587E</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал</t>
         </is>
       </c>
       <c r="AH19" t="n">
@@ -2924,7 +2939,7 @@
 Описание:
 Электронная плата мехатроника DSG7 DQ200 0AM927769D для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.
 Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.
-OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D 
+OEM: подходит только если на родной плате такой номер 0AM927769D 0AM 927 769 D
 Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D</t>
         </is>
       </c>
@@ -2935,7 +2950,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D</t>
+          <t>Электронная плата мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH20" t="n">
@@ -3014,7 +3029,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Прокладки электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
+          <t>Прокладки электронной платы мехатроника DSG7</t>
         </is>
       </c>
       <c r="AH21" t="n">
@@ -3184,7 +3199,7 @@
 • Volkswagen: Tiguan, Transporter T5/T6, Amarok (с DSG7 DQ500)
 • Seat, Skoda с коробкой DQ500 (по каталогу)
 📜 Номера детали:
-0BH325183B  
+0BH325183B
 🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!</t>
         </is>
       </c>
@@ -3285,7 +3300,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B, красный</t>
+          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
       <c r="AH24" t="n">
@@ -3362,7 +3377,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита</t>
         </is>
       </c>
       <c r="AH25" t="n">
@@ -3427,7 +3442,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F).  Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока. 
+          <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F). Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока.
 Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW
 Новая
 Отличное качество
@@ -3442,7 +3457,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Втулка (гильза) штока мехатроника DSG7 DQ200 0AM325025D</t>
+          <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH26" t="n">
@@ -3520,7 +3535,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH27" t="n">
@@ -3585,13 +3600,32 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах! 
+          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах!
 Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.
 БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА
 Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.
-Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200. 
-✅ Для каких автомобилей подходитVolkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.) Audi (A1, A3, TT, Q2 и др.) Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)⚠️ Почему часто нужен ремонт / замена мехатроника DQ200
-У блока DQ200 0AM/0CW есть типичные слабые места: Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.Типичные симптомы:ошибки давления (P17BF, P189C/P1895, P06293 и др.) грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях «Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи⚙️ Почему стоит купить именно этот мехатроникПолная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200. 📦 Что входит:Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки,  / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее📣 Почему стоит выбрать нас
+Он отвечает за всю логику переключения передач и управления сцеплениями, что делает его ключевым компонентом коробки DQ200.
+✅ Для каких автомобилей подходит
+Volkswagen (Golf, Polo, Jetta, Passat, Touran, Tiguan и др.)
+Audi (A1, A3, TT, Q2 и др.)
+Skoda, Seat — все модели с коробкой DSG7 DQ200 (0AM/0CW)
+⚠️ Почему часто нужен ремонт / замена мехатроника DQ200
+У блока DQ200 0AM/0CW есть типичные слабые места:
+Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.
+Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.
+Типичные симптомы:
+ошибки давления (P17BF, P189C/P1895, P06293 и др.)
+грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях
+«Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи
+⚙️ Почему стоит купить именно этот мехатроник
+Полная совместимость с коробками DSG7 DQ200 (0AM / 0CW) — подходит для широкого набора моделей Volkswagen, Audi, Skoda, Seat.
+Готовый к установке блок (ГИДРАВЛИКА, БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ)
+Ремонт или замена гидроблока — актуально при типичных проблемах (течь давления, износ втулок/штоков, соленоидов, гидроплиты,прокладок/ремкомплекта).
+Экономичность и надёжность — по сравнению с полной заменой коробки дешевле, при этом «свежий» блок возвращает ресурс КПП.
+Проверен временем и практикой: множество сервисов и специалистов на своих сайтах и в отзывах отмечают, что замена/ремонт мехатроника устраняет большинство «болезней» DQ200.
+📦 Что входит:
+Гидравлический блок управления (мехатроник) в который установлены - соленоиды, прокладки, / ремкомплекты, гидроаккумлуятор, втулки, ремкомплект штоков, пыльники, сальники, сепараторная пластина (под гидроплиту), прокладки на соленоиды и так далее
+📣 Почему стоит выбрать нас
 Мы предлагаем мехатроник DSG7 DQ200 0AM/0CW с гарантией работоспособности. После установки и адаптации вы получаете коробку, снова работающую «как новая», без постоянных ошибок, рывков и потери давления.
 🔩 Артикул: 0am325025H.</t>
         </is>
@@ -3668,20 +3702,20 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ. 
+          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ.
 Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)
-В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно - 
-Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200 
-Усовершенствованные 
+В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно -
+Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200
+Усовершенствованные
 Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)
 Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)
 Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)
-Качественный ремкомплект прокладок мехатроника DSG7 DQ200 
-Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник. 
+Качественный ремкомплект прокладок мехатроника DSG7 DQ200
+Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник.
 Электронная плата отличного качества, многолетний опыт производства и тестирования
-В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели) 
-И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге. 
-Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто. 
+В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели)
+И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге.
+Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто.
 Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!
 🔩 Артикул: 0am325025HX.</t>
         </is>
@@ -3693,7 +3727,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 в сборе с электронной платой 0AM927769D</t>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной</t>
         </is>
       </c>
       <c r="AH29" t="n">
@@ -3836,18 +3870,18 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D) 
+          <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D)
 Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.
-✅ Совместимость: 
-• DSG7 (DQ200, 7-ступ., сухое сцепление) 
-• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025) 
+✅ Совместимость:
+• DSG7 (DQ200, 7-ступ., сухое сцепление)
+• Мехатроники 0AM / 0CW • VW, Audi, Skoda, Seat (2007–2025)
 • Артикулы: 0AM325219C + 0AM325443D
-📌 Когда ставить: 
-• Утечка или влажность под мехатроником 
-• Снятие крышки (поддона) при ТО или замене фильтра 
+📌 Когда ставить:
+• Утечка или влажность под мехатроником
+• Снятие крышки (поддона) при ТО или замене фильтра
 • Деформация старой крышки или прокладки
-💡 Почему стоит выбрать: 
-• OEM-аналог — точная установка без доработок 
+💡 Почему стоит выбрать:
+• OEM-аналог — точная установка без доработок
 • Материал выдерживает давление и температуру
 📦 Очень быстрая отправка
 👉 Закажите сейчас — нужный комплект для обслуживания уже у вас в руках
@@ -3861,7 +3895,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
+          <t>Оригинальная крышка + усиленная прокладка</t>
         </is>
       </c>
       <c r="AH31" t="n">
@@ -4008,13 +4042,27 @@
         <is>
           <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)
 Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.
-📦 Комплектация:Сальник штокаПыльник штокаКрышка штока✅ Совместимость:Коробка DSG 7 DQ200Мехатроники с кодами 0AM, 0CWШтоки:0AM325091F — короткий, 99 мм (до 2012 года)0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа💡 Почему стоит купить:Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200Подходит для профилактики и ремонтаНе требует специнструмента — подходит для самостоятельной замены📦 Высылаем быстро
+📦 Комплектация:
+Сальник штока
+Пыльник штока
+Крышка штока
+✅ Совместимость:
+Коробка DSG 7 DQ200
+Мехатроники с кодами 0AM, 0CW
+Штоки:
+0AM325091F — короткий, 99 мм (до 2012 года)
+0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа
+💡 Почему стоит купить:
+Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200
+Подходит для профилактики и ремонта
+Не требует специнструмента — подходит для самостоятельной замены
+📦 Высылаем быстро
 👉 Готов к установке — бери и ставь без лишней головной боли
 В комплекте
 Пыльник штока dq200
 Сальник штока dsg7
 Крышка штока мехатроника
-Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника. 
+Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника.
 Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.
 Идеален для технического обслуживания и увеличения срока службы мехатроника.
 🔩 Артикул: 0am325025h.</t>
@@ -4027,7 +4075,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH33" t="n">
@@ -4109,7 +4157,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Сепараторная пластина + пластины на соленоиды</t>
         </is>
       </c>
       <c r="AH34" t="n">
@@ -4187,7 +4235,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200 0AM325025L</t>
+          <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH35" t="n">
@@ -4268,7 +4316,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH36" t="n">
@@ -4344,7 +4392,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N</t>
+          <t>Соленоид переключения (Shift) мехатроника DSG7</t>
         </is>
       </c>
       <c r="AH37" t="n">
@@ -4502,7 +4550,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Усиленное опорное кольцо толкателя мехатроника DSG7 DQ200 0AM325025R</t>
+          <t>Усиленное опорное кольцо толкателя мехатроника</t>
         </is>
       </c>
       <c r="AH39" t="n">
@@ -4578,7 +4626,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E</t>
         </is>
       </c>
       <c r="AH40" t="n">
@@ -4661,7 +4709,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами Bosch</t>
+          <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами</t>
         </is>
       </c>
       <c r="AH41" t="n">
@@ -4752,7 +4800,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F</t>
         </is>
       </c>
       <c r="AH42" t="n">
@@ -4829,7 +4877,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C</t>
+          <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH43" t="n">
@@ -4909,7 +4957,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>Усиленный поршень штока мехатроника DSG7 DQ200 0AM325066AC</t>
+          <t>Усиленный поршень штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH44" t="n">
@@ -4975,7 +5023,7 @@
       <c r="Q45" t="inlineStr">
         <is>
           <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW
-Новый сальник мехатроника DSG 7 DQ200 
+Новый сальник мехатроника DSG 7 DQ200
 Отличное качество материала манжета мехатроника DQ200 ДСГ 7
 🔩 Артикул: 0am325066ad.</t>
         </is>
@@ -4988,7 +5036,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Сальник-манжета штока сцепления мехатроника DSG7 DQ200 0AM325066AD</t>
+          <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
         </is>
       </c>
       <c r="AH45" t="n">
@@ -5084,7 +5132,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита мехатроника DSG7 DQ200 0AM325066AE</t>
+          <t>Усиленная гидроплита мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH46" t="n">
@@ -5158,11 +5206,11 @@
 📌 Заменять, если:
 • Появился люфт, коррозия или выработка
 • Проблемы при включении передач
-• Планируется плановый ремонт мехатроника 
+• Планируется плановый ремонт мехатроника
 💡 Особенности:
 • Длина — 101 мм
 📦 Очень быстрая отправка
-👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника 
+👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника
 Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.
 В наличии оригинальные штоки DSG7 DQ200 0AM 0CW
 Идеальное состояние - каждый шток дсг 7 dq200 проверяется
@@ -5183,7 +5231,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 101мм 0AM325091E</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 101мм</t>
         </is>
       </c>
       <c r="AH47" t="n">
@@ -5258,7 +5306,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2</t>
         </is>
       </c>
       <c r="AH48" t="n">
@@ -5326,12 +5374,12 @@
           <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)
 Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.
 ✅ Совместимость: • DSG7 DQ200 (7-ступ., сухое сцепление) • Мехатроник 0AM / 0CW • Авто VAG-группы: VW, Audi, Skoda, Seat (после 2012 года выпуска) • Артикул: 0AM325091F (шток нового образца, 99 мм)
-📌 Когда ставить: 
-• При замене вилки сцепления 
-• При ремонте гидроблока или штока 
+📌 Когда ставить:
+• При замене вилки сцепления
+• При ремонте гидроблока или штока
 • Восстановление точности включения сцепления
 Точная длина 99 мм
-📦 Очень быстрая отправка 
+📦 Очень быстрая отправка
 👉 Деталь для тех, кто ремонтирует точно и надолго — оформите заказ без переплат
 Шток мехатроника DSG7, длиной 99 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091f. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.
 💡В наличии оригинальные штоки DSG7 DQ200 0AM 0CW
@@ -5360,7 +5408,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 99мм короткий 0AM325091F</t>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм</t>
         </is>
       </c>
       <c r="AH49" t="n">
@@ -5435,7 +5483,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2</t>
         </is>
       </c>
       <c r="AH50" t="n">
@@ -5490,168 +5538,246 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>🔧 Планка (фиксатор) соленоидов мехатроника DSG7 DQ200 — пластиковая, 1 шт (половина комплекта, крепит 4 соленоида одной стороны блока). ✅ Подходит на оба поколения мехатроника — Bosch и Hilite, 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Артикул: 0am325477. ⭐ Нужна вторая планка? У нас есть комплект 2 шт — выгоднее при полной переборке мехатроника.</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="AH51" t="n">
+        <v>1450</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>0am325477ae</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti
 🔩 Артикул: 0am325477ae.</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png?v=368fa6503f</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200 0AM325477AE ОРИГИНАЛ VAG</t>
-        </is>
-      </c>
-      <c r="AH51" t="n">
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH52" t="n">
         <v>2479</v>
       </c>
-      <c r="AJ51" t="inlineStr">
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK51" t="inlineStr">
+      <c r="AK52" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL51" t="inlineStr">
+      <c r="AL52" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
+      <c r="AM52" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
+      <c r="AN52" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO51" t="inlineStr">
+      <c r="AO52" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR51" t="inlineStr">
+      <c r="AR52" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS51" t="inlineStr">
+      <c r="AS52" t="inlineStr">
         <is>
           <t>0am325477ae</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>0ambset</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КППОригинальное качество NSK10 шт в комплекте – полная заменаДобавляйте в корзину!
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП
+Оригинальное качество NSK
+10 шт в комплекте – полная замена
+Добавляйте в корзину!
 🔩 Артикул: 0ambset.</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png?v=51d4844731
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png?v=bcd5b49d99</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
-        </is>
-      </c>
-      <c r="AH52" t="n">
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10</t>
+        </is>
+      </c>
+      <c r="AH53" t="n">
         <v>11979</v>
       </c>
-      <c r="AJ52" t="inlineStr">
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK52" t="inlineStr">
+      <c r="AK53" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr">
+      <c r="AL53" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
+      <c r="AM53" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
+      <c r="AN53" t="inlineStr">
         <is>
           <t>Валы, муфты, шестерни и подшипники КПП</t>
         </is>
       </c>
-      <c r="AO52" t="inlineStr">
+      <c r="AO53" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR52" t="inlineStr">
+      <c r="AR53" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS52" t="inlineStr">
+      <c r="AS53" t="inlineStr">
         <is>
           <t>0ambset</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>0cw0am</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM
 Описание товара
@@ -5659,275 +5785,275 @@
 Совместимость
 Подходит для коробок передач DQ200 0AM на автомобилях Volkswagen, Audi, Skoda, SEAT с двигателями малой и средней мощности.
 Преимущества
-	•	Полная герметизация электронной платы.
-	•	Предотвращение коррозии контактов и сбоев в работе мехатроника.
-	•	Простая замена при обслуживании DSG.
-	•	Подходит как для автосервисов, так и для самостоятельного ремонта.
+• Полная герметизация электронной платы.
+• Предотвращение коррозии контактов и сбоев в работе мехатроника.
+• Простая замена при обслуживании DSG.
+• Подходит как для автосервисов, так и для самостоятельного ремонта.
 Кому подойдет
 Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH53" t="n">
+      <c r="AH54" t="n">
         <v>931</v>
       </c>
-      <c r="AJ53" t="inlineStr">
+      <c r="AJ54" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK53" t="inlineStr">
+      <c r="AK54" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL53" t="inlineStr">
+      <c r="AL54" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
+      <c r="AM54" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
+      <c r="AN54" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AO54" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
+      <c r="AR54" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS53" t="inlineStr">
+      <c r="AS54" t="inlineStr">
         <is>
           <t>0cw0am</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>0cw0am325025</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW
 В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.
 В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.
 Состав комплекта
-	•	Прокладка крышки мехатроника — 0AM325443D
-	•	Крышка мехатроника — 0AM325219C
-	•	Фильтр мехатроника — 0AM325433E
-	•	Прокладки электронного блока управления (электронной платы) — 0AM927769D
-	•	Усиленная гидравлическая плита — 0AM325066AE
-	•	Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)
+• Прокладка крышки мехатроника — 0AM325443D
+• Крышка мехатроника — 0AM325219C
+• Фильтр мехатроника — 0AM325433E
+• Прокладки электронного блока управления (электронной платы) — 0AM927769D
+• Усиленная гидравлическая плита — 0AM325066AE
+• Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)
 Совместимость
 Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.
 Преимущества
-	•	Полный набор деталей для комплексного ремонта мехатроника DSG7.
-	•	Повышенная надёжность за счёт усиленной гидроплиты.
-	•	Использование оригинальных сальников и пыльников Volkswagen (Германия).
-	•	Устранение течей по штокам и снижение риска повторных неисправностей.
-	•	Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!
+• Полный набор деталей для комплексного ремонта мехатроника DSG7.
+• Повышенная надёжность за счёт усиленной гидроплиты.
+• Использование оригинальных сальников и пыльников Volkswagen (Германия).
+• Устранение течей по штокам и снижение риска повторных неисправностей.
+• Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!
 🔩 Артикул: 0cw0am325025.</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
-        </is>
-      </c>
-      <c r="AH54" t="n">
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные</t>
+        </is>
+      </c>
+      <c r="AH55" t="n">
         <v>16890</v>
       </c>
-      <c r="AJ54" t="inlineStr">
+      <c r="AJ55" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK54" t="inlineStr">
+      <c r="AK55" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL54" t="inlineStr">
+      <c r="AL55" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AM55" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
+      <c r="AN55" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO54" t="inlineStr">
+      <c r="AO55" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR54" t="inlineStr">
+      <c r="AR55" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS54" t="inlineStr">
+      <c r="AS55" t="inlineStr">
         <is>
           <t>0cw0am325025</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.
 Совместимость
 Применяется в коробках передач DSG 7 DQ200 серии 0AM, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT с двигателями малой и средней мощности.
 Преимущества
-	•	Обеспечивает плотную и надежную герметизацию электронной платы.
-	•	Снижает риск коррозии контактов и отказов электронного блока.
-	•	Удобна в установке при техническом обслуживании и ремонте DSG.
-	•	Подходит для использования в автосервисах и при самостоятельном ремонте.
+• Обеспечивает плотную и надежную герметизацию электронной платы.
+• Снижает риск коррозии контактов и отказов электронного блока.
+• Удобна в установке при техническом обслуживании и ремонте DSG.
+• Подходит для использования в автосервисах и при самостоятельном ремонте.
 Намного дешевле полной ремкомплекта прокладок DSG7 DQ200 !
 🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=77a111eb34
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=40c2597cb3</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>Уплотнение электромотора гидроблока мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH55" t="n">
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Уплотнение электромотора гидроблока мехатроника</t>
+        </is>
+      </c>
+      <c r="AH56" t="n">
         <v>850</v>
       </c>
-      <c r="AJ55" t="inlineStr">
+      <c r="AJ56" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK55" t="inlineStr">
+      <c r="AK56" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL55" t="inlineStr">
+      <c r="AL56" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
+      <c r="AM56" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
+      <c r="AN56" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO55" t="inlineStr">
+      <c r="AO56" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR55" t="inlineStr">
+      <c r="AR56" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS55" t="inlineStr">
+      <c r="AS56" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377
 🔎
-Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU.  ￼
+Прокладка электронной платы мехатроника для DSG 7-ступенчатой трансмиссии DQ200 (код 0AM927377) — важный расходный элемент, обеспечивающий надежную герметизацию электронной части мехатроника коробки передач. Рекомендуется при разборке/сборке мехатроника, ремонте гидравлического блока или при выявлении неполадок в работе TCU. ￼
 📌 Совместимость:
-	•	Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW
-	•	Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением,  «сухая» (модели Volkswagen, Audi, Skoda, SEAT
+• Применяется в роботизированных коробках передач DSG-7 DQ200 0AM 0CW
+• Для легковых автомобилей с 7-скоростным DSG с сухим сцеплением, «сухая» (модели Volkswagen, Audi, Skoda, SEAT
 🔧 Особенности:
-	•	Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.
-	•	Новая деталь для эксплуатационного и сервисного обслуживания.  ￼
+• Код запчасти: 0AM927377 — Обеспечивает герметичность электронной платы и предотвращает попадание влаги/масла.
+• Новая деталь для эксплуатационного и сервисного обслуживания. ￼
 📦 Преимущества покупки:
 ✔ Быстрая и простая замена при обслуживании мехатроника
 ✔ Совместима с популярными моделями VAG-группы
@@ -5940,78 +6066,78 @@
 🔩 Артикул: 0cw325025h.</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>Прокладка электронной платы мехатроника DSG7 DQ200 0AM927769N</t>
-        </is>
-      </c>
-      <c r="AH56" t="n">
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Прокладка электронной платы мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH57" t="n">
         <v>1290</v>
       </c>
-      <c r="AJ56" t="inlineStr">
+      <c r="AJ57" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK56" t="inlineStr">
+      <c r="AK57" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL56" t="inlineStr">
+      <c r="AL57" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
+      <c r="AM57" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
+      <c r="AN57" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO56" t="inlineStr">
+      <c r="AO57" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR56" t="inlineStr">
+      <c r="AR57" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS56" t="inlineStr">
+      <c r="AS57" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>0сц</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.
 Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.
@@ -6023,88 +6149,88 @@
 Назначение
 Уплотнение штока мехатроника Восстановление герметичности Защита сухого сцепления DSG7
 Преимущества оригинала
-• Оригинальная деталь Volkswagen 
-• Точная заводская геометрия 
-• Устойчивость к температуре и давлению 
-• Длительный ресурс эксплуатации 
+• Оригинальная деталь Volkswagen
+• Точная заводская геометрия
+• Устойчивость к температуре и давлению
+• Длительный ресурс эксплуатации
 • Установка без доработок
 Оригинальный сальник штока мехатроника DSG7 DQ200, применяется в узле штока 0AM325091E / 0AM325091F.
 🔩 Артикул: 0сц.</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.jpg?v=3e0abf9ec7
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.jpg?v=b12c6dac21
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.jpg?v=bd237a81d2</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока мехатроника DSG7 DQ200 Volkswagen</t>
-        </is>
-      </c>
-      <c r="AH57" t="n">
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH58" t="n">
         <v>1490</v>
       </c>
-      <c r="AJ57" t="inlineStr">
+      <c r="AJ58" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK57" t="inlineStr">
+      <c r="AK58" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
+      <c r="AL58" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AM58" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
+      <c r="AN58" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO57" t="inlineStr">
+      <c r="AO58" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR57" t="inlineStr">
+      <c r="AR58" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS57" t="inlineStr">
+      <c r="AS58" t="inlineStr">
         <is>
           <t>0c</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>122390AK-AF</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект
 Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW
@@ -6117,78 +6243,78 @@
 🔩 Артикул: 122390AK-AF.</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=a2422623a6
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg?v=70e1dc8dfd</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
-      <c r="AH58" t="n">
+      <c r="AH59" t="n">
         <v>979</v>
       </c>
-      <c r="AJ58" t="inlineStr">
+      <c r="AJ59" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK58" t="inlineStr">
+      <c r="AK59" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
+      <c r="AL59" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AM59" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
+      <c r="AN59" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO58" t="inlineStr">
+      <c r="AO59" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR58" t="inlineStr">
+      <c r="AR59" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS58" t="inlineStr">
+      <c r="AS59" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)
 Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.
@@ -6218,154 +6344,162 @@
 🔩 Артикул: 122390AKAF.</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png?v=a2422623a6</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200 Volkswagen (Германия) 122390AKAF</t>
-        </is>
-      </c>
-      <c r="AH59" t="n">
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH60" t="n">
         <v>1490</v>
       </c>
-      <c r="AJ59" t="inlineStr">
+      <c r="AJ60" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK59" t="inlineStr">
+      <c r="AK60" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL59" t="inlineStr">
+      <c r="AL60" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
+      <c r="AM60" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
+      <c r="AN60" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO59" t="inlineStr">
+      <c r="AO60" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR59" t="inlineStr">
+      <c r="AR60" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS59" t="inlineStr">
+      <c r="AS60" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>123014‑AF</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества
-✅ Подходит для DSG‑7 (DL501 / 0B5 / 0BH)Устанавливается в соленоиды N436 / N440Аналог оригинала 0B5 325 421Обеспечивает тонкую фильтрацию маслаПродлевает срок службы гидроблокаКачественная фильтр‑сетка 123014‑AFИдеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
+✅
+Подходит для DSG‑7 (DL501 / 0B5 / 0BH)
+Устанавливается в соленоиды N436 / N440
+Аналог оригинала 0B5 325 421
+Обеспечивает тонкую фильтрацию масла
+Продлевает срок службы гидроблока
+Качественная фильтр‑сетка 123014‑AF
+Идеальное решение для профилактики выхода из строя соленоидов: обеспечивает тонкую фильтрацию, предотвращает засорение, продлевает срок службы КПП DQ500 / 0BH.
+Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=6a32ad2888
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=995613c21a</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF (аналог 0B5325421)</t>
-        </is>
-      </c>
-      <c r="AH60" t="n">
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
+        </is>
+      </c>
+      <c r="AH61" t="n">
         <v>1479</v>
       </c>
-      <c r="AJ60" t="inlineStr">
+      <c r="AJ61" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK60" t="inlineStr">
+      <c r="AK61" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL60" t="inlineStr">
+      <c r="AL61" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
+      <c r="AM61" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
+      <c r="AN61" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO60" t="inlineStr">
+      <c r="AO61" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR60" t="inlineStr">
+      <c r="AR61" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS60" t="inlineStr">
+      <c r="AS61" t="inlineStr">
         <is>
           <t>123014AF</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>31705-1XF0C</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.
 Описание товара
@@ -6378,169 +6512,195 @@
 • Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП
 Совместимость
 Тип КПП: вариатор CVT Модель: JF011E / RE0F10A
-Применяется в автомобилях:NissanMitsubishiRenaultJeep(модели с установленным вариатором JF011E — по каталогу производителя)
+Применяется в автомобилях:
+Nissan
+Mitsubishi
+Renault
+Jeep
+(модели с установленным вариатором JF011E — по каталогу производителя)
 Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый
 гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e
 🔩 Артикул: 31705-1XF0C.</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg?v=dc356035c7</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика, 31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="AH61" t="n">
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика</t>
+        </is>
+      </c>
+      <c r="AH62" t="n">
         <v>58900</v>
       </c>
-      <c r="AJ61" t="inlineStr">
+      <c r="AJ62" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK61" t="inlineStr">
+      <c r="AK62" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL61" t="inlineStr">
+      <c r="AL62" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
+      <c r="AM62" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
+      <c r="AN62" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO61" t="inlineStr">
+      <c r="AO62" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR61" t="inlineStr">
+      <c r="AR62" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS61" t="inlineStr">
+      <c r="AS62" t="inlineStr">
         <is>
           <t>317051XF0C</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>31705-X428B</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi —  новый
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi — новый
 Краткое описание (первые 3 строки — самое важное для Ozon)
 Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.
 Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.
 Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.
-Признаки неисправности гидроблока JF015E:рывки и пинки при разгонезадержка включения Drive / Reverseпробуксовка вариаторапереход в аварийный режимошибки по давлению масла и соленоидамвибрации и нестабильная работа CVTПреимущества:Полная совместимость с вариатором JF015E (RE0F11A)Восстанавливает корректное давление маслаУлучшает плавность хода и отклик трансмиссииОптимальное решение без замены всего вариатораПодходит для СТО и самостоятельного ремонтаСовместимость:
+Признаки неисправности гидроблока JF015E:
+рывки и пинки при разгоне
+задержка включения Drive / Reverse
+пробуксовка вариатора
+переход в аварийный режим
+ошибки по давлению масла и соленоидам
+вибрации и нестабильная работа CVT
+Преимущества:
+Полная совместимость с вариатором JF015E (RE0F11A)
+Восстанавливает корректное давление масла
+Улучшает плавность хода и отклик трансмиссии
+Оптимальное решение без замены всего вариатора
+Подходит для СТО и самостоятельного ремонта
+Совместимость:
 Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)
-Часто устанавливается на:Nissan JukeNissan QashqaiNissan NoteNissan SentraRenault FluenceRenault KapturMitsubishi ASX (и другие модели с вариатором JF015E)Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый
+Часто устанавливается на:
+Nissan Juke
+Nissan Qashqai
+Nissan Note
+Nissan Sentra
+Renault Fluence
+Renault Kaptur
+Mitsubishi ASX (и другие модели с вариатором JF015E)
+Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый
 гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор
 🔩 Артикул: 31705-X428B.</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png?v=6ac791003d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png?v=4bd4c0625c
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png?v=4e011c48be</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый, 31705-X428B</t>
-        </is>
-      </c>
-      <c r="AH62" t="n">
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый</t>
+        </is>
+      </c>
+      <c r="AH63" t="n">
         <v>58900</v>
       </c>
-      <c r="AJ62" t="inlineStr">
+      <c r="AJ63" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK62" t="inlineStr">
+      <c r="AK63" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL62" t="inlineStr">
+      <c r="AL63" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
+      <c r="AM63" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
+      <c r="AN63" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO62" t="inlineStr">
+      <c r="AO63" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR62" t="inlineStr">
+      <c r="AR63" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS62" t="inlineStr">
+      <c r="AS63" t="inlineStr">
         <is>
           <t>31705X428B</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.
 Описание товара
@@ -6553,217 +6713,151 @@
 • Совместимость с вариатором JF015E (RE0F11A) • Восстановление корректной работы соленоидов • Стабильное давление масла в системе • Улучшение плавности и отклика трансмиссии • Эффективная альтернатива полной замене вариатора
 Совместимость
 Тип КПП: вариатор CVT Модель: JF015E / RE0F11A
-Подходит для автомобилей:NissanRenaultMitsubishi(модели с установленным вариатором JF015E — по каталогу)
+Подходит для автомобилей:
+Nissan
+Renault
+Mitsubishi
+(модели с установленным вариатором JF015E — по каталогу)
 Техническая информация
-Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый 
+Назначение: гидроблок вариатора Тип установки: штатная Совместимость: JF015E / RE0F11A Состояние: новый
 гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan
 🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A) 317053TX0C</t>
-        </is>
-      </c>
-      <c r="AH63" t="n">
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
+        </is>
+      </c>
+      <c r="AH64" t="n">
         <v>58900</v>
       </c>
-      <c r="AJ63" t="inlineStr">
+      <c r="AJ64" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK63" t="inlineStr">
+      <c r="AK64" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL63" t="inlineStr">
+      <c r="AL64" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
+      <c r="AM64" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
+      <c r="AN64" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO63" t="inlineStr">
+      <c r="AO64" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR63" t="inlineStr">
+      <c r="AR64" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS63" t="inlineStr">
+      <c r="AS64" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>55565480</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>импульсная звёздочка датчика положения распредвалаЭто сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.Новое импульсное кольцо распредвала Opel Chevrolet 
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>импульсная звёздочка датчика положения распредвала
+Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.
+Оно взаимодействует с датчиком положения распредвала, обеспечивая считывание фазы ГРМ.
+Существует проблема разрушения кольца, что приводит к ошибке по синхронизации фаз (ошибка P0341 и др.)
+Оригинальное кольцо — штампованное, из металла, со временем может расслаиваться или ломаться, из-за чего его заменяют.
+Новое импульсное кольцо распредвала Opel Chevrolet 
 Звездочка привода Распредвала - в наличии 
 Датчик распредвала 55565480 GM</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>Импульсное кольцо распредвала GM 55565480 (5636119)</t>
-        </is>
-      </c>
-      <c r="AH64" t="n">
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Импульсное кольцо распредвала GM 55565480</t>
+        </is>
+      </c>
+      <c r="AH65" t="n">
         <v>999</v>
       </c>
-      <c r="AJ64" t="inlineStr">
+      <c r="AJ65" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK64" t="inlineStr">
+      <c r="AK65" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL64" t="inlineStr">
+      <c r="AL65" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
+      <c r="AM65" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
+      <c r="AN65" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO64" t="inlineStr">
+      <c r="AO65" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR64" t="inlineStr">
+      <c r="AR65" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS64" t="inlineStr">
+      <c r="AS65" t="inlineStr">
         <is>
           <t>55565480</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>6t30</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
-        </is>
-      </c>
-      <c r="AH65" t="n">
-        <v>19800</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL65" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr">
-        <is>
-          <t>6t30</t>
         </is>
       </c>
     </row>
@@ -6775,15 +6869,90 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>6t30</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+        </is>
+      </c>
+      <c r="AH66" t="n">
+        <v>19800</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>6t30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>DQ500</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH
 Новые
@@ -6792,7 +6961,7 @@
 Снижает температуру масла</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
@@ -6800,242 +6969,242 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
-        </is>
-      </c>
-      <c r="AH66" t="n">
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
+        </is>
+      </c>
+      <c r="AH67" t="n">
         <v>3850</v>
       </c>
-      <c r="AJ66" t="inlineStr">
+      <c r="AJ67" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK66" t="inlineStr">
+      <c r="AK67" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL66" t="inlineStr">
+      <c r="AL67" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
+      <c r="AM67" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
+      <c r="AN67" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO66" t="inlineStr">
+      <c r="AO67" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR66" t="inlineStr">
+      <c r="AR67" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS66" t="inlineStr">
+      <c r="AS67" t="inlineStr">
         <is>
           <t>DQ500</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Dq200dsg7</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!
 🔩 Артикул: Dq200dsg7.</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg?v=12b215cccc</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH67" t="n">
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH68" t="n">
         <v>979</v>
       </c>
-      <c r="AJ67" t="inlineStr">
+      <c r="AJ68" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK67" t="inlineStr">
+      <c r="AK68" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL67" t="inlineStr">
+      <c r="AL68" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
+      <c r="AM68" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
+      <c r="AN68" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO67" t="inlineStr">
+      <c r="AO68" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR67" t="inlineStr">
+      <c r="AR68" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS67" t="inlineStr">
+      <c r="AS68" t="inlineStr">
         <is>
           <t>Dq200dsg7</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Dq200dsg70am0cw</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)
 Описание товара
 Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.
 В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.
 Комплектация
-	•	Прокладка крышки мехатроника — 0AM325443D
-	•	Крышка мехатроника — 0AM325219C
-	•	Фильтр мехатроника — 0AM325433E
-	•	Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D
-	•	Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)
-И так далее как на фото! 
+• Прокладка крышки мехатроника — 0AM325443D
+• Крышка мехатроника — 0AM325219C
+• Фильтр мехатроника — 0AM325433E
+• Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D
+• Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)
+И так далее как на фото!
 Совместимость
 Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.
 Преимущества
-	•	Полный набор деталей для комплексного восстановления мехатроника DSG7.
-	•	Повышенный ресурс за счёт усиленной гидравлической плиты.
-	•	Оригинальные сальники и пыльники Volkswagen (Германия).
-	•	Минимизация риска повторных утечек и отказов.
-	•	Подходит для профессионального и сервисного ремонта, также для физ лиц!
+• Полный набор деталей для комплексного восстановления мехатроника DSG7.
+• Повышенный ресурс за счёт усиленной гидравлической плиты.
+• Оригинальные сальники и пыльники Volkswagen (Германия).
+• Минимизация риска повторных утечек и отказов.
+• Подходит для профессионального и сервисного ремонта, также для физ лиц!
 🔩 Артикул: Dq200dsg70am0cw.</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
-        </is>
-      </c>
-      <c r="AH68" t="n">
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH69" t="n">
         <v>8890</v>
       </c>
-      <c r="AJ68" t="inlineStr">
+      <c r="AJ69" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK68" t="inlineStr">
+      <c r="AK69" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL68" t="inlineStr">
+      <c r="AL69" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AM69" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
+      <c r="AN69" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO68" t="inlineStr">
+      <c r="AO69" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR68" t="inlineStr">
+      <c r="AR69" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS68" t="inlineStr">
+      <c r="AS69" t="inlineStr">
         <is>
           <t>Dq200dsg70am0cw</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>Улучшенный отвод тепла
 Уменьшает температуру масла КПП
@@ -7054,7 +7223,7 @@
 📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203
@@ -7072,434 +7241,359 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="AH69" t="n">
+      <c r="AH70" t="n">
         <v>3879</v>
       </c>
-      <c r="AJ69" t="inlineStr">
+      <c r="AJ70" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK69" t="inlineStr">
+      <c r="AK70" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL69" t="inlineStr">
+      <c r="AL70" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
+      <c r="AM70" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
+      <c r="AN70" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO69" t="inlineStr">
+      <c r="AO70" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR69" t="inlineStr">
+      <c r="AR70" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS69" t="inlineStr">
+      <c r="AS70" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>WHT001922</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный
 Новый Отличное качество
 🔩 Артикул: WHT001922.</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW WHT001922</t>
-        </is>
-      </c>
-      <c r="AH70" t="n">
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="AH71" t="n">
         <v>979</v>
       </c>
-      <c r="AJ70" t="inlineStr">
+      <c r="AJ71" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK70" t="inlineStr">
+      <c r="AK71" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL70" t="inlineStr">
+      <c r="AL71" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
+      <c r="AM71" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
+      <c r="AN71" t="inlineStr">
         <is>
           <t>Крепёж КПП</t>
         </is>
       </c>
-      <c r="AO70" t="inlineStr">
+      <c r="AO71" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR70" t="inlineStr">
+      <c r="AR71" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS70" t="inlineStr">
+      <c r="AS71" t="inlineStr">
         <is>
           <t>WHT001922</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=be20ada597
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=87268821a3</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5 DL501</t>
-        </is>
-      </c>
-      <c r="AH71" t="n">
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5</t>
+        </is>
+      </c>
+      <c r="AH72" t="n">
         <v>1490</v>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AJ72" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK71" t="inlineStr">
+      <c r="AK72" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL71" t="inlineStr">
+      <c r="AL72" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
+      <c r="AM72" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
+      <c r="AN72" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO71" t="inlineStr">
+      <c r="AO72" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR71" t="inlineStr">
+      <c r="AR72" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS71" t="inlineStr">
+      <c r="AS72" t="inlineStr">
         <is>
           <t>filtrsetka0b5orig</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>gidroakkumulyator-orig</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DSG7 DQ200 VAG</t>
-        </is>
-      </c>
-      <c r="AH72" t="n">
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH73" t="n">
         <v>8890</v>
       </c>
-      <c r="AJ72" t="inlineStr">
+      <c r="AJ73" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK72" t="inlineStr">
+      <c r="AK73" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL72" t="inlineStr">
+      <c r="AL73" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
+      <c r="AM73" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
+      <c r="AN73" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO72" t="inlineStr">
+      <c r="AO73" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR72" t="inlineStr">
+      <c r="AR73" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS72" t="inlineStr">
+      <c r="AS73" t="inlineStr">
         <is>
           <t>gidroakkumulyatororig</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>jf011e</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.
 В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
-        </is>
-      </c>
-      <c r="AH73" t="n">
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A)</t>
+        </is>
+      </c>
+      <c r="AH74" t="n">
         <v>12979</v>
       </c>
-      <c r="AJ73" t="inlineStr">
+      <c r="AJ74" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK73" t="inlineStr">
+      <c r="AK74" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL73" t="inlineStr">
+      <c r="AL74" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
+      <c r="AM74" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
+      <c r="AN74" t="inlineStr">
         <is>
           <t>Валы, муфты, шестерни и подшипники КПП</t>
         </is>
       </c>
-      <c r="AO73" t="inlineStr">
+      <c r="AO74" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR73" t="inlineStr">
+      <c r="AR74" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS73" t="inlineStr">
+      <c r="AS74" t="inlineStr">
         <is>
           <t>jf011e</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>klipsy-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
-        </is>
-      </c>
-      <c r="AH74" t="n">
-        <v>950</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL74" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr">
-        <is>
-          <t>klipsyshtokov2sht</t>
         </is>
       </c>
     </row>
@@ -7511,146 +7605,146 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>klipsy-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2</t>
+        </is>
+      </c>
+      <c r="AH75" t="n">
+        <v>950</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN75" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>klipsyshtokov2sht</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
           <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png?v=207791c0ab
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png?v=33f6b91718</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500 0BH325159 (без фильтра)</t>
-        </is>
-      </c>
-      <c r="AH75" t="n">
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500</t>
+        </is>
+      </c>
+      <c r="AH76" t="n">
         <v>3879</v>
       </c>
-      <c r="AJ75" t="inlineStr">
+      <c r="AJ76" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK75" t="inlineStr">
+      <c r="AK76" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL75" t="inlineStr">
+      <c r="AL76" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
+      <c r="AM76" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
+      <c r="AN76" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO75" t="inlineStr">
+      <c r="AO76" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR75" t="inlineStr">
+      <c r="AR76" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS75" t="inlineStr">
+      <c r="AS76" t="inlineStr">
         <is>
           <t>korpusfiltra0bh325159</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>planka-solenoid-2sht</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
-        </is>
-      </c>
-      <c r="AH76" t="n">
-        <v>2890</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL76" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>plankasolenoid2sht</t>
         </is>
       </c>
     </row>
@@ -7662,180 +7756,180 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>planka-solenoid-2sht</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Планки соленоидов мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH77" t="n">
+        <v>2890</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>plankasolenoid2sht</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
           <t>plastiny-solenoid-orig</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Оригинальные пластины на соленоиды VAG мехатроника DSG7 DQ200 (без сепараторной пластины)</t>
-        </is>
-      </c>
-      <c r="AH77" t="n">
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Оригинальные пластины на соленоиды VAG</t>
+        </is>
+      </c>
+      <c r="AH78" t="n">
         <v>990</v>
       </c>
-      <c r="AJ77" t="inlineStr">
+      <c r="AJ78" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK77" t="inlineStr">
+      <c r="AK78" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL77" t="inlineStr">
+      <c r="AL78" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
+      <c r="AM78" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
+      <c r="AN78" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO77" t="inlineStr">
+      <c r="AO78" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR77" t="inlineStr">
+      <c r="AR78" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS77" t="inlineStr">
+      <c r="AS78" t="inlineStr">
         <is>
           <t>plastinysolenoidorig</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>plita-filtr</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=efa8557d9d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=759d463fe2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=3f11b4e476</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
-        </is>
-      </c>
-      <c r="AH78" t="n">
-        <v>7500</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL78" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>plitafiltr</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>plita-filtr-orig</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.png?v=b8cb2f02a1</t>
-        </is>
-      </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7</t>
         </is>
       </c>
       <c r="AH79" t="n">
@@ -7878,7 +7972,7 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>plitafiltrorig</t>
+          <t>plitafiltr</t>
         </is>
       </c>
     </row>
@@ -7890,103 +7984,103 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t>plita-filtr-orig</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Усиленная плита + улучшенный фильтр мехатроника</t>
+        </is>
+      </c>
+      <c r="AH80" t="n">
+        <v>7500</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN80" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>plitafiltrorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
           <t>plita-filtr-pylniki</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
-        </is>
-      </c>
-      <c r="AH80" t="n">
-        <v>8500</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL80" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr">
-        <is>
-          <t>plitafiltrpylniki</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-orig</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
-        </is>
-      </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков</t>
         </is>
       </c>
       <c r="AH81" t="n">
@@ -8029,7 +8123,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikiorig</t>
+          <t>plitafiltrpylniki</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8135,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -8051,21 +8145,21 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
         </is>
       </c>
       <c r="AH82" t="n">
-        <v>9500</v>
+        <v>8500</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -8089,7 +8183,7 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -8104,7 +8198,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikisal</t>
+          <t>plitafiltrpylnikiorig</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8210,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -8126,17 +8220,17 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.png?v=e34fb25bfd</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2</t>
         </is>
       </c>
       <c r="AH83" t="n">
@@ -8179,7 +8273,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikisalorig</t>
+          <t>plitafiltrpylnikisal</t>
         </is>
       </c>
     </row>
@@ -8191,146 +8285,146 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t>plita-filtr-pylniki-sal-orig</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG</t>
+        </is>
+      </c>
+      <c r="AH84" t="n">
+        <v>9500</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN84" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>plitafiltrpylnikisalorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
           <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png?v=9157b6c42a</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
-        </is>
-      </c>
-      <c r="AH84" t="n">
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+        </is>
+      </c>
+      <c r="AH85" t="n">
         <v>8500</v>
       </c>
-      <c r="AJ84" t="inlineStr">
+      <c r="AJ85" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK84" t="inlineStr">
+      <c r="AK85" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL84" t="inlineStr">
+      <c r="AL85" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
+      <c r="AM85" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN84" t="inlineStr">
+      <c r="AN85" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO84" t="inlineStr">
+      <c r="AO85" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR84" t="inlineStr">
+      <c r="AR85" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS84" t="inlineStr">
+      <c r="AS85" t="inlineStr">
         <is>
           <t>plitafiltrsalnikiorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png?v=16f48e3b34</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект</t>
-        </is>
-      </c>
-      <c r="AH85" t="n">
-        <v>7500</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL85" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>plitafiltrv2</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8436,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -8352,21 +8446,21 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.png?v=fd0e412e14</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png?v=16f48e3b34</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200</t>
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>8500</v>
+        <v>7500</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -8390,7 +8484,7 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -8405,7 +8499,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>plitapylnikisalniki</t>
+          <t>plitafiltrv2</t>
         </is>
       </c>
     </row>
@@ -8417,7 +8511,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -8427,21 +8521,21 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=03ce24da06</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
         </is>
       </c>
       <c r="AH87" t="n">
-        <v>9500</v>
+        <v>8500</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -8480,7 +8574,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>plitapylnikisalnikiorig</t>
+          <t>plitapylnikisalniki</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8586,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -8507,12 +8601,12 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png?v=b98621fc0a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
         </is>
       </c>
       <c r="AH88" t="n">
@@ -8555,7 +8649,7 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>plitapylnikisalnikiorigv2</t>
+          <t>plitapylnikisalnikiorig</t>
         </is>
       </c>
     </row>
@@ -8567,146 +8661,146 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
+          <t>plita-pylniki-salniki-orig-v2</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png?v=b98621fc0a</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
+        </is>
+      </c>
+      <c r="AH89" t="n">
+        <v>9500</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN89" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>plitapylnikisalnikiorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
           <t>podshipnik-vilki-6</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7 DQ200, 1 шт</t>
-        </is>
-      </c>
-      <c r="AH89" t="n">
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
+        </is>
+      </c>
+      <c r="AH90" t="n">
         <v>1240</v>
       </c>
-      <c r="AJ89" t="inlineStr">
+      <c r="AJ90" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK89" t="inlineStr">
+      <c r="AK90" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL89" t="inlineStr">
+      <c r="AL90" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
+      <c r="AM90" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN89" t="inlineStr">
+      <c r="AN90" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO89" t="inlineStr">
+      <c r="AO90" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR89" t="inlineStr">
+      <c r="AR90" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS89" t="inlineStr">
+      <c r="AS90" t="inlineStr">
         <is>
           <t>podshipnikvilki6</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
-        </is>
-      </c>
-      <c r="AH90" t="n">
-        <v>3990</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>porshniusilpylnikikryshki</t>
         </is>
       </c>
     </row>
@@ -8718,146 +8812,146 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>porshni-usil-pylniki-kryshki</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня</t>
+        </is>
+      </c>
+      <c r="AH91" t="n">
+        <v>3990</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>porshniusilpylnikikryshki</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
           <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
-        </is>
-      </c>
-      <c r="AH91" t="n">
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня</t>
+        </is>
+      </c>
+      <c r="AH92" t="n">
         <v>3990</v>
       </c>
-      <c r="AJ91" t="inlineStr">
+      <c r="AJ92" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK91" t="inlineStr">
+      <c r="AK92" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL91" t="inlineStr">
+      <c r="AL92" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
+      <c r="AM92" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
+      <c r="AN92" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO91" t="inlineStr">
+      <c r="AO92" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR91" t="inlineStr">
+      <c r="AR92" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS91" t="inlineStr">
+      <c r="AS92" t="inlineStr">
         <is>
           <t>porshniusilpylnikikryshkiv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH92" t="n">
-        <v>1850</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr">
-        <is>
-          <t>pylnikishtokovorig</t>
         </is>
       </c>
     </row>
@@ -8869,7 +8963,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8884,12 +8978,12 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH93" t="n">
@@ -8932,7 +9026,7 @@
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>pylnikishtokovorigv2</t>
+          <t>pylnikishtokovorig</t>
         </is>
       </c>
     </row>
@@ -8944,7 +9038,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -8954,21 +9048,21 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="AH94" t="n">
-        <v>2850</v>
+        <v>1850</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -8992,7 +9086,7 @@
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Переключение передач</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -9007,7 +9101,7 @@
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>remkomplektshtokovorig</t>
+          <t>pylnikishtokovorigv2</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9113,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -9034,12 +9128,12 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
         </is>
       </c>
       <c r="AH95" t="n">
@@ -9082,7 +9176,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>remkomplektshtokovorigv2</t>
+          <t>remkomplektshtokovorig</t>
         </is>
       </c>
     </row>
@@ -9094,103 +9188,103 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>remkomplekt-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
+        </is>
+      </c>
+      <c r="AH96" t="n">
+        <v>2850</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>remkomplektshtokovorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
           <t>salnik-shtoka-orig</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="P97" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH96" t="n">
-        <v>1490</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL96" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>salnikshtokaorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig-v2</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="AH97" t="n">
@@ -9233,7 +9327,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>salnikshtokaorigv2</t>
+          <t>salnikshtokaorig</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9339,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -9255,21 +9349,21 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="AH98" t="n">
-        <v>2490</v>
+        <v>1490</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
@@ -9308,7 +9402,7 @@
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>salniktolkatelyaalum</t>
+          <t>salnikshtokaorigv2</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9414,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -9330,21 +9424,21 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленные алюминиевые сальники толкателя с</t>
         </is>
       </c>
       <c r="AH99" t="n">
-        <v>1690</v>
+        <v>2490</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
@@ -9383,7 +9477,7 @@
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>salnikishtokov2sht</t>
+          <t>salniktolkatelyaalum</t>
         </is>
       </c>
     </row>
@@ -9395,7 +9489,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -9405,21 +9499,21 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="AH100" t="n">
-        <v>1890</v>
+        <v>1690</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
@@ -9458,7 +9552,7 @@
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>salnikishtokovorig</t>
+          <t>salnikishtokov2sht</t>
         </is>
       </c>
     </row>
@@ -9470,146 +9564,146 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH101" t="n">
+        <v>1890</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN101" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>salnikishtokovorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
           <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr">
+      <c r="Q102" t="inlineStr">
         <is>
           <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr">
+      <c r="S102" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
         </is>
       </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
-        </is>
-      </c>
-      <c r="AH101" t="n">
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Полный комплект сальников толкателей вилок</t>
+        </is>
+      </c>
+      <c r="AH102" t="n">
         <v>1950</v>
       </c>
-      <c r="AJ101" t="inlineStr">
+      <c r="AJ102" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK101" t="inlineStr">
+      <c r="AK102" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL101" t="inlineStr">
+      <c r="AL102" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
+      <c r="AM102" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
+      <c r="AN102" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO101" t="inlineStr">
+      <c r="AO102" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR101" t="inlineStr">
+      <c r="AR102" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS101" t="inlineStr">
+      <c r="AS102" t="inlineStr">
         <is>
           <t>salnikitolkatelya4sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>salnikprivod-l</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH102" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>salnikprivodl</t>
         </is>
       </c>
     </row>
@@ -9621,7 +9715,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9631,17 +9725,17 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH103" t="n">
@@ -9684,7 +9778,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>salnikprivodr</t>
+          <t>salnikprivodl</t>
         </is>
       </c>
     </row>
@@ -9696,103 +9790,103 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t>salnikprivod-r</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Сальник привода правый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH104" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>salnikprivodr</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
           <t>salnikvhod</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="P105" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>Сальник входного вала DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH104" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL104" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH105" t="n">
@@ -9835,7 +9929,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnikvhod</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9941,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9857,21 +9951,21 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH106" t="n">
-        <v>1950</v>
+        <v>999</v>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
@@ -9895,7 +9989,7 @@
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>Электронное управление КПП</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -9910,7 +10004,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>stalnayavstavkaplity</t>
+          <t>salnikvihod</t>
         </is>
       </c>
     </row>
@@ -9922,7 +10016,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -9932,21 +10026,21 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH107" t="n">
-        <v>7400</v>
+        <v>1950</v>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
@@ -9970,7 +10064,7 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Электронное управление КПП</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -9985,7 +10079,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>tolkateli4salniki4</t>
+          <t>stalnayavstavkaplity</t>
         </is>
       </c>
     </row>
@@ -9997,7 +10091,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -10007,21 +10101,21 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7</t>
         </is>
       </c>
       <c r="AH108" t="n">
-        <v>8900</v>
+        <v>7400</v>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
@@ -10060,7 +10154,7 @@
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>tolkatelisalnikialumkomplekt</t>
+          <t>tolkateli4salniki4</t>
         </is>
       </c>
     </row>
@@ -10072,68 +10166,143 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Толкатели вилок + сальники + усиленные</t>
+        </is>
+      </c>
+      <c r="AH109" t="n">
+        <v>8900</v>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN109" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>tolkatelisalnikialumkomplekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr">
+      <c r="P110" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q109" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
+      <c r="S110" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
-        </is>
-      </c>
-      <c r="AH109" t="n">
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH110" t="n">
         <v>4990</v>
       </c>
-      <c r="AJ109" t="inlineStr">
+      <c r="AJ110" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK109" t="inlineStr">
+      <c r="AK110" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL109" t="inlineStr">
+      <c r="AL110" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
+      <c r="AM110" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN109" t="inlineStr">
+      <c r="AN110" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO109" t="inlineStr">
+      <c r="AO110" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR109" t="inlineStr">
+      <c r="AR110" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS109" t="inlineStr">
+      <c r="AS110" t="inlineStr">
         <is>
           <t>vtulkishtokov2sht</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF110"/>
+  <dimension ref="A1:BF104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="3"/>
@@ -1883,7 +1883,8 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg?v=0fc1c93a07</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png?v=853ce5f975
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg?v=0fc1c93a07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -2543,7 +2544,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
+          <t>Улучшенный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="AH15" t="n">
@@ -4692,7 +4693,7 @@
       <c r="Q41" t="inlineStr">
         <is>
           <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).
-Новые соленоиды Bosch
+2 новых соленоида Bosch регулятора давления
 Новый гидроаккумулятор
 Новые ремкомплект и прокладки dq200
 Втулки, штоки, сальники, пыльники, крышка мехатроника
@@ -5538,7 +5539,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5548,21 +5549,22 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>🔧 Планка (фиксатор) соленоидов мехатроника DSG7 DQ200 — пластиковая, 1 шт (половина комплекта, крепит 4 соленоида одной стороны блока). ✅ Подходит на оба поколения мехатроника — Bosch и Hilite, 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Артикул: 0am325477. ⭐ Нужна вторая планка? У нас есть комплект 2 шт — выгоднее при полной переборке мехатроника.</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti
+🔩 Артикул: 0am325477ae.</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png?v=368fa6503f</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>1450</v>
+        <v>2479</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -5601,7 +5603,7 @@
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325477ae</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5615,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0am325477ae</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5622,82 +5624,6 @@
         </is>
       </c>
       <c r="Q52" t="inlineStr">
-        <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti
-🔩 Артикул: 0am325477ae.</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png?v=368fa6503f</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH52" t="n">
-        <v>2479</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr">
-        <is>
-          <t>0am325477ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>0ambset</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
         <is>
           <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП
 Оригинальное качество NSK
@@ -5706,78 +5632,78 @@
 🔩 Артикул: 0ambset.</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png?v=51d4844731
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png?v=bcd5b49d99</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>Комплект подшипников мехатроника DSG7 DQ200, 10</t>
         </is>
       </c>
-      <c r="AH53" t="n">
+      <c r="AH52" t="n">
         <v>11979</v>
       </c>
-      <c r="AJ53" t="inlineStr">
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK53" t="inlineStr">
+      <c r="AK52" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL53" t="inlineStr">
+      <c r="AL52" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
+      <c r="AM52" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
+      <c r="AN52" t="inlineStr">
         <is>
           <t>Валы, муфты, шестерни и подшипники КПП</t>
         </is>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AO52" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
+      <c r="AR52" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS53" t="inlineStr">
+      <c r="AS52" t="inlineStr">
         <is>
           <t>0ambset</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>0cw0am</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM
 Описание товара
@@ -5793,79 +5719,79 @@
 Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH54" t="n">
+      <c r="AH53" t="n">
         <v>931</v>
       </c>
-      <c r="AJ54" t="inlineStr">
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK54" t="inlineStr">
+      <c r="AK53" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL54" t="inlineStr">
+      <c r="AL53" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AM53" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
+      <c r="AN53" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO54" t="inlineStr">
+      <c r="AO53" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR54" t="inlineStr">
+      <c r="AR53" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS54" t="inlineStr">
+      <c r="AS53" t="inlineStr">
         <is>
           <t>0cw0am</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>0cw0am325025</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW
 В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.
@@ -5888,77 +5814,77 @@
 🔩 Артикул: 0cw0am325025.</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные</t>
         </is>
       </c>
-      <c r="AH55" t="n">
+      <c r="AH54" t="n">
         <v>16890</v>
       </c>
-      <c r="AJ55" t="inlineStr">
+      <c r="AJ54" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK55" t="inlineStr">
+      <c r="AK54" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL55" t="inlineStr">
+      <c r="AL54" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
+      <c r="AM54" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
+      <c r="AN54" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO55" t="inlineStr">
+      <c r="AO54" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR55" t="inlineStr">
+      <c r="AR54" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS55" t="inlineStr">
+      <c r="AS54" t="inlineStr">
         <is>
           <t>0cw0am325025</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.
 Совместимость
@@ -5972,78 +5898,78 @@
 🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=77a111eb34
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=40c2597cb3</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>Уплотнение электромотора гидроблока мехатроника</t>
         </is>
       </c>
-      <c r="AH56" t="n">
+      <c r="AH55" t="n">
         <v>850</v>
       </c>
-      <c r="AJ56" t="inlineStr">
+      <c r="AJ55" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK56" t="inlineStr">
+      <c r="AK55" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL56" t="inlineStr">
+      <c r="AL55" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
+      <c r="AM55" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
+      <c r="AN55" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO56" t="inlineStr">
+      <c r="AO55" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR56" t="inlineStr">
+      <c r="AR55" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS56" t="inlineStr">
+      <c r="AS55" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377
 🔎
@@ -6066,78 +5992,78 @@
 🔩 Артикул: 0cw325025h.</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH57" t="n">
+      <c r="AH56" t="n">
         <v>1290</v>
       </c>
-      <c r="AJ57" t="inlineStr">
+      <c r="AJ56" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK57" t="inlineStr">
+      <c r="AK56" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
+      <c r="AL56" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AM56" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
+      <c r="AN56" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO57" t="inlineStr">
+      <c r="AO56" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR57" t="inlineStr">
+      <c r="AR56" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS57" t="inlineStr">
+      <c r="AS56" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>0сц</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.
 Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.
@@ -6158,79 +6084,79 @@
 🔩 Артикул: 0сц.</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.jpg?v=3e0abf9ec7
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.jpg?v=b12c6dac21
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.jpg?v=bd237a81d2</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH58" t="n">
+      <c r="AH57" t="n">
         <v>1490</v>
       </c>
-      <c r="AJ58" t="inlineStr">
+      <c r="AJ57" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK58" t="inlineStr">
+      <c r="AK57" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
+      <c r="AL57" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AM57" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
+      <c r="AN57" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO58" t="inlineStr">
+      <c r="AO57" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR58" t="inlineStr">
+      <c r="AR57" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS58" t="inlineStr">
+      <c r="AS57" t="inlineStr">
         <is>
           <t>0c</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>122390AK-AF</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект
 Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW
@@ -6243,78 +6169,78 @@
 🔩 Артикул: 122390AK-AF.</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=a2422623a6
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg?v=70e1dc8dfd</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
-      <c r="AH59" t="n">
+      <c r="AH58" t="n">
         <v>979</v>
       </c>
-      <c r="AJ59" t="inlineStr">
+      <c r="AJ58" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK59" t="inlineStr">
+      <c r="AK58" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL59" t="inlineStr">
+      <c r="AL58" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
+      <c r="AM58" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
+      <c r="AN58" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO59" t="inlineStr">
+      <c r="AO58" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR59" t="inlineStr">
+      <c r="AR58" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS59" t="inlineStr">
+      <c r="AS58" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)
 Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.
@@ -6344,77 +6270,77 @@
 🔩 Артикул: 122390AKAF.</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png?v=a2422623a6</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH60" t="n">
+      <c r="AH59" t="n">
         <v>1490</v>
       </c>
-      <c r="AJ60" t="inlineStr">
+      <c r="AJ59" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK60" t="inlineStr">
+      <c r="AK59" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL60" t="inlineStr">
+      <c r="AL59" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
+      <c r="AM59" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
+      <c r="AN59" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO60" t="inlineStr">
+      <c r="AO59" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR60" t="inlineStr">
+      <c r="AR59" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS60" t="inlineStr">
+      <c r="AS59" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>123014‑AF</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества
 ✅
@@ -6428,78 +6354,78 @@
 Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=6a32ad2888
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=995613c21a</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
         </is>
       </c>
-      <c r="AH61" t="n">
+      <c r="AH60" t="n">
         <v>1479</v>
       </c>
-      <c r="AJ61" t="inlineStr">
+      <c r="AJ60" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK61" t="inlineStr">
+      <c r="AK60" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL61" t="inlineStr">
+      <c r="AL60" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
+      <c r="AM60" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
+      <c r="AN60" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO61" t="inlineStr">
+      <c r="AO60" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR61" t="inlineStr">
+      <c r="AR60" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS61" t="inlineStr">
+      <c r="AS60" t="inlineStr">
         <is>
           <t>123014AF</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>31705-1XF0C</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.
 Описание товара
@@ -6523,77 +6449,77 @@
 🔩 Артикул: 31705-1XF0C.</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg?v=dc356035c7</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика</t>
         </is>
       </c>
-      <c r="AH62" t="n">
+      <c r="AH61" t="n">
         <v>58900</v>
       </c>
-      <c r="AJ62" t="inlineStr">
+      <c r="AJ61" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK62" t="inlineStr">
+      <c r="AK61" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL62" t="inlineStr">
+      <c r="AL61" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
+      <c r="AM61" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
+      <c r="AN61" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO62" t="inlineStr">
+      <c r="AO61" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR62" t="inlineStr">
+      <c r="AR61" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS62" t="inlineStr">
+      <c r="AS61" t="inlineStr">
         <is>
           <t>317051XF0C</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>31705-X428B</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi — новый
 Краткое описание (первые 3 строки — самое важное для Ozon)
@@ -6628,79 +6554,79 @@
 🔩 Артикул: 31705-X428B.</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png?v=6ac791003d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png?v=4bd4c0625c
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png?v=4e011c48be</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый</t>
         </is>
       </c>
-      <c r="AH63" t="n">
+      <c r="AH62" t="n">
         <v>58900</v>
       </c>
-      <c r="AJ63" t="inlineStr">
+      <c r="AJ62" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK63" t="inlineStr">
+      <c r="AK62" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL63" t="inlineStr">
+      <c r="AL62" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
+      <c r="AM62" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
+      <c r="AN62" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO63" t="inlineStr">
+      <c r="AO62" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR63" t="inlineStr">
+      <c r="AR62" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS63" t="inlineStr">
+      <c r="AS62" t="inlineStr">
         <is>
           <t>31705X428B</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.
 Описание товара
@@ -6724,78 +6650,78 @@
 🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
         </is>
       </c>
-      <c r="AH64" t="n">
+      <c r="AH63" t="n">
         <v>58900</v>
       </c>
-      <c r="AJ64" t="inlineStr">
+      <c r="AJ63" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK64" t="inlineStr">
+      <c r="AK63" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL64" t="inlineStr">
+      <c r="AL63" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
+      <c r="AM63" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
+      <c r="AN63" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO64" t="inlineStr">
+      <c r="AO63" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR64" t="inlineStr">
+      <c r="AR63" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS64" t="inlineStr">
+      <c r="AS63" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>55565480</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>импульсная звёздочка датчика положения распредвала
 Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.
@@ -6807,18 +6733,93 @@
 Датчик распредвала 55565480 GM</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Импульсное кольцо распредвала GM 55565480</t>
+        </is>
+      </c>
+      <c r="AH64" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN64" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr">
+        <is>
+          <t>55565480</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>6t30</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
+        </is>
+      </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Импульсное кольцо распредвала GM 55565480</t>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>999</v>
+        <v>19800</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -6842,7 +6843,7 @@
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Электронное управление КПП</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -6857,7 +6858,7 @@
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>6t30</t>
         </is>
       </c>
     </row>
@@ -6869,7 +6870,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>6t30</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -6878,81 +6879,6 @@
         </is>
       </c>
       <c r="Q66" t="inlineStr">
-        <is>
-          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
-        </is>
-      </c>
-      <c r="AH66" t="n">
-        <v>19800</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL66" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>6t30</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>DQ500</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
         <is>
           <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH
 Новые
@@ -6961,7 +6887,7 @@
 Снижает температуру масла</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
@@ -6969,13 +6895,89 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
+        </is>
+      </c>
+      <c r="AH66" t="n">
+        <v>3850</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>DQ500</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Dq200dsg7</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!
+🔩 Артикул: Dq200dsg7.</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg?v=12b215cccc</t>
+        </is>
+      </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
+          <t>Уплотнение насоса гидроблока мехатроника DSG7</t>
         </is>
       </c>
       <c r="AH67" t="n">
-        <v>3850</v>
+        <v>979</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
@@ -6999,7 +7001,7 @@
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>Система смазки и охлаждения КПП</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -7014,7 +7016,7 @@
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>Dq200dsg7</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7028,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Dq200dsg7</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7035,82 +7037,6 @@
         </is>
       </c>
       <c r="Q68" t="inlineStr">
-        <is>
-          <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!
-🔩 Артикул: Dq200dsg7.</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg?v=12b215cccc</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>Уплотнение насоса гидроблока мехатроника DSG7</t>
-        </is>
-      </c>
-      <c r="AH68" t="n">
-        <v>979</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL68" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>Dq200dsg7</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Dq200dsg70am0cw</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)
 Описание товара
@@ -7134,77 +7060,77 @@
 🔩 Артикул: Dq200dsg70am0cw.</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>Прокладки + сальники + пыльники мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH69" t="n">
+      <c r="AH68" t="n">
         <v>8890</v>
       </c>
-      <c r="AJ69" t="inlineStr">
+      <c r="AJ68" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK69" t="inlineStr">
+      <c r="AK68" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL69" t="inlineStr">
+      <c r="AL68" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
+      <c r="AM68" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
+      <c r="AN68" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO69" t="inlineStr">
+      <c r="AO68" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR69" t="inlineStr">
+      <c r="AR68" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS69" t="inlineStr">
+      <c r="AS68" t="inlineStr">
         <is>
           <t>Dq200dsg70am0cw</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>Улучшенный отвод тепла
 Уменьшает температуру масла КПП
@@ -7223,7 +7149,7 @@
 📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203
@@ -7241,90 +7167,166 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="AH70" t="n">
+      <c r="AH69" t="n">
         <v>3879</v>
       </c>
-      <c r="AJ70" t="inlineStr">
+      <c r="AJ69" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK70" t="inlineStr">
+      <c r="AK69" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL70" t="inlineStr">
+      <c r="AL69" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
+      <c r="AM69" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
+      <c r="AN69" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO70" t="inlineStr">
+      <c r="AO69" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR70" t="inlineStr">
+      <c r="AR69" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS70" t="inlineStr">
+      <c r="AS69" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>WHT001922</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный
 Новый Отличное качество
 🔩 Артикул: WHT001922.</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="AH70" t="n">
+        <v>979</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>Крепёж КПП</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>WHT001922</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
+        </is>
+      </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=be20ada597
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=87268821a3</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW</t>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5</t>
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>979</v>
+        <v>1490</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -7348,7 +7350,7 @@
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>Крепёж КПП</t>
+          <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -7363,7 +7365,7 @@
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>filtrsetka0b5orig</t>
         </is>
       </c>
     </row>
@@ -7375,7 +7377,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7385,99 +7387,100 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
+          <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=be20ada597
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=87268821a3</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5</t>
-        </is>
-      </c>
-      <c r="AH72" t="n">
-        <v>1490</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL72" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr">
-        <is>
-          <t>filtrsetka0b5orig</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>gidroakkumulyator-orig</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
         </is>
       </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH72" t="n">
+        <v>8890</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>gidroakkumulyatororig</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>jf011e</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.
+В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
+        </is>
+      </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DSG7</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A)</t>
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>8890</v>
+        <v>12979</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -7501,7 +7504,7 @@
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>Электронное управление КПП</t>
+          <t>Валы, муфты, шестерни и подшипники КПП</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -7516,7 +7519,7 @@
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>gidroakkumulyatororig</t>
+          <t>jf011e</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7531,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -7538,23 +7541,21 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.
-В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A)</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2</t>
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>12979</v>
+        <v>950</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -7578,7 +7579,7 @@
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>Валы, муфты, шестерни и подшипники КПП</t>
+          <t>Переключение передач</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -7593,7 +7594,7 @@
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>klipsyshtokov2sht</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7606,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -7615,21 +7616,21 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
+          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>950</v>
+        <v>2890</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -7653,7 +7654,7 @@
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Электронное управление КПП</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -7668,7 +7669,7 @@
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>klipsyshtokov2sht</t>
+          <t>plankasolenoid2sht</t>
         </is>
       </c>
     </row>
@@ -7680,7 +7681,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>korpus-filtra-0bh325159</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -7690,22 +7691,22 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
+          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png?v=207791c0ab
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png?v=33f6b91718</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Корпус масляного фильтра мехатроника DSG7 DQ500</t>
+          <t>Оригинальные пластины на соленоиды VAG</t>
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>3879</v>
+        <v>990</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -7729,7 +7730,7 @@
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>Система смазки и охлаждения КПП</t>
+          <t>Электронное управление КПП</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -7744,7 +7745,7 @@
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>korpusfiltra0bh325159</t>
+          <t>plastinysolenoidorig</t>
         </is>
       </c>
     </row>
@@ -7756,7 +7757,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -7766,174 +7767,174 @@
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH77" t="n">
-        <v>2890</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL77" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr">
-        <is>
-          <t>plankasolenoid2sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>plastiny-solenoid-orig</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Оригинальные пластины на соленоиды VAG</t>
-        </is>
-      </c>
-      <c r="AH78" t="n">
-        <v>990</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL78" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>plastinysolenoidorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>plita-filtr</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=efa8557d9d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=759d463fe2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=3f11b4e476</t>
         </is>
       </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH77" t="n">
+        <v>7500</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>plitafiltr</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>plita-filtr-orig</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Усиленная плита + улучшенный фильтр мехатроника</t>
+        </is>
+      </c>
+      <c r="AH78" t="n">
+        <v>7500</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>plitafiltrorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
+        </is>
+      </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DSG7</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков</t>
         </is>
       </c>
       <c r="AH79" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
@@ -7972,7 +7973,7 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>plitafiltr</t>
+          <t>plitafiltrpylniki</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7985,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7994,21 +7995,21 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
         </is>
       </c>
       <c r="AH80" t="n">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -8047,7 +8048,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>plitafiltrorig</t>
+          <t>plitafiltrpylnikiorig</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8060,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8069,22 +8070,21 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2</t>
         </is>
       </c>
       <c r="AH81" t="n">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>Система смазки и охлаждения КПП</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>plitafiltrpylniki</t>
+          <t>plitafiltrpylnikisal</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -8145,21 +8145,21 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG</t>
         </is>
       </c>
       <c r="AH82" t="n">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>Система смазки и охлаждения КПП</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikiorig</t>
+          <t>plitafiltrpylnikisalorig</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -8220,21 +8220,22 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png?v=9157b6c42a</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
         </is>
       </c>
       <c r="AH83" t="n">
-        <v>9500</v>
+        <v>8500</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -8273,7 +8274,7 @@
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikisal</t>
+          <t>plitafiltrsalnikiorig</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8286,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -8295,21 +8296,21 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=03ce24da06</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>9500</v>
+        <v>8500</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -8348,7 +8349,7 @@
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikisalorig</t>
+          <t>plitapylnikisalniki</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8361,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -8370,22 +8371,21 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png?v=9157b6c42a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>plitafiltrsalnikiorig</t>
+          <t>plitapylnikisalnikiorig</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -8446,21 +8446,22 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png?v=16f48e3b34</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>7500</v>
+        <v>1240</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -8484,7 +8485,7 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>Система смазки и охлаждения КПП</t>
+          <t>Переключение передач</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -8499,7 +8500,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>plitafiltrv2</t>
+          <t>podshipnikvilki6</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8512,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -8521,21 +8522,21 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=03ce24da06</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня</t>
         </is>
       </c>
       <c r="AH87" t="n">
-        <v>8500</v>
+        <v>3990</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -8559,7 +8560,7 @@
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Переключение передач</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -8574,7 +8575,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>plitapylnikisalniki</t>
+          <t>porshniusilpylnikikryshki</t>
         </is>
       </c>
     </row>
@@ -8586,7 +8587,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -8596,21 +8597,21 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH88" t="n">
-        <v>9500</v>
+        <v>1850</v>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -8634,7 +8635,7 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Переключение передач</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -8649,7 +8650,7 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>plitapylnikisalnikiorig</t>
+          <t>pylnikishtokovorig</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8662,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8671,21 +8672,21 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png?v=b98621fc0a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
         </is>
       </c>
       <c r="AH89" t="n">
-        <v>9500</v>
+        <v>2850</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -8724,7 +8725,7 @@
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>plitapylnikisalnikiorigv2</t>
+          <t>remkomplektshtokovorig</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8737,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -8746,22 +8747,22 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH90" t="n">
-        <v>1240</v>
+        <v>1490</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -8785,7 +8786,7 @@
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -8800,7 +8801,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>podshipnikvilki6</t>
+          <t>salnikshtokaorig</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8813,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8822,21 +8823,21 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня</t>
+          <t>Усиленные алюминиевые сальники толкателя с</t>
         </is>
       </c>
       <c r="AH91" t="n">
-        <v>3990</v>
+        <v>2490</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -8860,7 +8861,7 @@
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -8875,7 +8876,7 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>porshniusilpylnikikryshki</t>
+          <t>salniktolkatelyaalum</t>
         </is>
       </c>
     </row>
@@ -8887,7 +8888,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -8897,22 +8898,21 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="AH92" t="n">
-        <v>3990</v>
+        <v>1690</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>porshniusilpylnikikryshkiv2</t>
+          <t>salnikishtokov2sht</t>
         </is>
       </c>
     </row>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -8973,21 +8973,21 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH93" t="n">
-        <v>1850</v>
+        <v>1890</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="AS93" t="inlineStr">
         <is>
-          <t>pylnikishtokovorig</t>
+          <t>salnikishtokovorig</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -9048,21 +9048,22 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Полный комплект сальников толкателей вилок</t>
         </is>
       </c>
       <c r="AH94" t="n">
-        <v>1850</v>
+        <v>1950</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -9086,7 +9087,7 @@
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -9101,7 +9102,7 @@
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>pylnikishtokovorigv2</t>
+          <t>salnikitolkatelya4sht</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9114,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -9123,21 +9124,21 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH95" t="n">
-        <v>2850</v>
+        <v>999</v>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
@@ -9176,7 +9177,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>remkomplektshtokovorig</t>
+          <t>salnikprivodl</t>
         </is>
       </c>
     </row>
@@ -9188,7 +9189,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -9198,21 +9199,21 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH96" t="n">
-        <v>2850</v>
+        <v>999</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -9251,7 +9252,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>remkomplektshtokovorigv2</t>
+          <t>salnikprivodr</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9264,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -9273,22 +9274,22 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH97" t="n">
-        <v>1490</v>
+        <v>999</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -9327,7 +9328,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>salnikshtokaorig</t>
+          <t>salnikvhod</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9340,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -9349,21 +9350,21 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH98" t="n">
-        <v>1490</v>
+        <v>999</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
@@ -9402,7 +9403,7 @@
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>salnikshtokaorigv2</t>
+          <t>salnikvihod</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9415,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -9424,21 +9425,21 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH99" t="n">
-        <v>2490</v>
+        <v>1950</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
@@ -9462,7 +9463,7 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Электронное управление КПП</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -9477,7 +9478,7 @@
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>salniktolkatelyaalum</t>
+          <t>stalnayavstavkaplity</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9490,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -9499,21 +9500,21 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7</t>
         </is>
       </c>
       <c r="AH100" t="n">
-        <v>1690</v>
+        <v>7400</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
@@ -9552,7 +9553,7 @@
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>salnikishtokov2sht</t>
+          <t>tolkateli4salniki4</t>
         </is>
       </c>
     </row>
@@ -9564,7 +9565,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -9574,21 +9575,21 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Толкатели вилок + сальники + усиленные</t>
         </is>
       </c>
       <c r="AH101" t="n">
-        <v>1890</v>
+        <v>8900</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
@@ -9627,7 +9628,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>salnikishtokovorig</t>
+          <t>tolkatelisalnikialumkomplekt</t>
         </is>
       </c>
     </row>
@@ -9639,7 +9640,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9649,22 +9650,21 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
+          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок</t>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH102" t="n">
-        <v>1950</v>
+        <v>4990</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Переключение передач</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>salnikitolkatelya4sht</t>
+          <t>vtulkishtokov2sht</t>
         </is>
       </c>
     </row>
@@ -9715,7 +9715,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9725,21 +9725,21 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
+          <t>🔧 Планка (фиксатор) соленоидов мехатроника DSG7 DQ200 — пластиковая, 1 шт (половина комплекта, крепит 4 соленоида одной стороны блока). ✅ Подходит на оба поколения мехатроника — Bosch и Hilite, 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Артикул: 0am325477. ⭐ Нужна вторая планка? У нас есть комплект 2 шт — выгоднее при полной переборке мехатроника.</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="AH103" t="n">
-        <v>999</v>
+        <v>1450</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Электронное управление КПП</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>salnikprivodl</t>
+          <t>0am325477</t>
         </is>
       </c>
     </row>
@@ -9790,7 +9790,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9800,21 +9800,25 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+          <t>🔧 Масляный фильтр мехатроника DSG7 DQ200 (0AM/0CW) — стандартная версия для планового обслуживания и ремонта гидроблока АКПП.
+✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200 (0AM325025 и аналоги).
+📦 Новый, в наличии, отправка в день заказа.
+⭐ Нужен максимальный ресурс? У нас есть улучшенная версия фильтра — смотрите в нашем магазине.
+🔩 Артикул: filtr-dsg7-dq200.</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="AH104" t="n">
-        <v>999</v>
+        <v>980</v>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
@@ -9838,7 +9842,7 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -9853,458 +9857,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>salnikprivodr</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH105" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL105" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH106" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL106" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>stalnaya-vstavka-plity</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH107" t="n">
-        <v>1950</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL107" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>stalnayavstavkaplity</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>tolkateli-4-salniki-4</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7</t>
-        </is>
-      </c>
-      <c r="AH108" t="n">
-        <v>7400</v>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL108" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>tolkateli4salniki4</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Толкатели вилок + сальники + усиленные</t>
-        </is>
-      </c>
-      <c r="AH109" t="n">
-        <v>8900</v>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL109" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>tolkatelisalnikialumkomplekt</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>vtulki-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH110" t="n">
-        <v>4990</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL110" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>vtulkishtokov2sht</t>
+          <t>filtrdsg7dq200</t>
         </is>
       </c>
     </row>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>879</v>
+        <v>440</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>5879</v>
+        <v>2940</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1879</v>
+        <v>940</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>118000</v>
+        <v>59000</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>3879</v>
+        <v>1940</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1479</v>
+        <v>740</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>9479</v>
+        <v>4740</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>999</v>
+        <v>500</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>3479</v>
+        <v>1740</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>999</v>
+        <v>500</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>1479</v>
+        <v>740</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>1990</v>
+        <v>995</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>1990</v>
+        <v>995</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>11979</v>
+        <v>5990</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>9850</v>
+        <v>4925</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>78800</v>
+        <v>39400</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>3479</v>
+        <v>1740</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>3879</v>
+        <v>1940</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>7979</v>
+        <v>3990</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>7979</v>
+        <v>3990</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>12890</v>
+        <v>6445</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>2890</v>
+        <v>1445</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>3879</v>
+        <v>1940</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>68800</v>
+        <v>34400</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>128800</v>
+        <v>64400</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>979</v>
+        <v>490</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>4879</v>
+        <v>2440</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>3879</v>
+        <v>1940</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>1990</v>
+        <v>995</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>2879</v>
+        <v>1440</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>1490</v>
+        <v>745</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>8879</v>
+        <v>4440</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>8979</v>
+        <v>4490</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>979</v>
+        <v>490</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>1479</v>
+        <v>740</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>4490</v>
+        <v>2245</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>78475</v>
+        <v>39238</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>4490</v>
+        <v>2245</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>979</v>
+        <v>490</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>1479</v>
+        <v>740</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>979</v>
+        <v>490</v>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>8879</v>
+        <v>4440</v>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>2879</v>
+        <v>1440</v>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>8850</v>
+        <v>4425</v>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>2879</v>
+        <v>1440</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>8850</v>
+        <v>4425</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>2479</v>
+        <v>1240</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>11979</v>
+        <v>5990</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -5732,7 +5732,7 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>931</v>
+        <v>466</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>16890</v>
+        <v>8445</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>850</v>
+        <v>425</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="AH56" t="n">
-        <v>1290</v>
+        <v>645</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>1490</v>
+        <v>745</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>979</v>
+        <v>490</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="AH59" t="n">
-        <v>1490</v>
+        <v>745</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>1479</v>
+        <v>740</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>58900</v>
+        <v>29450</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>58900</v>
+        <v>29450</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>58900</v>
+        <v>29450</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>999</v>
+        <v>500</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>19800</v>
+        <v>9900</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>3850</v>
+        <v>1925</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="AH67" t="n">
-        <v>979</v>
+        <v>490</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="AH68" t="n">
-        <v>8890</v>
+        <v>4445</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>3879</v>
+        <v>1940</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>979</v>
+        <v>490</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>1490</v>
+        <v>745</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>8890</v>
+        <v>4445</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>12979</v>
+        <v>6490</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>950</v>
+        <v>475</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>2890</v>
+        <v>1445</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>990</v>
+        <v>495</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="AH79" t="n">
-        <v>8500</v>
+        <v>4250</v>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="AH80" t="n">
-        <v>8500</v>
+        <v>4250</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="AH81" t="n">
-        <v>9500</v>
+        <v>4750</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="AH82" t="n">
-        <v>9500</v>
+        <v>4750</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         </is>
       </c>
       <c r="AH83" t="n">
-        <v>8500</v>
+        <v>4250</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>8500</v>
+        <v>4250</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>9500</v>
+        <v>4750</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>1240</v>
+        <v>620</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         </is>
       </c>
       <c r="AH87" t="n">
-        <v>3990</v>
+        <v>1995</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="AH88" t="n">
-        <v>1850</v>
+        <v>925</v>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="AH89" t="n">
-        <v>2850</v>
+        <v>1425</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="AH90" t="n">
-        <v>1490</v>
+        <v>745</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         </is>
       </c>
       <c r="AH91" t="n">
-        <v>2490</v>
+        <v>1245</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="AH92" t="n">
-        <v>1690</v>
+        <v>845</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="AH93" t="n">
-        <v>1890</v>
+        <v>945</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         </is>
       </c>
       <c r="AH94" t="n">
-        <v>1950</v>
+        <v>975</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         </is>
       </c>
       <c r="AH95" t="n">
-        <v>999</v>
+        <v>500</v>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         </is>
       </c>
       <c r="AH96" t="n">
-        <v>999</v>
+        <v>500</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="AH97" t="n">
-        <v>999</v>
+        <v>500</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="AH98" t="n">
-        <v>999</v>
+        <v>500</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="AH99" t="n">
-        <v>1950</v>
+        <v>975</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="AH100" t="n">
-        <v>7400</v>
+        <v>3700</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="AH101" t="n">
-        <v>8900</v>
+        <v>4450</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         </is>
       </c>
       <c r="AH102" t="n">
-        <v>4990</v>
+        <v>2495</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="AH103" t="n">
-        <v>1450</v>
+        <v>725</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         </is>
       </c>
       <c r="AH104" t="n">
-        <v>980</v>
+        <v>490</v>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF104"/>
+  <dimension ref="A1:BF121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="3"/>
@@ -1883,8 +1883,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.png?v=853ce5f975
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg?v=0fc1c93a07</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/02E305051C_1.jpg?v=0fc1c93a07</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -2544,7 +2543,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Улучшенный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Фильтр мехатроника DSG7 DQ200 0AM325433E</t>
         </is>
       </c>
       <c r="AH15" t="n">
@@ -4693,7 +4692,7 @@
       <c r="Q41" t="inlineStr">
         <is>
           <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).
-2 новых соленоида Bosch регулятора давления
+Новые соленоиды Bosch
 Новый гидроаккумулятор
 Новые ремкомплект и прокладки dq200
 Втулки, штоки, сальники, пыльники, крышка мехатроника
@@ -5539,91 +5538,166 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>🔧 Планка (фиксатор) соленоидов мехатроника DSG7 DQ200 — пластиковая, 1 шт (половина комплекта, крепит 4 соленоида одной стороны блока). ✅ Подходит на оба поколения мехатроника — Bosch и Hilite, 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Артикул: 0am325477. ⭐ Нужна вторая планка? У нас есть комплект 2 шт — выгоднее при полной переборке мехатроника.</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="AH51" t="n">
+        <v>725</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>0am325477ae</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti
 🔩 Артикул: 0am325477ae.</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png?v=368fa6503f</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>Пластина соленоидов мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH51" t="n">
+      <c r="AH52" t="n">
         <v>1240</v>
       </c>
-      <c r="AJ51" t="inlineStr">
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK51" t="inlineStr">
+      <c r="AK52" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL51" t="inlineStr">
+      <c r="AL52" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
+      <c r="AM52" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
+      <c r="AN52" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO51" t="inlineStr">
+      <c r="AO52" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR51" t="inlineStr">
+      <c r="AR52" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS51" t="inlineStr">
+      <c r="AS52" t="inlineStr">
         <is>
           <t>0am325477ae</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>0ambset</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП
 Оригинальное качество NSK
@@ -5632,78 +5706,78 @@
 🔩 Артикул: 0ambset.</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png?v=51d4844731
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png?v=bcd5b49d99</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Комплект подшипников мехатроника DSG7 DQ200, 10</t>
         </is>
       </c>
-      <c r="AH52" t="n">
+      <c r="AH53" t="n">
         <v>5990</v>
       </c>
-      <c r="AJ52" t="inlineStr">
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK52" t="inlineStr">
+      <c r="AK53" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr">
+      <c r="AL53" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
+      <c r="AM53" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
+      <c r="AN53" t="inlineStr">
         <is>
           <t>Валы, муфты, шестерни и подшипники КПП</t>
         </is>
       </c>
-      <c r="AO52" t="inlineStr">
+      <c r="AO53" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR52" t="inlineStr">
+      <c r="AR53" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS52" t="inlineStr">
+      <c r="AS53" t="inlineStr">
         <is>
           <t>0ambset</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>0cw0am</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM
 Описание товара
@@ -5719,79 +5793,79 @@
 Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH53" t="n">
+      <c r="AH54" t="n">
         <v>466</v>
       </c>
-      <c r="AJ53" t="inlineStr">
+      <c r="AJ54" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK53" t="inlineStr">
+      <c r="AK54" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL53" t="inlineStr">
+      <c r="AL54" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
+      <c r="AM54" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
+      <c r="AN54" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AO54" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
+      <c r="AR54" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS53" t="inlineStr">
+      <c r="AS54" t="inlineStr">
         <is>
           <t>0cw0am</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>0cw0am325025</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW
 В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.
@@ -5814,77 +5888,77 @@
 🔩 Артикул: 0cw0am325025.</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные</t>
         </is>
       </c>
-      <c r="AH54" t="n">
+      <c r="AH55" t="n">
         <v>8445</v>
       </c>
-      <c r="AJ54" t="inlineStr">
+      <c r="AJ55" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK54" t="inlineStr">
+      <c r="AK55" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL54" t="inlineStr">
+      <c r="AL55" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AM55" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
+      <c r="AN55" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO54" t="inlineStr">
+      <c r="AO55" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR54" t="inlineStr">
+      <c r="AR55" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS54" t="inlineStr">
+      <c r="AS55" t="inlineStr">
         <is>
           <t>0cw0am325025</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.
 Совместимость
@@ -5898,78 +5972,78 @@
 🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=77a111eb34
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=40c2597cb3</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>Уплотнение электромотора гидроблока мехатроника</t>
         </is>
       </c>
-      <c r="AH55" t="n">
+      <c r="AH56" t="n">
         <v>425</v>
       </c>
-      <c r="AJ55" t="inlineStr">
+      <c r="AJ56" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK55" t="inlineStr">
+      <c r="AK56" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL55" t="inlineStr">
+      <c r="AL56" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
+      <c r="AM56" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
+      <c r="AN56" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO55" t="inlineStr">
+      <c r="AO56" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR55" t="inlineStr">
+      <c r="AR56" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS55" t="inlineStr">
+      <c r="AS56" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377
 🔎
@@ -5992,78 +6066,78 @@
 🔩 Артикул: 0cw325025h.</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH56" t="n">
+      <c r="AH57" t="n">
         <v>645</v>
       </c>
-      <c r="AJ56" t="inlineStr">
+      <c r="AJ57" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK56" t="inlineStr">
+      <c r="AK57" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL56" t="inlineStr">
+      <c r="AL57" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
+      <c r="AM57" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
+      <c r="AN57" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO56" t="inlineStr">
+      <c r="AO57" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR56" t="inlineStr">
+      <c r="AR57" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS56" t="inlineStr">
+      <c r="AS57" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>0сц</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.
 Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.
@@ -6084,79 +6158,79 @@
 🔩 Артикул: 0сц.</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.jpg?v=3e0abf9ec7
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.jpg?v=b12c6dac21
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.jpg?v=bd237a81d2</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH57" t="n">
+      <c r="AH58" t="n">
         <v>745</v>
       </c>
-      <c r="AJ57" t="inlineStr">
+      <c r="AJ58" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK57" t="inlineStr">
+      <c r="AK58" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
+      <c r="AL58" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AM58" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
+      <c r="AN58" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO57" t="inlineStr">
+      <c r="AO58" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR57" t="inlineStr">
+      <c r="AR58" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS57" t="inlineStr">
+      <c r="AS58" t="inlineStr">
         <is>
           <t>0c</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>122390AK-AF</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект
 Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW
@@ -6169,78 +6243,78 @@
 🔩 Артикул: 122390AK-AF.</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=a2422623a6
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg?v=70e1dc8dfd</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
-      <c r="AH58" t="n">
+      <c r="AH59" t="n">
         <v>490</v>
       </c>
-      <c r="AJ58" t="inlineStr">
+      <c r="AJ59" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK58" t="inlineStr">
+      <c r="AK59" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
+      <c r="AL59" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AM59" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
+      <c r="AN59" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO58" t="inlineStr">
+      <c r="AO59" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR58" t="inlineStr">
+      <c r="AR59" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS58" t="inlineStr">
+      <c r="AS59" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)
 Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.
@@ -6270,77 +6344,77 @@
 🔩 Артикул: 122390AKAF.</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png?v=a2422623a6</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH59" t="n">
+      <c r="AH60" t="n">
         <v>745</v>
       </c>
-      <c r="AJ59" t="inlineStr">
+      <c r="AJ60" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK59" t="inlineStr">
+      <c r="AK60" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL59" t="inlineStr">
+      <c r="AL60" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
+      <c r="AM60" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
+      <c r="AN60" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO59" t="inlineStr">
+      <c r="AO60" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR59" t="inlineStr">
+      <c r="AR60" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS59" t="inlineStr">
+      <c r="AS60" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>123014‑AF</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества
 ✅
@@ -6354,78 +6428,78 @@
 Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=6a32ad2888
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=995613c21a</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
         </is>
       </c>
-      <c r="AH60" t="n">
+      <c r="AH61" t="n">
         <v>740</v>
       </c>
-      <c r="AJ60" t="inlineStr">
+      <c r="AJ61" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK60" t="inlineStr">
+      <c r="AK61" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL60" t="inlineStr">
+      <c r="AL61" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
+      <c r="AM61" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
+      <c r="AN61" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO60" t="inlineStr">
+      <c r="AO61" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR60" t="inlineStr">
+      <c r="AR61" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS60" t="inlineStr">
+      <c r="AS61" t="inlineStr">
         <is>
           <t>123014AF</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>31705-1XF0C</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.
 Описание товара
@@ -6449,77 +6523,77 @@
 🔩 Артикул: 31705-1XF0C.</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg?v=dc356035c7</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика</t>
         </is>
       </c>
-      <c r="AH61" t="n">
+      <c r="AH62" t="n">
         <v>29450</v>
       </c>
-      <c r="AJ61" t="inlineStr">
+      <c r="AJ62" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK61" t="inlineStr">
+      <c r="AK62" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL61" t="inlineStr">
+      <c r="AL62" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
+      <c r="AM62" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
+      <c r="AN62" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO61" t="inlineStr">
+      <c r="AO62" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR61" t="inlineStr">
+      <c r="AR62" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS61" t="inlineStr">
+      <c r="AS62" t="inlineStr">
         <is>
           <t>317051XF0C</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>31705-X428B</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi — новый
 Краткое описание (первые 3 строки — самое важное для Ozon)
@@ -6554,79 +6628,79 @@
 🔩 Артикул: 31705-X428B.</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png?v=6ac791003d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png?v=4bd4c0625c
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png?v=4e011c48be</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый</t>
         </is>
       </c>
-      <c r="AH62" t="n">
+      <c r="AH63" t="n">
         <v>29450</v>
       </c>
-      <c r="AJ62" t="inlineStr">
+      <c r="AJ63" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK62" t="inlineStr">
+      <c r="AK63" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL62" t="inlineStr">
+      <c r="AL63" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
+      <c r="AM63" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
+      <c r="AN63" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO62" t="inlineStr">
+      <c r="AO63" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR62" t="inlineStr">
+      <c r="AR63" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS62" t="inlineStr">
+      <c r="AS63" t="inlineStr">
         <is>
           <t>31705X428B</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.
 Описание товара
@@ -6650,78 +6724,78 @@
 🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
         </is>
       </c>
-      <c r="AH63" t="n">
+      <c r="AH64" t="n">
         <v>29450</v>
       </c>
-      <c r="AJ63" t="inlineStr">
+      <c r="AJ64" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK63" t="inlineStr">
+      <c r="AK64" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL63" t="inlineStr">
+      <c r="AL64" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
+      <c r="AM64" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
+      <c r="AN64" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO63" t="inlineStr">
+      <c r="AO64" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR63" t="inlineStr">
+      <c r="AR64" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS63" t="inlineStr">
+      <c r="AS64" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>55565480</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>импульсная звёздочка датчика положения распредвала
 Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.
@@ -6733,132 +6807,57 @@
 Датчик распредвала 55565480 GM</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>Импульсное кольцо распредвала GM 55565480</t>
         </is>
       </c>
-      <c r="AH64" t="n">
+      <c r="AH65" t="n">
         <v>500</v>
       </c>
-      <c r="AJ64" t="inlineStr">
+      <c r="AJ65" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK64" t="inlineStr">
+      <c r="AK65" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL64" t="inlineStr">
+      <c r="AL65" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
+      <c r="AM65" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
+      <c r="AN65" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO64" t="inlineStr">
+      <c r="AO65" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR64" t="inlineStr">
+      <c r="AR65" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS64" t="inlineStr">
+      <c r="AS65" t="inlineStr">
         <is>
           <t>55565480</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>6t30</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
-        </is>
-      </c>
-      <c r="AH65" t="n">
-        <v>9900</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL65" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr">
-        <is>
-          <t>6t30</t>
         </is>
       </c>
     </row>
@@ -6870,15 +6869,90 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t>6t30</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
+        </is>
+      </c>
+      <c r="AH66" t="n">
+        <v>9900</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>6t30</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
           <t>DQ500</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH
 Новые
@@ -6887,7 +6961,7 @@
 Снижает температуру масла</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
@@ -6895,148 +6969,148 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="AH66" t="n">
+      <c r="AH67" t="n">
         <v>1925</v>
       </c>
-      <c r="AJ66" t="inlineStr">
+      <c r="AJ67" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK66" t="inlineStr">
+      <c r="AK67" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL66" t="inlineStr">
+      <c r="AL67" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
+      <c r="AM67" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
+      <c r="AN67" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO66" t="inlineStr">
+      <c r="AO67" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR66" t="inlineStr">
+      <c r="AR67" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS66" t="inlineStr">
+      <c r="AS67" t="inlineStr">
         <is>
           <t>DQ500</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Dq200dsg7</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!
 🔩 Артикул: Dq200dsg7.</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg?v=12b215cccc</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>Уплотнение насоса гидроблока мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH67" t="n">
+      <c r="AH68" t="n">
         <v>490</v>
       </c>
-      <c r="AJ67" t="inlineStr">
+      <c r="AJ68" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK67" t="inlineStr">
+      <c r="AK68" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL67" t="inlineStr">
+      <c r="AL68" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
+      <c r="AM68" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
+      <c r="AN68" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO67" t="inlineStr">
+      <c r="AO68" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR67" t="inlineStr">
+      <c r="AR68" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS67" t="inlineStr">
+      <c r="AS68" t="inlineStr">
         <is>
           <t>Dq200dsg7</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Dq200dsg70am0cw</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)
 Описание товара
@@ -7060,77 +7134,77 @@
 🔩 Артикул: Dq200dsg70am0cw.</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>Прокладки + сальники + пыльники мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH68" t="n">
+      <c r="AH69" t="n">
         <v>4445</v>
       </c>
-      <c r="AJ68" t="inlineStr">
+      <c r="AJ69" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK68" t="inlineStr">
+      <c r="AK69" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL68" t="inlineStr">
+      <c r="AL69" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AM69" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
+      <c r="AN69" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO68" t="inlineStr">
+      <c r="AO69" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR68" t="inlineStr">
+      <c r="AR69" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS68" t="inlineStr">
+      <c r="AS69" t="inlineStr">
         <is>
           <t>Dq200dsg70am0cw</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>Улучшенный отвод тепла
 Уменьшает температуру масла КПП
@@ -7149,7 +7223,7 @@
 📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203
@@ -7167,205 +7241,129 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="AH69" t="n">
+      <c r="AH70" t="n">
         <v>1940</v>
       </c>
-      <c r="AJ69" t="inlineStr">
+      <c r="AJ70" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK69" t="inlineStr">
+      <c r="AK70" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL69" t="inlineStr">
+      <c r="AL70" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
+      <c r="AM70" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
+      <c r="AN70" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO69" t="inlineStr">
+      <c r="AO70" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR69" t="inlineStr">
+      <c r="AR70" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS69" t="inlineStr">
+      <c r="AS70" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>WHT001922</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный
 Новый Отличное качество
 🔩 Артикул: WHT001922.</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH70" t="n">
+      <c r="AH71" t="n">
         <v>490</v>
       </c>
-      <c r="AJ70" t="inlineStr">
+      <c r="AJ71" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK70" t="inlineStr">
+      <c r="AK71" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL70" t="inlineStr">
+      <c r="AL71" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
+      <c r="AM71" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
+      <c r="AN71" t="inlineStr">
         <is>
           <t>Крепёж КПП</t>
         </is>
       </c>
-      <c r="AO70" t="inlineStr">
+      <c r="AO71" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR70" t="inlineStr">
+      <c r="AR71" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS70" t="inlineStr">
+      <c r="AS71" t="inlineStr">
         <is>
           <t>WHT001922</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>filtr-setka-0b5-orig</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=be20ada597
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=87268821a3</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5</t>
-        </is>
-      </c>
-      <c r="AH71" t="n">
-        <v>745</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL71" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS71" t="inlineStr">
-        <is>
-          <t>filtrsetka0b5orig</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7375,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7386,2419 +7384,6 @@
         </is>
       </c>
       <c r="Q72" t="inlineStr">
-        <is>
-          <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DSG7</t>
-        </is>
-      </c>
-      <c r="AH72" t="n">
-        <v>4445</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL72" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS72" t="inlineStr">
-        <is>
-          <t>gidroakkumulyatororig</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>jf011e</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.
-В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A)</t>
-        </is>
-      </c>
-      <c r="AH73" t="n">
-        <v>6490</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL73" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>Валы, муфты, шестерни и подшипники КПП</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS73" t="inlineStr">
-        <is>
-          <t>jf011e</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>klipsy-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2</t>
-        </is>
-      </c>
-      <c r="AH74" t="n">
-        <v>475</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL74" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr">
-        <is>
-          <t>klipsyshtokov2sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>planka-solenoid-2sht</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
-        </is>
-      </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH75" t="n">
-        <v>1445</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL75" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>plankasolenoid2sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>plastiny-solenoid-orig</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Оригинальные пластины на соленоиды VAG</t>
-        </is>
-      </c>
-      <c r="AH76" t="n">
-        <v>495</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL76" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>plastinysolenoidorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>plita-filtr</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=efa8557d9d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=759d463fe2
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=3f11b4e476</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DSG7</t>
-        </is>
-      </c>
-      <c r="AH77" t="n">
-        <v>3750</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL77" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr">
-        <is>
-          <t>plitafiltr</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>plita-filtr-orig</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
-        </is>
-      </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника</t>
-        </is>
-      </c>
-      <c r="AH78" t="n">
-        <v>3750</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL78" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>plitafiltrorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
-        </is>
-      </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков</t>
-        </is>
-      </c>
-      <c r="AH79" t="n">
-        <v>4250</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL79" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>plitafiltrpylniki</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-orig</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
-        </is>
-      </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
-        </is>
-      </c>
-      <c r="AH80" t="n">
-        <v>4250</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL80" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr">
-        <is>
-          <t>plitafiltrpylnikiorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-sal</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
-        </is>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2</t>
-        </is>
-      </c>
-      <c r="AH81" t="n">
-        <v>4750</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL81" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr">
-        <is>
-          <t>plitafiltrpylnikisal</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG</t>
-        </is>
-      </c>
-      <c r="AH82" t="n">
-        <v>4750</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>plitafiltrpylnikisalorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>plita-filtr-salniki-orig</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png?v=9157b6c42a</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
-        </is>
-      </c>
-      <c r="AH83" t="n">
-        <v>4250</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL83" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr">
-        <is>
-          <t>plitafiltrsalnikiorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=03ce24da06</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
-        </is>
-      </c>
-      <c r="AH84" t="n">
-        <v>4250</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>plitapylnikisalniki</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
-        </is>
-      </c>
-      <c r="AH85" t="n">
-        <v>4750</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL85" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>plitapylnikisalnikiorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>podshipnik-vilki-6</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
-        </is>
-      </c>
-      <c r="AH86" t="n">
-        <v>620</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL86" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr">
-        <is>
-          <t>podshipnikvilki6</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня</t>
-        </is>
-      </c>
-      <c r="AH87" t="n">
-        <v>1995</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL87" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr">
-        <is>
-          <t>porshniusilpylnikikryshki</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH88" t="n">
-        <v>925</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL88" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr">
-        <is>
-          <t>pylnikishtokovorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>remkomplekt-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
-        </is>
-      </c>
-      <c r="AH89" t="n">
-        <v>1425</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL89" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr">
-        <is>
-          <t>remkomplektshtokovorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH90" t="n">
-        <v>745</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>salnikshtokaorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>salnik-tolkatelya-alum</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>Усиленные алюминиевые сальники толкателя с</t>
-        </is>
-      </c>
-      <c r="AH91" t="n">
-        <v>1245</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL91" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr">
-        <is>
-          <t>salniktolkatelyaalum</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
-        </is>
-      </c>
-      <c r="AH92" t="n">
-        <v>845</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr">
-        <is>
-          <t>salnikishtokov2sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH93" t="n">
-        <v>945</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr">
-        <is>
-          <t>salnikishtokovorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>salniki-tolkatelya-4sht</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Полный комплект сальников толкателей вилок</t>
-        </is>
-      </c>
-      <c r="AH94" t="n">
-        <v>975</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL94" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>salnikitolkatelya4sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>salnikprivod-l</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH95" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL95" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>salnikprivodl</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>salnikprivod-r</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH96" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL96" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>salnikprivodr</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH97" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH98" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL98" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>stalnaya-vstavka-plity</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
-        </is>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH99" t="n">
-        <v>975</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL99" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>stalnayavstavkaplity</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>tolkateli-4-salniki-4</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7</t>
-        </is>
-      </c>
-      <c r="AH100" t="n">
-        <v>3700</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL100" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr">
-        <is>
-          <t>tolkateli4salniki4</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Толкатели вилок + сальники + усиленные</t>
-        </is>
-      </c>
-      <c r="AH101" t="n">
-        <v>4450</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL101" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr">
-        <is>
-          <t>tolkatelisalnikialumkomplekt</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>vtulki-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH102" t="n">
-        <v>2495</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>vtulkishtokov2sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>0am325477</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>🔧 Планка (фиксатор) соленоидов мехатроника DSG7 DQ200 — пластиковая, 1 шт (половина комплекта, крепит 4 соленоида одной стороны блока). ✅ Подходит на оба поколения мехатроника — Bosch и Hilite, 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Артикул: 0am325477. ⭐ Нужна вторая планка? У нас есть комплект 2 шт — выгоднее при полной переборке мехатроника.</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="AH103" t="n">
-        <v>725</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>0am325477</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>filtr-dsg7-dq200</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
         <is>
           <t>🔧 Масляный фильтр мехатроника DSG7 DQ200 (0AM/0CW) — стандартная версия для планового обслуживания и ремонта гидроблока АКПП.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200 (0AM325025 и аналоги).
@@ -9807,18 +7392,2413 @@
 🔩 Артикул: filtr-dsg7-dq200.</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="AH72" t="n">
+        <v>490</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR72" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS72" t="inlineStr">
+        <is>
+          <t>filtrdsg7dq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>filtr-dsg7-dq500</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>🔧 Масляный фильтр мехатроника DSG7 DQ500 0BH325183B — устанавливается в корпус фильтра (корпус — отдельная позиция, см. также в нашем магазине). ✅ Volkswagen Passat, Golf, Tiguan, T5/T6, Audi A3, Škoda Kodiaq и другие модели с DSG7 DQ500/DQ400E. 📦 Новый, с завода, в наличии, отправка в день заказа. 🔩 Артикул: 0BH325183B.</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
+        </is>
+      </c>
+      <c r="AH73" t="n">
+        <v>645</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN73" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>filtrdsg7dq500</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>filtr-setka-0b5-orig</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=be20ada597
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=87268821a3</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5</t>
+        </is>
+      </c>
+      <c r="AH74" t="n">
+        <v>745</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL74" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN74" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>filtrsetka0b5orig</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>gidroakkumulyator-orig</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH75" t="n">
+        <v>4445</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN75" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr">
+        <is>
+          <t>gidroakkumulyatororig</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>jf011e</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.
+В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A)</t>
+        </is>
+      </c>
+      <c r="AH76" t="n">
+        <v>6490</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN76" t="inlineStr">
+        <is>
+          <t>Валы, муфты, шестерни и подшипники КПП</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>jf011e</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>klipsy-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2</t>
+        </is>
+      </c>
+      <c r="AH77" t="n">
+        <v>475</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>klipsyshtokov2sht</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>korpus-filtra-0bh325159</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png?v=207791c0ab
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png?v=33f6b91718</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Корпус масляного фильтра мехатроника DSG7 DQ500</t>
+        </is>
+      </c>
+      <c r="AH78" t="n">
+        <v>3879</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>korpusfiltra0bh325159</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>kryshka-mehatronika-dq200</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>🔧 Крышка (поддон) мехатроника DSG7 DQ200 — герметично закрывает гидроблок, защищает от загрязнений и подтёков масла.
+✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
+📦 Новая, в наличии, отправка в день заказа.
+🔩 Совместима с 0AM325219C.</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="AH79" t="n">
+        <v>975</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN79" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>kryshkamehatronikadq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>planka-solenoid-2sht</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Планки соленоидов мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH80" t="n">
+        <v>1445</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN80" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>plankasolenoid2sht</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>plastina-solenoid-dq200</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>🔧 Пластина (фиксатор) на соленоиды мехатроника DSG7 DQ200, 1 шт.
+✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
+📦 Новая, с завода, отправка в день заказа.</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
+        </is>
+      </c>
+      <c r="AH81" t="n">
+        <v>245</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN81" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>plastinasolenoiddq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>plastiny-solenoid-dq200-2sht</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>🔧 Пластины (фиксаторы) на соленоиды мехатроника DSG7 DQ200 — комплект 2 шт на весь мехатроник.
+✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
+📦 Новые, с завода.</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Пластины на соленоиды мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH82" t="n">
+        <v>490</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>plastinysolenoiddq2002sht</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>plastiny-solenoid-orig</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Оригинальные пластины на соленоиды VAG</t>
+        </is>
+      </c>
+      <c r="AH83" t="n">
+        <v>495</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN83" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>plastinysolenoidorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>plita-filtr</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=efa8557d9d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=759d463fe2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=3f11b4e476</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH84" t="n">
+        <v>3750</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN84" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>plitafiltr</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>plita-filtr-orig</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Усиленная плита + улучшенный фильтр мехатроника</t>
+        </is>
+      </c>
+      <c r="AH85" t="n">
+        <v>3750</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN85" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>plitafiltrorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков</t>
+        </is>
+      </c>
+      <c r="AH86" t="n">
+        <v>4250</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN86" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>plitafiltrpylniki</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+        </is>
+      </c>
+      <c r="AH87" t="n">
+        <v>4250</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>plitafiltrpylnikiorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2</t>
+        </is>
+      </c>
+      <c r="AH88" t="n">
+        <v>4750</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN88" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>plitafiltrpylnikisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal-orig</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG</t>
+        </is>
+      </c>
+      <c r="AH89" t="n">
+        <v>4750</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN89" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>plitafiltrpylnikisalorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png?v=9157b6c42a</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+        </is>
+      </c>
+      <c r="AH90" t="n">
+        <v>4250</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN90" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>plitafiltrsalnikiorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>plita-filtr-v2</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png?v=16f48e3b34</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200</t>
+        </is>
+      </c>
+      <c r="AH91" t="n">
+        <v>7500</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>plitafiltrv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=03ce24da06</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
+        </is>
+      </c>
+      <c r="AH92" t="n">
+        <v>4250</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>plitapylnikisalniki</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
+        </is>
+      </c>
+      <c r="AH93" t="n">
+        <v>4750</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>plitapylnikisalnikiorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>plita-pylniki-salniki-orig-v2</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png?v=b98621fc0a</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
+        </is>
+      </c>
+      <c r="AH94" t="n">
+        <v>9500</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN94" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>plitapylnikisalnikiorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>podshipnik-vilki-6</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
+        </is>
+      </c>
+      <c r="AH95" t="n">
+        <v>620</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN95" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>podshipnikvilki6</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня</t>
+        </is>
+      </c>
+      <c r="AH96" t="n">
+        <v>1995</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>porshniusilpylnikikryshki</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня</t>
+        </is>
+      </c>
+      <c r="AH97" t="n">
+        <v>3990</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>porshniusilpylnikikryshkiv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>prokladka-kryshki-dq200</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>🔧 Прокладка крышки (поддона) мехатроника DSG7 DQ200 — герметизирует соединение крышки с корпусом, предотвращает подтёки масла.
+✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
+📦 Новая, в наличии, отправка в день заказа.
+⭐ Нужен увеличенный ресурс? У нас есть усиленная (утолщённая) версия прокладки — смотрите в нашем магазине.
+🔩 Артикул: prokladka-kryshki-dq200.</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="AH98" t="n">
+        <v>690</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>prokladkakryshkidq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>prokladka-vtulki-niz-dq200</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>🔧 Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.
+✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
+📦 Новое, в наличии, отправка в день заказа.
+🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Нижняя прокладка-кольцо втулки мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH99" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>prokladkavtulkinizdq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>prokladka-vtulki-verh-dq200</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>🔧 Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.
+✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
+📦 Новое, в наличии, отправка в день заказа.
+🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH100" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>prokladkavtulkiverhdq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH101" t="n">
+        <v>925</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN101" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>pylnikishtokovorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="AH102" t="n">
+        <v>1850</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN102" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>pylnikishtokovorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
+        </is>
+      </c>
+      <c r="AH103" t="n">
+        <v>1425</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM103" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN103" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr">
+        <is>
+          <t>remkomplektshtokovorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
         </is>
       </c>
       <c r="AH104" t="n">
-        <v>490</v>
+        <v>2850</v>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
@@ -9842,7 +9822,7 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>Система смазки и охлаждения КПП</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -9857,7 +9837,1278 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>filtrdsg7dq200</t>
+          <t>remkomplektshtokovorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH105" t="n">
+        <v>745</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN105" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>salnikshtokaorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig-v2</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
+        </is>
+      </c>
+      <c r="X106" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="AH106" t="n">
+        <v>1490</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM106" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN106" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>salnikshtokaorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>salnik-tolkatelya-alum</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Усиленные алюминиевые сальники толкателя с</t>
+        </is>
+      </c>
+      <c r="AH107" t="n">
+        <v>1245</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN107" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>salniktolkatelyaalum</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="AH108" t="n">
+        <v>845</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN108" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr">
+        <is>
+          <t>salnikishtokov2sht</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+        </is>
+      </c>
+      <c r="X109" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH109" t="n">
+        <v>945</v>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM109" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN109" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>salnikishtokovorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>salniki-tolkatelya-4sht</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Полный комплект сальников толкателей вилок</t>
+        </is>
+      </c>
+      <c r="AH110" t="n">
+        <v>975</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN110" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>salnikitolkatelya4sht</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>salnikprivod-l</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Сальник привода левый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH111" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN111" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>salnikprivodl</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>salnikprivod-r</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Сальник привода правый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH112" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN112" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>salnikprivodr</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>salnikvhod</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Сальник входного вала DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH113" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN113" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>salnikvhod</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>salnikvihod</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Сальник выходного вала DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH114" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN114" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr">
+        <is>
+          <t>salnikvihod</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>separatornaya-plastina-dq200</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>🔧 Сепараторная пластина мехатроника DSG7 DQ200 — устанавливается под гидроплиту, разделяет каналы.
+✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
+📦 Новая, с завода, отправка в день заказа.</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH115" t="n">
+        <v>245</v>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>separatornayaplastinadq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>🔧 Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.
+✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
+📦 Новые, с завода.</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>Сепараторная пластина + пластины на соленоиды</t>
+        </is>
+      </c>
+      <c r="AH116" t="n">
+        <v>935</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN116" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>separatornayaplastinysolenoiddq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>solenoid-02e-0b5-bolshoy</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>🔧 Восстановленный соленоид сцепления K1/K2 ("большой", multiplexer) — для DSG6 02E DQ250, DSG7 0BH/0BT DQ500, DL501 0B5.
+✅ Volkswagen, Audi, Škoda, Seat с коробками 02E/DQ250, DQ500, 0B5/DL501.
+🔄 Восстановлен: проверен и протестирован перед отправкой.
+📦 В наличии, отправка в день заказа.
+🔩 Артикул: solenoid-02e-0b5-bolshoy.</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500</t>
+        </is>
+      </c>
+      <c r="AH117" t="n">
+        <v>2850</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN117" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr">
+        <is>
+          <t>solenoid02e0b5bolshoy</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH118" t="n">
+        <v>975</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM118" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN118" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr">
+        <is>
+          <t>stalnayavstavkaplity</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7</t>
+        </is>
+      </c>
+      <c r="AH119" t="n">
+        <v>3700</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN119" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>tolkateli4salniki4</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Толкатели вилок + сальники + усиленные</t>
+        </is>
+      </c>
+      <c r="AH120" t="n">
+        <v>4450</v>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL120" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN120" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr">
+        <is>
+          <t>tolkatelisalnikialumkomplekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>vtulki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH121" t="n">
+        <v>2495</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN121" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>vtulkishtokov2sht</t>
         </is>
       </c>
     </row>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF121"/>
+  <dimension ref="A1:BF122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="3"/>
@@ -7467,6 +7467,11 @@
           <t>🔧 Масляный фильтр мехатроника DSG7 DQ500 0BH325183B — устанавливается в корпус фильтра (корпус — отдельная позиция, см. также в нашем магазине). ✅ Volkswagen Passat, Golf, Tiguan, T5/T6, Audi A3, Škoda Kodiaq и другие модели с DSG7 DQ500/DQ400E. 📦 Новый, с завода, в наличии, отправка в день заказа. 🔩 Артикул: 0BH325183B.</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq500_1.png?v=5a2f360fb5</t>
+        </is>
+      </c>
       <c r="X73" t="inlineStr">
         <is>
           <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
@@ -7921,6 +7926,11 @@
 🔩 Совместима с 0AM325219C.</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.png?v=637a263fe5</t>
+        </is>
+      </c>
       <c r="X79" t="inlineStr">
         <is>
           <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
@@ -8066,6 +8076,11 @@
           <t>🔧 Пластина (фиксатор) на соленоиды мехатроника DSG7 DQ200, 1 шт.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новая, с завода, отправка в день заказа.</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastina-solenoid-dq200_1.png?v=e86dd4da7d</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
@@ -9346,6 +9361,11 @@
 🔩 Артикул: prokladka-kryshki-dq200.</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-kryshki-dq200_1.png?v=be7cbb92a8</t>
+        </is>
+      </c>
       <c r="X98" t="inlineStr">
         <is>
           <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
@@ -9403,15 +9423,94 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
+          <t>prokladka-vtulki-dq200</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.
+✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0am325091F и длинные 101мм 0AM325091E.
+✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
+📦 Новые, в наличии, отправка в день заказа.
+🔩 Артикул: prokladka-vtulki-dq200.</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>2 кольца-прокладки на 1 втулку мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH99" t="n">
+        <v>420</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>prokladkavtulkidq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
           <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>🔧 Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -9419,72 +9518,72 @@
 🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>Нижняя прокладка-кольцо втулки мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH99" t="n">
+      <c r="AH100" t="n">
         <v>290</v>
       </c>
-      <c r="AJ99" t="inlineStr">
+      <c r="AJ100" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK99" t="inlineStr">
+      <c r="AK100" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL99" t="inlineStr">
+      <c r="AL100" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
+      <c r="AM100" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
+      <c r="AN100" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO99" t="inlineStr">
+      <c r="AO100" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR99" t="inlineStr">
+      <c r="AR100" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS99" t="inlineStr">
+      <c r="AS100" t="inlineStr">
         <is>
           <t>prokladkavtulkinizdq200</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>🔧 Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -9492,127 +9591,52 @@
 🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>Верхняя прокладка-кольцо втулки мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH100" t="n">
+      <c r="AH101" t="n">
         <v>290</v>
       </c>
-      <c r="AJ100" t="inlineStr">
+      <c r="AJ101" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK100" t="inlineStr">
+      <c r="AK101" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL100" t="inlineStr">
+      <c r="AL101" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
+      <c r="AM101" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
+      <c r="AN101" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO100" t="inlineStr">
+      <c r="AO101" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR100" t="inlineStr">
+      <c r="AR101" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS100" t="inlineStr">
+      <c r="AS101" t="inlineStr">
         <is>
           <t>prokladkavtulkiverhdq200</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>pylniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH101" t="n">
-        <v>925</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL101" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr">
-        <is>
-          <t>pylnikishtokovorig</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9648,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>pylniki-shtokov-orig</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9639,16 +9663,16 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH102" t="n">
-        <v>1850</v>
+        <v>925</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -9687,7 +9711,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>pylnikishtokovorigv2</t>
+          <t>pylnikishtokovorig</t>
         </is>
       </c>
     </row>
@@ -9699,7 +9723,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>pylniki-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9709,21 +9733,21 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="AH103" t="n">
-        <v>1425</v>
+        <v>1850</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
@@ -9747,7 +9771,7 @@
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Переключение передач</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -9762,7 +9786,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>remkomplektshtokovorig</t>
+          <t>pylnikishtokovorigv2</t>
         </is>
       </c>
     </row>
@@ -9774,7 +9798,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9789,7 +9813,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
@@ -9798,7 +9822,7 @@
         </is>
       </c>
       <c r="AH104" t="n">
-        <v>2850</v>
+        <v>1425</v>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
@@ -9837,7 +9861,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>remkomplektshtokovorigv2</t>
+          <t>remkomplektshtokovorig</t>
         </is>
       </c>
     </row>
@@ -9849,146 +9873,146 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
+          <t>remkomplekt-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
+        </is>
+      </c>
+      <c r="AH105" t="n">
+        <v>2850</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN105" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>remkomplektshtokovorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
           <t>salnik-shtoka-orig</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="P106" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="Q106" t="inlineStr">
         <is>
           <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH105" t="n">
+      <c r="AH106" t="n">
         <v>745</v>
       </c>
-      <c r="AJ105" t="inlineStr">
+      <c r="AJ106" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK105" t="inlineStr">
+      <c r="AK106" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL105" t="inlineStr">
+      <c r="AL106" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
+      <c r="AM106" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN105" t="inlineStr">
+      <c r="AN106" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO105" t="inlineStr">
+      <c r="AO106" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR105" t="inlineStr">
+      <c r="AR106" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS105" t="inlineStr">
+      <c r="AS106" t="inlineStr">
         <is>
           <t>salnikshtokaorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig-v2</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
-        </is>
-      </c>
-      <c r="AH106" t="n">
-        <v>1490</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL106" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>salnikshtokaorigv2</t>
         </is>
       </c>
     </row>
@@ -10000,7 +10024,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salnik-shtoka-orig-v2</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -10010,21 +10034,21 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с</t>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
         </is>
       </c>
       <c r="AH107" t="n">
-        <v>1245</v>
+        <v>1490</v>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
@@ -10063,7 +10087,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>salniktolkatelyaalum</t>
+          <t>salnikshtokaorigv2</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10099,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -10085,21 +10109,21 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
+          <t>Усиленные алюминиевые сальники толкателя с</t>
         </is>
       </c>
       <c r="AH108" t="n">
-        <v>845</v>
+        <v>1245</v>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
@@ -10138,7 +10162,7 @@
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>salnikishtokov2sht</t>
+          <t>salniktolkatelyaalum</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10174,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -10160,21 +10184,21 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="AH109" t="n">
-        <v>945</v>
+        <v>845</v>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
@@ -10213,7 +10237,7 @@
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>salnikishtokovorig</t>
+          <t>salnikishtokov2sht</t>
         </is>
       </c>
     </row>
@@ -10225,146 +10249,146 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH110" t="n">
+        <v>945</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN110" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>salnikishtokovorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
           <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
+      <c r="P111" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr">
+      <c r="Q111" t="inlineStr">
         <is>
           <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr">
+      <c r="S111" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>Полный комплект сальников толкателей вилок</t>
         </is>
       </c>
-      <c r="AH110" t="n">
+      <c r="AH111" t="n">
         <v>975</v>
       </c>
-      <c r="AJ110" t="inlineStr">
+      <c r="AJ111" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK110" t="inlineStr">
+      <c r="AK111" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL110" t="inlineStr">
+      <c r="AL111" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
+      <c r="AM111" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN110" t="inlineStr">
+      <c r="AN111" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO110" t="inlineStr">
+      <c r="AO111" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR110" t="inlineStr">
+      <c r="AR111" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS110" t="inlineStr">
+      <c r="AS111" t="inlineStr">
         <is>
           <t>salnikitolkatelya4sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>salnikprivod-l</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
-        </is>
-      </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH111" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL111" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>salnikprivodl</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10400,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -10386,17 +10410,17 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH112" t="n">
@@ -10439,7 +10463,7 @@
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>salnikprivodr</t>
+          <t>salnikprivodl</t>
         </is>
       </c>
     </row>
@@ -10451,103 +10475,103 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>salnikprivod-r</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Сальник привода правый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH113" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN113" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr">
+        <is>
+          <t>salnikprivodr</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
           <t>salnikvhod</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
+      <c r="P114" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr">
+      <c r="Q114" t="inlineStr">
         <is>
           <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
+      <c r="S114" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>Сальник входного вала DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH113" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL113" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH114" t="n">
@@ -10590,7 +10614,7 @@
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>salnikvihod</t>
+          <t>salnikvhod</t>
         </is>
       </c>
     </row>
@@ -10602,159 +10626,239 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
+          <t>salnikvihod</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Сальник выходного вала DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH115" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr">
+        <is>
+          <t>salnikvihod</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
           <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr">
+      <c r="P116" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr">
+      <c r="Q116" t="inlineStr">
         <is>
           <t>🔧 Сепараторная пластина мехатроника DSG7 DQ200 — устанавливается под гидроплиту, разделяет каналы.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новая, с завода, отправка в день заказа.</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastina-dq200_1.png?v=7ff85d1a3c</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
         <is>
           <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH115" t="n">
+      <c r="AH116" t="n">
         <v>245</v>
       </c>
-      <c r="AJ115" t="inlineStr">
+      <c r="AJ116" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK115" t="inlineStr">
+      <c r="AK116" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL115" t="inlineStr">
+      <c r="AL116" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
+      <c r="AM116" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN115" t="inlineStr">
+      <c r="AN116" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO115" t="inlineStr">
+      <c r="AO116" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR115" t="inlineStr">
+      <c r="AR116" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS115" t="inlineStr">
+      <c r="AS116" t="inlineStr">
         <is>
           <t>separatornayaplastinadq200</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr">
+      <c r="P117" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q116" t="inlineStr">
+      <c r="Q117" t="inlineStr">
         <is>
           <t>🔧 Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новые, с завода.</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>Сепараторная пластина + пластины на соленоиды</t>
         </is>
       </c>
-      <c r="AH116" t="n">
+      <c r="AH117" t="n">
         <v>935</v>
       </c>
-      <c r="AJ116" t="inlineStr">
+      <c r="AJ117" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK116" t="inlineStr">
+      <c r="AK117" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL116" t="inlineStr">
+      <c r="AL117" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
+      <c r="AM117" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN116" t="inlineStr">
+      <c r="AN117" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO116" t="inlineStr">
+      <c r="AO117" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR116" t="inlineStr">
+      <c r="AR117" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS116" t="inlineStr">
+      <c r="AS117" t="inlineStr">
         <is>
           <t>separatornayaplastinysolenoiddq200</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr">
+      <c r="P118" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr">
+      <c r="Q118" t="inlineStr">
         <is>
           <t>🔧 Восстановленный соленоид сцепления K1/K2 ("большой", multiplexer) — для DSG6 02E DQ250, DSG7 0BH/0BT DQ500, DL501 0B5.
 ✅ Volkswagen, Audi, Škoda, Seat с коробками 02E/DQ250, DQ500, 0B5/DL501.
@@ -10763,127 +10867,52 @@
 🔩 Артикул: solenoid-02e-0b5-bolshoy.</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500</t>
         </is>
       </c>
-      <c r="AH117" t="n">
+      <c r="AH118" t="n">
         <v>2850</v>
       </c>
-      <c r="AJ117" t="inlineStr">
+      <c r="AJ118" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK117" t="inlineStr">
+      <c r="AK118" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL117" t="inlineStr">
+      <c r="AL118" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
+      <c r="AM118" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN117" t="inlineStr">
+      <c r="AN118" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO117" t="inlineStr">
+      <c r="AO118" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR117" t="inlineStr">
+      <c r="AR118" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS117" t="inlineStr">
+      <c r="AS118" t="inlineStr">
         <is>
           <t>solenoid02e0b5bolshoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>stalnaya-vstavka-plity</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
-        </is>
-      </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH118" t="n">
-        <v>975</v>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL118" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>stalnayavstavkaplity</t>
         </is>
       </c>
     </row>
@@ -10895,7 +10924,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -10905,21 +10934,21 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH119" t="n">
-        <v>3700</v>
+        <v>975</v>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
@@ -10943,7 +10972,7 @@
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Электронное управление КПП</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -10958,7 +10987,7 @@
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>tolkateli4salniki4</t>
+          <t>stalnayavstavkaplity</t>
         </is>
       </c>
     </row>
@@ -10970,7 +10999,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
@@ -10980,21 +11009,21 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные</t>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7</t>
         </is>
       </c>
       <c r="AH120" t="n">
-        <v>4450</v>
+        <v>3700</v>
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
@@ -11033,7 +11062,7 @@
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>tolkatelisalnikialumkomplekt</t>
+          <t>tolkateli4salniki4</t>
         </is>
       </c>
     </row>
@@ -11045,68 +11074,143 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Толкатели вилок + сальники + усиленные</t>
+        </is>
+      </c>
+      <c r="AH121" t="n">
+        <v>4450</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN121" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>tolkatelisalnikialumkomplekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr">
+      <c r="P122" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
+      <c r="Q122" t="inlineStr">
         <is>
           <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
+      <c r="S122" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>
       </c>
-      <c r="X121" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH121" t="n">
+      <c r="AH122" t="n">
         <v>2495</v>
       </c>
-      <c r="AJ121" t="inlineStr">
+      <c r="AJ122" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK121" t="inlineStr">
+      <c r="AK122" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL121" t="inlineStr">
+      <c r="AL122" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
+      <c r="AM122" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN121" t="inlineStr">
+      <c r="AN122" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO121" t="inlineStr">
+      <c r="AO122" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR121" t="inlineStr">
+      <c r="AR122" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS121" t="inlineStr">
+      <c r="AS122" t="inlineStr">
         <is>
           <t>vtulkishtokov2sht</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF122"/>
+  <dimension ref="A1:BF115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="3"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2760,82 +2760,6 @@
         </is>
       </c>
       <c r="Q18" t="inlineStr">
-        <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM 0CW Hiltie контракт. проверены на стенде оригинал!
-🔩 Артикул: 0AM325473.</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=9d51d969ea</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>Соленоиды мехатроника DSG7 DQ200 0AM325473 Hiltie</t>
-        </is>
-      </c>
-      <c r="AH18" t="n">
-        <v>5990</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>0AM325473</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>0AM325587E</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
         <is>
           <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E)
 📦 Назначение:
@@ -2863,77 +2787,77 @@
 Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.jpg?v=6cc2257c48</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>Гидроаккумулятор мехатроника DSG7 DQ200 Оригинал</t>
         </is>
       </c>
-      <c r="AH19" t="n">
+      <c r="AH18" t="n">
         <v>4925</v>
       </c>
-      <c r="AJ19" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK19" t="inlineStr">
+      <c r="AK18" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL19" t="inlineStr">
+      <c r="AL18" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
+      <c r="AM18" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
+      <c r="AN18" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO19" t="inlineStr">
+      <c r="AO18" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR19" t="inlineStr">
+      <c r="AR18" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS19" t="inlineStr">
+      <c r="AS18" t="inlineStr">
         <is>
           <t>0AM325587E</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>0AM927769D</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Электронная плата мехатроника DSG7 DQ200 0AM927769D Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7
 Описание:
@@ -2943,77 +2867,77 @@
 Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769D</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_2.jpg?v=4529f855b6</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>Электронная плата мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH20" t="n">
+      <c r="AH19" t="n">
         <v>39400</v>
       </c>
-      <c r="AJ20" t="inlineStr">
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK20" t="inlineStr">
+      <c r="AK19" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr">
+      <c r="AL19" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AM19" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
+      <c r="AN19" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO20" t="inlineStr">
+      <c r="AO19" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
+      <c r="AR19" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
+      <c r="AS19" t="inlineStr">
         <is>
           <t>0AM927769D</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>0AM927769N</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Прокладка платы DSG7 DQ200 0AM 0CW
 Набор как на фото
@@ -3022,169 +2946,77 @@
 🔩 Артикул: 0AM927769N.</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.jpg?v=fbdb72784c</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Прокладки электронной платы мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH21" t="n">
+      <c r="AH20" t="n">
         <v>1740</v>
       </c>
-      <c r="AJ21" t="inlineStr">
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK21" t="inlineStr">
+      <c r="AK20" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
+      <c r="AL20" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AM20" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
+      <c r="AN20" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO21" t="inlineStr">
+      <c r="AO20" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
+      <c r="AR20" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
+      <c r="AS20" t="inlineStr">
         <is>
           <t>0AM927769N</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>0BH325</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0BH325183</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Улучшенный отвод тепла
-Уменьшает температуру масла КПП
-Резиновое кольцо в комплекте
-🔩 Алюминиевый корпус фильтра DSG7 DQ500 (0BH325183B)
-Усиленный корпус для надёжной замены пластика. Алюминий снижает риски трещин, улучшает теплоотвод, увеличивает ресурс фильтра и сцепления.
-✅ Подходит для:
-• DSG7 (DQ500), 7-ступенчатая коробка с мокрым сцеплением
-• Авто VAG-группы: VW, Audi, Skoda, Seat (2009–2023)
-• Артикулы: 0BH325183B, 0BH325159
-💡 Почему стоит взять:
-• Устойчив к перегреву и механическим нагрузкам
-• В комплекте уплотнительное кольцо
-• Простая установка без доработки
-📦 Очень быстрая отправка
-📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.png?v=207791c0ab
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_1.jpg?v=34d94b6ab7
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_2.png?v=8522c1e191
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325_3.png?v=a72d637b33</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
-        </is>
-      </c>
-      <c r="AH22" t="n">
-        <v>1940</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>0BH325</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0BH325183</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B
 🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.
@@ -3203,78 +3035,78 @@
 🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png?v=c5312dc0b8
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png?v=92f41095e4</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="AH23" t="n">
+      <c r="AH21" t="n">
         <v>3990</v>
       </c>
-      <c r="AJ23" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK23" t="inlineStr">
+      <c r="AK21" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
+      <c r="AL21" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AM21" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
+      <c r="AN21" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO23" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
+      <c r="AR21" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="AS21" t="inlineStr">
         <is>
           <t>0BH325183</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>0BH325183 B</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)
 🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.
@@ -3292,155 +3124,155 @@
 🚀 Закажите сейчас — максимально оперативная отправка!</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png?v=ed43613b04</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="AH24" t="n">
+      <c r="AH22" t="n">
         <v>3990</v>
       </c>
-      <c r="AJ24" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK24" t="inlineStr">
+      <c r="AK22" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
+      <c r="AL22" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AM22" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AN22" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
+      <c r="AO22" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR24" t="inlineStr">
+      <c r="AR22" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr">
+      <c r="AS22" t="inlineStr">
         <is>
           <t>0BH325183B</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>0am325025</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!
 Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.
 🔩 Артикул: 0am325025.</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png?v=5a785335c2</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита</t>
         </is>
       </c>
-      <c r="AH25" t="n">
+      <c r="AH23" t="n">
         <v>6445</v>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr">
+      <c r="AK23" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="AL23" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AM23" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AN23" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr">
+      <c r="AO23" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR25" t="inlineStr">
+      <c r="AR23" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS25" t="inlineStr">
+      <c r="AS23" t="inlineStr">
         <is>
           <t>0am325025</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>0am325025D</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F). Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока.
 Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW
@@ -3450,77 +3282,77 @@
 🔩 Артикул: 0am325025D.</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.jpg?v=bf2cf0a479</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH26" t="n">
+      <c r="AH24" t="n">
         <v>1445</v>
       </c>
-      <c r="AJ26" t="inlineStr">
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK26" t="inlineStr">
+      <c r="AK24" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr">
+      <c r="AL24" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
+      <c r="AM24" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AN24" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO26" t="inlineStr">
+      <c r="AO24" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR26" t="inlineStr">
+      <c r="AR24" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS26" t="inlineStr">
+      <c r="AS24" t="inlineStr">
         <is>
           <t>0am325025D</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>0am325025G</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки
 Новые
@@ -3528,77 +3360,77 @@
 🔩 Артикул: 0am325025G.</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.jpg?v=21cf6a4fc0</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH27" t="n">
+      <c r="AH25" t="n">
         <v>1940</v>
       </c>
-      <c r="AJ27" t="inlineStr">
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK27" t="inlineStr">
+      <c r="AK25" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr">
+      <c r="AL25" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AM25" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AN25" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr">
+      <c r="AO25" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR27" t="inlineStr">
+      <c r="AR25" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS27" t="inlineStr">
+      <c r="AS25" t="inlineStr">
         <is>
           <t>0am325025G</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>0am325025H</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах!
 Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.
@@ -3630,77 +3462,77 @@
 🔩 Артикул: 0am325025H.</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.jpg?v=df6ff84458</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>Мехатроник DSG7 DQ200 0AM/0CW ПРОВЕРЕН НА АВТО</t>
         </is>
       </c>
-      <c r="AH28" t="n">
+      <c r="AH26" t="n">
         <v>34400</v>
       </c>
-      <c r="AJ28" t="inlineStr">
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK28" t="inlineStr">
+      <c r="AK26" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL28" t="inlineStr">
+      <c r="AL26" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
+      <c r="AM26" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
+      <c r="AN26" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO28" t="inlineStr">
+      <c r="AO26" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR28" t="inlineStr">
+      <c r="AR26" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS28" t="inlineStr">
+      <c r="AS26" t="inlineStr">
         <is>
           <t>0am325025H</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>0am325025HX</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ.
 Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)
@@ -3720,77 +3552,77 @@
 🔩 Артикул: 0am325025HX.</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.jpg?v=815184defd</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Мехатроник DSG7 DQ200 в сборе с электронной</t>
         </is>
       </c>
-      <c r="AH29" t="n">
+      <c r="AH27" t="n">
         <v>64400</v>
       </c>
-      <c r="AJ29" t="inlineStr">
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK29" t="inlineStr">
+      <c r="AK27" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL29" t="inlineStr">
+      <c r="AL27" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
+      <c r="AM27" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
+      <c r="AN27" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO29" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR29" t="inlineStr">
+      <c r="AR27" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS29" t="inlineStr">
+      <c r="AS27" t="inlineStr">
         <is>
           <t>0am325025HX</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>0am325025P</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.
 Клипса штока мехатроника DQ200 DSG7 0AM 0CW
@@ -3798,77 +3630,77 @@
 Устанавливается внутрь штока</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png?v=4f093a4b63</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
-      <c r="AH30" t="n">
+      <c r="AH28" t="n">
         <v>490</v>
       </c>
-      <c r="AJ30" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK30" t="inlineStr">
+      <c r="AK28" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL30" t="inlineStr">
+      <c r="AL28" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
+      <c r="AM28" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
+      <c r="AN28" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO30" t="inlineStr">
+      <c r="AO28" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR30" t="inlineStr">
+      <c r="AR28" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS30" t="inlineStr">
+      <c r="AS28" t="inlineStr">
         <is>
           <t>0am325025P</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>0am325025ae</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D)
 Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.
@@ -3888,77 +3720,77 @@
 🔩 Артикул: 0am325025ae.</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.jpg?v=e1a894f60b</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>Оригинальная крышка + усиленная прокладка</t>
         </is>
       </c>
-      <c r="AH31" t="n">
+      <c r="AH29" t="n">
         <v>2440</v>
       </c>
-      <c r="AJ31" t="inlineStr">
+      <c r="AJ29" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK31" t="inlineStr">
+      <c r="AK29" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL31" t="inlineStr">
+      <c r="AL29" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
+      <c r="AM29" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
+      <c r="AN29" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO31" t="inlineStr">
+      <c r="AO29" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR31" t="inlineStr">
+      <c r="AR29" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS31" t="inlineStr">
+      <c r="AS29" t="inlineStr">
         <is>
           <t>0am325025ae</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>0am325025f</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.
 Болты мехатроника dq200 dsg 7 0am 0cw
@@ -3968,77 +3800,77 @@
 🔩 Артикул: 0am325025f.</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png?v=42835ce71d</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
-      <c r="AH32" t="n">
+      <c r="AH30" t="n">
         <v>1940</v>
       </c>
-      <c r="AJ32" t="inlineStr">
+      <c r="AJ30" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK32" t="inlineStr">
+      <c r="AK30" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL32" t="inlineStr">
+      <c r="AL30" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AM30" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
+      <c r="AN30" t="inlineStr">
         <is>
           <t>Крепёж КПП</t>
         </is>
       </c>
-      <c r="AO32" t="inlineStr">
+      <c r="AO30" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR32" t="inlineStr">
+      <c r="AR30" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS32" t="inlineStr">
+      <c r="AS30" t="inlineStr">
         <is>
           <t>0am325025f</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>0am325025hfe</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)
 Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.
@@ -4068,77 +3900,77 @@
 🔩 Артикул: 0am325025h.</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.jpg?v=23a46f0590</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>Ремкомплект штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH33" t="n">
+      <c r="AH31" t="n">
         <v>995</v>
       </c>
-      <c r="AJ33" t="inlineStr">
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK33" t="inlineStr">
+      <c r="AK31" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL33" t="inlineStr">
+      <c r="AL31" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AM31" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
+      <c r="AN31" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="AO31" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR33" t="inlineStr">
+      <c r="AR31" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS33" t="inlineStr">
+      <c r="AS31" t="inlineStr">
         <is>
           <t>0am325025hfe</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>0am325025j</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7
 Новые
@@ -4147,7 +3979,7 @@
 🔩 Артикул: 0am325025j.</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.jpg?v=5f0a06c746
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.jpg?v=f610170a4d
@@ -4155,72 +3987,72 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_4.jpg?v=714b21e00d</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>Сепараторная пластина + пластины на соленоиды</t>
         </is>
       </c>
-      <c r="AH34" t="n">
+      <c r="AH32" t="n">
         <v>1440</v>
       </c>
-      <c r="AJ34" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK34" t="inlineStr">
+      <c r="AK32" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL34" t="inlineStr">
+      <c r="AL32" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AM32" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
+      <c r="AN32" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO34" t="inlineStr">
+      <c r="AO32" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR34" t="inlineStr">
+      <c r="AR32" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS34" t="inlineStr">
+      <c r="AS32" t="inlineStr">
         <is>
           <t>0am325025j</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>0am325025l</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW
 Идентичен оригиналу 
@@ -4228,77 +4060,77 @@
 🔩 Артикул: 0am325025l.</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.jpg?v=c010c7bbdf</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH35" t="n">
+      <c r="AH33" t="n">
         <v>745</v>
       </c>
-      <c r="AJ35" t="inlineStr">
+      <c r="AJ33" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK35" t="inlineStr">
+      <c r="AK33" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL35" t="inlineStr">
+      <c r="AL33" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AM33" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AN33" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="AO33" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR35" t="inlineStr">
+      <c r="AR33" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS35" t="inlineStr">
+      <c r="AS33" t="inlineStr">
         <is>
           <t>0am325025l</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>0am325025m</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.
 Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото
@@ -4307,155 +4139,155 @@
 🔩 Артикул: 0am325025m.</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.jpg?v=ba44318fd7
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_2.jpg?v=fd9283f1f7
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_3.jpg?v=b7ac56b9b3</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH36" t="n">
+      <c r="AH34" t="n">
         <v>4440</v>
       </c>
-      <c r="AJ36" t="inlineStr">
+      <c r="AJ34" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK36" t="inlineStr">
+      <c r="AK34" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL36" t="inlineStr">
+      <c r="AL34" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
+      <c r="AM34" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
+      <c r="AN34" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO36" t="inlineStr">
+      <c r="AO34" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR36" t="inlineStr">
+      <c r="AR34" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS36" t="inlineStr">
+      <c r="AS34" t="inlineStr">
         <is>
           <t>0am325025m</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>0am325025n</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH
 🔩 Артикул: 0am325025n.</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg?v=e0223e07fa</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>Соленоид переключения (Shift) мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH37" t="n">
+      <c r="AH35" t="n">
         <v>4490</v>
       </c>
-      <c r="AJ37" t="inlineStr">
+      <c r="AJ35" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK37" t="inlineStr">
+      <c r="AK35" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL37" t="inlineStr">
+      <c r="AL35" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
+      <c r="AM35" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
+      <c r="AN35" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO37" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR37" t="inlineStr">
+      <c r="AR35" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS37" t="inlineStr">
+      <c r="AS35" t="inlineStr">
         <is>
           <t>0am325025n</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>0am325025q</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW
 Новая
@@ -4463,79 +4295,79 @@
 🔩 Артикул: 0am325025q.</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.jpg?v=5190638fc3
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.jpg?v=77fc244bbc
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_3.jpg?v=4d3606b157</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
-      <c r="AH38" t="n">
+      <c r="AH36" t="n">
         <v>490</v>
       </c>
-      <c r="AJ38" t="inlineStr">
+      <c r="AJ36" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK38" t="inlineStr">
+      <c r="AK36" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL38" t="inlineStr">
+      <c r="AL36" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
+      <c r="AM36" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
+      <c r="AN36" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO38" t="inlineStr">
+      <c r="AO36" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR38" t="inlineStr">
+      <c r="AR36" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS38" t="inlineStr">
+      <c r="AS36" t="inlineStr">
         <is>
           <t>0am325025q</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>0am325025r</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM
 Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото
@@ -4543,153 +4375,153 @@
 🔩 Артикул: 0am325025r.</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.jpg?v=3b3b076322</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>Усиленное опорное кольцо толкателя мехатроника</t>
         </is>
       </c>
-      <c r="AH39" t="n">
+      <c r="AH37" t="n">
         <v>740</v>
       </c>
-      <c r="AJ39" t="inlineStr">
+      <c r="AJ37" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK39" t="inlineStr">
+      <c r="AK37" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL39" t="inlineStr">
+      <c r="AL37" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
+      <c r="AM37" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
+      <c r="AN37" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO39" t="inlineStr">
+      <c r="AO37" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR39" t="inlineStr">
+      <c r="AR37" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS39" t="inlineStr">
+      <c r="AS37" t="inlineStr">
         <is>
           <t>0am325025r</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>0am325025u</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW
 🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png?v=c48648e856</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>Ремкомплект: Усиленный длинный шток 0AM325091E</t>
         </is>
       </c>
-      <c r="AH40" t="n">
+      <c r="AH38" t="n">
         <v>2245</v>
       </c>
-      <c r="AJ40" t="inlineStr">
+      <c r="AJ38" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK40" t="inlineStr">
+      <c r="AK38" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL40" t="inlineStr">
+      <c r="AL38" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
+      <c r="AM38" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
+      <c r="AN38" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO40" t="inlineStr">
+      <c r="AO38" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR40" t="inlineStr">
+      <c r="AR38" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS40" t="inlineStr">
+      <c r="AS38" t="inlineStr">
         <is>
           <t>0am325025u</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>0am325025x</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).
 Новые соленоиды Bosch
@@ -4702,77 +4534,77 @@
 🔩 Артикул: 0am325025x.</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=a1c5e406d3</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами</t>
         </is>
       </c>
-      <c r="AH41" t="n">
+      <c r="AH39" t="n">
         <v>39238</v>
       </c>
-      <c r="AJ41" t="inlineStr">
+      <c r="AJ39" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK41" t="inlineStr">
+      <c r="AK39" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL41" t="inlineStr">
+      <c r="AL39" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
+      <c r="AM39" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
+      <c r="AN39" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO41" t="inlineStr">
+      <c r="AO39" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR41" t="inlineStr">
+      <c r="AR39" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS41" t="inlineStr">
+      <c r="AS39" t="inlineStr">
         <is>
           <t>0am325025x</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>0am325025z</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!
 Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.
@@ -4793,154 +4625,154 @@
 🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного!</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>Ремкомплект: Усиленный короткий шток 0AM325091F</t>
         </is>
       </c>
-      <c r="AH42" t="n">
+      <c r="AH40" t="n">
         <v>2245</v>
       </c>
-      <c r="AJ42" t="inlineStr">
+      <c r="AJ40" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK42" t="inlineStr">
+      <c r="AK40" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL42" t="inlineStr">
+      <c r="AL40" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
+      <c r="AM40" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
+      <c r="AN40" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO42" t="inlineStr">
+      <c r="AO40" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR42" t="inlineStr">
+      <c r="AR40" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS42" t="inlineStr">
+      <c r="AS40" t="inlineStr">
         <is>
           <t>0am325025z</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>0am325025С</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Новое
 Отличное качество
 Всегда в наличии</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.jpg?v=3f30a503c8</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH43" t="n">
+      <c r="AH41" t="n">
         <v>490</v>
       </c>
-      <c r="AJ43" t="inlineStr">
+      <c r="AJ41" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK43" t="inlineStr">
+      <c r="AK41" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL43" t="inlineStr">
+      <c r="AL41" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
+      <c r="AM41" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
+      <c r="AN41" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO43" t="inlineStr">
+      <c r="AO41" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR43" t="inlineStr">
+      <c r="AR41" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS43" t="inlineStr">
+      <c r="AS41" t="inlineStr">
         <is>
           <t>0am325025C</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>0am325066AC</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре
 Поршень штока мехатроника DQ200 DSG 7 0AM 0CW
@@ -4950,77 +4782,77 @@
 🔩 Артикул: 0am325066AC.</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.jpg?v=693a4298e8</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>Усиленный поршень штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH44" t="n">
+      <c r="AH42" t="n">
         <v>740</v>
       </c>
-      <c r="AJ44" t="inlineStr">
+      <c r="AJ42" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK44" t="inlineStr">
+      <c r="AK42" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL44" t="inlineStr">
+      <c r="AL42" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
+      <c r="AM42" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
+      <c r="AN42" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO44" t="inlineStr">
+      <c r="AO42" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR44" t="inlineStr">
+      <c r="AR42" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS44" t="inlineStr">
+      <c r="AS42" t="inlineStr">
         <is>
           <t>0am325066AC</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>0am325066ad</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW
 Новый сальник мехатроника DSG 7 DQ200
@@ -5028,78 +4860,78 @@
 🔩 Артикул: 0am325066ad.</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=cbeca4b59a
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_2.jpg?v=a9a9967b4d</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH45" t="n">
+      <c r="AH43" t="n">
         <v>490</v>
       </c>
-      <c r="AJ45" t="inlineStr">
+      <c r="AJ43" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK45" t="inlineStr">
+      <c r="AK43" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL45" t="inlineStr">
+      <c r="AL43" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
+      <c r="AM43" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
+      <c r="AN43" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO45" t="inlineStr">
+      <c r="AO43" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR45" t="inlineStr">
+      <c r="AR43" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS45" t="inlineStr">
+      <c r="AS43" t="inlineStr">
         <is>
           <t>0am325066ad</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>0am325066ae</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW
 Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.
@@ -5124,78 +4956,78 @@
 📌 Главное - простукивайте шарики при установке!!!</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.jpg?v=ffb6e141cb
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.jpg?v=1af750811c</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>Усиленная гидроплита мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH46" t="n">
+      <c r="AH44" t="n">
         <v>4440</v>
       </c>
-      <c r="AJ46" t="inlineStr">
+      <c r="AJ44" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK46" t="inlineStr">
+      <c r="AK44" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL46" t="inlineStr">
+      <c r="AL44" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
+      <c r="AM44" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
+      <c r="AN44" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO46" t="inlineStr">
+      <c r="AO44" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR46" t="inlineStr">
+      <c r="AR44" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS46" t="inlineStr">
+      <c r="AS44" t="inlineStr">
         <is>
           <t>0am325066ae</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>0am325091e</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)
 Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом
@@ -5223,153 +5055,153 @@
 📦 Делайте заказ - отправим моментально!</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.jpg?v=ad51750acf
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_2.jpg?v=579c860e1a</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>Усиленный шток мехатроника DSG7 DQ200 101мм</t>
         </is>
       </c>
-      <c r="AH47" t="n">
+      <c r="AH45" t="n">
         <v>1440</v>
       </c>
-      <c r="AJ47" t="inlineStr">
+      <c r="AJ45" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK47" t="inlineStr">
+      <c r="AK45" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL47" t="inlineStr">
+      <c r="AL45" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
+      <c r="AM45" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
+      <c r="AN45" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO47" t="inlineStr">
+      <c r="AO45" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR47" t="inlineStr">
+      <c r="AR45" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS47" t="inlineStr">
+      <c r="AS45" t="inlineStr">
         <is>
           <t>0am325091e</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>0am325091e-set</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e-set_1.png?v=39677a9dd4</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2</t>
         </is>
       </c>
-      <c r="AH48" t="n">
+      <c r="AH46" t="n">
         <v>4425</v>
       </c>
-      <c r="AJ48" t="inlineStr">
+      <c r="AJ46" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK48" t="inlineStr">
+      <c r="AK46" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL48" t="inlineStr">
+      <c r="AL46" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
+      <c r="AM46" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
+      <c r="AN46" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO48" t="inlineStr">
+      <c r="AO46" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR48" t="inlineStr">
+      <c r="AR46" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS48" t="inlineStr">
+      <c r="AS46" t="inlineStr">
         <is>
           <t>0am325091eset</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>0am325091f</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)
 Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.
@@ -5400,19 +5232,169 @@
 👉Оформите заказ - отправим в лучшем виде!</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.jpg?v=fc28fbc227
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_2.jpg?v=94ce98509a</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Усиленный шток мехатроника DSG7 DQ200 99мм</t>
+        </is>
+      </c>
+      <c r="AH47" t="n">
+        <v>1440</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL47" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS47" t="inlineStr">
+        <is>
+          <t>0am325091f</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0am325091f-set</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_1.png?v=6b39215af5</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2</t>
+        </is>
+      </c>
+      <c r="AH48" t="n">
+        <v>4425</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS48" t="inlineStr">
+        <is>
+          <t>0am325091fset</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>🔧 Планка (фиксатор) соленоидов мехатроника DSG7 DQ200 — пластиковая, 1 шт (половина комплекта, крепит 4 соленоида одной стороны блока). ✅ Подходит на оба поколения мехатроника — Bosch и Hilite, 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Артикул: 0am325477. ⭐ Нужна вторая планка? У нас есть комплект 2 шт — выгоднее при полной переборке мехатроника.</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
+        </is>
+      </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Усиленный шток мехатроника DSG7 DQ200 99мм</t>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>1440</v>
+        <v>725</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -5436,7 +5418,7 @@
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Электронное управление КПП</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -5451,7 +5433,7 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325477</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5445,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5473,21 +5455,22 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
+          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti
+🔩 Артикул: 0am325477ae.</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_1.png?v=6b39215af5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png?v=368fa6503f</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2</t>
+          <t>Пластина соленоидов мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>4425</v>
+        <v>1240</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -5511,7 +5494,7 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Электронное управление КПП</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -5526,7 +5509,7 @@
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0am325091fset</t>
+          <t>0am325477ae</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5521,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -5547,237 +5530,6 @@
         </is>
       </c>
       <c r="Q51" t="inlineStr">
-        <is>
-          <t>🔧 Планка (фиксатор) соленоидов мехатроника DSG7 DQ200 — пластиковая, 1 шт (половина комплекта, крепит 4 соленоида одной стороны блока). ✅ Подходит на оба поколения мехатроника — Bosch и Hilite, 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Артикул: 0am325477. ⭐ Нужна вторая планка? У нас есть комплект 2 шт — выгоднее при полной переборке мехатроника.</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="AH51" t="n">
-        <v>725</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>0am325477</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>0am325477ae</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti
-🔩 Артикул: 0am325477ae.</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png?v=368fa6503f</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>Пластина соленоидов мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH52" t="n">
-        <v>1240</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr">
-        <is>
-          <t>0am325477ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>0ambset</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>Комплект подшипников для коробки передач DSG7 DQ200 (поколение 0AM/0CW), включает 10 штук подшипников NSK – идеальное решение при ремонте КПП
-Оригинальное качество NSK
-10 шт в комплекте – полная замена
-Добавляйте в корзину!
-🔩 Артикул: 0ambset.</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.png?v=51d4844731
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.png?v=bcd5b49d99</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10</t>
-        </is>
-      </c>
-      <c r="AH53" t="n">
-        <v>5990</v>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>Валы, муфты, шестерни и подшипники КПП</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr">
-        <is>
-          <t>0ambset</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>0cw0am</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM
 Описание товара
@@ -5793,79 +5545,79 @@
 Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH54" t="n">
+      <c r="AH51" t="n">
         <v>466</v>
       </c>
-      <c r="AJ54" t="inlineStr">
+      <c r="AJ51" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK54" t="inlineStr">
+      <c r="AK51" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL54" t="inlineStr">
+      <c r="AL51" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AM51" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
+      <c r="AN51" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO54" t="inlineStr">
+      <c r="AO51" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR54" t="inlineStr">
+      <c r="AR51" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS54" t="inlineStr">
+      <c r="AS51" t="inlineStr">
         <is>
           <t>0cw0am</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>0cw0am325025</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW
 В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.
@@ -5888,77 +5640,77 @@
 🔩 Артикул: 0cw0am325025.</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные</t>
         </is>
       </c>
-      <c r="AH55" t="n">
+      <c r="AH52" t="n">
         <v>8445</v>
       </c>
-      <c r="AJ55" t="inlineStr">
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK55" t="inlineStr">
+      <c r="AK52" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL55" t="inlineStr">
+      <c r="AL52" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
+      <c r="AM52" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
+      <c r="AN52" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO55" t="inlineStr">
+      <c r="AO52" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR55" t="inlineStr">
+      <c r="AR52" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS55" t="inlineStr">
+      <c r="AS52" t="inlineStr">
         <is>
           <t>0cw0am325025</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.
 Совместимость
@@ -5972,78 +5724,78 @@
 🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=77a111eb34
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=40c2597cb3</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Уплотнение электромотора гидроблока мехатроника</t>
         </is>
       </c>
-      <c r="AH56" t="n">
+      <c r="AH53" t="n">
         <v>425</v>
       </c>
-      <c r="AJ56" t="inlineStr">
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK56" t="inlineStr">
+      <c r="AK53" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL56" t="inlineStr">
+      <c r="AL53" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
+      <c r="AM53" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
+      <c r="AN53" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO56" t="inlineStr">
+      <c r="AO53" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR56" t="inlineStr">
+      <c r="AR53" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS56" t="inlineStr">
+      <c r="AS53" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377
 🔎
@@ -6066,78 +5818,78 @@
 🔩 Артикул: 0cw325025h.</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH57" t="n">
+      <c r="AH54" t="n">
         <v>645</v>
       </c>
-      <c r="AJ57" t="inlineStr">
+      <c r="AJ54" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK57" t="inlineStr">
+      <c r="AK54" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
+      <c r="AL54" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AM54" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
+      <c r="AN54" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO57" t="inlineStr">
+      <c r="AO54" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR57" t="inlineStr">
+      <c r="AR54" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS57" t="inlineStr">
+      <c r="AS54" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>0сц</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.
 Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.
@@ -6158,79 +5910,79 @@
 🔩 Артикул: 0сц.</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.jpg?v=3e0abf9ec7
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.jpg?v=b12c6dac21
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.jpg?v=bd237a81d2</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH58" t="n">
+      <c r="AH55" t="n">
         <v>745</v>
       </c>
-      <c r="AJ58" t="inlineStr">
+      <c r="AJ55" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK58" t="inlineStr">
+      <c r="AK55" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
+      <c r="AL55" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AM55" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
+      <c r="AN55" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO58" t="inlineStr">
+      <c r="AO55" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR58" t="inlineStr">
+      <c r="AR55" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS58" t="inlineStr">
+      <c r="AS55" t="inlineStr">
         <is>
           <t>0c</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>122390AK-AF</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект
 Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW
@@ -6243,78 +5995,78 @@
 🔩 Артикул: 122390AK-AF.</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=a2422623a6
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg?v=70e1dc8dfd</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
-      <c r="AH59" t="n">
+      <c r="AH56" t="n">
         <v>490</v>
       </c>
-      <c r="AJ59" t="inlineStr">
+      <c r="AJ56" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK59" t="inlineStr">
+      <c r="AK56" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL59" t="inlineStr">
+      <c r="AL56" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
+      <c r="AM56" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
+      <c r="AN56" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO59" t="inlineStr">
+      <c r="AO56" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR59" t="inlineStr">
+      <c r="AR56" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS59" t="inlineStr">
+      <c r="AS56" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)
 Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.
@@ -6344,77 +6096,77 @@
 🔩 Артикул: 122390AKAF.</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png?v=a2422623a6</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH60" t="n">
+      <c r="AH57" t="n">
         <v>745</v>
       </c>
-      <c r="AJ60" t="inlineStr">
+      <c r="AJ57" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK60" t="inlineStr">
+      <c r="AK57" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL60" t="inlineStr">
+      <c r="AL57" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
+      <c r="AM57" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
+      <c r="AN57" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO60" t="inlineStr">
+      <c r="AO57" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR60" t="inlineStr">
+      <c r="AR57" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS60" t="inlineStr">
+      <c r="AS57" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>123014‑AF</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества
 ✅
@@ -6428,279 +6180,78 @@
 Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=6a32ad2888
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=995613c21a</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
         </is>
       </c>
-      <c r="AH61" t="n">
+      <c r="AH58" t="n">
         <v>740</v>
       </c>
-      <c r="AJ61" t="inlineStr">
+      <c r="AJ58" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK61" t="inlineStr">
+      <c r="AK58" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL61" t="inlineStr">
+      <c r="AL58" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
+      <c r="AM58" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
+      <c r="AN58" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO61" t="inlineStr">
+      <c r="AO58" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR61" t="inlineStr">
+      <c r="AR58" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS61" t="inlineStr">
+      <c r="AS58" t="inlineStr">
         <is>
           <t>123014AF</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>31705-1XF0C</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>317053TX0C</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Гидроблок JF011E (Старое поколение, 2 датчика) для вариатора CVT RE0F10A. Обеспечивает точное управление давлением масла и стабильную работу коробки передач. Подходит для ремонта вариаторов Nissan, Mitsubishi, Renault и Jeep.
-Описание товара
-Гидроблок JF011E — ключевой управляющий элемент вариатора CVT, отвечающий за работу соленоидов, распределение давления масла и корректное функционирование трансмиссии. Устанавливается в вариаторах RE0F10A и широко применяется при ремонте коробок передач автомобилей Nissan, Mitsubishi, Renault и Jeep.
-Износ или загрязнение гидроблока JF011E приводит к рывкам при разгоне, задержкам включения режимов, пробуксовке ремня вариатора и появлению ошибок CVT. Замена гидроблока позволяет восстановить плавность хода, нормализовать давление масла и устранить аварийный режим без полной замены вариатора.
-Гидроблок полностью совместим с конструкцией вариатора JF011E и предназначен для штатной установки. Используется как при капитальном ремонте CVT, так и при частичном восстановлении трансмиссии.
-Когда требуется замена гидроблока
-• рывки и толчки при движении • задержка включения D / R • нестабильное давление масла • пробуксовка вариатора • ошибки по соленоидам • переход коробки в аварийный режим
-Преимущества
-• Полная совместимость с вариатором JF011E (RE0F10A) • Корректная работа соленоидов CVT • Стабильное давление масла в системе • Улучшение плавности переключений • Эффективное решение без замены всей КПП
-Совместимость
-Тип КПП: вариатор CVT Модель: JF011E / RE0F10A
-Применяется в автомобилях:
-Nissan
-Mitsubishi
-Renault
-Jeep
-(модели с установленным вариатором JF011E — по каталогу производителя)
-Назначение: гидроблок вариатора Тип установки: штатный Совместимость: JF011E / RE0F10A Состояние: новый
-гидроблок jf011e гидроблок вариатора jf011e гидроблок cvt jf011e гидроблок re0f10a гидроблок вариатора ниссан гидроблок вариатора mitsubishi гидроблок cvt nissan ремонт вариатора jf011e
-🔩 Артикул: 31705-1XF0C.</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-1XF0C_1.jpg?v=dc356035c7</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF011E (RE0F10A), 2 датчика</t>
-        </is>
-      </c>
-      <c r="AH62" t="n">
-        <v>29450</v>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL62" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>317051XF0C</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>31705-X428B</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Гидроблок JF015E CVT (RE0F11A) для Nissan, Renault, Mitsubishi — новый
-Краткое описание (первые 3 строки — самое важное для Ozon)
-Гидроблок вариатора JF015E (RE0F11A) для автомобилей Nissan, Renault, Mitsubishi. Решение проблем с пинками, пробуксовкой и ошибками вариатора.
-Гидроблок JF015E — ключевой элемент вариатора CVT, устанавливаемого на автомобили Nissan, Renault и Mitsubishi. Именно гидроблок управляет работой соленоидов, давлением масла и корректной работой трансмиссии. Износ или загрязнение гидроблока приводит к рывкам, толчкам, аварийному режиму и ошибкам коробки передач.
-Данный гидроблок JF015E предназначен для замены неисправного узла вариатора RE0F11A. Подходит для ремонта CVT без полной замены всей коробки. Может использоваться как при капитальном ремонте вариатора, так и при частичной замене узлов.
-Признаки неисправности гидроблока JF015E:
-рывки и пинки при разгоне
-задержка включения Drive / Reverse
-пробуксовка вариатора
-переход в аварийный режим
-ошибки по давлению масла и соленоидам
-вибрации и нестабильная работа CVT
-Преимущества:
-Полная совместимость с вариатором JF015E (RE0F11A)
-Восстанавливает корректное давление масла
-Улучшает плавность хода и отклик трансмиссии
-Оптимальное решение без замены всего вариатора
-Подходит для СТО и самостоятельного ремонта
-Совместимость:
-Вариатор JF015E / RE0F11A Автомобили Nissan, Renault, Mitsubishi (по каталогу)
-Часто устанавливается на:
-Nissan Juke
-Nissan Qashqai
-Nissan Note
-Nissan Sentra
-Renault Fluence
-Renault Kaptur
-Mitsubishi ASX (и другие модели с вариатором JF015E)
-Тип КПП: вариатор CVT Модель вариатора: JF015E / RE0F11A Назначение: управление давлением и соленоидами Установка: штатная, без доработок Состояние: новый
-гидроблок jf015e гидроблок вариатора jf015e гидроблок cvt jf015e гидроблок re0f11a гидроблок ниссан вариатор гидроблок вариатора ниссан ремонт вариатора jf015e гидроблок cvt nissan соленоиды jf015e гидроблок рено вариатор
-🔩 Артикул: 31705-X428B.</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_1.png?v=6ac791003d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_2.png?v=4bd4c0625c
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/31705-X428B_3.png?v=4e011c48be</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Гидроблок вариатора JF015E 1.6л (RE0F11A) новый</t>
-        </is>
-      </c>
-      <c r="AH63" t="n">
-        <v>29450</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL63" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr">
-        <is>
-          <t>31705X428B</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>317053TX0C</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.
 Описание товара
@@ -6724,78 +6275,78 @@
 🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
         </is>
       </c>
-      <c r="AH64" t="n">
+      <c r="AH59" t="n">
         <v>29450</v>
       </c>
-      <c r="AJ64" t="inlineStr">
+      <c r="AJ59" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK64" t="inlineStr">
+      <c r="AK59" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL64" t="inlineStr">
+      <c r="AL59" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
+      <c r="AM59" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
+      <c r="AN59" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO64" t="inlineStr">
+      <c r="AO59" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR64" t="inlineStr">
+      <c r="AR59" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS64" t="inlineStr">
+      <c r="AS59" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>55565480</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>импульсная звёздочка датчика положения распредвала
 Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.
@@ -6807,152 +6358,77 @@
 Датчик распредвала 55565480 GM</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>Импульсное кольцо распредвала GM 55565480</t>
         </is>
       </c>
-      <c r="AH65" t="n">
+      <c r="AH60" t="n">
         <v>500</v>
       </c>
-      <c r="AJ65" t="inlineStr">
+      <c r="AJ60" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK65" t="inlineStr">
+      <c r="AK60" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL65" t="inlineStr">
+      <c r="AL60" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
+      <c r="AM60" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
+      <c r="AN60" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO65" t="inlineStr">
+      <c r="AO60" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR65" t="inlineStr">
+      <c r="AR60" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS65" t="inlineStr">
+      <c r="AS60" t="inlineStr">
         <is>
           <t>55565480</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>6t30</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DQ500</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>🔧 Соленоиды автоматической коробки передач 6T30/6T40/6T45/6T50. ✅ Chevrolet Cruze, Opel Astra J/Insignia и другие модели с этими АКПП. 🔩 Уточните точную модификацию коробки (6T30/40/45/50) перед заказом. ⭐ Частая причина рывков и ошибок АКПП этого семейства.</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>Соленоиды АКПП 6T30/6T40/6T45/6T50</t>
-        </is>
-      </c>
-      <c r="AH66" t="n">
-        <v>9900</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL66" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>6t30</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>DQ500</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH
 Новые
@@ -6961,7 +6437,7 @@
 Снижает температуру масла</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
@@ -6969,148 +6445,148 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="AH67" t="n">
+      <c r="AH61" t="n">
         <v>1925</v>
       </c>
-      <c r="AJ67" t="inlineStr">
+      <c r="AJ61" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK67" t="inlineStr">
+      <c r="AK61" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL67" t="inlineStr">
+      <c r="AL61" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
+      <c r="AM61" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
+      <c r="AN61" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO67" t="inlineStr">
+      <c r="AO61" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR67" t="inlineStr">
+      <c r="AR61" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS67" t="inlineStr">
+      <c r="AS61" t="inlineStr">
         <is>
           <t>DQ500</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Dq200dsg7</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!
 🔩 Артикул: Dq200dsg7.</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg?v=12b215cccc</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>Уплотнение насоса гидроблока мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH68" t="n">
+      <c r="AH62" t="n">
         <v>490</v>
       </c>
-      <c r="AJ68" t="inlineStr">
+      <c r="AJ62" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK68" t="inlineStr">
+      <c r="AK62" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL68" t="inlineStr">
+      <c r="AL62" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AM62" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
+      <c r="AN62" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO68" t="inlineStr">
+      <c r="AO62" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR68" t="inlineStr">
+      <c r="AR62" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS68" t="inlineStr">
+      <c r="AS62" t="inlineStr">
         <is>
           <t>Dq200dsg7</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Dq200dsg70am0cw</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)
 Описание товара
@@ -7134,77 +6610,77 @@
 🔩 Артикул: Dq200dsg70am0cw.</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>Прокладки + сальники + пыльники мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH69" t="n">
+      <c r="AH63" t="n">
         <v>4445</v>
       </c>
-      <c r="AJ69" t="inlineStr">
+      <c r="AJ63" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK69" t="inlineStr">
+      <c r="AK63" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL69" t="inlineStr">
+      <c r="AL63" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
+      <c r="AM63" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
+      <c r="AN63" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO69" t="inlineStr">
+      <c r="AO63" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR69" t="inlineStr">
+      <c r="AR63" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS69" t="inlineStr">
+      <c r="AS63" t="inlineStr">
         <is>
           <t>Dq200dsg70am0cw</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Улучшенный отвод тепла
 Уменьшает температуру масла КПП
@@ -7223,7 +6699,7 @@
 📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203
@@ -7241,149 +6717,149 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="AH70" t="n">
+      <c r="AH64" t="n">
         <v>1940</v>
       </c>
-      <c r="AJ70" t="inlineStr">
+      <c r="AJ64" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK70" t="inlineStr">
+      <c r="AK64" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL70" t="inlineStr">
+      <c r="AL64" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
+      <c r="AM64" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
+      <c r="AN64" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO70" t="inlineStr">
+      <c r="AO64" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR70" t="inlineStr">
+      <c r="AR64" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS70" t="inlineStr">
+      <c r="AS64" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>WHT001922</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный
 Новый Отличное качество
 🔩 Артикул: WHT001922.</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH71" t="n">
+      <c r="AH65" t="n">
         <v>490</v>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AJ65" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK71" t="inlineStr">
+      <c r="AK65" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL71" t="inlineStr">
+      <c r="AL65" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
+      <c r="AM65" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
+      <c r="AN65" t="inlineStr">
         <is>
           <t>Крепёж КПП</t>
         </is>
       </c>
-      <c r="AO71" t="inlineStr">
+      <c r="AO65" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR71" t="inlineStr">
+      <c r="AR65" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS71" t="inlineStr">
+      <c r="AS65" t="inlineStr">
         <is>
           <t>WHT001922</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>filtr-dsg7-dq200</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>🔧 Масляный фильтр мехатроника DSG7 DQ200 (0AM/0CW) — стандартная версия для планового обслуживания и ремонта гидроблока АКПП.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200 (0AM325025 и аналоги).
@@ -7392,533 +6868,456 @@
 🔩 Артикул: filtr-dsg7-dq200.</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH72" t="n">
+      <c r="AH66" t="n">
         <v>490</v>
       </c>
-      <c r="AJ72" t="inlineStr">
+      <c r="AJ66" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK72" t="inlineStr">
+      <c r="AK66" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL72" t="inlineStr">
+      <c r="AL66" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
+      <c r="AM66" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
+      <c r="AN66" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO72" t="inlineStr">
+      <c r="AO66" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR72" t="inlineStr">
+      <c r="AR66" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS72" t="inlineStr">
+      <c r="AS66" t="inlineStr">
         <is>
           <t>filtrdsg7dq200</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>filtr-dsg7-dq500</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>🔧 Масляный фильтр мехатроника DSG7 DQ500 0BH325183B — устанавливается в корпус фильтра (корпус — отдельная позиция, см. также в нашем магазине). ✅ Volkswagen Passat, Golf, Tiguan, T5/T6, Audi A3, Škoda Kodiaq и другие модели с DSG7 DQ500/DQ400E. 📦 Новый, с завода, в наличии, отправка в день заказа. 🔩 Артикул: 0BH325183B.</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq500_1.png?v=5a2f360fb5</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="AH73" t="n">
+      <c r="AH67" t="n">
         <v>645</v>
       </c>
-      <c r="AJ73" t="inlineStr">
+      <c r="AJ67" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK73" t="inlineStr">
+      <c r="AK67" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL73" t="inlineStr">
+      <c r="AL67" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
+      <c r="AM67" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
+      <c r="AN67" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO73" t="inlineStr">
+      <c r="AO67" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR73" t="inlineStr">
+      <c r="AR67" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS73" t="inlineStr">
+      <c r="AS67" t="inlineStr">
         <is>
           <t>filtrdsg7dq500</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=be20ada597
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=87268821a3</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5</t>
         </is>
       </c>
-      <c r="AH74" t="n">
+      <c r="AH68" t="n">
         <v>745</v>
       </c>
-      <c r="AJ74" t="inlineStr">
+      <c r="AJ68" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK74" t="inlineStr">
+      <c r="AK68" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL74" t="inlineStr">
+      <c r="AL68" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
+      <c r="AM68" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
+      <c r="AN68" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO74" t="inlineStr">
+      <c r="AO68" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR74" t="inlineStr">
+      <c r="AR68" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS74" t="inlineStr">
+      <c r="AS68" t="inlineStr">
         <is>
           <t>filtrsetka0b5orig</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>gidroakkumulyator-orig</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>Восстановленный гидроаккумулятор мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH75" t="n">
+      <c r="AH69" t="n">
         <v>4445</v>
       </c>
-      <c r="AJ75" t="inlineStr">
+      <c r="AJ69" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK75" t="inlineStr">
+      <c r="AK69" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL75" t="inlineStr">
+      <c r="AL69" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
+      <c r="AM69" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
+      <c r="AN69" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO75" t="inlineStr">
+      <c r="AO69" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR75" t="inlineStr">
+      <c r="AR69" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS75" t="inlineStr">
+      <c r="AS69" t="inlineStr">
         <is>
           <t>gidroakkumulyatororig</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>jf011e</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>klipsy-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>Комплект подшипников JF011E (RE0F10A) — это надёжное решение для обслуживания и ремонта вариаторной трансмиссии CVT, устанавливаемой на популярные модели Nissan, Mitsubishi, Renault и другие.
-В комплект входят 4 оригинальных подшипника NSK, обеспечивающих плавную работу шкивов вариатора, снижение шума и повышение срока службы трансмиссии.</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A)</t>
-        </is>
-      </c>
-      <c r="AH76" t="n">
-        <v>6490</v>
-      </c>
-      <c r="AJ76" t="inlineStr">
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2</t>
+        </is>
+      </c>
+      <c r="AH70" t="n">
+        <v>475</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK76" t="inlineStr">
+      <c r="AK70" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL76" t="inlineStr">
+      <c r="AL70" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
+      <c r="AM70" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>Валы, муфты, шестерни и подшипники КПП</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR76" t="inlineStr">
+      <c r="AR70" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>jf011e</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>klipsyshtokov2sht</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>klipsy-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>korpus-filtra-0bh325159</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2</t>
-        </is>
-      </c>
-      <c r="AH77" t="n">
-        <v>475</v>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL77" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr">
-        <is>
-          <t>klipsyshtokov2sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>korpus-filtra-0bh325159</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png?v=207791c0ab
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png?v=33f6b91718</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="AH78" t="n">
+      <c r="AH71" t="n">
         <v>3879</v>
       </c>
-      <c r="AJ78" t="inlineStr">
+      <c r="AJ71" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK78" t="inlineStr">
+      <c r="AK71" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL78" t="inlineStr">
+      <c r="AL71" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
+      <c r="AM71" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
+      <c r="AN71" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO78" t="inlineStr">
+      <c r="AO71" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR78" t="inlineStr">
+      <c r="AR71" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS78" t="inlineStr">
+      <c r="AS71" t="inlineStr">
         <is>
           <t>korpusfiltra0bh325159</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>🔧 Крышка (поддон) мехатроника DSG7 DQ200 — герметично закрывает гидроблок, защищает от загрязнений и подтёков масла.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -7926,395 +7325,922 @@
 🔩 Совместима с 0AM325219C.</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.png?v=637a263fe5</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH79" t="n">
+      <c r="AH72" t="n">
         <v>975</v>
       </c>
-      <c r="AJ79" t="inlineStr">
+      <c r="AJ72" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK79" t="inlineStr">
+      <c r="AK72" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL79" t="inlineStr">
+      <c r="AL72" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
+      <c r="AM72" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
+      <c r="AN72" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO79" t="inlineStr">
+      <c r="AO72" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR79" t="inlineStr">
+      <c r="AR72" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS79" t="inlineStr">
+      <c r="AS72" t="inlineStr">
         <is>
           <t>kryshkamehatronikadq200</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>planka-solenoid-2sht</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>Планки соленоидов мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH80" t="n">
+      <c r="AH73" t="n">
         <v>1445</v>
       </c>
-      <c r="AJ80" t="inlineStr">
+      <c r="AJ73" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK80" t="inlineStr">
+      <c r="AK73" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL80" t="inlineStr">
+      <c r="AL73" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
+      <c r="AM73" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
+      <c r="AN73" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO80" t="inlineStr">
+      <c r="AO73" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR80" t="inlineStr">
+      <c r="AR73" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS80" t="inlineStr">
+      <c r="AS73" t="inlineStr">
         <is>
           <t>plankasolenoid2sht</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>plastina-solenoid-dq200</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>🔧 Пластина (фиксатор) на соленоиды мехатроника DSG7 DQ200, 1 шт.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новая, с завода, отправка в день заказа.</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastina-solenoid-dq200_1.png?v=e86dd4da7d</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
         </is>
       </c>
-      <c r="AH81" t="n">
+      <c r="AH74" t="n">
         <v>245</v>
       </c>
-      <c r="AJ81" t="inlineStr">
+      <c r="AJ74" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK81" t="inlineStr">
+      <c r="AK74" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL81" t="inlineStr">
+      <c r="AL74" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
+      <c r="AM74" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
+      <c r="AN74" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO81" t="inlineStr">
+      <c r="AO74" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR81" t="inlineStr">
+      <c r="AR74" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS81" t="inlineStr">
+      <c r="AS74" t="inlineStr">
         <is>
           <t>plastinasolenoiddq200</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>🔧 Пластины (фиксаторы) на соленоиды мехатроника DSG7 DQ200 — комплект 2 шт на весь мехатроник.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новые, с завода.</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>Пластины на соленоиды мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH82" t="n">
+      <c r="AH75" t="n">
         <v>490</v>
       </c>
-      <c r="AJ82" t="inlineStr">
+      <c r="AJ75" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK82" t="inlineStr">
+      <c r="AK75" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL82" t="inlineStr">
+      <c r="AL75" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
+      <c r="AM75" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
+      <c r="AN75" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO82" t="inlineStr">
+      <c r="AO75" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR82" t="inlineStr">
+      <c r="AR75" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS82" t="inlineStr">
+      <c r="AS75" t="inlineStr">
         <is>
           <t>plastinysolenoiddq2002sht</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>plastiny-solenoid-orig</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>Оригинальные пластины на соленоиды VAG</t>
         </is>
       </c>
-      <c r="AH83" t="n">
+      <c r="AH76" t="n">
         <v>495</v>
       </c>
-      <c r="AJ83" t="inlineStr">
+      <c r="AJ76" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK83" t="inlineStr">
+      <c r="AK76" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL83" t="inlineStr">
+      <c r="AL76" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
+      <c r="AM76" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN83" t="inlineStr">
+      <c r="AN76" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO83" t="inlineStr">
+      <c r="AO76" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR83" t="inlineStr">
+      <c r="AR76" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS83" t="inlineStr">
+      <c r="AS76" t="inlineStr">
         <is>
           <t>plastinysolenoidorig</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>plita-filtr</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=efa8557d9d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=759d463fe2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=3f11b4e476</t>
         </is>
       </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH77" t="n">
+        <v>3750</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>plitafiltr</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>plita-filtr-orig</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Усиленная плита + улучшенный фильтр мехатроника</t>
+        </is>
+      </c>
+      <c r="AH78" t="n">
+        <v>3750</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>plitafiltrorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков</t>
+        </is>
+      </c>
+      <c r="AH79" t="n">
+        <v>4250</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN79" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>plitafiltrpylniki</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+        </is>
+      </c>
+      <c r="AH80" t="n">
+        <v>4250</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL80" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN80" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>plitafiltrpylnikiorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2</t>
+        </is>
+      </c>
+      <c r="AH81" t="n">
+        <v>4750</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN81" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>plitafiltrpylnikisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal-orig</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG</t>
+        </is>
+      </c>
+      <c r="AH82" t="n">
+        <v>4750</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS82" t="inlineStr">
+        <is>
+          <t>plitafiltrpylnikisalorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png?v=9157b6c42a</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+        </is>
+      </c>
+      <c r="AH83" t="n">
+        <v>4250</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN83" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>plitafiltrsalnikiorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>plita-filtr-v2</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png?v=16f48e3b34</t>
+        </is>
+      </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DSG7</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200</t>
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>3750</v>
+        <v>7500</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -8353,7 +8279,7 @@
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>plitafiltr</t>
+          <t>plitafiltrv2</t>
         </is>
       </c>
     </row>
@@ -8365,7 +8291,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -8375,21 +8301,21 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=03ce24da06</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>3750</v>
+        <v>4250</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -8413,7 +8339,7 @@
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>Система смазки и охлаждения КПП</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -8428,7 +8354,7 @@
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>plitafiltrorig</t>
+          <t>plitapylnikisalniki</t>
         </is>
       </c>
     </row>
@@ -8440,7 +8366,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -8450,22 +8376,21 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>4250</v>
+        <v>4750</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -8489,7 +8414,7 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>Система смазки и охлаждения КПП</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -8504,7 +8429,7 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>plitafiltrpylniki</t>
+          <t>plitapylnikisalnikiorig</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8441,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -8526,21 +8451,21 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png?v=b98621fc0a</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
         </is>
       </c>
       <c r="AH87" t="n">
-        <v>4250</v>
+        <v>9500</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -8564,7 +8489,7 @@
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>Система смазки и охлаждения КПП</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -8579,7 +8504,7 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikiorig</t>
+          <t>plitapylnikisalnikiorigv2</t>
         </is>
       </c>
     </row>
@@ -8591,7 +8516,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -8601,21 +8526,22 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2</t>
+          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
         </is>
       </c>
       <c r="AH88" t="n">
-        <v>4750</v>
+        <v>620</v>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -8639,7 +8565,7 @@
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Переключение передач</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -8654,7 +8580,7 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikisal</t>
+          <t>podshipnikvilki6</t>
         </is>
       </c>
     </row>
@@ -8666,7 +8592,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -8676,21 +8602,21 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG</t>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня</t>
         </is>
       </c>
       <c r="AH89" t="n">
-        <v>4750</v>
+        <v>1995</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -8714,7 +8640,7 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Переключение передач</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -8729,7 +8655,7 @@
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikisalorig</t>
+          <t>porshniusilpylnikikryshki</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8667,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -8751,22 +8677,22 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png?v=9157b6c42a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня</t>
         </is>
       </c>
       <c r="AH90" t="n">
-        <v>4250</v>
+        <v>3990</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -8790,7 +8716,7 @@
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Переключение передач</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -8805,7 +8731,7 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>plitafiltrsalnikiorig</t>
+          <t>porshniusilpylnikikryshkiv2</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8743,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -8826,533 +8752,6 @@
         </is>
       </c>
       <c r="Q91" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
-        </is>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png?v=16f48e3b34</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200</t>
-        </is>
-      </c>
-      <c r="AH91" t="n">
-        <v>7500</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL91" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr">
-        <is>
-          <t>plitafiltrv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
-        </is>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=03ce24da06</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
-        </is>
-      </c>
-      <c r="AH92" t="n">
-        <v>4250</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr">
-        <is>
-          <t>plitapylnikisalniki</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
-        </is>
-      </c>
-      <c r="AH93" t="n">
-        <v>4750</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr">
-        <is>
-          <t>plitapylnikisalnikiorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png?v=b98621fc0a</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
-        </is>
-      </c>
-      <c r="AH94" t="n">
-        <v>9500</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL94" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>plitapylnikisalnikiorigv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>podshipnik-vilki-6</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
-        </is>
-      </c>
-      <c r="AH95" t="n">
-        <v>620</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL95" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>podshipnikvilki6</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
-        </is>
-      </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
-        </is>
-      </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня</t>
-        </is>
-      </c>
-      <c r="AH96" t="n">
-        <v>1995</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL96" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>porshniusilpylnikikryshki</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
-        </is>
-      </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня</t>
-        </is>
-      </c>
-      <c r="AH97" t="n">
-        <v>3990</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr">
-        <is>
-          <t>porshniusilpylnikikryshkiv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>prokladka-kryshki-dq200</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q98" t="inlineStr">
         <is>
           <t>🔧 Прокладка крышки (поддона) мехатроника DSG7 DQ200 — герметизирует соединение крышки с корпусом, предотвращает подтёки масла.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -9361,77 +8760,77 @@
 🔩 Артикул: prokladka-kryshki-dq200.</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="S91" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-kryshki-dq200_1.png?v=be7cbb92a8</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH98" t="n">
+      <c r="AH91" t="n">
         <v>690</v>
       </c>
-      <c r="AJ98" t="inlineStr">
+      <c r="AJ91" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK98" t="inlineStr">
+      <c r="AK91" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL98" t="inlineStr">
+      <c r="AL91" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
+      <c r="AM91" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
+      <c r="AN91" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO98" t="inlineStr">
+      <c r="AO91" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR98" t="inlineStr">
+      <c r="AR91" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS98" t="inlineStr">
+      <c r="AS91" t="inlineStr">
         <is>
           <t>prokladkakryshkidq200</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.
 ✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0am325091F и длинные 101мм 0AM325091E.
@@ -9440,77 +8839,77 @@
 🔩 Артикул: prokladka-vtulki-dq200.</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="S92" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>2 кольца-прокладки на 1 втулку мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH99" t="n">
+      <c r="AH92" t="n">
         <v>420</v>
       </c>
-      <c r="AJ99" t="inlineStr">
+      <c r="AJ92" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK99" t="inlineStr">
+      <c r="AK92" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL99" t="inlineStr">
+      <c r="AL92" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
+      <c r="AM92" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
+      <c r="AN92" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO99" t="inlineStr">
+      <c r="AO92" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR99" t="inlineStr">
+      <c r="AR92" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS99" t="inlineStr">
+      <c r="AS92" t="inlineStr">
         <is>
           <t>prokladkavtulkidq200</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>🔧 Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -9518,72 +8917,72 @@
 🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>Нижняя прокладка-кольцо втулки мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH100" t="n">
+      <c r="AH93" t="n">
         <v>290</v>
       </c>
-      <c r="AJ100" t="inlineStr">
+      <c r="AJ93" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK100" t="inlineStr">
+      <c r="AK93" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL100" t="inlineStr">
+      <c r="AL93" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
+      <c r="AM93" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
+      <c r="AN93" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO100" t="inlineStr">
+      <c r="AO93" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR100" t="inlineStr">
+      <c r="AR93" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS100" t="inlineStr">
+      <c r="AS93" t="inlineStr">
         <is>
           <t>prokladkavtulkinizdq200</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q101" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>🔧 Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -9591,13 +8990,539 @@
 🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
         </is>
       </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH94" t="n">
+        <v>290</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN94" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>prokladkavtulkiverhdq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH95" t="n">
+        <v>925</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN95" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>pylnikishtokovorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="AH96" t="n">
+        <v>1850</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>pylnikishtokovorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
+        </is>
+      </c>
+      <c r="AH97" t="n">
+        <v>1425</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>remkomplektshtokovorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>remkomplekt-shtokov-orig-v2</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
+        </is>
+      </c>
+      <c r="AH98" t="n">
+        <v>2850</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>remkomplektshtokovorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH99" t="n">
+        <v>745</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>salnikshtokaorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig-v2</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="AH100" t="n">
+        <v>1490</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>salnikshtokaorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>salnik-tolkatelya-alum</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+        </is>
+      </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7</t>
+          <t>Усиленные алюминиевые сальники толкателя с</t>
         </is>
       </c>
       <c r="AH101" t="n">
-        <v>290</v>
+        <v>1245</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
@@ -9636,7 +9561,7 @@
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>prokladkavtulkiverhdq200</t>
+          <t>salniktolkatelyaalum</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9573,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -9658,21 +9583,21 @@
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="AH102" t="n">
-        <v>925</v>
+        <v>845</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -9696,7 +9621,7 @@
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -9711,7 +9636,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>pylnikishtokovorig</t>
+          <t>salnikishtokov2sht</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9648,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9733,21 +9658,21 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH103" t="n">
-        <v>1850</v>
+        <v>945</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
@@ -9771,7 +9696,7 @@
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -9786,7 +9711,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>pylnikishtokovorigv2</t>
+          <t>salnikishtokovorig</t>
         </is>
       </c>
     </row>
@@ -9798,7 +9723,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -9808,21 +9733,22 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
+          <t>Полный комплект сальников толкателей вилок</t>
         </is>
       </c>
       <c r="AH104" t="n">
-        <v>1425</v>
+        <v>975</v>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
@@ -9861,7 +9787,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>remkomplektshtokovorig</t>
+          <t>salnikitolkatelya4sht</t>
         </is>
       </c>
     </row>
@@ -9873,7 +9799,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -9883,21 +9809,21 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH105" t="n">
-        <v>2850</v>
+        <v>500</v>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
@@ -9936,7 +9862,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>remkomplektshtokovorigv2</t>
+          <t>salnikprivodl</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9874,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -9958,22 +9884,21 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH106" t="n">
-        <v>745</v>
+        <v>500</v>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
@@ -10012,7 +9937,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>salnikshtokaorig</t>
+          <t>salnikprivodr</t>
         </is>
       </c>
     </row>
@@ -10024,7 +9949,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig-v2</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -10034,21 +9959,22 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH107" t="n">
-        <v>1490</v>
+        <v>500</v>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
@@ -10087,7 +10013,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>salnikshtokaorigv2</t>
+          <t>salnikvhod</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10025,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -10109,21 +10035,21 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH108" t="n">
-        <v>1245</v>
+        <v>500</v>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
@@ -10162,7 +10088,7 @@
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>salniktolkatelyaalum</t>
+          <t>salnikvihod</t>
         </is>
       </c>
     </row>
@@ -10174,7 +10100,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -10183,682 +10109,155 @@
         </is>
       </c>
       <c r="Q109" t="inlineStr">
-        <is>
-          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
-        </is>
-      </c>
-      <c r="X109" t="inlineStr">
-        <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
-        </is>
-      </c>
-      <c r="AH109" t="n">
-        <v>845</v>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL109" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr">
-        <is>
-          <t>salnikishtokov2sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH110" t="n">
-        <v>945</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL110" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>salnikishtokovorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>salniki-tolkatelya-4sht</t>
-        </is>
-      </c>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
-        </is>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
-        </is>
-      </c>
-      <c r="X111" t="inlineStr">
-        <is>
-          <t>Полный комплект сальников толкателей вилок</t>
-        </is>
-      </c>
-      <c r="AH111" t="n">
-        <v>975</v>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL111" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>salnikitolkatelya4sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>salnikprivod-l</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH112" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL112" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr">
-        <is>
-          <t>salnikprivodl</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>salnikprivod-r</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
-        </is>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH113" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL113" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS113" t="inlineStr">
-        <is>
-          <t>salnikprivodr</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH114" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL114" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS114" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
-        </is>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
-        </is>
-      </c>
-      <c r="X115" t="inlineStr">
-        <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH115" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL115" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS115" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>separatornaya-plastina-dq200</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
         <is>
           <t>🔧 Сепараторная пластина мехатроника DSG7 DQ200 — устанавливается под гидроплиту, разделяет каналы.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новая, с завода, отправка в день заказа.</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr">
+      <c r="S109" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastina-dq200_1.png?v=7ff85d1a3c</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH116" t="n">
+      <c r="AH109" t="n">
         <v>245</v>
       </c>
-      <c r="AJ116" t="inlineStr">
+      <c r="AJ109" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK116" t="inlineStr">
+      <c r="AK109" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL116" t="inlineStr">
+      <c r="AL109" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM116" t="inlineStr">
+      <c r="AM109" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN116" t="inlineStr">
+      <c r="AN109" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO116" t="inlineStr">
+      <c r="AO109" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR116" t="inlineStr">
+      <c r="AR109" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS116" t="inlineStr">
+      <c r="AS109" t="inlineStr">
         <is>
           <t>separatornayaplastinadq200</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr">
+      <c r="P110" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>🔧 Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новые, с завода.</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>Сепараторная пластина + пластины на соленоиды</t>
         </is>
       </c>
-      <c r="AH117" t="n">
+      <c r="AH110" t="n">
         <v>935</v>
       </c>
-      <c r="AJ117" t="inlineStr">
+      <c r="AJ110" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK117" t="inlineStr">
+      <c r="AK110" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL117" t="inlineStr">
+      <c r="AL110" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM117" t="inlineStr">
+      <c r="AM110" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN117" t="inlineStr">
+      <c r="AN110" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO117" t="inlineStr">
+      <c r="AO110" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR117" t="inlineStr">
+      <c r="AR110" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS117" t="inlineStr">
+      <c r="AS110" t="inlineStr">
         <is>
           <t>separatornayaplastinysolenoiddq200</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr">
+      <c r="P111" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr">
+      <c r="Q111" t="inlineStr">
         <is>
           <t>🔧 Восстановленный соленоид сцепления K1/K2 ("большой", multiplexer) — для DSG6 02E DQ250, DSG7 0BH/0BT DQ500, DL501 0B5.
 ✅ Volkswagen, Audi, Škoda, Seat с коробками 02E/DQ250, DQ500, 0B5/DL501.
@@ -10867,350 +10266,350 @@
 🔩 Артикул: solenoid-02e-0b5-bolshoy.</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500</t>
         </is>
       </c>
-      <c r="AH118" t="n">
+      <c r="AH111" t="n">
         <v>2850</v>
       </c>
-      <c r="AJ118" t="inlineStr">
+      <c r="AJ111" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK118" t="inlineStr">
+      <c r="AK111" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL118" t="inlineStr">
+      <c r="AL111" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM118" t="inlineStr">
+      <c r="AM111" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN118" t="inlineStr">
+      <c r="AN111" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO118" t="inlineStr">
+      <c r="AO111" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR118" t="inlineStr">
+      <c r="AR111" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS118" t="inlineStr">
+      <c r="AS111" t="inlineStr">
         <is>
           <t>solenoid02e0b5bolshoy</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+    <row r="112">
+      <c r="A112" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D112" t="inlineStr">
         <is>
           <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr">
+      <c r="P112" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q119" t="inlineStr">
+      <c r="Q112" t="inlineStr">
         <is>
           <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr">
+      <c r="S112" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH119" t="n">
+      <c r="AH112" t="n">
         <v>975</v>
       </c>
-      <c r="AJ119" t="inlineStr">
+      <c r="AJ112" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK119" t="inlineStr">
+      <c r="AK112" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL119" t="inlineStr">
+      <c r="AL112" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM119" t="inlineStr">
+      <c r="AM112" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN119" t="inlineStr">
+      <c r="AN112" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO119" t="inlineStr">
+      <c r="AO112" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR119" t="inlineStr">
+      <c r="AR112" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS119" t="inlineStr">
+      <c r="AS112" t="inlineStr">
         <is>
           <t>stalnayavstavkaplity</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
+    <row r="113">
+      <c r="A113" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr">
+      <c r="P113" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q120" t="inlineStr">
+      <c r="Q113" t="inlineStr">
         <is>
           <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr">
+      <c r="S113" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>Комплект 4 толкателей вилок + 4 сальника DSG7</t>
         </is>
       </c>
-      <c r="AH120" t="n">
+      <c r="AH113" t="n">
         <v>3700</v>
       </c>
-      <c r="AJ120" t="inlineStr">
+      <c r="AJ113" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK120" t="inlineStr">
+      <c r="AK113" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL120" t="inlineStr">
+      <c r="AL113" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM120" t="inlineStr">
+      <c r="AM113" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN120" t="inlineStr">
+      <c r="AN113" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO120" t="inlineStr">
+      <c r="AO113" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR120" t="inlineStr">
+      <c r="AR113" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS120" t="inlineStr">
+      <c r="AS113" t="inlineStr">
         <is>
           <t>tolkateli4salniki4</t>
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr">
+      <c r="P114" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q121" t="inlineStr">
+      <c r="Q114" t="inlineStr">
         <is>
           <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr">
+      <c r="S114" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
         </is>
       </c>
-      <c r="X121" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>Толкатели вилок + сальники + усиленные</t>
         </is>
       </c>
-      <c r="AH121" t="n">
+      <c r="AH114" t="n">
         <v>4450</v>
       </c>
-      <c r="AJ121" t="inlineStr">
+      <c r="AJ114" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK121" t="inlineStr">
+      <c r="AK114" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL121" t="inlineStr">
+      <c r="AL114" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM121" t="inlineStr">
+      <c r="AM114" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN121" t="inlineStr">
+      <c r="AN114" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO121" t="inlineStr">
+      <c r="AO114" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR121" t="inlineStr">
+      <c r="AR114" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS121" t="inlineStr">
+      <c r="AS114" t="inlineStr">
         <is>
           <t>tolkatelisalnikialumkomplekt</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr">
+      <c r="P115" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q122" t="inlineStr">
+      <c r="Q115" t="inlineStr">
         <is>
           <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr">
+      <c r="S115" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH122" t="n">
+      <c r="AH115" t="n">
         <v>2495</v>
       </c>
-      <c r="AJ122" t="inlineStr">
+      <c r="AJ115" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK122" t="inlineStr">
+      <c r="AK115" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL122" t="inlineStr">
+      <c r="AL115" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM122" t="inlineStr">
+      <c r="AM115" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN122" t="inlineStr">
+      <c r="AN115" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO122" t="inlineStr">
+      <c r="AO115" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR122" t="inlineStr">
+      <c r="AR115" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS122" t="inlineStr">
+      <c r="AS115" t="inlineStr">
         <is>
           <t>vtulkishtokov2sht</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -3204,7 +3204,8 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025.png?v=5a785335c2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpeg?v=816487a239
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpg?v=45096a261b</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -1877,7 +1877,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 - отличное качество
+          <t>Масляный фильтр DQ250 DSG6 02E - отличное качество
 🔩 Артикул: 02E305051C.</t>
         </is>
       </c>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2389,6 +2389,11 @@
       <c r="AH13" t="n">
         <v>1740</v>
       </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_video.mp4?v=7ceaaba450</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>Запчасти</t>
@@ -2549,6 +2554,11 @@
       <c r="AH15" t="n">
         <v>740</v>
       </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_video.mp4?v=bde8c4c289</t>
+        </is>
+      </c>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>Запчасти</t>
@@ -2624,6 +2634,11 @@
       </c>
       <c r="AH16" t="n">
         <v>995</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_video.mp4?v=6c70471405</t>
+        </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -2701,6 +2716,11 @@
       </c>
       <c r="AH17" t="n">
         <v>995</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_video.mp4?v=7b0b51498e</t>
+        </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
@@ -5070,6 +5090,11 @@
       <c r="AH45" t="n">
         <v>1440</v>
       </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
       <c r="AJ45" t="inlineStr">
         <is>
           <t>Запчасти</t>
@@ -5144,6 +5169,11 @@
       </c>
       <c r="AH46" t="n">
         <v>4425</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e-set_video.mp4?v=4573c3be6d</t>
+        </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
@@ -5247,6 +5277,11 @@
       <c r="AH47" t="n">
         <v>1440</v>
       </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
       <c r="AJ47" t="inlineStr">
         <is>
           <t>Запчасти</t>
@@ -5321,6 +5356,11 @@
       </c>
       <c r="AH48" t="n">
         <v>4425</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_video.mp4?v=4573c3be6d</t>
+        </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -3496,6 +3496,11 @@
       <c r="AH26" t="n">
         <v>34400</v>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_video.mp4?v=15fc20f523</t>
+        </is>
+      </c>
       <c r="AJ26" t="inlineStr">
         <is>
           <t>Запчасти</t>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6228,8 +6228,8 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=6a32ad2888
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=995613c21a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=e9725022b3
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.jpg?v=68afdfa370</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6228,8 +6228,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=e9725022b3
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.jpg?v=68afdfa370</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=e9725022b3</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -8200,8 +8200,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.png?v=9157b6c42a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -9191,7 +9190,7 @@
         </is>
       </c>
       <c r="AH96" t="n">
-        <v>1850</v>
+        <v>2980</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2289,7 +2289,8 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png?v=b6b7265cda</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_0.jpg?v=7094a0c934
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png?v=b6b7265cda</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -7136,7 +7137,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
+          <t>🔧 Гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Применимость: 0AM325587E. ⭐ Отличное качество</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7148,7 +7149,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Восстановленный гидроаккумулятор мехатроника DSG7</t>
+          <t>Гидроаккумулятор мехатроника DSG7 DQ200 для VAG</t>
         </is>
       </c>
       <c r="AH69" t="n">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2289,8 +2289,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_0.jpg?v=7094a0c934
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.png?v=b6b7265cda</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_0.jpg?v=7094a0c934</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -7136,7 +7136,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>🔧 Гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Применимость: 0AM325587E. ⭐ Отличное качество</t>
+          <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Гидроаккумулятор мехатроника DSG7 DQ200 для VAG</t>
+          <t>Восстановленный гидроаккумулятор мехатроника DSG7</t>
         </is>
       </c>
       <c r="AH69" t="n">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>440</v>
+        <v>620</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>2940</v>
+        <v>4120</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>940</v>
+        <v>1320</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>59000</v>
+        <v>70800</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1940</v>
+        <v>2720</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>740</v>
+        <v>1040</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>4740</v>
+        <v>6640</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>1740</v>
+        <v>2440</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>740</v>
+        <v>1040</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>995</v>
+        <v>1390</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>995</v>
+        <v>1390</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>4925</v>
+        <v>6900</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>39400</v>
+        <v>47280</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>1740</v>
+        <v>2440</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>3990</v>
+        <v>5590</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>3990</v>
+        <v>5590</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>6445</v>
+        <v>9020</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>1445</v>
+        <v>2020</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3383,7 +3383,8 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.jpg?v=21cf6a4fc0</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.jpg?v=5bd8ad5ac3
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.jpg?v=21cf6a4fc0</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3392,7 +3393,7 @@
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>1940</v>
+        <v>2720</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3485,7 +3486,8 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.jpg?v=df6ff84458</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.png?v=0593c687c2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_2.jpg?v=df6ff84458</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3494,7 +3496,7 @@
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>34400</v>
+        <v>41280</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
@@ -3589,7 +3591,7 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>64400</v>
+        <v>77280</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -3667,7 +3669,7 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -3757,7 +3759,7 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>2440</v>
+        <v>3420</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -3837,7 +3839,7 @@
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>1940</v>
+        <v>2720</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -3937,7 +3939,7 @@
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>995</v>
+        <v>1390</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4019,7 +4021,7 @@
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>1440</v>
+        <v>2020</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4097,7 +4099,7 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>745</v>
+        <v>1040</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4178,7 +4180,7 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>4440</v>
+        <v>6220</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4254,7 +4256,7 @@
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>4490</v>
+        <v>6290</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -4334,7 +4336,7 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -4412,7 +4414,7 @@
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>740</v>
+        <v>1040</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -4488,7 +4490,7 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>2245</v>
+        <v>3140</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -4571,7 +4573,7 @@
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>39238</v>
+        <v>47090</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -4662,7 +4664,7 @@
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>2245</v>
+        <v>3140</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -4730,7 +4732,8 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.jpg?v=3f30a503c8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.jpg?v=32a4eaa349
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._2.jpg?v=3f30a503c8</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -4739,7 +4742,7 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -4819,7 +4822,7 @@
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>740</v>
+        <v>1040</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -4898,7 +4901,7 @@
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -4994,7 +4997,7 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>4440</v>
+        <v>6220</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -5093,7 +5096,7 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>1440</v>
+        <v>2020</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
@@ -5173,7 +5176,7 @@
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>4425</v>
+        <v>6200</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
@@ -5280,7 +5283,7 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>1440</v>
+        <v>2020</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
@@ -5360,7 +5363,7 @@
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>4425</v>
+        <v>6200</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
@@ -5440,7 +5443,7 @@
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>725</v>
+        <v>1010</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -5516,7 +5519,7 @@
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>1240</v>
+        <v>1740</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -5604,7 +5607,7 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>466</v>
+        <v>650</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -5697,7 +5700,7 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>8445</v>
+        <v>11820</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -5772,8 +5775,9 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=77a111eb34
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=40c2597cb3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=d2723138aa
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=77a111eb34
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_3.jpg?v=40c2597cb3</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -5782,7 +5786,7 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>425</v>
+        <v>600</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -5876,7 +5880,7 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>645</v>
+        <v>900</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -5969,7 +5973,7 @@
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>745</v>
+        <v>1040</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -6053,7 +6057,7 @@
         </is>
       </c>
       <c r="AH56" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -6153,7 +6157,7 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>745</v>
+        <v>1040</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -6237,7 +6241,7 @@
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>740</v>
+        <v>1040</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -6332,7 +6336,7 @@
         </is>
       </c>
       <c r="AH59" t="n">
-        <v>29450</v>
+        <v>35340</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -6414,7 +6418,7 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -6496,7 +6500,7 @@
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>1925</v>
+        <v>2700</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
@@ -6572,7 +6576,7 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -6666,7 +6670,7 @@
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>4445</v>
+        <v>6220</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
@@ -6768,7 +6772,7 @@
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>1940</v>
+        <v>2720</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
@@ -6845,7 +6849,7 @@
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -6915,7 +6919,8 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_2.png?v=b1ce9f5f30</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
@@ -6924,7 +6929,7 @@
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
@@ -6999,7 +7004,7 @@
         </is>
       </c>
       <c r="AH67" t="n">
-        <v>645</v>
+        <v>900</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
@@ -7065,8 +7070,9 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=be20ada597
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=87268821a3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=96f21d0cb5
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=be20ada597
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_3.jpg?v=87268821a3</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
@@ -7075,7 +7081,7 @@
         </is>
       </c>
       <c r="AH68" t="n">
-        <v>745</v>
+        <v>1650</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
@@ -7152,7 +7158,7 @@
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>4445</v>
+        <v>6220</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -7227,7 +7233,7 @@
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>475</v>
+        <v>670</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
@@ -7303,7 +7309,7 @@
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>3879</v>
+        <v>2720</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -7381,7 +7387,7 @@
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>975</v>
+        <v>1370</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -7456,7 +7462,7 @@
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>1445</v>
+        <v>2020</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -7533,7 +7539,7 @@
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>245</v>
+        <v>340</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -7605,7 +7611,7 @@
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>490</v>
+        <v>690</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -7681,7 +7687,7 @@
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>495</v>
+        <v>690</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -7747,9 +7753,10 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=efa8557d9d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=759d463fe2
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=3f11b4e476</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=7c348500b1
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=efa8557d9d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=759d463fe2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_4.jpg?v=3f11b4e476</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
@@ -7758,7 +7765,7 @@
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>3750</v>
+        <v>5250</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -7833,7 +7840,7 @@
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>3750</v>
+        <v>5250</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -7909,7 +7916,7 @@
         </is>
       </c>
       <c r="AH79" t="n">
-        <v>4250</v>
+        <v>5950</v>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
@@ -7975,7 +7982,8 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.png?v=e41c86e98b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.jpg?v=ea76b2dfed
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_2.jpg?v=13840cc30d</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
@@ -7984,7 +7992,7 @@
         </is>
       </c>
       <c r="AH80" t="n">
-        <v>4250</v>
+        <v>5950</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -8059,7 +8067,7 @@
         </is>
       </c>
       <c r="AH81" t="n">
-        <v>4750</v>
+        <v>6650</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -8134,7 +8142,7 @@
         </is>
       </c>
       <c r="AH82" t="n">
-        <v>4750</v>
+        <v>6650</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -8200,7 +8208,8 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig.png?v=7c1d8ce6bd</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.jpg?v=38f0e2c7db
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_2.jpg?v=2107be3341</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
@@ -8209,7 +8218,7 @@
         </is>
       </c>
       <c r="AH83" t="n">
-        <v>4250</v>
+        <v>5950</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -8275,7 +8284,8 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.png?v=16f48e3b34</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.jpg?v=17dc040af2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_2.jpg?v=aba4a8da4b</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
@@ -8284,7 +8294,7 @@
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>7500</v>
+        <v>5850</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -8350,7 +8360,8 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=03ce24da06</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=fe0eb62b49
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_2.jpg?v=03ce24da06</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -8359,7 +8370,7 @@
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>4250</v>
+        <v>5950</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -8425,7 +8436,8 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.png?v=b98621fc0a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.jpg?v=d138fd63ef
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_2.jpg?v=ca60bf2a09</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
@@ -8434,7 +8446,7 @@
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>4750</v>
+        <v>6650</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -8500,7 +8512,8 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.png?v=b98621fc0a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.jpg?v=851807b7d1
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_2.jpg?v=ca60bf2a09</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
@@ -8509,7 +8522,7 @@
         </is>
       </c>
       <c r="AH87" t="n">
-        <v>9500</v>
+        <v>6650</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -8575,8 +8588,9 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=2476776fae
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=1755bb55b2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_3.jpg?v=db91a4455e</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
@@ -8585,7 +8599,7 @@
         </is>
       </c>
       <c r="AH88" t="n">
-        <v>620</v>
+        <v>870</v>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -8660,7 +8674,7 @@
         </is>
       </c>
       <c r="AH89" t="n">
-        <v>1995</v>
+        <v>2790</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -8736,7 +8750,7 @@
         </is>
       </c>
       <c r="AH90" t="n">
-        <v>3990</v>
+        <v>2790</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -8815,7 +8829,7 @@
         </is>
       </c>
       <c r="AH91" t="n">
-        <v>690</v>
+        <v>970</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -8894,7 +8908,7 @@
         </is>
       </c>
       <c r="AH92" t="n">
-        <v>420</v>
+        <v>590</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -8967,7 +8981,7 @@
         </is>
       </c>
       <c r="AH93" t="n">
-        <v>290</v>
+        <v>410</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -9040,7 +9054,7 @@
         </is>
       </c>
       <c r="AH94" t="n">
-        <v>290</v>
+        <v>410</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -9115,7 +9129,7 @@
         </is>
       </c>
       <c r="AH95" t="n">
-        <v>925</v>
+        <v>2090</v>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
@@ -9190,7 +9204,7 @@
         </is>
       </c>
       <c r="AH96" t="n">
-        <v>2980</v>
+        <v>2090</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -9265,7 +9279,7 @@
         </is>
       </c>
       <c r="AH97" t="n">
-        <v>1425</v>
+        <v>1990</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -9340,7 +9354,7 @@
         </is>
       </c>
       <c r="AH98" t="n">
-        <v>2850</v>
+        <v>1990</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
@@ -9416,7 +9430,7 @@
         </is>
       </c>
       <c r="AH99" t="n">
-        <v>745</v>
+        <v>1040</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
@@ -9491,7 +9505,7 @@
         </is>
       </c>
       <c r="AH100" t="n">
-        <v>1490</v>
+        <v>1040</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
@@ -9566,7 +9580,7 @@
         </is>
       </c>
       <c r="AH101" t="n">
-        <v>1245</v>
+        <v>1740</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
@@ -9632,7 +9646,8 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=08b49883ce
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_2.jpg?v=aa8f5c5cf2</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
@@ -9641,7 +9656,7 @@
         </is>
       </c>
       <c r="AH102" t="n">
-        <v>845</v>
+        <v>1180</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -9716,7 +9731,7 @@
         </is>
       </c>
       <c r="AH103" t="n">
-        <v>945</v>
+        <v>1320</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
@@ -9792,7 +9807,7 @@
         </is>
       </c>
       <c r="AH104" t="n">
-        <v>975</v>
+        <v>1370</v>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
@@ -9867,7 +9882,7 @@
         </is>
       </c>
       <c r="AH105" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
@@ -9942,7 +9957,7 @@
         </is>
       </c>
       <c r="AH106" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
@@ -10018,7 +10033,7 @@
         </is>
       </c>
       <c r="AH107" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
@@ -10093,7 +10108,7 @@
         </is>
       </c>
       <c r="AH108" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
@@ -10170,7 +10185,7 @@
         </is>
       </c>
       <c r="AH109" t="n">
-        <v>245</v>
+        <v>340</v>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
@@ -10242,7 +10257,7 @@
         </is>
       </c>
       <c r="AH110" t="n">
-        <v>935</v>
+        <v>1310</v>
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
@@ -10316,7 +10331,7 @@
         </is>
       </c>
       <c r="AH111" t="n">
-        <v>2850</v>
+        <v>3990</v>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
@@ -10391,7 +10406,7 @@
         </is>
       </c>
       <c r="AH112" t="n">
-        <v>975</v>
+        <v>1370</v>
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
@@ -10466,7 +10481,7 @@
         </is>
       </c>
       <c r="AH113" t="n">
-        <v>3700</v>
+        <v>5180</v>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
@@ -10541,7 +10556,7 @@
         </is>
       </c>
       <c r="AH114" t="n">
-        <v>4450</v>
+        <v>6230</v>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
@@ -10616,7 +10631,7 @@
         </is>
       </c>
       <c r="AH115" t="n">
-        <v>2495</v>
+        <v>3490</v>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4732,8 +4732,8 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.jpg?v=32a4eaa349
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._2.jpg?v=3f30a503c8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025-cyr-s_1.jpg?v=32a4eaa349
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025-cyr-s_2.jpg?v=3f30a503c8</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
@@ -5962,9 +5962,9 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.jpg?v=3e0abf9ec7
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.jpg?v=b12c6dac21
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.jpg?v=bd237a81d2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_1.jpg?v=3e0abf9ec7
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_2.jpg?v=b12c6dac21
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_3.jpg?v=bd237a81d2</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>1010</v>
+        <v>1720</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>2440</v>
+        <v>2890</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>1390</v>
+        <v>1780</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>3420</v>
+        <v>4240</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>690</v>
+        <v>870</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>1040</v>
+        <v>1320</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>690</v>
+        <v>870</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>2020</v>
+        <v>2530</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>1740</v>
+        <v>2000</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>900</v>
+        <v>1130</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>1040</v>
+        <v>1130</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4564,7 +4564,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=a1c5e406d3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=7f59b31f49</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6232,7 +6232,8 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.png?v=e9725022b3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.jpg?v=7eebff5ddc
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=e9725022b3</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -6751,11 +6752,6 @@
       <c r="S64" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_11.jpg?v=b00b729a6f
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_12.jpg?v=3e5bb95f61
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_13.jpg?v=b5e4690bb8
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_14.jpg?v=293affdbb4
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_3.jpg?v=8b53715593
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_4.jpg?v=87672fa5cf
@@ -6763,7 +6759,8 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_6.jpg?v=60c3947305
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_7.jpg?v=6455c2a999
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_8.jpg?v=1c56d278b5
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b</t>
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
@@ -7378,7 +7375,8 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.png?v=637a263fe5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.jpg?v=8e1deb51de
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_2.png?v=637a263fe5</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
@@ -7906,8 +7904,9 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=6562ad9b05
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=de55e47d7c
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_3.jpg?v=f0ac7e97a2</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -8133,7 +8132,8 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=d831bae612
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_2.jpg?v=663e730ff0</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF115"/>
+  <dimension ref="A1:BF104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="3"/>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -5667,99 +5667,6 @@
         </is>
       </c>
       <c r="Q52" t="inlineStr">
-        <is>
-          <t>Полный ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW
-В наличии полный ремкомплект мехатроника для роботизированной коробки передач DSG 7 DQ200 серий 0AM и 0CW. Комплект предназначен для капитального ремонта и восстановления мехатроника с заменой всех ключевых узлов и расходных элементов, подверженных наибольшей нагрузке в процессе эксплуатации.
-В данном комплекте сальники и пыльники заменены на оригинальные детали Volkswagen (производство Германия). Это позволяет устранить одну из самых распространённых проблем DSG7 — утечки по штокам, и значительно повысить ресурс мехатроника после ремонта.
-Состав комплекта
-• Прокладка крышки мехатроника — 0AM325443D
-• Крышка мехатроника — 0AM325219C
-• Фильтр мехатроника — 0AM325433E
-• Прокладки электронного блока управления (электронной платы) — 0AM927769D
-• Усиленная гидравлическая плита — 0AM325066AE
-• Прокладки, сальники и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)
-Совместимость
-Подходит для коробок передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.
-Преимущества
-• Полный набор деталей для комплексного ремонта мехатроника DSG7.
-• Повышенная надёжность за счёт усиленной гидроплиты.
-• Использование оригинальных сальников и пыльников Volkswagen (Германия).
-• Устранение течей по штокам и снижение риска повторных неисправностей.
-• Подходит для профессионального ремонта в автосервисах и специализированных мастерских, также для физических лиц!
-🔩 Артикул: 0cw0am325025.</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные</t>
-        </is>
-      </c>
-      <c r="AH52" t="n">
-        <v>11820</v>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr">
-        <is>
-          <t>0cw0am325025</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>0cw0amdsgdq200</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.
 Совместимость
@@ -5773,79 +5680,79 @@
 🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=d2723138aa
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=77a111eb34
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_3.jpg?v=40c2597cb3</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>Уплотнение электромотора гидроблока мехатроника</t>
         </is>
       </c>
-      <c r="AH53" t="n">
+      <c r="AH52" t="n">
         <v>600</v>
       </c>
-      <c r="AJ53" t="inlineStr">
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK53" t="inlineStr">
+      <c r="AK52" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL53" t="inlineStr">
+      <c r="AL52" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
+      <c r="AM52" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
+      <c r="AN52" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AO52" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
+      <c r="AR52" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS53" t="inlineStr">
+      <c r="AS52" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377
 🔎
@@ -5868,78 +5775,78 @@
 🔩 Артикул: 0cw325025h.</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH54" t="n">
+      <c r="AH53" t="n">
         <v>1130</v>
       </c>
-      <c r="AJ54" t="inlineStr">
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK54" t="inlineStr">
+      <c r="AK53" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL54" t="inlineStr">
+      <c r="AL53" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AM53" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
+      <c r="AN53" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO54" t="inlineStr">
+      <c r="AO53" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR54" t="inlineStr">
+      <c r="AR53" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS54" t="inlineStr">
+      <c r="AS53" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>0сц</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.
 Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.
@@ -5960,79 +5867,79 @@
 🔩 Артикул: 0сц.</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_1.jpg?v=3e0abf9ec7
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_2.jpg?v=b12c6dac21
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_3.jpg?v=bd237a81d2</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH55" t="n">
+      <c r="AH54" t="n">
         <v>1040</v>
       </c>
-      <c r="AJ55" t="inlineStr">
+      <c r="AJ54" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK55" t="inlineStr">
+      <c r="AK54" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL55" t="inlineStr">
+      <c r="AL54" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
+      <c r="AM54" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
+      <c r="AN54" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO55" t="inlineStr">
+      <c r="AO54" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR55" t="inlineStr">
+      <c r="AR54" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS55" t="inlineStr">
+      <c r="AS54" t="inlineStr">
         <is>
           <t>0c</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>122390AK-AF</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект
 Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW
@@ -6045,178 +5952,78 @@
 🔩 Артикул: 122390AK-AF.</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=a2422623a6
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg?v=70e1dc8dfd</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
-      <c r="AH56" t="n">
+      <c r="AH55" t="n">
         <v>690</v>
       </c>
-      <c r="AJ56" t="inlineStr">
+      <c r="AJ55" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK56" t="inlineStr">
+      <c r="AK55" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL56" t="inlineStr">
+      <c r="AL55" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
+      <c r="AM55" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
+      <c r="AN55" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO56" t="inlineStr">
+      <c r="AO55" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR56" t="inlineStr">
+      <c r="AR55" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS56" t="inlineStr">
+      <c r="AS55" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>122390AKAF</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>123014‑AF</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 0AM — оригинал Volkswagen (Германия)
-Оригинальный пыльник штока мехатроника DSG7 DQ200 предназначен для восстановления герметичности узла сцепления коробок передач с кодами 0AM и 0CW. Деталь устанавливается в мехатроник роботизированной трансмиссии DSG 7 с сухим сцеплением и защищает шток толкателя вилки от загрязнений, влаги и утечки масла.
-Использование оригинального пыльника Volkswagen, произведённого в Германии, гарантирует точное соответствие заводским допускам, длительный ресурс и стабильную работу мехатроника после ремонта. В отличие от неоригинальных аналогов, оригинал сохраняет эластичность при высоких температурах и не теряет форму со временем.
-Пыльник является критически важным элементом при ремонте DSG7 DQ200. Его износ часто приводит к попаданию масла в сухую часть сцепления, ошибкам мехатроника, рывкам при трогании и некорректной работе коробки передач. Замена пыльника рекомендуется при любом демонтаже мехатроника, ремонте штока или профилактическом обслуживании.
-Применение и совместимость
-Деталь подходит для автомобилей концерна VAG с коробкой передач DSG7 DQ200 (0AM / 0CW):
-Volkswagen
-Audi
-Skoda
-Seat
-Устанавливается в мехатроник трансмиссий с сухим сцеплением.
-Преимущества оригинальной детали Volkswagen
-Оригинальное производство Volkswagen AG (Германия)
-Точное соответствие заводским размерам
-Надёжная защита штока мехатроника
-Устойчивость к маслу, температуре и износу
-Предотвращает утечку масла и загрязнение сцепления
-Рекомендован для профессионального ремонта DSG
-Когда требуется замена пыльника
-Обнаружена утечка масла из мехатроника
-Ремонт или замена штока сцепления DSG7
-Ошибки по мехатронику DQ200
-Рывки, вибрации, нестабильная работа коробки
-Профилактика при разборке узла
-шток мехатроника dsg7 dq200 шток сцепления dsg 7 шток толкателя вилки dq200 шток мехатроника 0am 0cw пыльник штока мехатроника dq200 ремкомплект мехатроника dsg7 122390 af a-suk-0am-ca b82568 217492-s
-🔩 Артикул: 122390AKAF.</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AKAF_1.png?v=a2422623a6</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>Оригинальный пыльник штока мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH57" t="n">
-        <v>1130</v>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>122390AKAF</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>123014‑AF</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества
 ✅
@@ -6230,78 +6037,78 @@
 Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.jpg?v=7eebff5ddc
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=e9725022b3</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
         </is>
       </c>
-      <c r="AH58" t="n">
+      <c r="AH56" t="n">
         <v>1040</v>
       </c>
-      <c r="AJ58" t="inlineStr">
+      <c r="AJ56" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK58" t="inlineStr">
+      <c r="AK56" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
+      <c r="AL56" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AM56" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
+      <c r="AN56" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO58" t="inlineStr">
+      <c r="AO56" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR58" t="inlineStr">
+      <c r="AR56" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS58" t="inlineStr">
+      <c r="AS56" t="inlineStr">
         <is>
           <t>123014AF</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.
 Описание товара
@@ -6325,78 +6132,78 @@
 🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
         </is>
       </c>
-      <c r="AH59" t="n">
+      <c r="AH57" t="n">
         <v>35340</v>
       </c>
-      <c r="AJ59" t="inlineStr">
+      <c r="AJ57" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK59" t="inlineStr">
+      <c r="AK57" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL59" t="inlineStr">
+      <c r="AL57" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
+      <c r="AM57" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
+      <c r="AN57" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO59" t="inlineStr">
+      <c r="AO57" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR59" t="inlineStr">
+      <c r="AR57" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS59" t="inlineStr">
+      <c r="AS57" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>55565480</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>импульсная звёздочка датчика положения распредвала
 Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.
@@ -6408,77 +6215,77 @@
 Датчик распредвала 55565480 GM</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>Импульсное кольцо распредвала GM 55565480</t>
         </is>
       </c>
-      <c r="AH60" t="n">
+      <c r="AH58" t="n">
         <v>700</v>
       </c>
-      <c r="AJ60" t="inlineStr">
+      <c r="AJ58" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK60" t="inlineStr">
+      <c r="AK58" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL60" t="inlineStr">
+      <c r="AL58" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
+      <c r="AM58" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
+      <c r="AN58" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO60" t="inlineStr">
+      <c r="AO58" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR60" t="inlineStr">
+      <c r="AR58" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS60" t="inlineStr">
+      <c r="AS58" t="inlineStr">
         <is>
           <t>55565480</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>DQ500</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH
 Новые
@@ -6487,7 +6294,7 @@
 Снижает температуру масла</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
@@ -6495,242 +6302,148 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="AH61" t="n">
+      <c r="AH59" t="n">
         <v>2700</v>
       </c>
-      <c r="AJ61" t="inlineStr">
+      <c r="AJ59" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK61" t="inlineStr">
+      <c r="AK59" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL61" t="inlineStr">
+      <c r="AL59" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
+      <c r="AM59" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
+      <c r="AN59" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO61" t="inlineStr">
+      <c r="AO59" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR61" t="inlineStr">
+      <c r="AR59" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS61" t="inlineStr">
+      <c r="AS59" t="inlineStr">
         <is>
           <t>DQ500</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Dq200dsg7</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!
 🔩 Артикул: Dq200dsg7.</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg?v=12b215cccc</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>Уплотнение насоса гидроблока мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH62" t="n">
+      <c r="AH60" t="n">
         <v>690</v>
       </c>
-      <c r="AJ62" t="inlineStr">
+      <c r="AJ60" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK62" t="inlineStr">
+      <c r="AK60" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL62" t="inlineStr">
+      <c r="AL60" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
+      <c r="AM60" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
+      <c r="AN60" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO62" t="inlineStr">
+      <c r="AO60" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR62" t="inlineStr">
+      <c r="AR60" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS62" t="inlineStr">
+      <c r="AS60" t="inlineStr">
         <is>
           <t>Dq200dsg7</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Dq200dsg70am0cw</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Dq500</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Ремкомплект мехатроника DSG 7 DQ200 0AM / 0CW (полный комплект прокладок + оригинальные сальники и пыльники Германия Volkswagen)
-Описание товара
-Полный комплект для ремонта мехатроника роботизированной трансмиссии DSG 7 DQ200 серий 0AM и 0CW. Предназначен для восстановления работоспособности мехатроника с заменой основных узлов и расходных элементов, наиболее подверженных износу и утечкам в процессе эксплуатации.
-В комплекте используются оригинальные сальники и пыльники Volkswagen (производство Германия), которыми заменены стандартные расходные элементы. Это решение позволяет устранить течи по штокам и повысить общую надёжность мехатроника после ремонта.
-Комплектация
-• Прокладка крышки мехатроника — 0AM325443D
-• Крышка мехатроника — 0AM325219C
-• Фильтр мехатроника — 0AM325433E
-• Прокладки и уплотнения для Электронного блока управления (электронная плата) — 0AM927769D
-• Комплект прокладок, сальников и манжета штока — 0AM325091E (оригинал Volkswagen, Германия)
-И так далее как на фото!
-Совместимость
-Применяется на коробках передач DSG 7 DQ200 серий 0AM и 0CW, устанавливаемых на автомобили Volkswagen, Audi, Skoda и SEAT.
-Преимущества
-• Полный набор деталей для комплексного восстановления мехатроника DSG7.
-• Повышенный ресурс за счёт усиленной гидравлической плиты.
-• Оригинальные сальники и пыльники Volkswagen (Германия).
-• Минимизация риска повторных утечек и отказов.
-• Подходит для профессионального и сервисного ремонта, также для физ лиц!
-🔩 Артикул: Dq200dsg70am0cw.</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7</t>
-        </is>
-      </c>
-      <c r="AH63" t="n">
-        <v>6220</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL63" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS63" t="inlineStr">
-        <is>
-          <t>Dq200dsg70am0cw</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Dq500</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Улучшенный отвод тепла
 Уменьшает температуру масла КПП
@@ -6749,7 +6462,7 @@
 📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda
@@ -6763,149 +6476,149 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="AH64" t="n">
+      <c r="AH61" t="n">
         <v>2720</v>
       </c>
-      <c r="AJ64" t="inlineStr">
+      <c r="AJ61" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK64" t="inlineStr">
+      <c r="AK61" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL64" t="inlineStr">
+      <c r="AL61" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
+      <c r="AM61" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
+      <c r="AN61" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO64" t="inlineStr">
+      <c r="AO61" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR64" t="inlineStr">
+      <c r="AR61" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS64" t="inlineStr">
+      <c r="AS61" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>WHT001922</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный
 Новый Отличное качество
 🔩 Артикул: WHT001922.</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH65" t="n">
+      <c r="AH62" t="n">
         <v>690</v>
       </c>
-      <c r="AJ65" t="inlineStr">
+      <c r="AJ62" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK65" t="inlineStr">
+      <c r="AK62" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL65" t="inlineStr">
+      <c r="AL62" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
+      <c r="AM62" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
+      <c r="AN62" t="inlineStr">
         <is>
           <t>Крепёж КПП</t>
         </is>
       </c>
-      <c r="AO65" t="inlineStr">
+      <c r="AO62" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR65" t="inlineStr">
+      <c r="AR62" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS65" t="inlineStr">
+      <c r="AS62" t="inlineStr">
         <is>
           <t>WHT001922</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>filtr-dsg7-dq200</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>🔧 Масляный фильтр мехатроника DSG7 DQ200 (0AM/0CW) — стандартная версия для планового обслуживания и ремонта гидроблока АКПП.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200 (0AM325025 и аналоги).
@@ -6914,458 +6627,458 @@
 🔩 Артикул: filtr-dsg7-dq200.</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_2.png?v=b1ce9f5f30</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH66" t="n">
+      <c r="AH63" t="n">
         <v>690</v>
       </c>
-      <c r="AJ66" t="inlineStr">
+      <c r="AJ63" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK66" t="inlineStr">
+      <c r="AK63" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL66" t="inlineStr">
+      <c r="AL63" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
+      <c r="AM63" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
+      <c r="AN63" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO66" t="inlineStr">
+      <c r="AO63" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR66" t="inlineStr">
+      <c r="AR63" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS66" t="inlineStr">
+      <c r="AS63" t="inlineStr">
         <is>
           <t>filtrdsg7dq200</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>filtr-dsg7-dq500</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>🔧 Масляный фильтр мехатроника DSG7 DQ500 0BH325183B — устанавливается в корпус фильтра (корпус — отдельная позиция, см. также в нашем магазине). ✅ Volkswagen Passat, Golf, Tiguan, T5/T6, Audi A3, Škoda Kodiaq и другие модели с DSG7 DQ500/DQ400E. 📦 Новый, с завода, в наличии, отправка в день заказа. 🔩 Артикул: 0BH325183B.</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq500_1.png?v=5a2f360fb5</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="AH67" t="n">
+      <c r="AH64" t="n">
         <v>900</v>
       </c>
-      <c r="AJ67" t="inlineStr">
+      <c r="AJ64" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK67" t="inlineStr">
+      <c r="AK64" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL67" t="inlineStr">
+      <c r="AL64" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
+      <c r="AM64" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
+      <c r="AN64" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO67" t="inlineStr">
+      <c r="AO64" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR67" t="inlineStr">
+      <c r="AR64" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS67" t="inlineStr">
+      <c r="AS64" t="inlineStr">
         <is>
           <t>filtrdsg7dq500</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=96f21d0cb5
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=be20ada597
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_3.jpg?v=87268821a3</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5</t>
         </is>
       </c>
-      <c r="AH68" t="n">
+      <c r="AH65" t="n">
         <v>1650</v>
       </c>
-      <c r="AJ68" t="inlineStr">
+      <c r="AJ65" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK68" t="inlineStr">
+      <c r="AK65" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL68" t="inlineStr">
+      <c r="AL65" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AM65" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
+      <c r="AN65" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO68" t="inlineStr">
+      <c r="AO65" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR68" t="inlineStr">
+      <c r="AR65" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS68" t="inlineStr">
+      <c r="AS65" t="inlineStr">
         <is>
           <t>filtrsetka0b5orig</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>gidroakkumulyator-orig</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>Восстановленный гидроаккумулятор мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH69" t="n">
+      <c r="AH66" t="n">
         <v>6220</v>
       </c>
-      <c r="AJ69" t="inlineStr">
+      <c r="AJ66" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK69" t="inlineStr">
+      <c r="AK66" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL69" t="inlineStr">
+      <c r="AL66" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
+      <c r="AM66" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
+      <c r="AN66" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO69" t="inlineStr">
+      <c r="AO66" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR69" t="inlineStr">
+      <c r="AR66" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS69" t="inlineStr">
+      <c r="AS66" t="inlineStr">
         <is>
           <t>gidroakkumulyatororig</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2</t>
         </is>
       </c>
-      <c r="AH70" t="n">
+      <c r="AH67" t="n">
         <v>670</v>
       </c>
-      <c r="AJ70" t="inlineStr">
+      <c r="AJ67" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK70" t="inlineStr">
+      <c r="AK67" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL70" t="inlineStr">
+      <c r="AL67" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
+      <c r="AM67" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
+      <c r="AN67" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO70" t="inlineStr">
+      <c r="AO67" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR70" t="inlineStr">
+      <c r="AR67" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS70" t="inlineStr">
+      <c r="AS67" t="inlineStr">
         <is>
           <t>klipsyshtokov2sht</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png?v=207791c0ab
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png?v=33f6b91718</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="AH71" t="n">
+      <c r="AH68" t="n">
         <v>2720</v>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AJ68" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK71" t="inlineStr">
+      <c r="AK68" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL71" t="inlineStr">
+      <c r="AL68" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
+      <c r="AM68" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
+      <c r="AN68" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO71" t="inlineStr">
+      <c r="AO68" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR71" t="inlineStr">
+      <c r="AR68" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS71" t="inlineStr">
+      <c r="AS68" t="inlineStr">
         <is>
           <t>korpusfiltra0bh325159</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>🔧 Крышка (поддон) мехатроника DSG7 DQ200 — герметично закрывает гидроблок, защищает от загрязнений и подтёков масла.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -7373,383 +7086,383 @@
 🔩 Совместима с 0AM325219C.</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.jpg?v=8e1deb51de
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_2.png?v=637a263fe5</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH72" t="n">
+      <c r="AH69" t="n">
         <v>1370</v>
       </c>
-      <c r="AJ72" t="inlineStr">
+      <c r="AJ69" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK72" t="inlineStr">
+      <c r="AK69" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL72" t="inlineStr">
+      <c r="AL69" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
+      <c r="AM69" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
+      <c r="AN69" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO72" t="inlineStr">
+      <c r="AO69" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR72" t="inlineStr">
+      <c r="AR69" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS72" t="inlineStr">
+      <c r="AS69" t="inlineStr">
         <is>
           <t>kryshkamehatronikadq200</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>planka-solenoid-2sht</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>Планки соленоидов мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH73" t="n">
+      <c r="AH70" t="n">
         <v>2020</v>
       </c>
-      <c r="AJ73" t="inlineStr">
+      <c r="AJ70" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK73" t="inlineStr">
+      <c r="AK70" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL73" t="inlineStr">
+      <c r="AL70" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
+      <c r="AM70" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
+      <c r="AN70" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO73" t="inlineStr">
+      <c r="AO70" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR73" t="inlineStr">
+      <c r="AR70" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS73" t="inlineStr">
+      <c r="AS70" t="inlineStr">
         <is>
           <t>plankasolenoid2sht</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>plastina-solenoid-dq200</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>🔧 Пластина (фиксатор) на соленоиды мехатроника DSG7 DQ200, 1 шт.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новая, с завода, отправка в день заказа.</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastina-solenoid-dq200_1.png?v=e86dd4da7d</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
         </is>
       </c>
-      <c r="AH74" t="n">
+      <c r="AH71" t="n">
         <v>340</v>
       </c>
-      <c r="AJ74" t="inlineStr">
+      <c r="AJ71" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK74" t="inlineStr">
+      <c r="AK71" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL74" t="inlineStr">
+      <c r="AL71" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
+      <c r="AM71" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
+      <c r="AN71" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO74" t="inlineStr">
+      <c r="AO71" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR74" t="inlineStr">
+      <c r="AR71" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS74" t="inlineStr">
+      <c r="AS71" t="inlineStr">
         <is>
           <t>plastinasolenoiddq200</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>🔧 Пластины (фиксаторы) на соленоиды мехатроника DSG7 DQ200 — комплект 2 шт на весь мехатроник.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новые, с завода.</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>Пластины на соленоиды мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH75" t="n">
+      <c r="AH72" t="n">
         <v>690</v>
       </c>
-      <c r="AJ75" t="inlineStr">
+      <c r="AJ72" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK75" t="inlineStr">
+      <c r="AK72" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL75" t="inlineStr">
+      <c r="AL72" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
+      <c r="AM72" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
+      <c r="AN72" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO75" t="inlineStr">
+      <c r="AO72" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR75" t="inlineStr">
+      <c r="AR72" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS75" t="inlineStr">
+      <c r="AS72" t="inlineStr">
         <is>
           <t>plastinysolenoiddq2002sht</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>plastiny-solenoid-orig</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>Оригинальные пластины на соленоиды VAG</t>
         </is>
       </c>
-      <c r="AH76" t="n">
+      <c r="AH73" t="n">
         <v>690</v>
       </c>
-      <c r="AJ76" t="inlineStr">
+      <c r="AJ73" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK76" t="inlineStr">
+      <c r="AK73" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL76" t="inlineStr">
+      <c r="AL73" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
+      <c r="AM73" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
+      <c r="AN73" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO76" t="inlineStr">
+      <c r="AO73" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR76" t="inlineStr">
+      <c r="AR73" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS76" t="inlineStr">
+      <c r="AS73" t="inlineStr">
         <is>
           <t>plastinysolenoidorig</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>plita-filtr</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=7c348500b1
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=efa8557d9d
@@ -7757,165 +7470,392 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_4.jpg?v=3f11b4e476</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + фильтр мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH77" t="n">
+      <c r="AH74" t="n">
         <v>5250</v>
       </c>
-      <c r="AJ77" t="inlineStr">
+      <c r="AJ74" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK77" t="inlineStr">
+      <c r="AK74" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL77" t="inlineStr">
+      <c r="AL74" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
+      <c r="AM74" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
+      <c r="AN74" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO77" t="inlineStr">
+      <c r="AO74" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR77" t="inlineStr">
+      <c r="AR74" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS77" t="inlineStr">
+      <c r="AS74" t="inlineStr">
         <is>
           <t>plitafiltr</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>plita-filtr-orig</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>Усиленная плита + улучшенный фильтр мехатроника</t>
         </is>
       </c>
-      <c r="AH78" t="n">
+      <c r="AH75" t="n">
         <v>5250</v>
       </c>
-      <c r="AJ78" t="inlineStr">
+      <c r="AJ75" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK78" t="inlineStr">
+      <c r="AK75" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL78" t="inlineStr">
+      <c r="AL75" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
+      <c r="AM75" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
+      <c r="AN75" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO78" t="inlineStr">
+      <c r="AO75" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR78" t="inlineStr">
+      <c r="AR75" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS78" t="inlineStr">
+      <c r="AS75" t="inlineStr">
         <is>
           <t>plitafiltrorig</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>plita-filtr-pylniki</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=6562ad9b05
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=de55e47d7c
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_3.jpg?v=f0ac7e97a2</t>
         </is>
       </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков</t>
+        </is>
+      </c>
+      <c r="AH76" t="n">
+        <v>5950</v>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN76" t="inlineStr">
+        <is>
+          <t>Система смазки и охлаждения КПП</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr">
+        <is>
+          <t>plitafiltrpylniki</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-sal</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2</t>
+        </is>
+      </c>
+      <c r="AH77" t="n">
+        <v>6650</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr">
+        <is>
+          <t>plitafiltrpylnikisal</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.jpg?v=38f0e2c7db
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_2.jpg?v=2107be3341</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+        </is>
+      </c>
+      <c r="AH78" t="n">
+        <v>5950</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>plitafiltrsalnikiorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>plita-filtr-v2</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.jpg?v=17dc040af2
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_2.jpg?v=aba4a8da4b</t>
+        </is>
+      </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков</t>
+          <t>Усиленная гидроплита + фильтр мехатроника DQ200</t>
         </is>
       </c>
       <c r="AH79" t="n">
-        <v>5950</v>
+        <v>5850</v>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
@@ -7954,7 +7894,7 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>plitafiltrpylniki</t>
+          <t>plitafiltrv2</t>
         </is>
       </c>
     </row>
@@ -7966,7 +7906,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -7976,18 +7916,18 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ пыльника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные пыльники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные пыльники VAG вместо аналогов — для тех, кому важен только оригинал.</t>
+          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.jpg?v=ea76b2dfed
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_2.jpg?v=13840cc30d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=fe0eb62b49
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_2.jpg?v=03ce24da06</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
         </is>
       </c>
       <c r="AH80" t="n">
@@ -8015,7 +7955,7 @@
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>Система смазки и охлаждения КПП</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -8030,7 +7970,7 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>plitafiltrpylnikiorig</t>
+          <t>plitapylnikisalniki</t>
         </is>
       </c>
     </row>
@@ -8042,7 +7982,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -8052,764 +7992,233 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
+          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2</t>
-        </is>
-      </c>
-      <c r="AH81" t="n">
-        <v>6650</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL81" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr">
-        <is>
-          <t>plitafiltrpylnikisal</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + УЛУЧШЕННЫЙ фильтр + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе, только оригинальные расходники. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный вариант линейки — для тех, кому важен только оригинал VAG на самых ответственных узлах.</t>
-        </is>
-      </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=d831bae612
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_2.jpg?v=663e730ff0</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG</t>
-        </is>
-      </c>
-      <c r="AH82" t="n">
-        <v>6650</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS82" t="inlineStr">
-        <is>
-          <t>plitafiltrpylnikisalorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>plita-filtr-salniki-orig</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
-        </is>
-      </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.jpg?v=38f0e2c7db
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_2.jpg?v=2107be3341</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных</t>
-        </is>
-      </c>
-      <c r="AH83" t="n">
-        <v>5950</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL83" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr">
-        <is>
-          <t>plitafiltrsalnikiorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>plita-filtr-v2</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
-        </is>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.jpg?v=17dc040af2
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_2.jpg?v=aba4a8da4b</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200</t>
-        </is>
-      </c>
-      <c r="AH84" t="n">
-        <v>5850</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL84" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>Система смазки и охлаждения КПП</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>plitafiltrv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
-        </is>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=fe0eb62b49
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_2.jpg?v=03ce24da06</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
-        </is>
-      </c>
-      <c r="AH85" t="n">
-        <v>5950</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL85" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>plitapylnikisalniki</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
-        </is>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.jpg?v=d138fd63ef
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_2.jpg?v=ca60bf2a09</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
-        </is>
-      </c>
-      <c r="AH86" t="n">
-        <v>6650</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL86" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr">
-        <is>
-          <t>plitapylnikisalnikiorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 ОРИГИНАЛЬНЫХ (VAG) пыльника + 2 ОРИГИНАЛЬНЫХ (VAG) сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника — оригинальные VAG. ⭐ Оригинальные расходники герметичнее и служат дольше аналогов; комплектом дешевле, чем по отдельности.</t>
-        </is>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.jpg?v=851807b7d1
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_2.jpg?v=ca60bf2a09</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника +</t>
-        </is>
-      </c>
-      <c r="AH87" t="n">
-        <v>6650</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL87" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr">
-        <is>
-          <t>plitapylnikisalnikiorigv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>podshipnik-vilki-6</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
-        </is>
-      </c>
-      <c r="S88" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=2476776fae
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=1755bb55b2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_3.jpg?v=db91a4455e</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
         </is>
       </c>
-      <c r="AH88" t="n">
+      <c r="AH81" t="n">
         <v>870</v>
       </c>
-      <c r="AJ88" t="inlineStr">
+      <c r="AJ81" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK88" t="inlineStr">
+      <c r="AK81" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL88" t="inlineStr">
+      <c r="AL81" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
+      <c r="AM81" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
+      <c r="AN81" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO88" t="inlineStr">
+      <c r="AO81" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR88" t="inlineStr">
+      <c r="AR81" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS88" t="inlineStr">
+      <c r="AS81" t="inlineStr">
         <is>
           <t>podshipnikvilki6</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня</t>
         </is>
       </c>
-      <c r="AH89" t="n">
+      <c r="AH82" t="n">
         <v>2790</v>
       </c>
-      <c r="AJ89" t="inlineStr">
+      <c r="AJ82" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK89" t="inlineStr">
+      <c r="AK82" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL89" t="inlineStr">
+      <c r="AL82" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
+      <c r="AM82" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN89" t="inlineStr">
+      <c r="AN82" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO89" t="inlineStr">
+      <c r="AO82" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR89" t="inlineStr">
+      <c r="AR82" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS89" t="inlineStr">
+      <c r="AS82" t="inlineStr">
         <is>
           <t>porshniusilpylnikikryshki</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня</t>
         </is>
       </c>
-      <c r="AH90" t="n">
+      <c r="AH83" t="n">
         <v>2790</v>
       </c>
-      <c r="AJ90" t="inlineStr">
+      <c r="AJ83" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK90" t="inlineStr">
+      <c r="AK83" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL90" t="inlineStr">
+      <c r="AL83" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
+      <c r="AM83" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
+      <c r="AN83" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO90" t="inlineStr">
+      <c r="AO83" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR90" t="inlineStr">
+      <c r="AR83" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS90" t="inlineStr">
+      <c r="AS83" t="inlineStr">
         <is>
           <t>porshniusilpylnikikryshkiv2</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>🔧 Прокладка крышки (поддона) мехатроника DSG7 DQ200 — герметизирует соединение крышки с корпусом, предотвращает подтёки масла.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -8818,77 +8227,77 @@
 🔩 Артикул: prokladka-kryshki-dq200.</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-kryshki-dq200_1.png?v=be7cbb92a8</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH91" t="n">
+      <c r="AH84" t="n">
         <v>970</v>
       </c>
-      <c r="AJ91" t="inlineStr">
+      <c r="AJ84" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK91" t="inlineStr">
+      <c r="AK84" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL91" t="inlineStr">
+      <c r="AL84" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
+      <c r="AM84" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
+      <c r="AN84" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO91" t="inlineStr">
+      <c r="AO84" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR91" t="inlineStr">
+      <c r="AR84" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS91" t="inlineStr">
+      <c r="AS84" t="inlineStr">
         <is>
           <t>prokladkakryshkidq200</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.
 ✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0am325091F и длинные 101мм 0AM325091E.
@@ -8897,77 +8306,77 @@
 🔩 Артикул: prokladka-vtulki-dq200.</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>2 кольца-прокладки на 1 втулку мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH92" t="n">
+      <c r="AH85" t="n">
         <v>590</v>
       </c>
-      <c r="AJ92" t="inlineStr">
+      <c r="AJ85" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK92" t="inlineStr">
+      <c r="AK85" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL92" t="inlineStr">
+      <c r="AL85" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
+      <c r="AM85" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr">
+      <c r="AN85" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO92" t="inlineStr">
+      <c r="AO85" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR92" t="inlineStr">
+      <c r="AR85" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS92" t="inlineStr">
+      <c r="AS85" t="inlineStr">
         <is>
           <t>prokladkavtulkidq200</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>🔧 Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -8975,72 +8384,72 @@
 🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>Нижняя прокладка-кольцо втулки мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH93" t="n">
+      <c r="AH86" t="n">
         <v>410</v>
       </c>
-      <c r="AJ93" t="inlineStr">
+      <c r="AJ86" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK93" t="inlineStr">
+      <c r="AK86" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL93" t="inlineStr">
+      <c r="AL86" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
+      <c r="AM86" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN93" t="inlineStr">
+      <c r="AN86" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO93" t="inlineStr">
+      <c r="AO86" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR93" t="inlineStr">
+      <c r="AR86" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS93" t="inlineStr">
+      <c r="AS86" t="inlineStr">
         <is>
           <t>prokladkavtulkinizdq200</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>🔧 Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -9048,13 +8457,541 @@
 🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
         </is>
       </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7</t>
+        </is>
+      </c>
+      <c r="AH87" t="n">
+        <v>410</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>prokladkavtulkiverhdq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH88" t="n">
+        <v>1040</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN88" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>salnikshtokaorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig-v2</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="AH89" t="n">
+        <v>1040</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN89" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>salnikshtokaorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>salnik-tolkatelya-alum</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Усиленные алюминиевые сальники толкателя с</t>
+        </is>
+      </c>
+      <c r="AH90" t="n">
+        <v>1740</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN90" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>salniktolkatelyaalum</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=08b49883ce
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_2.jpg?v=aa8f5c5cf2</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="AH91" t="n">
+        <v>1180</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>salnikishtokov2sht</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH92" t="n">
+        <v>1320</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>salnikishtokovorig</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>salniki-tolkatelya-4sht</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Полный комплект сальников толкателей вилок</t>
+        </is>
+      </c>
+      <c r="AH93" t="n">
+        <v>1370</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>salnikitolkatelya4sht</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>salnikprivod-l</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
+        </is>
+      </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7</t>
+          <t>Сальник привода левый DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH94" t="n">
-        <v>410</v>
+        <v>700</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -9093,7 +9030,7 @@
       </c>
       <c r="AS94" t="inlineStr">
         <is>
-          <t>prokladkavtulkiverhdq200</t>
+          <t>salnikprivodl</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9042,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -9115,21 +9052,21 @@
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig_1.png?v=4b4f837537</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH95" t="n">
-        <v>2090</v>
+        <v>700</v>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
@@ -9153,7 +9090,7 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -9168,7 +9105,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>pylnikishtokovorig</t>
+          <t>salnikprivodr</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9117,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>pylniki-shtokov-orig-v2</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -9190,21 +9127,22 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>🔧 Оригинальные (VAG) пыльники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал — плотнее прилегает и дольше служит, чем аналоги.</t>
+          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/pylniki-shtokov-orig-v2_1.png?v=4b4f837537</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Оригинальные пыльники штоков VAG, 2 шт, DQ200 DSG7</t>
+          <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH96" t="n">
-        <v>2090</v>
+        <v>700</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -9228,7 +9166,7 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>Переключение передач</t>
+          <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -9243,7 +9181,7 @@
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>pylnikishtokovorigv2</t>
+          <t>salnikvhod</t>
         </is>
       </c>
     </row>
@@ -9255,7 +9193,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>salnikvihod</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -9265,21 +9203,21 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
+          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig_1.png?v=45a69e38a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
+          <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH97" t="n">
-        <v>1990</v>
+        <v>700</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -9318,7 +9256,7 @@
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>remkomplektshtokovorig</t>
+          <t>salnikvihod</t>
         </is>
       </c>
     </row>
@@ -9330,7 +9268,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -9339,984 +9277,155 @@
         </is>
       </c>
       <c r="Q98" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальный (VAG) ремкомплект на оба штока мехатроника DSG7 DQ200: 2 пыльника + 2 сальника + 2 крышки. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока полностью, оригинал. ⭐ Оригинал VAG вместо аналога — для тех, кто хочет исключить повторный ремонт.</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники</t>
-        </is>
-      </c>
-      <c r="AH98" t="n">
-        <v>1990</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL98" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr">
-        <is>
-          <t>remkomplektshtokovorigv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
-        </is>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
-        </is>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH99" t="n">
-        <v>1040</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL99" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>salnikshtokaorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig-v2</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
-        </is>
-      </c>
-      <c r="AH100" t="n">
-        <v>1040</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL100" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr">
-        <is>
-          <t>salnikshtokaorigv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>salnik-tolkatelya-alum</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Усиленные алюминиевые сальники толкателя с</t>
-        </is>
-      </c>
-      <c r="AH101" t="n">
-        <v>1740</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL101" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr">
-        <is>
-          <t>salniktolkatelyaalum</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=08b49883ce
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_2.jpg?v=aa8f5c5cf2</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
-        </is>
-      </c>
-      <c r="AH102" t="n">
-        <v>1180</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>salnikishtokov2sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-orig</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
-        </is>
-      </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH103" t="n">
-        <v>1320</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>salnikishtokovorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>salniki-tolkatelya-4sht</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
-        </is>
-      </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>Полный комплект сальников толкателей вилок</t>
-        </is>
-      </c>
-      <c r="AH104" t="n">
-        <v>1370</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL104" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>salnikitolkatelya4sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>salnikprivod-l</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
-        </is>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
-        </is>
-      </c>
-      <c r="X105" t="inlineStr">
-        <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH105" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL105" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS105" t="inlineStr">
-        <is>
-          <t>salnikprivodl</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>salnikprivod-r</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
-        </is>
-      </c>
-      <c r="X106" t="inlineStr">
-        <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH106" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL106" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>salnikprivodr</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>Сальник входного вала DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH107" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL107" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>salnikvhod</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
-        </is>
-      </c>
-      <c r="X108" t="inlineStr">
-        <is>
-          <t>Сальник выходного вала DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH108" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL108" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS108" t="inlineStr">
-        <is>
-          <t>salnikvihod</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>separatornaya-plastina-dq200</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q109" t="inlineStr">
         <is>
           <t>🔧 Сепараторная пластина мехатроника DSG7 DQ200 — устанавливается под гидроплиту, разделяет каналы.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новая, с завода, отправка в день заказа.</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastina-dq200_1.png?v=7ff85d1a3c</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH109" t="n">
+      <c r="AH98" t="n">
         <v>340</v>
       </c>
-      <c r="AJ109" t="inlineStr">
+      <c r="AJ98" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK109" t="inlineStr">
+      <c r="AK98" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL109" t="inlineStr">
+      <c r="AL98" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
+      <c r="AM98" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN109" t="inlineStr">
+      <c r="AN98" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO109" t="inlineStr">
+      <c r="AO98" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR109" t="inlineStr">
+      <c r="AR98" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS109" t="inlineStr">
+      <c r="AS98" t="inlineStr">
         <is>
           <t>separatornayaplastinadq200</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>🔧 Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новые, с завода.</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>Сепараторная пластина + пластины на соленоиды</t>
         </is>
       </c>
-      <c r="AH110" t="n">
+      <c r="AH99" t="n">
         <v>1310</v>
       </c>
-      <c r="AJ110" t="inlineStr">
+      <c r="AJ99" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK110" t="inlineStr">
+      <c r="AK99" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL110" t="inlineStr">
+      <c r="AL99" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
+      <c r="AM99" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN110" t="inlineStr">
+      <c r="AN99" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO110" t="inlineStr">
+      <c r="AO99" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR110" t="inlineStr">
+      <c r="AR99" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS110" t="inlineStr">
+      <c r="AS99" t="inlineStr">
         <is>
           <t>separatornayaplastinysolenoiddq200</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q111" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>🔧 Восстановленный соленоид сцепления K1/K2 ("большой", multiplexer) — для DSG6 02E DQ250, DSG7 0BH/0BT DQ500, DL501 0B5.
 ✅ Volkswagen, Audi, Škoda, Seat с коробками 02E/DQ250, DQ500, 0B5/DL501.
@@ -10325,350 +9434,350 @@
 🔩 Артикул: solenoid-02e-0b5-bolshoy.</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500</t>
         </is>
       </c>
-      <c r="AH111" t="n">
+      <c r="AH100" t="n">
         <v>3990</v>
       </c>
-      <c r="AJ111" t="inlineStr">
+      <c r="AJ100" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK111" t="inlineStr">
+      <c r="AK100" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL111" t="inlineStr">
+      <c r="AL100" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
+      <c r="AM100" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN111" t="inlineStr">
+      <c r="AN100" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO111" t="inlineStr">
+      <c r="AO100" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR111" t="inlineStr">
+      <c r="AR100" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS111" t="inlineStr">
+      <c r="AS100" t="inlineStr">
         <is>
           <t>solenoid02e0b5bolshoy</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q112" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr">
+      <c r="S101" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH112" t="n">
+      <c r="AH101" t="n">
         <v>1370</v>
       </c>
-      <c r="AJ112" t="inlineStr">
+      <c r="AJ101" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK112" t="inlineStr">
+      <c r="AK101" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL112" t="inlineStr">
+      <c r="AL101" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
+      <c r="AM101" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN112" t="inlineStr">
+      <c r="AN101" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO112" t="inlineStr">
+      <c r="AO101" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR112" t="inlineStr">
+      <c r="AR101" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS112" t="inlineStr">
+      <c r="AS101" t="inlineStr">
         <is>
           <t>stalnayavstavkaplity</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q113" t="inlineStr">
+      <c r="Q102" t="inlineStr">
         <is>
           <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr">
+      <c r="S102" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>Комплект 4 толкателей вилок + 4 сальника DSG7</t>
         </is>
       </c>
-      <c r="AH113" t="n">
+      <c r="AH102" t="n">
         <v>5180</v>
       </c>
-      <c r="AJ113" t="inlineStr">
+      <c r="AJ102" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK113" t="inlineStr">
+      <c r="AK102" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL113" t="inlineStr">
+      <c r="AL102" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM113" t="inlineStr">
+      <c r="AM102" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN113" t="inlineStr">
+      <c r="AN102" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO113" t="inlineStr">
+      <c r="AO102" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR113" t="inlineStr">
+      <c r="AR102" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS113" t="inlineStr">
+      <c r="AS102" t="inlineStr">
         <is>
           <t>tolkateli4salniki4</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr">
+      <c r="P103" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q114" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>Толкатели вилок + сальники + усиленные</t>
         </is>
       </c>
-      <c r="AH114" t="n">
+      <c r="AH103" t="n">
         <v>6230</v>
       </c>
-      <c r="AJ114" t="inlineStr">
+      <c r="AJ103" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK114" t="inlineStr">
+      <c r="AK103" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL114" t="inlineStr">
+      <c r="AL103" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM114" t="inlineStr">
+      <c r="AM103" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN114" t="inlineStr">
+      <c r="AN103" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO114" t="inlineStr">
+      <c r="AO103" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR114" t="inlineStr">
+      <c r="AR103" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS114" t="inlineStr">
+      <c r="AS103" t="inlineStr">
         <is>
           <t>tolkatelisalnikialumkomplekt</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
+    <row r="104">
+      <c r="A104" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q115" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH115" t="n">
+      <c r="AH104" t="n">
         <v>3490</v>
       </c>
-      <c r="AJ115" t="inlineStr">
+      <c r="AJ104" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK115" t="inlineStr">
+      <c r="AK104" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL115" t="inlineStr">
+      <c r="AL104" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM115" t="inlineStr">
+      <c r="AM104" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN115" t="inlineStr">
+      <c r="AN104" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO115" t="inlineStr">
+      <c r="AO104" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR115" t="inlineStr">
+      <c r="AR104" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS115" t="inlineStr">
+      <c r="AS104" t="inlineStr">
         <is>
           <t>vtulkishtokov2sht</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>340</v>
+        <v>690</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>690</v>
+        <v>1040</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>690</v>
+        <v>1180</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="AH81" t="n">
-        <v>870</v>
+        <v>1180</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="AH94" t="n">
-        <v>700</v>
+        <v>1040</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="AH95" t="n">
-        <v>700</v>
+        <v>1040</v>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="AH96" t="n">
-        <v>700</v>
+        <v>1040</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="AH97" t="n">
-        <v>700</v>
+        <v>1040</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="AH98" t="n">
-        <v>340</v>
+        <v>690</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="AH99" t="n">
-        <v>1310</v>
+        <v>1600</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="AH101" t="n">
-        <v>1370</v>
+        <v>1950</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>6220</v>
+        <v>4890</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>620</v>
+        <v>670</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>4120</v>
+        <v>4090</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1320</v>
+        <v>1300</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>70800</v>
+        <v>71310</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2720</v>
+        <v>2700</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>6640</v>
+        <v>6550</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>2890</v>
+        <v>3050</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>1780</v>
+        <v>1650</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>1390</v>
+        <v>1300</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>47280</v>
+        <v>47310</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>2440</v>
+        <v>2350</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>5590</v>
+        <v>5500</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>5590</v>
+        <v>5500</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>9020</v>
+        <v>9000</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>2020</v>
+        <v>1990</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>2720</v>
+        <v>2700</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>41280</v>
+        <v>41310</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>77280</v>
+        <v>77310</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>4240</v>
+        <v>4450</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>2720</v>
+        <v>2700</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>1390</v>
+        <v>1300</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>2020</v>
+        <v>1990</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>6220</v>
+        <v>6200</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>6290</v>
+        <v>6200</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>870</v>
+        <v>940</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>1320</v>
+        <v>1300</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>3140</v>
+        <v>3050</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>47090</v>
+        <v>47310</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>3140</v>
+        <v>3050</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>870</v>
+        <v>940</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>4890</v>
+        <v>4800</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>2530</v>
+        <v>2700</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>2020</v>
+        <v>1990</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>1720</v>
+        <v>1650</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>2000</v>
+        <v>1990</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>600</v>
+        <v>670</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>1130</v>
+        <v>1300</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="AH56" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>35340</v>
+        <v>35310</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>700</v>
+        <v>670</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>2720</v>
+        <v>2700</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>900</v>
+        <v>940</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>6220</v>
+        <v>6200</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         </is>
       </c>
       <c r="AH68" t="n">
-        <v>2720</v>
+        <v>2700</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>1370</v>
+        <v>1300</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>2020</v>
+        <v>1990</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>1180</v>
+        <v>1300</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>5250</v>
+        <v>5500</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>5250</v>
+        <v>5500</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>5950</v>
+        <v>6200</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>6650</v>
+        <v>6900</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>5950</v>
+        <v>6200</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="AH80" t="n">
-        <v>5950</v>
+        <v>6200</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="AH81" t="n">
-        <v>1180</v>
+        <v>1300</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="AH82" t="n">
-        <v>2790</v>
+        <v>2700</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="AH83" t="n">
-        <v>2790</v>
+        <v>2700</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>970</v>
+        <v>940</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>590</v>
+        <v>670</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         </is>
       </c>
       <c r="AH87" t="n">
-        <v>410</v>
+        <v>320</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="AH88" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         </is>
       </c>
       <c r="AH89" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         </is>
       </c>
       <c r="AH90" t="n">
-        <v>1740</v>
+        <v>1650</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="AH91" t="n">
-        <v>1180</v>
+        <v>1300</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="AH92" t="n">
-        <v>1320</v>
+        <v>1300</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="AH93" t="n">
-        <v>1370</v>
+        <v>1300</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="AH94" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="AH95" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="AH96" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="AH97" t="n">
-        <v>1040</v>
+        <v>940</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="AH98" t="n">
-        <v>690</v>
+        <v>670</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="AH99" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="AH100" t="n">
-        <v>3990</v>
+        <v>4090</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="AH101" t="n">
-        <v>1950</v>
+        <v>1990</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="AH102" t="n">
-        <v>5180</v>
+        <v>5150</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="AH103" t="n">
-        <v>6230</v>
+        <v>6200</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         </is>
       </c>
       <c r="AH104" t="n">
-        <v>3490</v>
+        <v>3400</v>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>47310</v>
+        <v>44910</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>77310</v>
+        <v>71310</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -1816,7 +1816,7 @@
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>4090</v>
+        <v>2350</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>2700</v>
+        <v>1850</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>5500</v>
+        <v>3850</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>5500</v>
+        <v>3850</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         </is>
       </c>
       <c r="AH59" t="n">
-        <v>2700</v>
+        <v>2250</v>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>2700</v>
+        <v>1850</v>
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>940</v>
+        <v>450</v>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
@@ -7019,7 +7019,7 @@
         </is>
       </c>
       <c r="AH68" t="n">
-        <v>2700</v>
+        <v>1850</v>
       </c>
       <c r="AJ68" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>71310</v>
+        <v>68500</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>6550</v>
+        <v>4850</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>3050</v>
+        <v>2350</v>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>1650</v>
+        <v>1350</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
@@ -2818,7 +2818,7 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>6900</v>
+        <v>4850</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>44910</v>
+        <v>42500</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>2350</v>
+        <v>1850</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
         </is>
       </c>
       <c r="AH21" t="n">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
+          <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
         </is>
       </c>
       <c r="AH22" t="n">
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>9000</v>
+        <v>6350</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>1990</v>
+        <v>1350</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>2700</v>
+        <v>1850</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>41310</v>
+        <v>36500</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>71310</v>
+        <v>68500</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>4450</v>
+        <v>3350</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>2700</v>
+        <v>1850</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>1990</v>
+        <v>1350</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
@@ -4180,7 +4180,7 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>6200</v>
+        <v>4350</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4256,7 +4256,7 @@
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>6200</v>
+        <v>4350</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -4336,7 +4336,7 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>3050</v>
+        <v>2350</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>47310</v>
+        <v>42500</v>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>3050</v>
+        <v>2350</v>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>4800</v>
+        <v>3350</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>2700</v>
+        <v>1850</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>6200</v>
+        <v>4350</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>1990</v>
+        <v>1350</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>
@@ -5363,7 +5363,7 @@
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>6200</v>
+        <v>4350</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>1650</v>
+        <v>1350</v>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>1990</v>
+        <v>1350</v>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>670</v>
+        <v>950</v>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="AH56" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>35310</v>
+        <v>32500</v>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>670</v>
+        <v>950</v>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -6639,7 +6639,7 @@
         </is>
       </c>
       <c r="AH63" t="n">
-        <v>670</v>
+        <v>950</v>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>1650</v>
+        <v>1350</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>6200</v>
+        <v>4350</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
@@ -6943,7 +6943,7 @@
         </is>
       </c>
       <c r="AH67" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>1990</v>
+        <v>1350</v>
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>5500</v>
+        <v>5150</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>5500</v>
+        <v>3850</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>6200</v>
+        <v>4350</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>6900</v>
+        <v>4850</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>6200</v>
+        <v>4350</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="AH80" t="n">
-        <v>6200</v>
+        <v>4350</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         </is>
       </c>
       <c r="AH81" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         </is>
       </c>
       <c r="AH82" t="n">
-        <v>2700</v>
+        <v>1850</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -8159,7 +8159,7 @@
         </is>
       </c>
       <c r="AH83" t="n">
-        <v>2700</v>
+        <v>1850</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="AH88" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         </is>
       </c>
       <c r="AH89" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
@@ -8689,7 +8689,7 @@
         </is>
       </c>
       <c r="AH90" t="n">
-        <v>1650</v>
+        <v>1350</v>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         </is>
       </c>
       <c r="AH91" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
@@ -8840,7 +8840,7 @@
         </is>
       </c>
       <c r="AH92" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="AH93" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="AH94" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="AH95" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="AH96" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         </is>
       </c>
       <c r="AH97" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="AH98" t="n">
-        <v>670</v>
+        <v>450</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         </is>
       </c>
       <c r="AH101" t="n">
-        <v>1990</v>
+        <v>1350</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="AH102" t="n">
-        <v>5150</v>
+        <v>3850</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         </is>
       </c>
       <c r="AH103" t="n">
-        <v>6200</v>
+        <v>4350</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         </is>
       </c>
       <c r="AH104" t="n">
-        <v>3400</v>
+        <v>2350</v>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>3350</v>
+        <v>2350</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -4152,6 +4152,9 @@
         <is>
           <t>0am325025m</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>4573121040</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>1850</v>
+        <v>1350</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>2850</v>
+        <v>2350</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>1850</v>
+        <v>1350</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -1877,7 +1877,9 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Масляный фильтр DQ250 DSG6 02E - отличное качество
+          <t>⚙️ Масляный фильтр мехатроника DSG6 DQ250 02E305051C — новый, отличное качество.
+✅ Устанавливается в коробки DSG6 02E (DQ250) на VW, Audi, Skoda, Seat.
+🛠 Рекомендуется менять при каждой замене масла в коробке DSG6.
 🔩 Артикул: 02E305051C.</t>
         </is>
       </c>
@@ -3314,7 +3316,7 @@
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
@@ -4244,7 +4246,9 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>Новый соленоид DQ200 0am 0cw шифт - отличное качество BOSCH
+          <t>⚙️ Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N — новый соленоид Bosch, отличное качество.
+✅ Подходит для мехатроников 0AM и 0CW коробки DSG7 DQ200.
+🛠 Применяется при ремонте мехатроника: рывки, ошибки и сбои переключения передач.
 🔩 Артикул: 0am325025n.</t>
         </is>
       </c>
@@ -4493,7 +4497,7 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
@@ -4728,9 +4732,10 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Новое
-Отличное качество
-Всегда в наличии</t>
+          <t>⚙️ Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C — новое, отличное качество.
+✅ Подходит для мехатроников 0AM и 0CW коробки DSG7 DQ200.
+🛠 Применяется при ремонте мехатроника и замене гидроаккумулятора: устраняет утечку и падение давления.
+🔩 Артикул: 0am325025С.</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -5286,7 +5291,7 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="AI47" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4165,10 +4165,10 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq300 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.
-Пoлный кoмплeкт прокладки dsg 7 dq200 0am как на фото
-Пoлный кoмплeкт для ремoнтa мexaтpoникa DSG 7 DQ200 0АМ 0СW Ремкомплeкт мeхaтpоника DSG 7 DQ200 всeгдa в наличии
-Kак нa фoтo: фильтp мeхатpoника, пыльники штокoв, ceпaратoрнaя пластинa, пpоклaдкa поддона и вcе дpугие необxoдимыe прoкладки меxaтpoникa
+          <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq200 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.
+Полный комплект прокладки dsg 7 dq200 0am как на фото
+Полный комплект для ремонта мехатроника DSG 7 DQ200 0AM 0CW Ремкомплект мехатроника DSG 7 DQ200 всегда в наличии
+Как на фото: фильтр мехатроника, пыльники штоков, сепараторная пластина, прокладка поддона и все другие необходимые прокладки мехатроника
 🔩 Артикул: 0am325025m.</t>
         </is>
       </c>
@@ -4984,9 +4984,9 @@
 👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7
 Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw
 🔩 Подходит для СТО и самостоятельного ремонта.
-Всегда в наличии усилeннaя гидрoплита мexaтpoника DSG7 DQ200 0АM 325066 0CW
-Устанoвкa дaннoй плиты ДСГ7 рeшаeт проблeму c давлeниeм в мехатpоникe 0am325025 (oшибки р17bf и т.д.).
-Уcиление cтeнки увеличиваeт pеcуpс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).
+Всегда в наличии усиленная гидроплита мехатроника DSG7 DQ200 0AM325066 0CW
+Установка данной плиты ДСГ7 решает проблему c давлением в мехатронике 0am325025 (ошибки P17BF и т.д.).
+Усиление стенки увеличивает ресурс мехатроника dq200 (оригинальная плита с тонкой стенкой часто лопается).
 Сотрудничаем с заводом несколько лет
 Отличное качество гидроплиты dq200
 Наша плита dsg 7 не лопается и держит давление!

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2283,15 +2283,15 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Заглушка мехатроника DSG7 DQ200 0AM 0CW Транспортная
-Новая
-Отличное качество
+          <t>⚙️ Транспортная заглушка мехатроника DSG7 DQ200 0AM325120A (0AM, 0CW) — новая, отличное качество.
+✅ Закрывает отверстие мехатроника при снятии, хранении и перевозке: защищает от грязи и влаги.
+🛠 Пригодится при ремонте DSG7 и отправке блока.
 🔩 Артикул: 0AM325120A.</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_0.jpg?v=7094a0c934</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.jpg?v=53131c62ab</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -6304,8 +6304,8 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4324,9 +4324,9 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DQ200 DSG7 0AM 0CW
-Новая
-Отличное качество
+          <t>⚙️ Крышка штока мехатроника DSG7 DQ200 0AM325025Q (0AM, 0CW) — новая, отличное качество.
+✅ Подходит для мехатроников коробки DSG7 DQ200.
+🛠 Применяется при ремонте мехатроника и замене штоков, сальников и пыльников.
 🔩 Артикул: 0am325025q.</t>
         </is>
       </c>
@@ -6304,8 +6304,8 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>3350</v>
+        <v>3850</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>3850</v>
+        <v>4350</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -1737,7 +1737,7 @@
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
@@ -6304,8 +6304,8 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="AH67" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>950</v>
+        <v>1350</v>
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         </is>
       </c>
       <c r="AH71" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="AH98" t="n">
-        <v>450</v>
+        <v>950</v>
       </c>
       <c r="AJ98" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6304,8 +6304,8 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>4850</v>
+        <v>5350</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>4850</v>
+        <v>5850</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>6350</v>
+        <v>7850</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>3850</v>
+        <v>4850</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>940</v>
+        <v>950</v>
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>5150</v>
+        <v>5350</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>4350</v>
+        <v>5350</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>4350</v>
+        <v>5350</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>4850</v>
+        <v>5350</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>4350</v>
+        <v>5350</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         </is>
       </c>
       <c r="AH80" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="AH82" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="AH83" t="n">
-        <v>1850</v>
+        <v>2350</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         </is>
       </c>
       <c r="AH87" t="n">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="AH101" t="n">
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         </is>
       </c>
       <c r="AH102" t="n">
-        <v>3850</v>
+        <v>4350</v>
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         </is>
       </c>
       <c r="AH103" t="n">
-        <v>4350</v>
+        <v>4850</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="AH104" t="n">
-        <v>2350</v>
+        <v>2850</v>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6304,8 +6304,8 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -8398,7 +8398,7 @@
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         </is>
       </c>
       <c r="AH87" t="n">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
@@ -9374,7 +9374,7 @@
         </is>
       </c>
       <c r="AH99" t="n">
-        <v>1650</v>
+        <v>1850</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="AH100" t="n">
-        <v>4090</v>
+        <v>4350</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6304,8 +6304,8 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=6e4db825ca</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -8386,15 +8386,22 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>🔧 Нижняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.
-✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
+          <t>🔧 Черное кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на нижнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.
+✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.
+✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
+💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).
 📦 Новое, в наличии, отправка в день заказа.
 🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
         </is>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-niz-dq200_1.png?v=c467de34e5</t>
+        </is>
+      </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Нижняя прокладка-кольцо втулки мехатроника DSG7</t>
+          <t>Черное кольцо-прокладка втулки мехатроника DSG7</t>
         </is>
       </c>
       <c r="AH86" t="n">
@@ -8459,15 +8466,22 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>🔧 Верхняя прокладка-кольцо втулки штока мехатроника DSG7 DQ200 — уплотняет посадку втулки, предотвращает потерю давления.
-✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
+          <t>🔧 Зеленое кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на верхнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.
+✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.
+✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
+💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).
 📦 Новое, в наличии, отправка в день заказа.
 🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
         </is>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-verh-dq200_1.png?v=9ac6f4aac3</t>
+        </is>
+      </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Верхняя прокладка-кольцо втулки мехатроника DSG7</t>
+          <t>Зеленое кольцо-прокладка втулки мехатроника DSG7</t>
         </is>
       </c>
       <c r="AH87" t="n">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -8308,7 +8308,7 @@
       <c r="Q85" t="inlineStr">
         <is>
           <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.
-✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0am325091F и длинные 101мм 0AM325091E.
+✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0am325091F и длинные 101мм 0AM325091E.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
 📦 Новые, в наличии, отправка в день заказа.
 🔩 Артикул: prokladka-vtulki-dq200.</t>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=6e4db825ca</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=8312c47b41</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -8387,7 +8387,7 @@
       <c r="Q86" t="inlineStr">
         <is>
           <t>🔧 Черное кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на нижнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.
-✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.
+✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
 💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).
 📦 Новое, в наличии, отправка в день заказа.
@@ -8396,7 +8396,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-niz-dq200_1.png?v=c467de34e5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-niz-dq200_1.png?v=b00fa3937b</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
@@ -8467,7 +8467,7 @@
       <c r="Q87" t="inlineStr">
         <is>
           <t>🔧 Зеленое кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на верхнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.
-✅ Подходит на все виды штоков и гильз DSG7 DQ200 (гильзы одинаковые): короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.
+✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
 💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).
 📦 Новое, в наличии, отправка в день заказа.
@@ -8476,7 +8476,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-verh-dq200_1.png?v=9ac6f4aac3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-verh-dq200_1.png?v=28c553abfe</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2136,7 +2136,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=65c46f9b97</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=94573cf68b</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -8307,8 +8307,8 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (верхняя + нижняя) — уплотняют посадку втулки, предотвращают потерю давления.
-✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0am325091F и длинные 101мм 0AM325091E.
+          <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (зеленое + черное) — уплотняют посадку втулки, предотвращают потерю давления.
+✅ Подходит на все гильзы (втулки) штоков.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
 📦 Новые, в наличии, отправка в день заказа.
 🔩 Артикул: prokladka-vtulki-dq200.</t>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=8312c47b41</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=e3f97523c1</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -8386,8 +8386,8 @@
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>🔧 Черное кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на нижнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.
-✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.
+          <t>🔧 Черное кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Уплотняет посадку втулки, предотвращает потерю давления.
+✅ Подходит на все гильзы (втулки) штоков.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
 💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).
 📦 Новое, в наличии, отправка в день заказа.
@@ -8396,7 +8396,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-niz-dq200_1.png?v=b00fa3937b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-niz-dq200_1.png?v=6c730c6907</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
@@ -8466,8 +8466,8 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>🔧 Зеленое кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Ставится на верхнюю часть втулки — уплотняет посадку втулки, предотвращает потерю давления.
-✅ Подходит на все гильзы (втулки) штоков DSG7 DQ200: короткие 99мм 0AM325091F и длинные 101мм 0AM325091E.
+          <t>🔧 Зеленое кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Уплотняет посадку втулки, предотвращает потерю давления.
+✅ Подходит на все гильзы (втулки) штоков.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
 💡 Нужны оба кольца на одну втулку? Есть комплект: зеленое + черное кольцо (артикул prokladka-vtulki-dq200).
 📦 Новое, в наличии, отправка в день заказа.
@@ -8476,7 +8476,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-verh-dq200_1.png?v=28c553abfe</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-verh-dq200_1.png?v=f7366cb6a0</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -7324,6 +7324,11 @@
 📦 Новые, с завода.</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-dq200-2sht_1.png?v=98c47f4555</t>
+        </is>
+      </c>
       <c r="X72" t="inlineStr">
         <is>
           <t>Пластины на соленоиды мехатроника DSG7 DQ200</t>
@@ -9380,6 +9385,11 @@
           <t>🔧 Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новые, с завода.</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastiny-solenoid-dq200_1.png?v=6b8ccfb635</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4499,6 +4499,11 @@
       <c r="AH38" t="n">
         <v>2850</v>
       </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
       <c r="AJ38" t="inlineStr">
         <is>
           <t>Запчасти</t>
@@ -4672,6 +4677,11 @@
       </c>
       <c r="AH40" t="n">
         <v>2350</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_video.mp4?v=4573c3be6d</t>
+        </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
@@ -9398,7 +9408,7 @@
         </is>
       </c>
       <c r="AH99" t="n">
-        <v>1850</v>
+        <v>1350</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -3456,7 +3456,8 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах!
+          <t>🔄 Цена по обмену на ваш старый мехатроник (без платы): 32 500 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
+Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах!
 Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.
 БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА
 Мехатроник DSG7 DQ200 (маркировки 0AM / 0CW) — гидравлический блок управления 7-ступенчатой роботизированной коробки передач с «сухими» сцеплениями.
@@ -3564,7 +3565,8 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ.
+          <t>🔄 Цена по обмену на ваш старый мехатроник (с платой): 62 500 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
+КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ.
 Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)
 В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно -
 Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200
@@ -4563,7 +4565,8 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).
+          <t>🔄 Цена по обмену на ваш старый мехатроник (без платы): 38 500 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
+Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).
 Новые соленоиды Bosch
 Новый гидроаккумулятор
 Новые ремкомплект и прокладки dq200

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>4850</v>
+        <v>5350</v>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
@@ -6317,8 +6317,8 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
@@ -7502,7 +7502,7 @@
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>5350</v>
+        <v>5850</v>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
@@ -7577,7 +7577,7 @@
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>5350</v>
+        <v>5850</v>
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>5350</v>
+        <v>6350</v>
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>5350</v>
+        <v>6850</v>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>5350</v>
+        <v>6350</v>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         </is>
       </c>
       <c r="AH80" t="n">
-        <v>4850</v>
+        <v>6350</v>
       </c>
       <c r="AJ80" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6317,8 +6317,8 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -786,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF104"/>
+  <dimension ref="A1:BF106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="3"/>
@@ -2951,15 +2951,95 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>0AM927769F</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Электронная плата мехатроника DSG7 DQ200 0AM927769F Volkswagen Audi Skoda Seat электронный блок управления мехатроника АКПП DSG 7
+Описание:
+Электронная плата мехатроника DSG7 DQ200 0AM927769F для автомобилей концерна VAG. Используется для ремонта мехатроника роботизированной коробки передач DSG 7. Подходит для Volkswagen, Audi, Skoda и Seat с трансмиссией DQ200. Решение для восстановления работоспособности блока управления коробкой передач при неисправностях электронного характера в мехатрониках dq200, ошибках переключения передач, аварийном режиме КПП и сбоях электроники.
+Плата мехатроника DSG7 изготовлена с соблюдением требований к надежности электронных компонентов и предназначена для профессионального ремонта трансмиссий DSG. Перед отправкой рекомендуется сверить OEM номер детали.
+OEM: подходит только если на родной плате такой номер 0AM927769F 0AM 927 769 F
+Применяемость: Volkswagen Golf, Passat, Jetta, Caddy, Touran, Tiguan Audi A1, A3 Skoda Octavia, Superb, Rapid, Yeti Seat Leon и другие модели с коробкой DSG7 DQ200 и платой ИМЕННО 0AM927769F</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_1.png?v=866128ed82</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Электронная плата мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>42500</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>0AM927769F</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>0AM927769N</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Прокладка платы DSG7 DQ200 0AM 0CW
 Набор как на фото
@@ -2968,77 +3048,77 @@
 🔩 Артикул: 0AM927769N.</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.jpg?v=fbdb72784c</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Прокладки электронной платы мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH20" t="n">
+      <c r="AH21" t="n">
         <v>1850</v>
       </c>
-      <c r="AJ20" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK20" t="inlineStr">
+      <c r="AK21" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL20" t="inlineStr">
+      <c r="AL21" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AM21" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
+      <c r="AN21" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO20" t="inlineStr">
+      <c r="AO21" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR20" t="inlineStr">
+      <c r="AR21" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS20" t="inlineStr">
+      <c r="AS21" t="inlineStr">
         <is>
           <t>0AM927769N</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>0BH325183</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра DQ500 DSG7 0BH325183B
 🔍 Алюминиевый корпус масляного фильтра трансмиссии DSG7 (тип DQ500) для автомобилей концерна VAG. Прочная альтернатива пластиковому корпусу, рассчитанная на высокие нагрузки и длительный срок службы. Используется в узле фильтрации масла коробок передач 0BH, 0BT и аналогичных модификаций.
@@ -3057,78 +3137,78 @@
 🛒 Добавьте в корзину и оформите заказ — надёжная деталь для вашей DSG7 будет уже в пути!</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_1.png?v=c5312dc0b8
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183_2.png?v=92f41095e4</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="AH21" t="n">
+      <c r="AH22" t="n">
         <v>3850</v>
       </c>
-      <c r="AJ21" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK21" t="inlineStr">
+      <c r="AK22" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL21" t="inlineStr">
+      <c r="AL22" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
+      <c r="AM22" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
+      <c r="AN22" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO21" t="inlineStr">
+      <c r="AO22" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR21" t="inlineStr">
+      <c r="AR22" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS21" t="inlineStr">
+      <c r="AS22" t="inlineStr">
         <is>
           <t>0BH325183</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>0BH325183 B</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Корпус фильтра DQ500 DSG7 0BH325183B (красный)
 🔍 Усиленный алюминиевый корпус фильтра трансмиссии DSG7 (тип DQ500) в анодированном красном исполнении. Предназначен для установки в узел фильтрации масла коробок передач автомобилей концерна VAG. Обеспечивает надёжную фиксацию и герметичность фильтрующего элемента, эффективно заменяет стандартный пластиковый корпус, увеличивая ресурс узла за счёт высокой прочности и улучшенного теплоотвода. Красное анодированное покрытие не только придаёт эффектный внешний вид, но и дополнительно защищает металл от коррозии.
@@ -3146,156 +3226,156 @@
 🚀 Закажите сейчас — максимально оперативная отправка!</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0BH325183.B_2.png?v=ed43613b04</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Корпус фильтра ребристый мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="AH22" t="n">
+      <c r="AH23" t="n">
         <v>3850</v>
       </c>
-      <c r="AJ22" t="inlineStr">
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK22" t="inlineStr">
+      <c r="AK23" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL22" t="inlineStr">
+      <c r="AL23" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
+      <c r="AM23" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
+      <c r="AN23" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
+      <c r="AO23" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
+      <c r="AR23" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
+      <c r="AS23" t="inlineStr">
         <is>
           <t>0BH325183B</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>0am325025</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!
 Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.
 🔩 Артикул: 0am325025.</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpeg?v=816487a239
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpg?v=45096a261b</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита</t>
         </is>
       </c>
-      <c r="AH23" t="n">
+      <c r="AH24" t="n">
         <v>7850</v>
       </c>
-      <c r="AJ23" t="inlineStr">
+      <c r="AJ24" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK23" t="inlineStr">
+      <c r="AK24" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL23" t="inlineStr">
+      <c r="AL24" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
+      <c r="AM24" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
+      <c r="AN24" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO23" t="inlineStr">
+      <c r="AO24" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR23" t="inlineStr">
+      <c r="AR24" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="AS24" t="inlineStr">
         <is>
           <t>0am325025</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>0am325025D</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Новая втулка (гильза) для штока сцепления мехатроника DSG7 DQ200 (0AM / 0CW). Предназначена для защиты штока и обеспечения точного хода без боковых люфтов. Новая втулка нужна чтобы не было задиров и царапин (они появляются при больших пробегах и большом износе рабочей поверхности - внутри втулки гильзы мехатроника dq200). Совместима с короткой и длинной версиями штока (артикулы 0AM325091E 0AM325091F). Используется при ремонте мехатроника DSG 7 DQ200, рекомендуется заменить при каждом вскрытии блока.
 Применяется при ремонте мехатроника DSG7 DQ200 0AM 0CW
@@ -3305,77 +3385,77 @@
 🔩 Артикул: 0am325025D.</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.jpg?v=bf2cf0a479</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Втулка (гильза) штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH24" t="n">
+      <c r="AH25" t="n">
         <v>1850</v>
       </c>
-      <c r="AJ24" t="inlineStr">
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK24" t="inlineStr">
+      <c r="AK25" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
+      <c r="AL25" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AM25" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AN25" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
+      <c r="AO25" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR24" t="inlineStr">
+      <c r="AR25" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr">
+      <c r="AS25" t="inlineStr">
         <is>
           <t>0am325025D</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>0am325025G</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>Ремкомплект штоков DQ200 DSG7 0AM 0CW 2 пыльника 2 сальника 2 крышки
 Новые
@@ -3383,78 +3463,78 @@
 🔩 Артикул: 0am325025G.</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.jpg?v=5bd8ad5ac3
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.jpg?v=21cf6a4fc0</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH25" t="n">
+      <c r="AH26" t="n">
         <v>2350</v>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr">
+      <c r="AK26" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="AL26" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AM26" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AN26" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr">
+      <c r="AO26" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR25" t="inlineStr">
+      <c r="AR26" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS25" t="inlineStr">
+      <c r="AS26" t="inlineStr">
         <is>
           <t>0am325025G</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>0am325025H</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>🔄 Цена по обмену на ваш старый мехатроник (без платы): 32 500 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
 Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах!
@@ -3487,83 +3567,83 @@
 🔩 Артикул: 0am325025H.</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.png?v=0593c687c2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_2.jpg?v=df6ff84458</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>Мехатроник DSG7 DQ200 0AM/0CW ПРОВЕРЕН НА АВТО</t>
         </is>
       </c>
-      <c r="AH26" t="n">
+      <c r="AH27" t="n">
         <v>36500</v>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI27" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_video.mp4?v=15fc20f523</t>
         </is>
       </c>
-      <c r="AJ26" t="inlineStr">
+      <c r="AJ27" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK26" t="inlineStr">
+      <c r="AK27" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr">
+      <c r="AL27" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
+      <c r="AM27" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AN27" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO26" t="inlineStr">
+      <c r="AO27" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR26" t="inlineStr">
+      <c r="AR27" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS26" t="inlineStr">
+      <c r="AS27" t="inlineStr">
         <is>
           <t>0am325025H</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>0am325025HX</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>🔄 Цена по обмену на ваш старый мехатроник (с платой): 62 500 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
 КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ.
@@ -3584,77 +3664,171 @@
 🔩 Артикул: 0am325025HX.</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.jpg?v=815184defd</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>Мехатроник DSG7 DQ200 в сборе с электронной</t>
         </is>
       </c>
-      <c r="AH27" t="n">
+      <c r="AH28" t="n">
         <v>68500</v>
       </c>
-      <c r="AJ27" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK27" t="inlineStr">
+      <c r="AK28" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL27" t="inlineStr">
+      <c r="AL28" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
+      <c r="AM28" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
+      <c r="AN28" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr">
+      <c r="AO28" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR27" t="inlineStr">
+      <c r="AR28" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS27" t="inlineStr">
+      <c r="AS28" t="inlineStr">
         <is>
           <t>0am325025HX</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>0am325025HXF</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>🔄 Цена по обмену на ваш старый мехатроник (с платой): 62 500 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
+КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ.
+Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)
+В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно -
+Оригинальные - крышка мехатроника, сепараторная пластина под гидроплиту 0am, пластины на соленоиды, втулки штоков мехатроника DSG7 DQ200
+Усовершенствованные
+Усиленная прокладка крышки мехатроника с утолщением, алюминивые сальники толкателей вилок (желтые, отличное качество алюминия - не пластик и не дешевые алюминиевые аналоги)
+Усиленные штоки dq200 с дополнительной резинкой (ресурс намного дольше, проверено временем)
+Стальная вставка очень хорошего качества + резинки в комплекте отличного качества (не пропускают давление после эксплуатации - смотрите фото)
+Качественный ремкомплект прокладок мехатроника DSG7 DQ200
+Каждый соленоид оригинальный и тестируется на стенде и сравнивается с идеальным графиком, загруженным в компьютер, если графики не совпадают, такой соленоид выбрасывается. Без этого теста не собирается ни один мехатроник.
+Электронная плата отличного качества, многолетний опыт производства и тестирования
+В обязательном порядке КАЖДЫЙ мехатроник проверяетсяа на мини-стенде на давление (накачивается на давление и проверяется за сколько секунд сбрасывает, как ходят толкатели)
+И самое главное - ГАРАНТИЯ проверки КАЖДОГО мехатроника на авто (не просто на подъемнике, а именно обкатка на дороге) - такой проверкой не занимаются 99% автосервисов, в основном собрали и отдали клиенту, а дальше - лотерея едет не едет. Проверка на автомобиле в условиях полного функционирования всех систем на дороге - это единственный способ утверждать, что мехатроник работоспособен. Все другие способы проверки тестируют отдельные элементы мехатроника (соленоиды, гидроаккумулятор и т д), но не тестируют агрегат в целом в реальных условиях эксплуатации на дороге.
+Мы собрали все лучшее что есть на рынке запчастей на DQ200 + оригиналы VAG + тест мехатроников DSG7 на авто.
+Заказывайте восстановленные и протестированные на авто мехатроники, с оригинальными и улучшенными запчастями по отличной цене!
+🔌 Электронная плата: 0AM927769F (0AM 927 769 F). Перед заказом сверьте номер платы на вашем мехатронике или пришлите VIN — подберём.
+🔩 Артикул: 0am325025HXF.</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HXF_1.png?v=098d4c588e
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HXF_2.png?v=838071f395
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HXF_3.png?v=b93ad38a77</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Мехатроник DSG7 DQ200 в сборе с электронной</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>68500</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>0am325025HXF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>0am325025P</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Клипса фиксации пыльника толкателя вилок для коробки передач DSG7 DQ200 (0AM / 0CW). Применяется в мехатронике для удержания пыльника штока вилок сцепления переключения передач.
 Клипса штока мехатроника DQ200 DSG7 0AM 0CW
@@ -3662,77 +3836,77 @@
 Устанавливается внутрь штока</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025P_1.png?v=4f093a4b63</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
         </is>
       </c>
-      <c r="AH28" t="n">
+      <c r="AH30" t="n">
         <v>950</v>
       </c>
-      <c r="AJ28" t="inlineStr">
+      <c r="AJ30" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK28" t="inlineStr">
+      <c r="AK30" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL28" t="inlineStr">
+      <c r="AL30" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
+      <c r="AM30" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
+      <c r="AN30" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO28" t="inlineStr">
+      <c r="AO30" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR28" t="inlineStr">
+      <c r="AR30" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS28" t="inlineStr">
+      <c r="AS30" t="inlineStr">
         <is>
           <t>0am325025P</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>0am325025ae</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>🔧 Крышка (поддон) + прокладка мехатроника DSG7 DQ200 (0AM325219C + 0AM325443D)
 Комплект для герметизации масляного поддона (крышки) мехатроника. Исключает утечки масла после обслуживания. Подходит для DSG7 — 7-ступенчатая трансмиссия с сухим сцеплением.
@@ -3752,77 +3926,77 @@
 🔩 Артикул: 0am325025ae.</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.jpg?v=e1a894f60b</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>Оригинальная крышка + усиленная прокладка</t>
         </is>
       </c>
-      <c r="AH29" t="n">
+      <c r="AH31" t="n">
         <v>2850</v>
       </c>
-      <c r="AJ29" t="inlineStr">
+      <c r="AJ31" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK29" t="inlineStr">
+      <c r="AK31" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL29" t="inlineStr">
+      <c r="AL31" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
+      <c r="AM31" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
+      <c r="AN31" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO29" t="inlineStr">
+      <c r="AO31" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR29" t="inlineStr">
+      <c r="AR31" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS29" t="inlineStr">
+      <c r="AS31" t="inlineStr">
         <is>
           <t>0am325025ae</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>0am325025f</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Комплект болтов для крепления крышки мехатроника (гидроблока) DSG7 (DQ200, версии 0AM/0CW) от VAG. Включает 7 болтов: 4 длинных (M8×90 мм, артикул WHT001922) и 3 коротких (M8×35 мм, артикул 01X301127C). Используются при обслуживании и ремонтных работах мехатроника, обеспечивают надёжную и герметичную установку. Аналог оригинальной заводской комплектации, подходят для Audi, VW, Skoda, Seat. Изготовлены из качественного алюминиевого сплава.
 Болты мехатроника dq200 dsg 7 0am 0cw
@@ -3832,77 +4006,77 @@
 🔩 Артикул: 0am325025f.</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025f_1.png?v=42835ce71d</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
-      <c r="AH30" t="n">
+      <c r="AH32" t="n">
         <v>2350</v>
       </c>
-      <c r="AJ30" t="inlineStr">
+      <c r="AJ32" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK30" t="inlineStr">
+      <c r="AK32" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL30" t="inlineStr">
+      <c r="AL32" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
+      <c r="AM32" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
+      <c r="AN32" t="inlineStr">
         <is>
           <t>Крепёж КПП</t>
         </is>
       </c>
-      <c r="AO30" t="inlineStr">
+      <c r="AO32" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR30" t="inlineStr">
+      <c r="AR32" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS30" t="inlineStr">
+      <c r="AS32" t="inlineStr">
         <is>
           <t>0am325025f</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>0am325025hfe</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)
 Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.
@@ -3932,77 +4106,77 @@
 🔩 Артикул: 0am325025h.</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.jpg?v=23a46f0590</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>Ремкомплект штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH31" t="n">
+      <c r="AH33" t="n">
         <v>950</v>
       </c>
-      <c r="AJ31" t="inlineStr">
+      <c r="AJ33" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK31" t="inlineStr">
+      <c r="AK33" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL31" t="inlineStr">
+      <c r="AL33" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
+      <c r="AM33" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
+      <c r="AN33" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO31" t="inlineStr">
+      <c r="AO33" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR31" t="inlineStr">
+      <c r="AR33" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS31" t="inlineStr">
+      <c r="AS33" t="inlineStr">
         <is>
           <t>0am325025hfe</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>0am325025j</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>В наличии прокладки dq200 сепараторные пластины мехатроника dsg 7
 Новые
@@ -4011,7 +4185,7 @@
 🔩 Артикул: 0am325025j.</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.jpg?v=5f0a06c746
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.jpg?v=f610170a4d
@@ -4019,72 +4193,72 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_4.jpg?v=714b21e00d</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>Сепараторная пластина + пластины на соленоиды</t>
         </is>
       </c>
-      <c r="AH32" t="n">
+      <c r="AH34" t="n">
         <v>1350</v>
       </c>
-      <c r="AJ32" t="inlineStr">
+      <c r="AJ34" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK32" t="inlineStr">
+      <c r="AK34" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL32" t="inlineStr">
+      <c r="AL34" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
+      <c r="AM34" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
+      <c r="AN34" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO32" t="inlineStr">
+      <c r="AO34" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR32" t="inlineStr">
+      <c r="AR34" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS32" t="inlineStr">
+      <c r="AS34" t="inlineStr">
         <is>
           <t>0am325025j</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>0am325025l</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Новый поршень вилки мехатроника DQ200 DSG 7 0AM 0CW
 Идентичен оригиналу 
@@ -4092,80 +4266,80 @@
 🔩 Артикул: 0am325025l.</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.jpg?v=c010c7bbdf</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>Поршень (толкатель) вилки мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH33" t="n">
+      <c r="AH35" t="n">
         <v>950</v>
       </c>
-      <c r="AJ33" t="inlineStr">
+      <c r="AJ35" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK33" t="inlineStr">
+      <c r="AK35" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL33" t="inlineStr">
+      <c r="AL35" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
+      <c r="AM35" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
+      <c r="AN35" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="AO35" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR33" t="inlineStr">
+      <c r="AR35" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS33" t="inlineStr">
+      <c r="AS35" t="inlineStr">
         <is>
           <t>0am325025l</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>0am325025m</t>
         </is>
       </c>
-      <c r="I34" t="n">
+      <c r="I36" t="n">
         <v>4573121040</v>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Полный ремкомплект прокладок и уплотнений для капитального ремонта мехатроника DSG7 DQ200 (0AM / 0CW). В набор входят: прокладка крышки (0AM325443D), прокладка поддона, сепараторные пластины, уплотнения электронного блока, манжеты и пыльники штоков, сальники, фильтры и кольца аккумулятора и соленоидов. Комплект покрывает все узловые точки герметизации при разборке мехатроника dq200 и позволяет выполнить полный ремонт. Подходит для автомобилей VW, Audi, Skoda, Seat с коробкой DSG7 dq 200. артикулы 0AM327377, 0AM325219C, 0AM325025 и др.
 Полный комплект прокладки dsg 7 dq200 0am как на фото
@@ -4174,79 +4348,79 @@
 🔩 Артикул: 0am325025m.</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.jpg?v=ba44318fd7
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_2.jpg?v=fd9283f1f7
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_3.jpg?v=b7ac56b9b3</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>Ремкомплект прокладок мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH34" t="n">
+      <c r="AH36" t="n">
         <v>4850</v>
       </c>
-      <c r="AJ34" t="inlineStr">
+      <c r="AJ36" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK34" t="inlineStr">
+      <c r="AK36" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL34" t="inlineStr">
+      <c r="AL36" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
+      <c r="AM36" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
+      <c r="AN36" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO34" t="inlineStr">
+      <c r="AO36" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR34" t="inlineStr">
+      <c r="AR36" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS34" t="inlineStr">
+      <c r="AS36" t="inlineStr">
         <is>
           <t>0am325025m</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>0am325025n</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>⚙️ Соленоид переключения (Shift) мехатроника DSG7 DQ200 0AM325025N — новый соленоид Bosch, отличное качество.
 ✅ Подходит для мехатроников 0AM и 0CW коробки DSG7 DQ200.
@@ -4254,77 +4428,77 @@
 🔩 Артикул: 0am325025n.</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025n_1.jpg?v=e0223e07fa</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>Соленоид переключения (Shift) мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH35" t="n">
+      <c r="AH37" t="n">
         <v>4850</v>
       </c>
-      <c r="AJ35" t="inlineStr">
+      <c r="AJ37" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK35" t="inlineStr">
+      <c r="AK37" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL35" t="inlineStr">
+      <c r="AL37" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AM37" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
+      <c r="AN37" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="AO37" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR35" t="inlineStr">
+      <c r="AR37" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS35" t="inlineStr">
+      <c r="AS37" t="inlineStr">
         <is>
           <t>0am325025n</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>0am325025q</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>⚙️ Крышка штока мехатроника DSG7 DQ200 0AM325025Q (0AM, 0CW) — новая, отличное качество.
 ✅ Подходит для мехатроников коробки DSG7 DQ200.
@@ -4332,79 +4506,79 @@
 🔩 Артикул: 0am325025q.</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.jpg?v=5190638fc3
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.jpg?v=77fc244bbc
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_3.jpg?v=4d3606b157</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
         </is>
       </c>
-      <c r="AH36" t="n">
+      <c r="AH38" t="n">
         <v>950</v>
       </c>
-      <c r="AJ36" t="inlineStr">
+      <c r="AJ38" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK36" t="inlineStr">
+      <c r="AK38" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL36" t="inlineStr">
+      <c r="AL38" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
+      <c r="AM38" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
+      <c r="AN38" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO36" t="inlineStr">
+      <c r="AO38" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR36" t="inlineStr">
+      <c r="AR38" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS36" t="inlineStr">
+      <c r="AS38" t="inlineStr">
         <is>
           <t>0am325025q</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>0am325025r</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Усиленное опорное кольцо толкателя DSG7 DQ200 0AM
 Алюминиевое кольцо толкателя мехатроника dsg 7 dq200 как на фото
@@ -4412,158 +4586,158 @@
 🔩 Артикул: 0am325025r.</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.jpg?v=3b3b076322</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>Усиленное опорное кольцо толкателя мехатроника</t>
         </is>
       </c>
-      <c r="AH37" t="n">
+      <c r="AH39" t="n">
         <v>950</v>
       </c>
-      <c r="AJ37" t="inlineStr">
+      <c r="AJ39" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK37" t="inlineStr">
+      <c r="AK39" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL37" t="inlineStr">
+      <c r="AL39" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
+      <c r="AM39" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
+      <c r="AN39" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO37" t="inlineStr">
+      <c r="AO39" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR37" t="inlineStr">
+      <c r="AR39" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS37" t="inlineStr">
+      <c r="AS39" t="inlineStr">
         <is>
           <t>0am325025r</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>0am325025u</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Ремкомплект Усиленный (с доп. Резинкой) Длинный шток 0AM325091E 101 мм + втулка (гильза) мехатроника DSG 7 DQ200 0AM 0CW
 🔩 Отличное качество, усиленнве штоки ходят намного дольше обычных!</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_1.png?v=c48648e856</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>Ремкомплект: Усиленный длинный шток 0AM325091E</t>
         </is>
       </c>
-      <c r="AH38" t="n">
+      <c r="AH40" t="n">
         <v>2850</v>
       </c>
-      <c r="AI38" t="inlineStr">
+      <c r="AI40" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025u_video.mp4?v=4573c3be6d</t>
         </is>
       </c>
-      <c r="AJ38" t="inlineStr">
+      <c r="AJ40" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK38" t="inlineStr">
+      <c r="AK40" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL38" t="inlineStr">
+      <c r="AL40" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
+      <c r="AM40" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
+      <c r="AN40" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO38" t="inlineStr">
+      <c r="AO40" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR38" t="inlineStr">
+      <c r="AR40" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS38" t="inlineStr">
+      <c r="AS40" t="inlineStr">
         <is>
           <t>0am325025u</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>0am325025x</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>🔄 Цена по обмену на ваш старый мехатроник (без платы): 38 500 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
 Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).
@@ -4577,77 +4751,77 @@
 🔩 Артикул: 0am325025x.</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=7f59b31f49</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>Мехатроник DSG7 DQ200 0AM с новыми соленоидами</t>
         </is>
       </c>
-      <c r="AH39" t="n">
+      <c r="AH41" t="n">
         <v>42500</v>
       </c>
-      <c r="AJ39" t="inlineStr">
+      <c r="AJ41" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK39" t="inlineStr">
+      <c r="AK41" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL39" t="inlineStr">
+      <c r="AL41" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
+      <c r="AM41" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
+      <c r="AN41" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO39" t="inlineStr">
+      <c r="AO41" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR39" t="inlineStr">
+      <c r="AR41" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS39" t="inlineStr">
+      <c r="AS41" t="inlineStr">
         <is>
           <t>0am325025x</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>0am325025z</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>🔩 Ремкомплект: Усиленный (с доп. Резинкой) шток DSG7 DQ200 — 0AM325091F 99мм + втулка без задиров и царапин!
 Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.
@@ -4668,82 +4842,82 @@
 🔩 Отличное качество запчастей и долговечность - усиленный шток ходит намного дольше обычного!</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>Ремкомплект: Усиленный короткий шток 0AM325091F</t>
         </is>
       </c>
-      <c r="AH40" t="n">
+      <c r="AH42" t="n">
         <v>2350</v>
       </c>
-      <c r="AI40" t="inlineStr">
+      <c r="AI42" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_video.mp4?v=4573c3be6d</t>
         </is>
       </c>
-      <c r="AJ40" t="inlineStr">
+      <c r="AJ42" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK40" t="inlineStr">
+      <c r="AK42" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL40" t="inlineStr">
+      <c r="AL42" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
+      <c r="AM42" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
+      <c r="AN42" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO40" t="inlineStr">
+      <c r="AO42" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR40" t="inlineStr">
+      <c r="AR42" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS40" t="inlineStr">
+      <c r="AS42" t="inlineStr">
         <is>
           <t>0am325025z</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>0am325025С</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>⚙️ Кольцо гидроаккумулятора мехатроника DSG7 DQ200 0AM325025C — новое, отличное качество.
 ✅ Подходит для мехатроников 0AM и 0CW коробки DSG7 DQ200.
@@ -4751,78 +4925,78 @@
 🔩 Артикул: 0am325025С.</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025-cyr-s_1.jpg?v=32a4eaa349
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025-cyr-s_2.jpg?v=3f30a503c8</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>Кольцо гидроаккумулятора мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH41" t="n">
+      <c r="AH43" t="n">
         <v>950</v>
       </c>
-      <c r="AJ41" t="inlineStr">
+      <c r="AJ43" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK41" t="inlineStr">
+      <c r="AK43" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL41" t="inlineStr">
+      <c r="AL43" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
+      <c r="AM43" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
+      <c r="AN43" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO41" t="inlineStr">
+      <c r="AO43" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR41" t="inlineStr">
+      <c r="AR43" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS41" t="inlineStr">
+      <c r="AS43" t="inlineStr">
         <is>
           <t>0am325025C</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>0am325066AC</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Поршень толкателя вилки сцепления DSG7 DQ200 (0AM / 0CW), используется в мехатронике для передачи усилия к вилке сцепления. Является важным элементом сцепления, обеспечивает точную и стабильную работу коробки передач. Изготовлен из прочного металла с высокой устойчивостью к трению и температуре
 Поршень штока мехатроника DQ200 DSG 7 0AM 0CW
@@ -4832,77 +5006,77 @@
 🔩 Артикул: 0am325066AC.</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.jpg?v=693a4298e8</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>Усиленный поршень штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH42" t="n">
+      <c r="AH44" t="n">
         <v>950</v>
       </c>
-      <c r="AJ42" t="inlineStr">
+      <c r="AJ44" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK42" t="inlineStr">
+      <c r="AK44" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL42" t="inlineStr">
+      <c r="AL44" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
+      <c r="AM44" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
+      <c r="AN44" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO42" t="inlineStr">
+      <c r="AO44" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR42" t="inlineStr">
+      <c r="AR44" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS42" t="inlineStr">
+      <c r="AS44" t="inlineStr">
         <is>
           <t>0am325066AC</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>0am325066ad</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Манжет Сальник штока мехатроника DSG7 DQ200 0AM 0CW
 Новый сальник мехатроника DSG 7 DQ200
@@ -4910,78 +5084,78 @@
 🔩 Артикул: 0am325066ad.</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=cbeca4b59a
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_2.jpg?v=a9a9967b4d</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>Сальник-манжета штока сцепления мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH43" t="n">
+      <c r="AH45" t="n">
         <v>950</v>
       </c>
-      <c r="AJ43" t="inlineStr">
+      <c r="AJ45" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK43" t="inlineStr">
+      <c r="AK45" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL43" t="inlineStr">
+      <c r="AL45" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
+      <c r="AM45" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
+      <c r="AN45" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO43" t="inlineStr">
+      <c r="AO45" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR43" t="inlineStr">
+      <c r="AR45" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS43" t="inlineStr">
+      <c r="AS45" t="inlineStr">
         <is>
           <t>0am325066ad</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>0am325066ae</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW
 Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.
@@ -5006,78 +5180,78 @@
 📌 Главное - простукивайте шарики при установке!!!</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.jpg?v=ffb6e141cb
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.jpg?v=1af750811c</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>Усиленная гидроплита мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH44" t="n">
+      <c r="AH46" t="n">
         <v>5350</v>
       </c>
-      <c r="AJ44" t="inlineStr">
+      <c r="AJ46" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK44" t="inlineStr">
+      <c r="AK46" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL44" t="inlineStr">
+      <c r="AL46" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
+      <c r="AM46" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
+      <c r="AN46" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO44" t="inlineStr">
+      <c r="AO46" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR44" t="inlineStr">
+      <c r="AR46" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS44" t="inlineStr">
+      <c r="AS46" t="inlineStr">
         <is>
           <t>0am325066ae</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>0am325091e</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)
 Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом
@@ -5105,163 +5279,163 @@
 📦 Делайте заказ - отправим моментально!</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.jpg?v=ad51750acf
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_2.jpg?v=579c860e1a</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>Усиленный шток мехатроника DSG7 DQ200 101мм</t>
         </is>
       </c>
-      <c r="AH45" t="n">
+      <c r="AH47" t="n">
         <v>2350</v>
       </c>
-      <c r="AI45" t="inlineStr">
+      <c r="AI47" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_video.mp4?v=4573c3be6d</t>
         </is>
       </c>
-      <c r="AJ45" t="inlineStr">
+      <c r="AJ47" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK45" t="inlineStr">
+      <c r="AK47" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL45" t="inlineStr">
+      <c r="AL47" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
+      <c r="AM47" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
+      <c r="AN47" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO45" t="inlineStr">
+      <c r="AO47" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR45" t="inlineStr">
+      <c r="AR47" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS45" t="inlineStr">
+      <c r="AS47" t="inlineStr">
         <is>
           <t>0am325091e</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>0am325091e-set</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>🔧 Оба усиленных штока (101 мм, 0AM325091E) + 2 новые втулки (гильзы) мехатроника DSG7 DQ200 — комплект на весь мехатроник сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ — выгоднее, чем покупать по отдельности. 🔩 Артикул штока 0AM325091E. ⭐ Усиленная версия штоков — снижает риск повторных задиров.</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e-set_1.png?v=39677a9dd4</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2</t>
         </is>
       </c>
-      <c r="AH46" t="n">
+      <c r="AH48" t="n">
         <v>4850</v>
       </c>
-      <c r="AI46" t="inlineStr">
+      <c r="AI48" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e-set_video.mp4?v=4573c3be6d</t>
         </is>
       </c>
-      <c r="AJ46" t="inlineStr">
+      <c r="AJ48" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK46" t="inlineStr">
+      <c r="AK48" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL46" t="inlineStr">
+      <c r="AL48" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
+      <c r="AM48" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
+      <c r="AN48" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO46" t="inlineStr">
+      <c r="AO48" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR46" t="inlineStr">
+      <c r="AR48" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS46" t="inlineStr">
+      <c r="AS48" t="inlineStr">
         <is>
           <t>0am325091eset</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>0am325091f</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>🔩 Усиленный шток мехатроника DSG7 DQ200 0AM325091F (99 мм)
 Оригинальный шток (clutch pusher rod) длиной 99 мм — для мехатроника коробки передач DSG7 DQ200 с сухим сцеплением. Отвечает за точную передачу усилия к вилке сцепления, входит в состав гидроблока.
@@ -5292,218 +5466,63 @@
 👉Оформите заказ - отправим в лучшем виде!</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.jpg?v=fc28fbc227
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_2.jpg?v=94ce98509a</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>Усиленный шток мехатроника DSG7 DQ200 99мм</t>
         </is>
       </c>
-      <c r="AH47" t="n">
+      <c r="AH49" t="n">
         <v>1850</v>
       </c>
-      <c r="AI47" t="inlineStr">
+      <c r="AI49" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_video.mp4?v=4573c3be6d</t>
         </is>
       </c>
-      <c r="AJ47" t="inlineStr">
+      <c r="AJ49" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK47" t="inlineStr">
+      <c r="AK49" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL47" t="inlineStr">
+      <c r="AL49" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
+      <c r="AM49" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
+      <c r="AN49" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO47" t="inlineStr">
+      <c r="AO49" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR47" t="inlineStr">
+      <c r="AR49" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS47" t="inlineStr">
+      <c r="AS49" t="inlineStr">
         <is>
           <t>0am325091f</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>0am325091f-set</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_1.png?v=6b39215af5</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2</t>
-        </is>
-      </c>
-      <c r="AH48" t="n">
-        <v>4850</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_video.mp4?v=4573c3be6d</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>Переключение передач</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>0am325091fset</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>0am325477</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>🔧 Планка (фиксатор) соленоидов мехатроника DSG7 DQ200 — пластиковая, 1 шт (половина комплекта, крепит 4 соленоида одной стороны блока). ✅ Подходит на оба поколения мехатроника — Bosch и Hilite, 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Артикул: 0am325477. ⭐ Нужна вторая планка? У нас есть комплект 2 шт — выгоднее при полной переборке мехатроника.</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW</t>
-        </is>
-      </c>
-      <c r="AH49" t="n">
-        <v>1350</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>0am325477</t>
         </is>
       </c>
     </row>
@@ -5515,91 +5534,246 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>0am325091f-set</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>🔧 Оба усиленных коротких штока (99 мм, 0AM325091F) + 2 новые втулки мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 2 штока + 2 втулки за один заказ. 🔩 Артикул штока 0AM325091F. ⭐ Усиленная версия — для тех, кто хочет исключить повторный ремонт этого узла.</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_1.png?v=6b39215af5</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2</t>
+        </is>
+      </c>
+      <c r="AH50" t="n">
+        <v>4850</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f-set_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>Переключение передач</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS50" t="inlineStr">
+        <is>
+          <t>0am325091fset</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>🔧 Планка (фиксатор) соленоидов мехатроника DSG7 DQ200 — пластиковая, 1 шт (половина комплекта, крепит 4 соленоида одной стороны блока). ✅ Подходит на оба поколения мехатроника — Bosch и Hilite, 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Артикул: 0am325477. ⭐ Нужна вторая планка? У нас есть комплект 2 шт — выгоднее при полной переборке мехатроника.</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Планка соленоидов мехатроника DSG7 DQ200 0AM 0CW</t>
+        </is>
+      </c>
+      <c r="AH51" t="n">
+        <v>1350</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>Электронное управление КПП</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS51" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
           <t>0am325477ae</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Планка соленоидов DQ200 0am 0cw подходят на старую версию (поколение) Bosch так и новую Hilti
 🔩 Артикул: 0am325477ae.</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477ae_1.png?v=368fa6503f</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>Пластина соленоидов мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH50" t="n">
+      <c r="AH52" t="n">
         <v>1350</v>
       </c>
-      <c r="AJ50" t="inlineStr">
+      <c r="AJ52" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK50" t="inlineStr">
+      <c r="AK52" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL50" t="inlineStr">
+      <c r="AL52" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
+      <c r="AM52" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
+      <c r="AN52" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO50" t="inlineStr">
+      <c r="AO52" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR50" t="inlineStr">
+      <c r="AR52" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS50" t="inlineStr">
+      <c r="AS52" t="inlineStr">
         <is>
           <t>0am325477ae</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>0cw0am</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG 7 DQ200 0AM
 Описание товара
@@ -5615,79 +5789,79 @@
 Запчасть подходит для владельцев автомобилей VAG с DSG 7, механиков и сервисных центров, выполняющих ремонт и диагностику трансмиссий DQ200.</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH51" t="n">
+      <c r="AH53" t="n">
         <v>950</v>
       </c>
-      <c r="AJ51" t="inlineStr">
+      <c r="AJ53" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK51" t="inlineStr">
+      <c r="AK53" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL51" t="inlineStr">
+      <c r="AL53" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
+      <c r="AM53" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
+      <c r="AN53" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO51" t="inlineStr">
+      <c r="AO53" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR51" t="inlineStr">
+      <c r="AR53" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS51" t="inlineStr">
+      <c r="AS53" t="inlineStr">
         <is>
           <t>0cw0am</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника для роботизированной трансмиссии DSG 7 DQ20 (Уплотнение электромотора гидроблока (мехатроника) DQ200 0AM DSG 7 ). Предназначена для герметизации электронного блока управления мехатроника и защиты платы от попадания масла, влаги и загрязнений. Используется при ремонте мехатроника, разборке гидравлического блока, а также при устранении неисправностей, связанных с работой электроники TCU.
 Совместимость
@@ -5701,79 +5875,79 @@
 🔩 Артикул: 0cw0amdsgdq200.</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=d2723138aa
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=77a111eb34
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_3.jpg?v=40c2597cb3</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>Уплотнение электромотора гидроблока мехатроника</t>
         </is>
       </c>
-      <c r="AH52" t="n">
+      <c r="AH54" t="n">
         <v>950</v>
       </c>
-      <c r="AJ52" t="inlineStr">
+      <c r="AJ54" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK52" t="inlineStr">
+      <c r="AK54" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL52" t="inlineStr">
+      <c r="AL54" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
+      <c r="AM54" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
+      <c r="AN54" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO52" t="inlineStr">
+      <c r="AO54" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR52" t="inlineStr">
+      <c r="AR54" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS52" t="inlineStr">
+      <c r="AS54" t="inlineStr">
         <is>
           <t>0cw0amdsgdq200</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>🛠️ Прокладка электронной платы мехатроника DSG 7 DQ200 0AM — 0AM927377
 🔎
@@ -5796,78 +5970,78 @@
 🔩 Артикул: 0cw325025h.</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>Прокладка электронной платы мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH53" t="n">
+      <c r="AH55" t="n">
         <v>950</v>
       </c>
-      <c r="AJ53" t="inlineStr">
+      <c r="AJ55" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK53" t="inlineStr">
+      <c r="AK55" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL53" t="inlineStr">
+      <c r="AL55" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
+      <c r="AM55" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
+      <c r="AN55" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AO55" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR53" t="inlineStr">
+      <c r="AR55" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS53" t="inlineStr">
+      <c r="AS55" t="inlineStr">
         <is>
           <t>0cw325025h</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>0сц</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200 предназначен для восстановления заводской герметичности узла толкателя вилки сцепления в 7-ступенчатой коробке передач с сухим сцеплением. Используется в мехатрониках 0AM и 0CW, устанавливаемых на автомобили концерна Volkswagen Group.
 Данный сальник является штатным уплотнительным элементом мехатроника и предотвращает утечку трансмиссионного масла из гидравлической части коробки передач. Исправное состояние сальника критически важно для защиты сухого сцепления DSG7 DQ200 от попадания масла, что напрямую влияет на ресурс сцепления и стабильность работы коробки.
@@ -5888,79 +6062,79 @@
 🔩 Артикул: 0сц.</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_1.jpg?v=3e0abf9ec7
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_2.jpg?v=b12c6dac21
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_3.jpg?v=bd237a81d2</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH54" t="n">
+      <c r="AH56" t="n">
         <v>950</v>
       </c>
-      <c r="AJ54" t="inlineStr">
+      <c r="AJ56" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK54" t="inlineStr">
+      <c r="AK56" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL54" t="inlineStr">
+      <c r="AL56" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
+      <c r="AM56" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
+      <c r="AN56" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO54" t="inlineStr">
+      <c r="AO56" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR54" t="inlineStr">
+      <c r="AR56" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS54" t="inlineStr">
+      <c r="AS56" t="inlineStr">
         <is>
           <t>0c</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>122390AK-AF</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект
 Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW
@@ -5973,78 +6147,78 @@
 🔩 Артикул: 122390AK-AF.</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=a2422623a6
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.jpg?v=70e1dc8dfd</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>https://ir-20.ozone.ru/s3/multimedia-1-a/14848106518.jpg
+https://ir-20.ozone.ru/s3/multimedia-1-q/7418270474.jpg</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
         <is>
           <t>Пыльник штока мехатроника DSG7 DQ200 122390AK-AF</t>
         </is>
       </c>
-      <c r="AH55" t="n">
+      <c r="AH57" t="n">
         <v>950</v>
       </c>
-      <c r="AJ55" t="inlineStr">
+      <c r="AJ57" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK55" t="inlineStr">
+      <c r="AK57" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL55" t="inlineStr">
+      <c r="AL57" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
+      <c r="AM57" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
+      <c r="AN57" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO55" t="inlineStr">
+      <c r="AO57" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR55" t="inlineStr">
+      <c r="AR57" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS55" t="inlineStr">
+      <c r="AS57" t="inlineStr">
         <is>
           <t>122390AKAF</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>123014‑AF</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Фильтр‑сетка 123014‑AF предназначена для замены в соленоидах N436 и N440 автоматической коробки передач DSG‑7 (DL501 / 0B5 / DQ500 / 0BH). Используется для точечной фильтрации масла, предотвращает загрязнение соленоидов и продлевает срок службы гидроблока. Совместима с автомобилями Audi Q5, A4, A5 и другими с коробками DSG‑7. Лёгкий монтаж, аналог оригинала 0B5 325 421. Идеальное решение для тех, кто хочет быстро и недорого восстановить работоспособность АКПП. Неоригинал высокого качества
 ✅
@@ -6058,78 +6232,78 @@
 Фильтр-сетка соленоидов АКПП DSG 7 0B5 DL501 Новая</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.jpg?v=7eebff5ddc
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=e9725022b3</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>Фильтр-сетка соленоидов DSG7 0B5 DL501 123014AF</t>
         </is>
       </c>
-      <c r="AH56" t="n">
+      <c r="AH58" t="n">
         <v>950</v>
       </c>
-      <c r="AJ56" t="inlineStr">
+      <c r="AJ58" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK56" t="inlineStr">
+      <c r="AK58" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL56" t="inlineStr">
+      <c r="AL58" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
+      <c r="AM58" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
+      <c r="AN58" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO56" t="inlineStr">
+      <c r="AO58" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR56" t="inlineStr">
+      <c r="AR58" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS56" t="inlineStr">
+      <c r="AS58" t="inlineStr">
         <is>
           <t>123014AF</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Гидроблок JF015E для вариатора CVT RE0F11A 1.8 Л! . Обеспечивает стабильное давление масла и корректную работу трансмиссии. Подходит для ремонта вариаторов Nissan, Renault и Mitsubishi.
 Описание товара
@@ -6153,78 +6327,78 @@
 🔩 Артикул: 317053TX0C.</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>Гидроблок вариатора JF015E 1.8л (RE0F11A)</t>
         </is>
       </c>
-      <c r="AH57" t="n">
+      <c r="AH59" t="n">
         <v>32500</v>
       </c>
-      <c r="AJ57" t="inlineStr">
+      <c r="AJ59" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK57" t="inlineStr">
+      <c r="AK59" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL57" t="inlineStr">
+      <c r="AL59" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AM59" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
+      <c r="AN59" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO57" t="inlineStr">
+      <c r="AO59" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR57" t="inlineStr">
+      <c r="AR59" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS57" t="inlineStr">
+      <c r="AS59" t="inlineStr">
         <is>
           <t>317053TX0C</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>55565480</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>импульсная звёздочка датчика положения распредвала
 Это сигнальное (импульсное) кольцо распредвала, установлено на распределительный вал.
@@ -6236,77 +6410,77 @@
 Датчик распредвала 55565480 GM</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>Импульсное кольцо распредвала GM 55565480</t>
         </is>
       </c>
-      <c r="AH58" t="n">
+      <c r="AH60" t="n">
         <v>950</v>
       </c>
-      <c r="AJ58" t="inlineStr">
+      <c r="AJ60" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK58" t="inlineStr">
+      <c r="AK60" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL58" t="inlineStr">
+      <c r="AL60" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
+      <c r="AM60" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
+      <c r="AN60" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO58" t="inlineStr">
+      <c r="AO60" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR58" t="inlineStr">
+      <c r="AR60" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS58" t="inlineStr">
+      <c r="AS60" t="inlineStr">
         <is>
           <t>55565480</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>DQ500</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Набор корпус фильтра + фильтр DQ500 DSG7 0BH
 Новые
@@ -6315,7 +6489,7 @@
 Снижает температуру масла</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
@@ -6323,148 +6497,148 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="AH59" t="n">
+      <c r="AH61" t="n">
         <v>2250</v>
       </c>
-      <c r="AJ59" t="inlineStr">
+      <c r="AJ61" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK59" t="inlineStr">
+      <c r="AK61" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL59" t="inlineStr">
+      <c r="AL61" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
+      <c r="AM61" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
+      <c r="AN61" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO59" t="inlineStr">
+      <c r="AO61" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR59" t="inlineStr">
+      <c r="AR61" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS59" t="inlineStr">
+      <c r="AS61" t="inlineStr">
         <is>
           <t>DQ500</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Dq200dsg7</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Уплотнение насоса гидроблока (мехатроника) DQ200 0AM DSG 7 - как на фото продается поштучно, входит в состам ремкомплекта прикладок электронного блока управления dsg7 dq200 0am 0cw!
 🔩 Артикул: Dq200dsg7.</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg7_1.jpg?v=12b215cccc</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>Уплотнение насоса гидроблока мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH60" t="n">
+      <c r="AH62" t="n">
         <v>950</v>
       </c>
-      <c r="AJ60" t="inlineStr">
+      <c r="AJ62" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK60" t="inlineStr">
+      <c r="AK62" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL60" t="inlineStr">
+      <c r="AL62" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
+      <c r="AM62" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
+      <c r="AN62" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO60" t="inlineStr">
+      <c r="AO62" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR60" t="inlineStr">
+      <c r="AR62" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS60" t="inlineStr">
+      <c r="AS62" t="inlineStr">
         <is>
           <t>Dq200dsg7</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Улучшенный отвод тепла
 Уменьшает температуру масла КПП
@@ -6483,7 +6657,7 @@
 📍 Отличный выбор для тех, кто не хочет рисковать на трассе и в городе</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda
@@ -6497,149 +6671,149 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>Корпус фильтра мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="AH61" t="n">
+      <c r="AH63" t="n">
         <v>1850</v>
       </c>
-      <c r="AJ61" t="inlineStr">
+      <c r="AJ63" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK61" t="inlineStr">
+      <c r="AK63" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL61" t="inlineStr">
+      <c r="AL63" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
+      <c r="AM63" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
+      <c r="AN63" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO61" t="inlineStr">
+      <c r="AO63" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR61" t="inlineStr">
+      <c r="AR63" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS61" t="inlineStr">
+      <c r="AS63" t="inlineStr">
         <is>
           <t>Dq500</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>WHT001922</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>Болт крышки мехатроника DSG7 DQ200 0AM 0CW Длинный
 Новый Отличное качество
 🔩 Артикул: WHT001922.</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>Болт мехатроника длинный DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH62" t="n">
+      <c r="AH64" t="n">
         <v>950</v>
       </c>
-      <c r="AJ62" t="inlineStr">
+      <c r="AJ64" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK62" t="inlineStr">
+      <c r="AK64" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL62" t="inlineStr">
+      <c r="AL64" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
+      <c r="AM64" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
+      <c r="AN64" t="inlineStr">
         <is>
           <t>Крепёж КПП</t>
         </is>
       </c>
-      <c r="AO62" t="inlineStr">
+      <c r="AO64" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR62" t="inlineStr">
+      <c r="AR64" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS62" t="inlineStr">
+      <c r="AS64" t="inlineStr">
         <is>
           <t>WHT001922</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>filtr-dsg7-dq200</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>🔧 Масляный фильтр мехатроника DSG7 DQ200 (0AM/0CW) — стандартная версия для планового обслуживания и ремонта гидроблока АКПП.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200 (0AM325025 и аналоги).
@@ -6648,458 +6822,458 @@
 🔩 Артикул: filtr-dsg7-dq200.</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_2.png?v=b1ce9f5f30</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>Масляный фильтр мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH63" t="n">
+      <c r="AH65" t="n">
         <v>950</v>
       </c>
-      <c r="AJ63" t="inlineStr">
+      <c r="AJ65" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK63" t="inlineStr">
+      <c r="AK65" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL63" t="inlineStr">
+      <c r="AL65" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
+      <c r="AM65" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
+      <c r="AN65" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO63" t="inlineStr">
+      <c r="AO65" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR63" t="inlineStr">
+      <c r="AR65" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS63" t="inlineStr">
+      <c r="AS65" t="inlineStr">
         <is>
           <t>filtrdsg7dq200</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>filtr-dsg7-dq500</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>🔧 Масляный фильтр мехатроника DSG7 DQ500 0BH325183B — устанавливается в корпус фильтра (корпус — отдельная позиция, см. также в нашем магазине). ✅ Volkswagen Passat, Golf, Tiguan, T5/T6, Audi A3, Škoda Kodiaq и другие модели с DSG7 DQ500/DQ400E. 📦 Новый, с завода, в наличии, отправка в день заказа. 🔩 Артикул: 0BH325183B.</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq500_1.png?v=5a2f360fb5</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>Масляный фильтр мехатроника DSG7 DQ500 0BH325183B</t>
         </is>
       </c>
-      <c r="AH64" t="n">
+      <c r="AH66" t="n">
         <v>450</v>
       </c>
-      <c r="AJ64" t="inlineStr">
+      <c r="AJ66" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK64" t="inlineStr">
+      <c r="AK66" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL64" t="inlineStr">
+      <c r="AL66" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
+      <c r="AM66" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
+      <c r="AN66" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO64" t="inlineStr">
+      <c r="AO66" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR64" t="inlineStr">
+      <c r="AR66" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS64" t="inlineStr">
+      <c r="AS66" t="inlineStr">
         <is>
           <t>filtrdsg7dq500</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>🔧 Оригинальная фильтр-сетка на соленоиды мехатроника DSG7 0B5 (DL501). ✅ Audi Q5, A4, A5 и другие модели с коробкой 0B5 DL501. 🔩 Оригинал, аналог артикула 123014AF/0B5325421. ⭐ Оригинал вместо аналога — для тех, кому важна заводская фильтрация.</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=96f21d0cb5
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=be20ada597
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_3.jpg?v=87268821a3</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>Оригинальная фильтр-сетка на соленоиды DSG7 0B5</t>
         </is>
       </c>
-      <c r="AH65" t="n">
+      <c r="AH67" t="n">
         <v>1350</v>
       </c>
-      <c r="AJ65" t="inlineStr">
+      <c r="AJ67" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK65" t="inlineStr">
+      <c r="AK67" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL65" t="inlineStr">
+      <c r="AL67" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
+      <c r="AM67" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
+      <c r="AN67" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO65" t="inlineStr">
+      <c r="AO67" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR65" t="inlineStr">
+      <c r="AR67" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS65" t="inlineStr">
+      <c r="AS67" t="inlineStr">
         <is>
           <t>filtrsetka0b5orig</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>gidroakkumulyator-orig</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>🔧 Восстановленный гидроаккумулятор мехатроника DQ200 DSG7 — поддерживает рабочее давление в гидросистеме. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 Артикул 0AM325587E. ⭐ Восстановленный оригинал VAG — отличное качество</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>Восстановленный гидроаккумулятор мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH66" t="n">
+      <c r="AH68" t="n">
         <v>4850</v>
       </c>
-      <c r="AJ66" t="inlineStr">
+      <c r="AJ68" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK66" t="inlineStr">
+      <c r="AK68" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL66" t="inlineStr">
+      <c r="AL68" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
+      <c r="AM68" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
+      <c r="AN68" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO66" t="inlineStr">
+      <c r="AO68" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR66" t="inlineStr">
+      <c r="AR68" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS66" t="inlineStr">
+      <c r="AS68" t="inlineStr">
         <is>
           <t>gidroakkumulyatororig</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>🔧 Клипсы (фиксаторы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Мелкие детали, которые часто теряются или ломаются при разборке — удобно взять сразу парой.</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2</t>
         </is>
       </c>
-      <c r="AH67" t="n">
+      <c r="AH69" t="n">
         <v>950</v>
       </c>
-      <c r="AJ67" t="inlineStr">
+      <c r="AJ69" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK67" t="inlineStr">
+      <c r="AK69" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL67" t="inlineStr">
+      <c r="AL69" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
+      <c r="AM69" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
+      <c r="AN69" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO67" t="inlineStr">
+      <c r="AO69" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR67" t="inlineStr">
+      <c r="AR69" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS67" t="inlineStr">
+      <c r="AS69" t="inlineStr">
         <is>
           <t>klipsyshtokov2sht</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>korpus-filtra-0bh325159</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>🔧 Корпус масляного фильтра мехатроника DSG7 DQ500, без фильтрующего элемента (только корпус). ✅ Volkswagen, Škoda, Audi, Seat, Porsche с DQ500. 🔩 Артикул 0BH325159. ⭐ Для тех, у кого треснул/потерян корпус, а сам фильтр менять пока не нужно — для комплекта корпус+фильтр см. позицию DQ500.</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_1.png?v=207791c0ab
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/korpus-filtra-0bh325159_2.png?v=33f6b91718</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>Корпус масляного фильтра мехатроника DSG7 DQ500</t>
         </is>
       </c>
-      <c r="AH68" t="n">
+      <c r="AH70" t="n">
         <v>1850</v>
       </c>
-      <c r="AJ68" t="inlineStr">
+      <c r="AJ70" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK68" t="inlineStr">
+      <c r="AK70" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL68" t="inlineStr">
+      <c r="AL70" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
+      <c r="AM70" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
+      <c r="AN70" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO68" t="inlineStr">
+      <c r="AO70" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR68" t="inlineStr">
+      <c r="AR70" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS68" t="inlineStr">
+      <c r="AS70" t="inlineStr">
         <is>
           <t>korpusfiltra0bh325159</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>🔧 Крышка (поддон) мехатроника DSG7 DQ200 — герметично закрывает гидроблок, защищает от загрязнений и подтёков масла.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -7107,388 +7281,388 @@
 🔩 Совместима с 0AM325219C.</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.jpg?v=8e1deb51de
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_2.png?v=637a263fe5</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>Крышка мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH69" t="n">
+      <c r="AH71" t="n">
         <v>1350</v>
       </c>
-      <c r="AJ69" t="inlineStr">
+      <c r="AJ71" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK69" t="inlineStr">
+      <c r="AK71" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL69" t="inlineStr">
+      <c r="AL71" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
+      <c r="AM71" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
+      <c r="AN71" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO69" t="inlineStr">
+      <c r="AO71" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR69" t="inlineStr">
+      <c r="AR71" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS69" t="inlineStr">
+      <c r="AS71" t="inlineStr">
         <is>
           <t>kryshkamehatronikadq200</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>planka-solenoid-2sht</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>🔧 Обе пластиковые планки (фиксаторы) соленоидов мехатроника DSG7 DQ200 — комплект на весь мехатроник. ✅ 0AM, Volkswagen/Škoda/Audi/Seat. 📦 2 шт за один заказ. ⭐ Удобно взять сразу обе планки при полной переборке мехатроника.</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="S72" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>Планки соленоидов мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH70" t="n">
+      <c r="AH72" t="n">
         <v>1350</v>
       </c>
-      <c r="AJ70" t="inlineStr">
+      <c r="AJ72" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK70" t="inlineStr">
+      <c r="AK72" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL70" t="inlineStr">
+      <c r="AL72" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
+      <c r="AM72" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
+      <c r="AN72" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO70" t="inlineStr">
+      <c r="AO72" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR70" t="inlineStr">
+      <c r="AR72" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS70" t="inlineStr">
+      <c r="AS72" t="inlineStr">
         <is>
           <t>plankasolenoid2sht</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>plastina-solenoid-dq200</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>🔧 Пластина (фиксатор) на соленоиды мехатроника DSG7 DQ200, 1 шт.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новая, с завода, отправка в день заказа.</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="S73" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastina-solenoid-dq200_1.png?v=e86dd4da7d</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>Пластина на соленоиды мехатроника DSG7 DQ200, 1 шт</t>
         </is>
       </c>
-      <c r="AH71" t="n">
+      <c r="AH73" t="n">
         <v>950</v>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AJ73" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK71" t="inlineStr">
+      <c r="AK73" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL71" t="inlineStr">
+      <c r="AL73" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
+      <c r="AM73" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
+      <c r="AN73" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO71" t="inlineStr">
+      <c r="AO73" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR71" t="inlineStr">
+      <c r="AR73" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS71" t="inlineStr">
+      <c r="AS73" t="inlineStr">
         <is>
           <t>plastinasolenoiddq200</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>🔧 Пластины (фиксаторы) на соленоиды мехатроника DSG7 DQ200 — комплект 2 шт на весь мехатроник.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новые, с завода.</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr">
+      <c r="S74" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-dq200-2sht_1.png?v=98c47f4555</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>Пластины на соленоиды мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH72" t="n">
+      <c r="AH74" t="n">
         <v>950</v>
       </c>
-      <c r="AJ72" t="inlineStr">
+      <c r="AJ74" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK72" t="inlineStr">
+      <c r="AK74" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL72" t="inlineStr">
+      <c r="AL74" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
+      <c r="AM74" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
+      <c r="AN74" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO72" t="inlineStr">
+      <c r="AO74" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR72" t="inlineStr">
+      <c r="AR74" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS72" t="inlineStr">
+      <c r="AS74" t="inlineStr">
         <is>
           <t>plastinysolenoiddq2002sht</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>plastiny-solenoid-orig</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) пластины-прокладки на соленоиды мехатроника DSG7 DQ200, без сепараторной пластины (для сепараторной пластины отдельно — см. 0AM325467J). ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Оригинал — важно для точного прилегания и герметичности каналов давления соленоидов.</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>Оригинальные пластины на соленоиды VAG</t>
         </is>
       </c>
-      <c r="AH73" t="n">
+      <c r="AH75" t="n">
         <v>950</v>
       </c>
-      <c r="AJ73" t="inlineStr">
+      <c r="AJ75" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK73" t="inlineStr">
+      <c r="AK75" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL73" t="inlineStr">
+      <c r="AL75" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
+      <c r="AM75" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
+      <c r="AN75" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO73" t="inlineStr">
+      <c r="AO75" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR73" t="inlineStr">
+      <c r="AR75" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS73" t="inlineStr">
+      <c r="AS75" t="inlineStr">
         <is>
           <t>plastinysolenoidorig</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>plita-filtr</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=7c348500b1
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=efa8557d9d
@@ -7496,755 +7670,755 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_4.jpg?v=3f11b4e476</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + фильтр мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH74" t="n">
+      <c r="AH76" t="n">
         <v>5850</v>
       </c>
-      <c r="AJ74" t="inlineStr">
+      <c r="AJ76" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK74" t="inlineStr">
+      <c r="AK76" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL74" t="inlineStr">
+      <c r="AL76" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
+      <c r="AM76" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
+      <c r="AN76" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO74" t="inlineStr">
+      <c r="AO76" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR74" t="inlineStr">
+      <c r="AR76" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS74" t="inlineStr">
+      <c r="AS76" t="inlineStr">
         <is>
           <t>plitafiltr</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>plita-filtr-orig</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + УЛУЧШЕННЫЙ масляный фильтр — комплект для ремонта гидравлической части повышенного ресурса. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + улучшенный фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Улучшенный фильтр с более высоким ресурсом по сравнению со стандартным — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>Усиленная плита + улучшенный фильтр мехатроника</t>
         </is>
       </c>
-      <c r="AH75" t="n">
+      <c r="AH77" t="n">
         <v>5850</v>
       </c>
-      <c r="AJ75" t="inlineStr">
+      <c r="AJ77" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK75" t="inlineStr">
+      <c r="AK77" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL75" t="inlineStr">
+      <c r="AL77" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
+      <c r="AM77" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
+      <c r="AN77" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO75" t="inlineStr">
+      <c r="AO77" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR75" t="inlineStr">
+      <c r="AR77" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS75" t="inlineStr">
+      <c r="AS77" t="inlineStr">
         <is>
           <t>plitafiltrorig</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>plita-filtr-pylniki</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 пыльника штоков мехатроника DSG7 DQ200 — расширенный комплект. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оба пыльника в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Дешевле, чем покупать плиту, фильтр и пыльники по отдельности.</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="S78" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=6562ad9b05
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=de55e47d7c
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_3.jpg?v=f0ac7e97a2</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + фильтр + 2 пыльника штоков</t>
         </is>
       </c>
-      <c r="AH76" t="n">
+      <c r="AH78" t="n">
         <v>6350</v>
       </c>
-      <c r="AJ76" t="inlineStr">
+      <c r="AJ78" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK76" t="inlineStr">
+      <c r="AK78" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL76" t="inlineStr">
+      <c r="AL78" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
+      <c r="AM78" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
+      <c r="AN78" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO76" t="inlineStr">
+      <c r="AO78" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR76" t="inlineStr">
+      <c r="AR78" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS76" t="inlineStr">
+      <c r="AS78" t="inlineStr">
         <is>
           <t>plitafiltrpylniki</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>🔧 Полный комплект для ремонта гидравлической части мехатроника DSG7 DQ200: усиленная гидроплита + фильтр + 2 пыльника + 2 сальника штоков. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Всё необходимое в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Самый полный и выгодный из линейки комплектов на базе усиленной плиты.</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="S79" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal_1.png?v=a621eafd77</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + фильтр + 2 пыльника + 2</t>
         </is>
       </c>
-      <c r="AH77" t="n">
+      <c r="AH79" t="n">
         <v>6850</v>
       </c>
-      <c r="AJ77" t="inlineStr">
+      <c r="AJ79" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK77" t="inlineStr">
+      <c r="AK79" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL77" t="inlineStr">
+      <c r="AL79" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
+      <c r="AM79" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
+      <c r="AN79" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO77" t="inlineStr">
+      <c r="AO79" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR77" t="inlineStr">
+      <c r="AR79" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS77" t="inlineStr">
+      <c r="AS79" t="inlineStr">
         <is>
           <t>plitafiltrpylnikisal</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита + фильтр + 2 ОРИГИНАЛЬНЫХ сальника Volkswagen мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита, фильтр и оригинальные сальники в одном заказе. 🔩 Артикул плиты 0AM325066AE. ⭐ Оригинальные сальники VAG — герметичнее аналогов на самом ответственном узле.</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr">
+      <c r="S80" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.jpg?v=38f0e2c7db
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_2.jpg?v=2107be3341</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>Усиленная плита + фильтр + 2 оригинальных</t>
         </is>
       </c>
-      <c r="AH78" t="n">
+      <c r="AH80" t="n">
         <v>6350</v>
       </c>
-      <c r="AJ78" t="inlineStr">
+      <c r="AJ80" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK78" t="inlineStr">
+      <c r="AK80" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL78" t="inlineStr">
+      <c r="AL80" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
+      <c r="AM80" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
+      <c r="AN80" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO78" t="inlineStr">
+      <c r="AO80" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR78" t="inlineStr">
+      <c r="AR80" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS78" t="inlineStr">
+      <c r="AS80" t="inlineStr">
         <is>
           <t>plitafiltrsalnikiorig</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>plita-filtr-v2</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + масляный фильтр — базовый комплект для ремонта гидравлической части. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Плита + фильтр за один заказ. 🔩 Артикул плиты 0AM325066AE. ⭐ Усиленная плита прочнее штатной — для вариантов с пыльниками/сальниками см. другие комплекты этой линейки.</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.jpg?v=17dc040af2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_2.jpg?v=aba4a8da4b</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + фильтр мехатроника DQ200</t>
         </is>
       </c>
-      <c r="AH79" t="n">
+      <c r="AH81" t="n">
         <v>5850</v>
       </c>
-      <c r="AJ79" t="inlineStr">
+      <c r="AJ81" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK79" t="inlineStr">
+      <c r="AK81" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL79" t="inlineStr">
+      <c r="AL81" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
+      <c r="AM81" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
+      <c r="AN81" t="inlineStr">
         <is>
           <t>Система смазки и охлаждения КПП</t>
         </is>
       </c>
-      <c r="AO79" t="inlineStr">
+      <c r="AO81" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR79" t="inlineStr">
+      <c r="AR81" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS79" t="inlineStr">
+      <c r="AS81" t="inlineStr">
         <is>
           <t>plitafiltrv2</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>plita-pylniki-salniki</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>🔧 Усиленная гидроплита мехатроника DSG7 DQ200 + 2 пыльника + 2 сальника штоков — комплект для ремонта гидравлической части без масляного фильтра. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: усиленная гидроплита, 2 пыльника и 2 сальника. ⭐ Стандартные расходники — доступная альтернатива версии с оригинальными VAG деталями (см. plita-pylniki-salniki-orig).</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr">
+      <c r="S82" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=fe0eb62b49
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_2.jpg?v=03ce24da06</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>Усиленная гидроплита + 2 пыльника + 2 сальника</t>
         </is>
       </c>
-      <c r="AH80" t="n">
+      <c r="AH82" t="n">
         <v>6350</v>
       </c>
-      <c r="AJ80" t="inlineStr">
+      <c r="AJ82" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK80" t="inlineStr">
+      <c r="AK82" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL80" t="inlineStr">
+      <c r="AL82" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
+      <c r="AM82" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
+      <c r="AN82" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO80" t="inlineStr">
+      <c r="AO82" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR80" t="inlineStr">
+      <c r="AR82" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS80" t="inlineStr">
+      <c r="AS82" t="inlineStr">
         <is>
           <t>plitapylnikisalniki</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>podshipnik-vilki-6</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>🔧 Подшипник вилки переключения 6-й передачи и заднего хода мехатроника DSG7 DQ200 — эти две передачи переключаются одной общей вилкой, поэтому подшипник один. ✅ Подходит на 0AM/0CW, устанавливается на Volkswagen (в т.ч. Jetta), Škoda, Audi, Seat. 📦 1 шт — именно на эту вилку, по сути мини-ремкомплект вилки задней передачи DSG7 DQ200.</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=2476776fae
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=1755bb55b2
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_3.jpg?v=db91a4455e</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>Подшипник вилки 6-й передачи и заднего хода DSG7</t>
         </is>
       </c>
-      <c r="AH81" t="n">
+      <c r="AH83" t="n">
         <v>950</v>
       </c>
-      <c r="AJ81" t="inlineStr">
+      <c r="AJ83" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK81" t="inlineStr">
+      <c r="AK83" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL81" t="inlineStr">
+      <c r="AL83" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
+      <c r="AM83" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
+      <c r="AN83" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO81" t="inlineStr">
+      <c r="AO83" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR81" t="inlineStr">
+      <c r="AR83" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS81" t="inlineStr">
+      <c r="AS83" t="inlineStr">
         <is>
           <t>podshipnikvilki6</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr">
+      <c r="S84" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki_1.png?v=b93ad38a77</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня</t>
         </is>
       </c>
-      <c r="AH82" t="n">
+      <c r="AH84" t="n">
         <v>2350</v>
       </c>
-      <c r="AJ82" t="inlineStr">
+      <c r="AJ84" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK82" t="inlineStr">
+      <c r="AK84" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL82" t="inlineStr">
+      <c r="AL84" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
+      <c r="AM84" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
+      <c r="AN84" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO82" t="inlineStr">
+      <c r="AO84" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR82" t="inlineStr">
+      <c r="AR84" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS82" t="inlineStr">
+      <c r="AS84" t="inlineStr">
         <is>
           <t>porshniusilpylnikikryshki</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>🔧 Ремкомплект обоих штоков мехатроника DSG7 DQ200: 2 УСИЛЕННЫХ поршня + 2 пыльника + 2 крышки. ✅ Подходит для мехатроников 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 В комплекте: 2 усиленных поршня толкателя, 2 пыльника, 2 крышки — меняете прямо на своих штоках, без разборки штока целиком. ⭐ Усиленный поршень — больше ресурс, чем у штатного.</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
+      <c r="S85" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня</t>
         </is>
       </c>
-      <c r="AH83" t="n">
+      <c r="AH85" t="n">
         <v>2350</v>
       </c>
-      <c r="AJ83" t="inlineStr">
+      <c r="AJ85" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK83" t="inlineStr">
+      <c r="AK85" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL83" t="inlineStr">
+      <c r="AL85" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
+      <c r="AM85" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN83" t="inlineStr">
+      <c r="AN85" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO83" t="inlineStr">
+      <c r="AO85" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR83" t="inlineStr">
+      <c r="AR85" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS83" t="inlineStr">
+      <c r="AS85" t="inlineStr">
         <is>
           <t>porshniusilpylnikikryshkiv2</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>🔧 Прокладка крышки (поддона) мехатроника DSG7 DQ200 — герметизирует соединение крышки с корпусом, предотвращает подтёки масла.
 ✅ Подходит: Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200, мехатроники 0AM / 0CW.
@@ -8253,77 +8427,77 @@
 🔩 Артикул: prokladka-kryshki-dq200.</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr">
+      <c r="S86" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-kryshki-dq200_1.png?v=be7cbb92a8</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>Прокладка крышки мехатроника DSG7 DQ200 0AM 0CW</t>
         </is>
       </c>
-      <c r="AH84" t="n">
+      <c r="AH86" t="n">
         <v>950</v>
       </c>
-      <c r="AJ84" t="inlineStr">
+      <c r="AJ86" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK84" t="inlineStr">
+      <c r="AK86" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL84" t="inlineStr">
+      <c r="AL86" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
+      <c r="AM86" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN84" t="inlineStr">
+      <c r="AN86" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO84" t="inlineStr">
+      <c r="AO86" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR84" t="inlineStr">
+      <c r="AR86" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS84" t="inlineStr">
+      <c r="AS86" t="inlineStr">
         <is>
           <t>prokladkakryshkidq200</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>🔧 Комплект 2 шт колец-прокладок на 1 втулку (гильзу) штока мехатроника DSG7 DQ200 (зеленое + черное) — уплотняют посадку втулки, предотвращают потерю давления.
 ✅ Подходит на все гильзы (втулки) штоков.
@@ -8332,77 +8506,77 @@
 🔩 Артикул: prokladka-vtulki-dq200.</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=e3f97523c1</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>2 кольца-прокладки на 1 втулку мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH85" t="n">
+      <c r="AH87" t="n">
         <v>950</v>
       </c>
-      <c r="AJ85" t="inlineStr">
+      <c r="AJ87" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK85" t="inlineStr">
+      <c r="AK87" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL85" t="inlineStr">
+      <c r="AL87" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
+      <c r="AM87" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN85" t="inlineStr">
+      <c r="AN87" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO85" t="inlineStr">
+      <c r="AO87" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR85" t="inlineStr">
+      <c r="AR87" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS85" t="inlineStr">
+      <c r="AS87" t="inlineStr">
         <is>
           <t>prokladkavtulkidq200</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>prokladka-vtulki-niz-dq200</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>🔧 Черное кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Уплотняет посадку втулки, предотвращает потерю давления.
 ✅ Подходит на все гильзы (втулки) штоков.
@@ -8412,77 +8586,77 @@
 🔩 Артикул: prokladka-vtulki-niz-dq200.</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="S88" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-niz-dq200_1.png?v=6c730c6907</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>Черное кольцо-прокладка втулки мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH86" t="n">
+      <c r="AH88" t="n">
         <v>650</v>
       </c>
-      <c r="AJ86" t="inlineStr">
+      <c r="AJ88" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK86" t="inlineStr">
+      <c r="AK88" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL86" t="inlineStr">
+      <c r="AL88" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
+      <c r="AM88" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN86" t="inlineStr">
+      <c r="AN88" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO86" t="inlineStr">
+      <c r="AO88" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR86" t="inlineStr">
+      <c r="AR88" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS86" t="inlineStr">
+      <c r="AS88" t="inlineStr">
         <is>
           <t>prokladkavtulkinizdq200</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>prokladka-vtulki-verh-dq200</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>🔧 Зеленое кольцо-прокладка втулки (гильзы) штока мехатроника DSG7 DQ200, 1 шт. Уплотняет посадку втулки, предотвращает потерю давления.
 ✅ Подходит на все гильзы (втулки) штоков.
@@ -8492,283 +8666,133 @@
 🔩 Артикул: prokladka-vtulki-verh-dq200.</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr">
+      <c r="S89" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-verh-dq200_1.png?v=f7366cb6a0</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>Зеленое кольцо-прокладка втулки мехатроника DSG7</t>
         </is>
       </c>
-      <c r="AH87" t="n">
+      <c r="AH89" t="n">
         <v>650</v>
       </c>
-      <c r="AJ87" t="inlineStr">
+      <c r="AJ89" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK87" t="inlineStr">
+      <c r="AK89" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL87" t="inlineStr">
+      <c r="AL89" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
+      <c r="AM89" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN87" t="inlineStr">
+      <c r="AN89" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO87" t="inlineStr">
+      <c r="AO89" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR87" t="inlineStr">
+      <c r="AR89" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS87" t="inlineStr">
+      <c r="AS89" t="inlineStr">
         <is>
           <t>prokladkavtulkiverhdq200</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>salnik-shtoka-orig</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr">
+      <c r="S90" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH88" t="n">
+      <c r="AH90" t="n">
         <v>950</v>
       </c>
-      <c r="AJ88" t="inlineStr">
+      <c r="AJ90" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK88" t="inlineStr">
+      <c r="AK90" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL88" t="inlineStr">
+      <c r="AL90" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
+      <c r="AM90" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
+      <c r="AN90" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO88" t="inlineStr">
+      <c r="AO90" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR88" t="inlineStr">
+      <c r="AR90" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS88" t="inlineStr">
+      <c r="AS90" t="inlineStr">
         <is>
           <t>salnikshtokaorig</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>salnik-shtoka-orig-v2</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
-        </is>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
-        </is>
-      </c>
-      <c r="AH89" t="n">
-        <v>950</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL89" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr">
-        <is>
-          <t>salnikshtokaorigv2</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>salnik-tolkatelya-alum</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
-        </is>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Усиленные алюминиевые сальники толкателя с</t>
-        </is>
-      </c>
-      <c r="AH90" t="n">
-        <v>1350</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>salniktolkatelyaalum</t>
         </is>
       </c>
     </row>
@@ -8780,329 +8804,329 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
+          <t>salnik-shtoka-orig-v2</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>🔧 Оригинальный (VAG) сальник одного штока мехатроника DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Продаётся поштучно — для комплекта на 2 штока см. salniki-shtokov-orig.</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig-v2_1.png?v=197acf8189</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DQ200 DSG7</t>
+        </is>
+      </c>
+      <c r="AH91" t="n">
+        <v>950</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR91" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>salnikshtokaorigv2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>salnik-tolkatelya-alum</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>🔧 Усиленные сальники толкателя мехатроника DSG7 DQ200 на алюминиевой основе с гальваническим покрытием — комплект 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте, прочнее штатных пластиковых/резиновых аналогов. ⭐ Для тех, кто уже не раз менял штатные сальники толкателей и хочет более долговечное решение.</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Усиленные алюминиевые сальники толкателя с</t>
+        </is>
+      </c>
+      <c r="AH92" t="n">
+        <v>1350</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR92" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>salniktolkatelyaalum</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
           <t>salniki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>🔧 Сальники обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Устраняет течь масла сразу с обеих сторон, а не только с одной.</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr">
+      <c r="S93" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=08b49883ce
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_2.jpg?v=aa8f5c5cf2</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>Сальники штоков мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
-      <c r="AH91" t="n">
+      <c r="AH93" t="n">
         <v>950</v>
       </c>
-      <c r="AJ91" t="inlineStr">
+      <c r="AJ93" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK91" t="inlineStr">
+      <c r="AK93" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL91" t="inlineStr">
+      <c r="AL93" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
+      <c r="AM93" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
+      <c r="AN93" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO91" t="inlineStr">
+      <c r="AO93" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR91" t="inlineStr">
+      <c r="AR93" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS91" t="inlineStr">
+      <c r="AS93" t="inlineStr">
         <is>
           <t>salnikishtokov2sht</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>salniki-shtokov-orig</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="P94" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>🔧 Оригинальные (VAG) сальники обоих штоков мехатроника DSG7 DQ200 — 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект на 2 штока. ⭐ Оригинал VAG — герметичнее аналогов, меньше риск повторной течи.</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr">
+      <c r="S94" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH92" t="n">
+      <c r="AH94" t="n">
         <v>950</v>
       </c>
-      <c r="AJ92" t="inlineStr">
+      <c r="AJ94" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK92" t="inlineStr">
+      <c r="AK94" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL92" t="inlineStr">
+      <c r="AL94" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
+      <c r="AM94" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr">
+      <c r="AN94" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO92" t="inlineStr">
+      <c r="AO94" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR92" t="inlineStr">
+      <c r="AR94" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS92" t="inlineStr">
+      <c r="AS94" t="inlineStr">
         <is>
           <t>salnikishtokovorig</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="P95" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>🔧 Полный комплект сальников толкателей (поршней) вилок мехатроника DSG7 DQ200 — 4 шт, на все толкатели сразу. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4 шт в комплекте — без поршней/толкателей, только сами сальники. ⭐ Для замены сальников без разборки под замену самих толкателей.</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr">
+      <c r="S95" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>Полный комплект сальников толкателей вилок</t>
-        </is>
-      </c>
-      <c r="AH93" t="n">
-        <v>950</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr">
-        <is>
-          <t>salnikitolkatelya4sht</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>salnikprivod-l</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>Сальник привода левый DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH94" t="n">
-        <v>950</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL94" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>Прокладки и уплотнения КПП</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>salnikprivodl</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>salnikprivod-r</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Сальник привода правый DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH95" t="n">
@@ -9145,7 +9169,7 @@
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>salnikprivodr</t>
+          <t>salnikitolkatelya4sht</t>
         </is>
       </c>
     </row>
@@ -9157,320 +9181,470 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
+          <t>salnikprivod-l</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>🔧 Сальник левого привода мехатроника/коробки DSG7 DQ200 — уплотняет место выхода левого приводного вала. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также правый сальник привода (отдельная позиция). ⭐ Частая причина масляных пятен под левым колесом при работающем двигателе.</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Сальник привода левый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH96" t="n">
+        <v>950</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>salnikprivodl</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>salnikprivod-r</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>🔧 Сальник правого привода мехатроника/коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 🔩 См. также левый сальник привода (отдельная позиция). ⭐ Меняется при течи со стороны правого приводного вала.</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Сальник привода правый DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="AH97" t="n">
+        <v>950</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>salnikprivodr</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
           <t>salnikvhod</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr">
+      <c r="P98" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="Q98" t="inlineStr">
         <is>
           <t>🔧 Сальник входного вала коробки DSG7 DQ200 — со стороны двигателя, уплотняет вход первичного вала в коробку. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Течь масла в зоне соединения двигателя и коробки чаще всего связана именно с этим сальником.</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr">
+      <c r="S98" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>Сальник входного вала DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH96" t="n">
+      <c r="AH98" t="n">
         <v>950</v>
       </c>
-      <c r="AJ96" t="inlineStr">
+      <c r="AJ98" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK96" t="inlineStr">
+      <c r="AK98" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL96" t="inlineStr">
+      <c r="AL98" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
+      <c r="AM98" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN96" t="inlineStr">
+      <c r="AN98" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO96" t="inlineStr">
+      <c r="AO98" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR96" t="inlineStr">
+      <c r="AR98" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS96" t="inlineStr">
+      <c r="AS98" t="inlineStr">
         <is>
           <t>salnikvhod</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>salnikvihod</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q97" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>🔧 Сальник выходного вала коробки DSG7 DQ200. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Меняется при течи масла со стороны выходного (вторичного) вала коробки.</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvihod_1.png?v=eed61310d0</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>Сальник выходного вала DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH97" t="n">
+      <c r="AH99" t="n">
         <v>950</v>
       </c>
-      <c r="AJ97" t="inlineStr">
+      <c r="AJ99" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK97" t="inlineStr">
+      <c r="AK99" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL97" t="inlineStr">
+      <c r="AL99" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
+      <c r="AM99" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN97" t="inlineStr">
+      <c r="AN99" t="inlineStr">
         <is>
           <t>Прокладки и уплотнения КПП</t>
         </is>
       </c>
-      <c r="AO97" t="inlineStr">
+      <c r="AO99" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR97" t="inlineStr">
+      <c r="AR99" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS97" t="inlineStr">
+      <c r="AS99" t="inlineStr">
         <is>
           <t>salnikvihod</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="P100" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>🔧 Сепараторная пластина мехатроника DSG7 DQ200 — устанавливается под гидроплиту, разделяет каналы.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новая, с завода, отправка в день заказа.</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="S100" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastina-dq200_1.png?v=7ff85d1a3c</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>Сепараторная пластина мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH98" t="n">
+      <c r="AH100" t="n">
         <v>950</v>
       </c>
-      <c r="AJ98" t="inlineStr">
+      <c r="AJ100" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK98" t="inlineStr">
+      <c r="AK100" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL98" t="inlineStr">
+      <c r="AL100" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
+      <c r="AM100" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
+      <c r="AN100" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO98" t="inlineStr">
+      <c r="AO100" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR98" t="inlineStr">
+      <c r="AR100" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS98" t="inlineStr">
+      <c r="AS100" t="inlineStr">
         <is>
           <t>separatornayaplastinadq200</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="P101" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q99" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>🔧 Комплект: сепараторная пластина + 2 пластины на соленоиды мехатроника DSG7 DQ200.
 ✅ Volkswagen, Škoda, Audi, Seat с коробкой DSG7 DQ200.
 📦 Новые, с завода.</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr">
+      <c r="S101" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastiny-solenoid-dq200_1.png?v=6b8ccfb635</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>Сепараторная пластина + пластины на соленоиды</t>
         </is>
       </c>
-      <c r="AH99" t="n">
+      <c r="AH101" t="n">
         <v>1350</v>
       </c>
-      <c r="AJ99" t="inlineStr">
+      <c r="AJ101" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK99" t="inlineStr">
+      <c r="AK101" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL99" t="inlineStr">
+      <c r="AL101" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
+      <c r="AM101" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
+      <c r="AN101" t="inlineStr">
         <is>
           <t>Электронное управление КПП</t>
         </is>
       </c>
-      <c r="AO99" t="inlineStr">
+      <c r="AO101" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR99" t="inlineStr">
+      <c r="AR101" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS99" t="inlineStr">
+      <c r="AS101" t="inlineStr">
         <is>
           <t>separatornayaplastinysolenoiddq200</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="102">
+      <c r="A102" t="inlineStr">
         <is>
           <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D102" t="inlineStr">
         <is>
           <t>solenoid-02e-0b5-bolshoy</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr">
+      <c r="P102" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="Q102" t="inlineStr">
         <is>
           <t>🔧 Восстановленный соленоид сцепления K1/K2 ("большой", multiplexer) — для DSG6 02E DQ250, DSG7 0BH/0BT DQ500, DL501 0B5.
 ✅ Volkswagen, Audi, Škoda, Seat с коробками 02E/DQ250, DQ500, 0B5/DL501.
@@ -9479,159 +9653,9 @@
 🔩 Артикул: solenoid-02e-0b5-bolshoy.</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>Восстановленный соленоид 02E 0B5 DQ250 DQ500</t>
-        </is>
-      </c>
-      <c r="AH100" t="n">
-        <v>4350</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL100" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr">
-        <is>
-          <t>solenoid02e0b5bolshoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>stalnaya-vstavka-plity</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
-        </is>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
-        </is>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="AH101" t="n">
-        <v>1850</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>Запчасти</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Товар приобретен на продажу</t>
-        </is>
-      </c>
-      <c r="AL101" t="inlineStr">
-        <is>
-          <t>Для автомобилей</t>
-        </is>
-      </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>Трансмиссия и привод</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>Электронное управление КПП</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Новое</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>VOLKSWAGEN</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr">
-        <is>
-          <t>stalnayavstavkaplity</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>tolkateli-4-salniki-4</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>Запчасти и аксессуары</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
-        </is>
-      </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7</t>
         </is>
       </c>
       <c r="AH102" t="n">
@@ -9659,7 +9683,7 @@
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Электронное управление КПП</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -9674,7 +9698,7 @@
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>tolkateli4salniki4</t>
+          <t>solenoid02e0b5bolshoy</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9710,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -9696,21 +9720,21 @@
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+          <t>🔧 Стальная вставка гидроплиты мехатроника DSG7 DQ200 — усиливает посадочные места плиты, снижает риск деформации каналов. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. ⭐ Ставится вместе с гидроплитой при капитальном ремонте гидравлической части.</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные</t>
+          <t>Стальная вставка гидроплиты мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH103" t="n">
-        <v>4850</v>
+        <v>1850</v>
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
@@ -9734,7 +9758,7 @@
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>Прокладки и уплотнения КПП</t>
+          <t>Электронное управление КПП</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -9749,7 +9773,7 @@
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>tolkatelisalnikialumkomplekt</t>
+          <t>stalnayavstavkaplity</t>
         </is>
       </c>
     </row>
@@ -9761,68 +9785,218 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>🔧 Все 4 толкателя (поршня) вилок переключения + все 4 сальника толкателей мехатроника DSG7 DQ200 — полный комплект на весь мехатроник. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 4+4 деталей в одном заказе — не нужно докупать по отдельности. ⭐ Самый выгодный вариант при капитальном ремонте всех вилок мехатроника сразу.</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
+        </is>
+      </c>
+      <c r="X104" t="inlineStr">
+        <is>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7</t>
+        </is>
+      </c>
+      <c r="AH104" t="n">
+        <v>4350</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>tolkateli4salniki4</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Запчасти и аксессуары</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>🔧 Полный набор для капитального ремонта вилок мехатроника DSG7 DQ200: 4 толкателя (поршня) + 4 штатных сальника + 4 усиленных алюминиевых сальника с гальваническим покрытием. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 Комплект 4+4+4 — 12 деталей одним заказом. ⭐ Самый полный вариант: если ставите усиленные алюминиевые сальники, штатные тоже пригодятся про запас.</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Толкатели вилок + сальники + усиленные</t>
+        </is>
+      </c>
+      <c r="AH105" t="n">
+        <v>4850</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>Запчасти</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Товар приобретен на продажу</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr">
+        <is>
+          <t>Для автомобилей</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>Трансмиссия и привод</t>
+        </is>
+      </c>
+      <c r="AN105" t="inlineStr">
+        <is>
+          <t>Прокладки и уплотнения КПП</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>Новое</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>VOLKSWAGEN</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>tolkatelisalnikialumkomplekt</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Московская область, Ленинский городской округ, рабочий посёлок Дрожжино, Южная улица, 13, Щербинка</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="P106" t="inlineStr">
         <is>
           <t>Запчасти и аксессуары</t>
         </is>
       </c>
-      <c r="Q104" t="inlineStr">
+      <c r="Q106" t="inlineStr">
         <is>
           <t>🔧 Втулки (гильзы) обоих штоков мехатроника DSG7 DQ200 — комплект 2 шт. ✅ 0AM/0CW, Volkswagen/Škoda/Audi/Seat. 📦 На оба штока сразу. ⭐ Меняются парой со штоками — новые втулки без новых штоков не устранят люфт полностью.</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
-      <c r="AH104" t="n">
+      <c r="AH106" t="n">
         <v>2850</v>
       </c>
-      <c r="AJ104" t="inlineStr">
+      <c r="AJ106" t="inlineStr">
         <is>
           <t>Запчасти</t>
         </is>
       </c>
-      <c r="AK104" t="inlineStr">
+      <c r="AK106" t="inlineStr">
         <is>
           <t>Товар приобретен на продажу</t>
         </is>
       </c>
-      <c r="AL104" t="inlineStr">
+      <c r="AL106" t="inlineStr">
         <is>
           <t>Для автомобилей</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
+      <c r="AM106" t="inlineStr">
         <is>
           <t>Трансмиссия и привод</t>
         </is>
       </c>
-      <c r="AN104" t="inlineStr">
+      <c r="AN106" t="inlineStr">
         <is>
           <t>Переключение передач</t>
         </is>
       </c>
-      <c r="AO104" t="inlineStr">
+      <c r="AO106" t="inlineStr">
         <is>
           <t>Новое</t>
         </is>
       </c>
-      <c r="AR104" t="inlineStr">
+      <c r="AR106" t="inlineStr">
         <is>
           <t>VOLKSWAGEN</t>
         </is>
       </c>
-      <c r="AS104" t="inlineStr">
+      <c r="AS106" t="inlineStr">
         <is>
           <t>vtulkishtokov2sht</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -9736,6 +9736,11 @@
       <c r="AH103" t="n">
         <v>1850</v>
       </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_video.mp4?v=c4a1d424d7</t>
+        </is>
+      </c>
       <c r="AJ103" t="inlineStr">
         <is>
           <t>Запчасти</t>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -5019,6 +5019,11 @@
       <c r="AH44" t="n">
         <v>950</v>
       </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_video.mp4?v=4573c3be6d</t>
+        </is>
+      </c>
       <c r="AJ44" t="inlineStr">
         <is>
           <t>Запчасти</t>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -8910,6 +8910,11 @@
       <c r="AH92" t="n">
         <v>1350</v>
       </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_video.mp4?v=bbf75624cd</t>
+        </is>
+      </c>
       <c r="AJ92" t="inlineStr">
         <is>
           <t>Запчасти</t>
@@ -9895,6 +9900,11 @@
       </c>
       <c r="AH105" t="n">
         <v>4850</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_video.mp4?v=bbf75624cd</t>
+        </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -3677,6 +3677,11 @@
       <c r="AH28" t="n">
         <v>68500</v>
       </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_video.mp4?v=15fc20f523</t>
+        </is>
+      </c>
       <c r="AJ28" t="inlineStr">
         <is>
           <t>Запчасти</t>
@@ -3770,6 +3775,11 @@
       </c>
       <c r="AH29" t="n">
         <v>68500</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HXF_video.mp4?v=15fc20f523</t>
+        </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4338,7 +4338,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025m-av</t>
         </is>
       </c>
       <c r="I36" t="n">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2196,8 +2196,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0AM325025B</t>
-        </is>
+          <t>0AM325025B-av</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4124730141</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -2773,8 +2776,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
-        </is>
+          <t>0AM325587E-av</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>4284880578</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -3289,8 +3295,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0am325025</t>
-        </is>
+          <t>0am325025-av</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>4220978299</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -3367,8 +3376,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0am325025D</t>
-        </is>
+          <t>0am325025D-av</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>3964711787</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -3447,8 +3459,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0am325025G</t>
-        </is>
+          <t>0am325025G-av</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>4572853508</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -5083,8 +5098,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
-        </is>
+          <t>0am325066ad-av</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>4124845206</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -6225,8 +6243,11 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
-        </is>
+          <t>123014‑AF-av</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>4284733993</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -6506,8 +6527,8 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6527,8 +6527,8 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2908,6 +2908,11 @@
       <c r="AH19" t="n">
         <v>42500</v>
       </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_video.mp4?v=843d5fd39f</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>Запчасти</t>
@@ -2987,6 +2992,11 @@
       </c>
       <c r="AH20" t="n">
         <v>42500</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_video.mp4?v=843d5fd39f</t>
+        </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6537,8 +6537,8 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -3326,7 +3326,11 @@
       <c r="S24" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpeg?v=816487a239
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_1.jpg?v=45096a261b</t>
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png?v=0a275c4f18
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_3.png?v=9f571585c3
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_4.png?v=2ec99b161d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_5.png?v=fce0696edd
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_6.png?v=19f05c95c1</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6183,9 +6183,9 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, комплект
-Пыльники штоков мехатроника DSG 7 DQ200 0AM 0CW
-Набор пыльников (чехлов) защитных для штоков толкателей мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.
+          <t>Пыльник штока мехатроника DSG7 DQ200 (0AM / 0CW), защита толкателя вилки сцепления, 1 шт
+Пыльник штока мехатроника DSG 7 DQ200 0AM 0CW
+Пыльник (чехол) защитный для штока толкателя мехатроника DSG7 DQ200 (варианты 0AM / 0CW). Используется при ремонте мехатроника автомобиля Audi, VW, Skoda, Seat — защищает элементы штоков от загрязнений, продлевая срок службы коробки передач.
 ✔️Используется в мехатроник DSG 7 DQ200 0AM 0CW
 ✔️Новый пыльник штоков мехатроника DSG 7 DQ200 поставляется напрямую с завода!
 ✔️Пыльник мехатроника DSG 7 всегда в наличии
@@ -6541,8 +6541,8 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6196,8 +6196,11 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>https://ir-20.ozone.ru/s3/multimedia-1-a/14848106518.jpg
-https://ir-20.ozone.ru/s3/multimedia-1-q/7418270474.jpg</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_1.png?v=2c2ec12303
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_2.png?v=6165752180
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_3.png?v=bd6892c018
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_4.png?v=cfa7b1abb1
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/122390AK-AF_5.png?v=58f7e9e533</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -6541,8 +6544,8 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2791,28 +2791,18 @@
         <is>
           <t>🔩 Гидроаккумулятор мехатроника DSG 7 DQ200 (0AM325587E)
 📦 Назначение:
-Компенсирует утечку давления, возникающую при перегреве или износе уплотнений.
-Поддерживает давление в системе до срабатывания предохранительного клапана и перегрева масла (до ~60 бар).
+Хранит запас давления масла в гидравлике мехатроника DSG7 DQ200 и обеспечивает быстрое срабатывание сцеплений и переключение передач.
+Газовый (азотный) гидроаккумулятор, устанавливается в штатное место в гидроплите мехатроника.
 ✅ Совместимость:
-DSG 7 (DQ200), мехатроники 0AM/0CW
-Volkswagen, Audi, Skoda, Seat (2007–2023 и далее)
+DSG 7 (DQ200), мехатроники 0AM / 0CW
+Volkswagen, Audi, Skoda, Seat
 Артикул: 0AM325587E
-📌 Признаки износа/неисправности:
-Рывки при трогании с места
-Долгое задержание передач D/R
-Код ошибки (например, P0841)
-Появление металлической стружки в масле
-Вибрация или «выстрел» в момент переключения - все это ВОЗМОЖНЫЕ симптомы неисправности гидроаккумулятора DSG7 DQ200
-💡 Преимущества замены:
-Снижает риск повреждения мехатроника и сцепления
-Увеличивает ресурс гидроблока
-📦 Отправка — максимально быстро
-Новый газо-масляный гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW). Устанавливается в штатное место в корпусе гидроблока, стабилизирует давление масла, предотвращая ошибки P17BF, P189C и P1895.
-Современно выполненный, соответствует заводской спецификации, совместим с VW, Audi, Skoda, Seat. Отличная замена при утечке или потере давления.
-Номер 0am325587e
-Отличное качество гидроаккумулятора дсг7
-Гидроаккумулятор dsg 7 всегда в наличии
-Новые гидроаккумуляторы мехатроника dsg7 dq200 напрямую с завода!</t>
+📌 Когда проверяют гидроаккумулятор:
+Ошибки P17BF / P189C — давление в гидравлике мехатроника не держится, насос работает дольше обычного
+Такие же ошибки бывают при трещине гидроплиты и износе уплотнений. Точную причину показывает диагностика давления и времени работы насоса мехатроника.
+🔧 Уплотнительное кольцо — в комплекте (как на фото).
+Новый гидроаккумулятор для мехатроника DSG7 DQ200 (0AM / 0CW) — Volkswagen, Audi, Skoda, Seat. Номер 0am325587e.
+📦 Отправка — максимально быстро</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -3309,7 +3309,7 @@
       <c r="Q24" t="inlineStr">
         <is>
           <t>Ремкомплект мехатроника DSG 7 DQ200 подходит для восстановления и обслуживания трансмиссии DQ200. В комплект входят прокладки мехатроника, прокладка крышки, плита мехатроника, сальники, уплотнения и гидроплита DSG как на фото. Используется когда нужно заменить гидроплиту DSG 7 и ремкомплект dq200 прокладок мехатроника. Совместим с коробками DQ200 DSG 7 0am и DSG 7 DQ200 0cw. Детали подходят на все мехатроники DSG DQ200, имеют высокое качество и подходят для самостоятельного или профессионального ремонта. Идеальное решение, если вам нужно купить прокладки, ремкомплект мехатроника DSG или гидроплиту для DSG 7 вместе!
-Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C, P1895. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.
+Полный ремкомплект для ремонта мехатроника DSG7 DQ200 (0AM / 0CW). Включает усиленную алюминиевую гидроплиту и полный набор прокладок: уплотнение крышки мехатроника, прокладку поддона, кольца под соленоиды, сальники штоков, пыльники, манжеты и другие уплотнения. Решает проблему просадок давления, износа герметиков и трещин в гидроплите. Используется при капитальном ремонте DSG7 и профилактике ошибок P17BF, P189C. Подходит для автомобилей Volkswagen, Audi, Skoda, Seat.
 🔩 Артикул: 0am325025.</t>
         </is>
       </c>
@@ -3319,7 +3319,7 @@
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_2.png?v=0a275c4f18
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_3.png?v=9f571585c3
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_4.png?v=2ec99b161d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_5.png?v=fce0696edd
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_5.png?v=325f3a05a7
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025_6.png?v=19f05c95c1</t>
         </is>
       </c>
@@ -3570,7 +3570,7 @@
 Высокое гидравлическое давление + тонкая стенка корпуса → трещины и утечка давления. При этом страдают гидравлическая плита, соленоиды, гидроаккумулятор → проявляются ошибки, неадекватные переключения, потеря тяги.
 Поломки соленоидов, износ манжет и прокладок, проблемы с герметичностью.
 Типичные симптомы:
-ошибки давления (P17BF, P189C/P1895, P06293 и др.)
+ошибки давления (P17BF, P189C и др.)
 грубые переключения, рывки, потеря передачи, «толчки» при старте или переключениях
 «Мёртвый» режим (лимп-мод), невозможность переключения, отсутствие задней или 6-й передачи
 ⚙️ Почему стоит купить именно этот мехатроник
@@ -5195,7 +5195,7 @@
       <c r="Q46" t="inlineStr">
         <is>
           <t>🔩 Усиленная гидроплита DSG7 DQ200 0AM325066AE / 0CW
-Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P1895 и тд при интенсивной эксплуатации.
+Алюминиевая усиленная гидроплита для мехатроника DSG7 DQ200 (0AM/0CW). Утолщенная стенка обеспечивает увеличение ресурса, предупреждает трещины и ошибки P17BF/P189C и тд при интенсивной эксплуатации.
 ✅ Совместимость:
 • DSG7 DQ200 (7‑ступ., сухое сцепление)
 • VW, Audi, Skoda, Seat (2007–2025)
@@ -6534,8 +6534,8 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -5202,11 +5202,11 @@
 • Артикулы: 0AM325066AE, 0AM325066AC, 0AM325066C
 📌 Когда ставить:
 • OEM‑плита деформирована или треснула
-• При появлении ошибок гидроплита (P17BF, P1895 и др.)
+• При появлении ошибок давления (P17BF, P189C)
 • В условиях городской езды или частого переключения передач
 📦 Очень быстрая отправка
 👉 Обновите гидроплиту сейчас — забудьте о трещинах и падении давления DSG7
-Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Исключает ошибки P17BF, P189C, P1895 и тд. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw
+Усиленная алюминиевая гидроплита для мехатроника коробки DSG7 DQ200 (0AM / 0CW). Заменяет штатную плиту, подверженную трещинам и деформации. Убирает ошибки давления P17BF, P189C, если их причина — трещина штатной плиты. Устанавливается в штатное посадочное место без доработок. Совместима с автомобилями Volkswagen, Audi, Skoda, Seat, оборудованными 7-ступенчатой коробкой DSG DQ200 0am 0cw
 🔩 Подходит для СТО и самостоятельного ремонта.
 Всегда в наличии усиленная гидроплита мехатроника DSG7 DQ200 0AM325066 0CW
 Установка данной плиты ДСГ7 решает проблему c давлением в мехатронике 0am325025 (ошибки P17BF и т.д.).

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6534,8 +6534,8 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4856,11 +4856,10 @@
 Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.
 ✅ Совместимость:
 • DSG7 DQ200 (7 ступ., сухое сцепление)
-• VW/Audi/Skoda/Seat (до 2012 г)
+• VW/Audi/Skoda/Seat
 • Артикул штока: 0AM325091F
 📌 Когда нужен:
 • Люфт или износ штока или втулки (гильзы)
-• Ошибки сцепления / гидроблока
 • Профилактика или ремонт мехатроника
 💡 Особенности:
 • Шток 99 мм — точный, заводской размер
@@ -4873,7 +4872,9 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_2.png?v=ceee164228
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_3.png?v=2ca83e0e5a</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -6535,8 +6535,8 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4117,8 +4117,9 @@
 Коробка DSG 7 DQ200
 Мехатроники с кодами 0AM, 0CW
 Штоки:
-0AM325091F — короткий, 99 мм (до 2012 года)
-0AM325091E — длинный, 101 мм (после 2012 года) - ремкомплект подходит на оба типа
+0AM325091F — короткий, 99 мм (примерно с 2012 модельного года)
+0AM325091E — длинный, 101 мм (примерно до 2012 модельного года) — ремкомплект подходит на оба типа
+⚠️ Не путайте длинный 101 мм (0AM325091E) и короткий 99 мм (0AM325091F) — сверяйте длину старого штока и год машины
 💡 Почему стоит купить:
 Устраняет подтёки и продлевает срок службы мехатроника dsg7 dq200
 Подходит для профилактики и ремонта
@@ -4856,13 +4857,14 @@
 Комплект: короткий шток сцепления 0AM325091F (99 мм) + гильза мехатроника dsg7 dq200. Устранит люфт, обеспечит точность и надёжность сцепления.
 ✅ Совместимость:
 • DSG7 DQ200 (7 ступ., сухое сцепление)
-• VW/Audi/Skoda/Seat
+• VW/Audi/Skoda/Seat (примерно с 2012 модельного года)
 • Артикул штока: 0AM325091F
 📌 Когда нужен:
 • Люфт или износ штока или втулки (гильзы)
 • Профилактика или ремонт мехатроника
 💡 Особенности:
-• Шток 99 мм — точный, заводской размер
+• Шток 99 мм — точный, заводской размер
+⚠️ Не путайте длинный 101 мм (0AM325091E) и короткий 99 мм (0AM325091F) — сверяйте длину старого штока и год машины
 • Новая втулка — без царапин и задиров
 • Отличное качество материалов
 📦 Очень быстрая отправка
@@ -5292,21 +5294,20 @@
       <c r="Q47" t="inlineStr">
         <is>
           <t>🔩 Усиленный (с доп. Резинкой) Шток мехатроника DSG7 DQ200 0AM325091E (101 мм)
-Длинный шток 101 мм для DSG7 DQ200 (0AM/0CW), нового образца — после 2012 года. Обеспечивает точную и стабильную работу сцепления и коробки передач в целом
+Длинный шток 101 мм первого поколения для DSG7 DQ200 (0AM/0CW) — автомобили примерно до 2012 модельного года (мехатроник 0AM325025D). Обеспечивает точную и стабильную работу сцепления и коробки передач в целом
 ✅ Совместимость:
 • DSG7 DQ200 (7‑ступ., сухое сцепление)
-• VW, Audi, Skoda, Seat (2012–2025)
-• Артикул: 0AM325091E (длинный шток, новый тип)
+• VW, Audi, Skoda, Seat (примерно до 2012 модельного года)
+• Артикул: 0AM325091E (длинный шток, первое поколение)
 📌 Заменять, если:
 • Появился люфт, коррозия или выработка
-• Проблемы при включении передач
 • Планируется плановый ремонт мехатроника
 💡 Особенности:
 • Длина — 101 мм
+⚠️ Не путайте длинный 101 мм (0AM325091E) и короткий 99 мм (0AM325091F) — сверяйте длину старого штока и год машины
 📦 Очень быстрая отправка
-👉 Избавьтесь от ошибок включения передач или течи в штоках— обновите шток и увеличите ресурс мехатроника
-Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7, устраняет проблемы в том числе с включением передач.
-В наличии оригинальные штоки DSG7 DQ200 0AM 0CW
+👉 Обновите шток и увеличьте ресурс мехатроника
+Шток мехатроника DSG7, длиной 101 мм, используется в роботизированных коробках передач DQ200 (0AM / 0CW) для корректной работы мехатроника. Артикул 0AM325091E. Подходит для автомобилей Volkswagen, Skoda и Audi с коробкой DSG7. Применяется при ремонте мехатроника dq200 dsg7.
 Идеальное состояние - каждый шток дсг 7 dq200 проверяется
 Штоки dq200 всегда в наличии
 Длинные 0am325091e

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4109,10 +4109,10 @@
         <is>
           <t>🔧 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW)
 Для устранения подтёков масла без полной разборки мехатроника. Подходит под оба типа штока: короткий и длинный.
-📦 Комплектация:
-Сальник штока
-Пыльник штока
-Крышка штока
+📦 Комплектация (на оба штока):
+Сальник штока — 2 шт.
+Пыльник штока — 2 шт.
+Крышка штока — 2 шт.
 ✅ Совместимость:
 Коробка DSG 7 DQ200
 Мехатроники с кодами 0AM, 0CW
@@ -4126,10 +4126,10 @@
 Не требует специнструмента — подходит для самостоятельной замены
 📦 Высылаем быстро
 👉 Готов к установке — бери и ставь без лишней головной боли
-В комплекте
-Пыльник штока dq200
-Сальник штока dsg7
-Крышка штока мехатроника
+В комплекте на 2 штока
+Пыльник штока dq200 — 2 шт.
+Сальник штока dsg7 — 2 шт.
+Крышка штока мехатроника — 2 шт.
 Ремкомплект штока мехатроника DSG7 DQ200 (0AM / 0CW) предназначен для восстановления герметичности в области штока мехатроника.
 Применяется при устранении утечек масла и проведении профилактического ремонта. Изготовлен из термостойких и маслостойких материалов. Совместим с блоками мехатроника DSG7 моделей 0AM и 0CW.
 Идеален для технического обслуживания и увеличения срока службы мехатроника.

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4143,7 +4143,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: 2</t>
         </is>
       </c>
       <c r="AH33" t="n">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4876,7 +4876,7 @@
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z.png?v=2afa281dcb
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_2.png?v=ceee164228
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_3.png?v=2ca83e0e5a</t>
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025z_3.png?v=1a52462bed</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
@@ -6536,8 +6536,8 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2221,7 +2221,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Соленоид регулятор давления DSG7 DQ200 0AM325025B</t>
+          <t>Соленоид регулятор давления DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH11" t="n">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Клипса штока мехатроника DSG7 DQ200 0AM325025P</t>
+          <t>Клипса штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH30" t="n">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Крышка штока мехатроника DSG7 DQ200 0AM325025Q</t>
+          <t>Крышка штока мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH38" t="n">
@@ -6536,8 +6536,8 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4143,11 +4143,11 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: 2</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>950</v>
+        <v>2350</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2972,7 +2972,9 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_1.png?v=866128ed82</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_1.png?v=866128ed82
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_2.png?v=dc60c0af48
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769F_3.png?v=92286a8a02</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -6536,8 +6538,8 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
-https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_a-2.png?v=b13bc04517
+https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500-a-1.png?v=11bced952d
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_1.png?v=33f6b91718
 https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/DQ500_3.png?v=207791c0ab</t>
         </is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -4785,7 +4785,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=7f59b31f49</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025x_1.jpg?v=01d97a7972</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>42500</v>
+        <v>39500</v>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>42500</v>
+        <v>39500</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>🔄 Цена по обмену на ваш старый мехатроник (без платы): 32 500 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
+          <t>🔄 Обмен: пришлите свой старый мехатроник (без платы) — вернём 4 000 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
 Проверен на специализированном КПП DSG7 DQ200 стенде для проверки мехатроников, НО дополнительно после сборки КАЖДЫЙ мехатроник тестируется на авто (НЕ на подъемнике, а обкатывается на дороге, проверяется работоспособность в реальных условиях, все узлы работают одновременно, а не по отдельности как на стендах!
 Максимально профессиональное восстановление в заводских условиях + проверка на стенде и на авто = отличный результат и гарантия работоспособности.
 БЕЗ ЭЛЕКТРОННОЙ ПЛАТЫ, ТОЛЬКО ГИДРАВЛИКА
@@ -3600,7 +3600,7 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>36500</v>
+        <v>33500</v>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>🔄 Цена по обмену на ваш старый мехатроник (с платой): 62 500 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
+          <t>🔄 Обмен: пришлите свой старый мехатроник (с платой) — вернём 6 000 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
 КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ.
 Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)
 В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно -
@@ -3762,7 +3762,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>🔄 Цена по обмену на ваш старый мехатроник (с платой): 62 500 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
+          <t>🔄 Обмен: пришлите свой старый мехатроник (с платой) — вернём 6 000 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
 КАЖДЫЙ МЕХАТРОНИК DSG7 ПРОВЕРЯЕТСЯ НА АВТО ПОСЛЕ СБОРКИ.
 Каждый соленоид проверен на стенде. Электронная плата отличного качества (смотрите фото)
 В наших мехатрониках dq200 используются оригинальные и усовершенствованные запчасти, которых вы не найдете больше нигде, а именно -
@@ -4771,7 +4771,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>🔄 Цена по обмену на ваш старый мехатроник (без платы): 38 500 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
+          <t>🔄 Обмен: пришлите свой старый мехатроник (без платы) — вернём 4 000 ₽. Доставку старого оплачиваем мы; принимаем, если не ржавый, не был в воде и подлежит восстановлению. Напишите «обмен» в сообщения.
 Абсолюно новый мехатроник DQ200 DSG7 0AM 0CW Без Электронной платы (гидравлическая часть как на фото).
 Новые соленоиды Bosch
 Новый гидроаккумулятор
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>42500</v>
+        <v>38500</v>
       </c>
       <c r="AJ41" t="inlineStr">
         <is>

--- a/data/avito_feed.xlsx
+++ b/data/avito_feed.xlsx
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>68500</v>
+        <v>64500</v>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>68500</v>
+        <v>64500</v>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
